--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5456,6 +5456,15 @@
       <c r="T48" t="n">
         <v>23.7</v>
       </c>
+      <c r="V48" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -5464,6 +5473,15 @@
       </c>
       <c r="AA48" t="n">
         <v>8.199999999999999</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF48" t="n">
         <v>222.86</v>
@@ -5967,6 +5985,12 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.25</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
@@ -6018,6 +6042,24 @@
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>46278</v>
+      </c>
+      <c r="B55" t="n">
+        <v>141</v>
+      </c>
+      <c r="D55" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>7.5</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5964,8 +5964,14 @@
       <c r="B53" t="n">
         <v>133.9</v>
       </c>
+      <c r="C53" t="n">
+        <v>59.3</v>
+      </c>
       <c r="D53" t="n">
         <v>34.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>26.4</v>
       </c>
       <c r="F53" t="n">
         <v>3.3</v>
@@ -6008,8 +6014,14 @@
       <c r="B54" t="n">
         <v>137.5</v>
       </c>
+      <c r="C54" t="n">
+        <v>66.90000000000001</v>
+      </c>
       <c r="D54" t="n">
         <v>32.8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>25.7</v>
       </c>
       <c r="F54" t="n">
         <v>2.3</v>
@@ -6046,8 +6058,14 @@
       <c r="B55" t="n">
         <v>141</v>
       </c>
+      <c r="C55" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="D55" t="n">
         <v>31.9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>25.9</v>
       </c>
       <c r="F55" t="n">
         <v>2.3</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>22.6</v>
       </c>
-      <c r="V2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -695,15 +686,6 @@
       </c>
       <c r="AA2" t="n">
         <v>11.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.5</v>
       </c>
       <c r="AF2" t="n">
         <v>216.02</v>
@@ -791,15 +773,6 @@
       <c r="T3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -808,15 +781,6 @@
       </c>
       <c r="AA3" t="n">
         <v>12.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.7</v>
       </c>
       <c r="AF3" t="n">
         <v>216.02</v>
@@ -871,15 +835,6 @@
       <c r="O4" t="n">
         <v>39.2</v>
       </c>
-      <c r="V4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
@@ -888,15 +843,6 @@
       </c>
       <c r="AA4" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.4</v>
       </c>
       <c r="AF4" t="n">
         <v>224.53</v>
@@ -945,15 +891,6 @@
       <c r="O5" t="n">
         <v>39.3</v>
       </c>
-      <c r="V5" t="n">
-        <v>8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y5" t="n">
         <v>11</v>
       </c>
@@ -962,15 +899,6 @@
       </c>
       <c r="AA5" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
         <v>230.27</v>
@@ -1052,15 +980,6 @@
       <c r="T6" t="n">
         <v>21.7</v>
       </c>
-      <c r="V6" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1069,15 +988,6 @@
       </c>
       <c r="AA6" t="n">
         <v>15.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.1</v>
       </c>
       <c r="AF6" t="n">
         <v>237.43</v>
@@ -1132,15 +1042,6 @@
       <c r="O7" t="n">
         <v>37.9</v>
       </c>
-      <c r="V7" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X7" t="n">
-        <v>17.8</v>
-      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1149,15 +1050,6 @@
       </c>
       <c r="AA7" t="n">
         <v>16</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.9</v>
       </c>
       <c r="AF7" t="n">
         <v>236.14</v>
@@ -1239,15 +1131,6 @@
       <c r="T8" t="n">
         <v>20.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>27</v>
-      </c>
-      <c r="X8" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1256,15 +1139,6 @@
       </c>
       <c r="AA8" t="n">
         <v>14.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.4</v>
       </c>
       <c r="AF8" t="n">
         <v>236.13</v>
@@ -1352,15 +1226,6 @@
       <c r="T9" t="n">
         <v>19</v>
       </c>
-      <c r="V9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
@@ -1369,15 +1234,6 @@
       </c>
       <c r="AA9" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.7</v>
       </c>
       <c r="AF9" t="n">
         <v>218.6</v>
@@ -1465,15 +1321,6 @@
       <c r="T10" t="n">
         <v>21.6</v>
       </c>
-      <c r="V10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y10" t="n">
         <v>11</v>
       </c>
@@ -1482,15 +1329,6 @@
       </c>
       <c r="AA10" t="n">
         <v>13.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>218.84</v>
@@ -1545,15 +1383,6 @@
       <c r="O11" t="n">
         <v>35.1</v>
       </c>
-      <c r="V11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>19</v>
-      </c>
       <c r="Y11" t="n">
         <v>14</v>
       </c>
@@ -1562,15 +1391,6 @@
       </c>
       <c r="AA11" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF11" t="n">
         <v>221.78</v>
@@ -1619,15 +1439,6 @@
       <c r="O12" t="n">
         <v>31.6</v>
       </c>
-      <c r="V12" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y12" t="n">
         <v>14</v>
       </c>
@@ -1636,15 +1447,6 @@
       </c>
       <c r="AA12" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
         <v>224.78</v>
@@ -1726,15 +1528,6 @@
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1743,15 +1536,6 @@
       </c>
       <c r="AA13" t="n">
         <v>15.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.2</v>
       </c>
       <c r="AF13" t="n">
         <v>232.22</v>
@@ -1839,15 +1623,6 @@
       <c r="T14" t="n">
         <v>21.1</v>
       </c>
-      <c r="V14" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
@@ -1856,15 +1631,6 @@
       </c>
       <c r="AA14" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>229.69</v>
@@ -1952,15 +1718,6 @@
       <c r="T15" t="n">
         <v>21.3</v>
       </c>
-      <c r="V15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>20</v>
-      </c>
       <c r="Y15" t="n">
         <v>11</v>
       </c>
@@ -1969,15 +1726,6 @@
       </c>
       <c r="AA15" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
         <v>228.57</v>
@@ -2065,15 +1813,6 @@
       <c r="T16" t="n">
         <v>20.9</v>
       </c>
-      <c r="V16" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
@@ -2082,15 +1821,6 @@
       </c>
       <c r="AA16" t="n">
         <v>14.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.6</v>
       </c>
       <c r="AF16" t="n">
         <v>225.08</v>
@@ -2178,15 +1908,6 @@
       <c r="T17" t="n">
         <v>21</v>
       </c>
-      <c r="V17" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>27</v>
-      </c>
-      <c r="X17" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y17" t="n">
         <v>9</v>
       </c>
@@ -2195,15 +1916,6 @@
       </c>
       <c r="AA17" t="n">
         <v>11.4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.3</v>
       </c>
       <c r="AF17" t="n">
         <v>225</v>
@@ -2252,15 +1964,6 @@
       <c r="F18" t="n">
         <v>5.4</v>
       </c>
-      <c r="V18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>14</v>
-      </c>
       <c r="Y18" t="n">
         <v>5</v>
       </c>
@@ -2269,15 +1972,6 @@
       </c>
       <c r="AA18" t="n">
         <v>9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-1.4</v>
       </c>
       <c r="AF18" t="n">
         <v>221.37</v>
@@ -2326,15 +2020,6 @@
       <c r="O19" t="n">
         <v>35.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
@@ -2343,15 +2028,6 @@
       </c>
       <c r="AA19" t="n">
         <v>10</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-1.5</v>
       </c>
       <c r="AF19" t="n">
         <v>224.37</v>
@@ -2400,15 +2076,6 @@
       <c r="O20" t="n">
         <v>35.1</v>
       </c>
-      <c r="V20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y20" t="n">
         <v>3</v>
       </c>
@@ -2417,15 +2084,6 @@
       </c>
       <c r="AA20" t="n">
         <v>9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-3.3</v>
       </c>
       <c r="AF20" t="n">
         <v>225.93</v>
@@ -2507,15 +2165,6 @@
       <c r="T21" t="n">
         <v>22.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
@@ -2524,15 +2173,6 @@
       </c>
       <c r="AA21" t="n">
         <v>8.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-5.1</v>
       </c>
       <c r="AF21" t="n">
         <v>218.63</v>
@@ -2620,15 +2260,6 @@
       <c r="T22" t="n">
         <v>23</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X22" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y22" t="n">
         <v>6</v>
       </c>
@@ -2637,15 +2268,6 @@
       </c>
       <c r="AA22" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>-1.4</v>
       </c>
       <c r="AF22" t="n">
         <v>216.39</v>
@@ -2745,15 +2367,6 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y23" t="n">
         <v>8</v>
       </c>
@@ -2762,15 +2375,6 @@
       </c>
       <c r="AA23" t="n">
         <v>10</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
         <v>217.16</v>
@@ -2837,15 +2441,6 @@
       <c r="O24" t="n">
         <v>40.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2854,15 +2449,6 @@
       </c>
       <c r="AA24" t="n">
         <v>10</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF24" t="n">
         <v>220.31</v>
@@ -2923,15 +2509,6 @@
       <c r="O25" t="n">
         <v>38.5</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X25" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>10</v>
       </c>
@@ -2940,15 +2517,6 @@
       </c>
       <c r="AA25" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.5</v>
       </c>
       <c r="AF25" t="n">
         <v>221.99</v>
@@ -3009,15 +2577,6 @@
       <c r="O26" t="n">
         <v>39.8</v>
       </c>
-      <c r="V26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X26" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y26" t="n">
         <v>13</v>
       </c>
@@ -3026,15 +2585,6 @@
       </c>
       <c r="AA26" t="n">
         <v>14</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.9</v>
       </c>
       <c r="AF26" t="n">
         <v>225.14</v>
@@ -3095,15 +2645,6 @@
       <c r="O27" t="n">
         <v>35.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y27" t="n">
         <v>12</v>
       </c>
@@ -3112,15 +2653,6 @@
       </c>
       <c r="AA27" t="n">
         <v>15</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>-0.4</v>
       </c>
       <c r="AF27" t="n">
         <v>229.98</v>
@@ -3214,15 +2746,6 @@
       <c r="T28" t="n">
         <v>23.2</v>
       </c>
-      <c r="V28" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>13</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3231,15 +2754,6 @@
       </c>
       <c r="AA28" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>-0.6</v>
       </c>
       <c r="AF28" t="n">
         <v>229.96</v>
@@ -3339,15 +2853,6 @@
       <c r="T29" t="n">
         <v>23.8</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y29" t="n">
         <v>7</v>
       </c>
@@ -3356,15 +2861,6 @@
       </c>
       <c r="AA29" t="n">
         <v>10.1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4.4</v>
       </c>
       <c r="AF29" t="n">
         <v>227.01</v>
@@ -3464,15 +2960,6 @@
       <c r="T30" t="n">
         <v>23.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>6</v>
       </c>
@@ -3481,15 +2968,6 @@
       </c>
       <c r="AA30" t="n">
         <v>11</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>6.5</v>
       </c>
       <c r="AF30" t="n">
         <v>228.35</v>
@@ -3589,15 +3067,6 @@
       <c r="T31" t="n">
         <v>23.7</v>
       </c>
-      <c r="V31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y31" t="n">
         <v>8</v>
       </c>
@@ -3606,15 +3075,6 @@
       </c>
       <c r="AA31" t="n">
         <v>12.6</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>5.8</v>
       </c>
       <c r="AF31" t="n">
         <v>231.16</v>
@@ -3681,15 +3141,6 @@
       <c r="O32" t="n">
         <v>34.4</v>
       </c>
-      <c r="V32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y32" t="n">
         <v>6</v>
       </c>
@@ -3698,15 +3149,6 @@
       </c>
       <c r="AA32" t="n">
         <v>9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.8</v>
       </c>
       <c r="AF32" t="n">
         <v>228.13</v>
@@ -3767,15 +3209,6 @@
       <c r="O33" t="n">
         <v>35.2</v>
       </c>
-      <c r="V33" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W33" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X33" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y33" t="n">
         <v>4</v>
       </c>
@@ -3784,15 +3217,6 @@
       </c>
       <c r="AA33" t="n">
         <v>9</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4</v>
       </c>
       <c r="AF33" t="n">
         <v>229.16</v>
@@ -3886,15 +3310,6 @@
       <c r="T34" t="n">
         <v>23.5</v>
       </c>
-      <c r="V34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>4</v>
       </c>
@@ -3903,15 +3318,6 @@
       </c>
       <c r="AA34" t="n">
         <v>9.300000000000001</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.3</v>
       </c>
       <c r="AF34" t="n">
         <v>228.55</v>
@@ -4011,15 +3417,6 @@
       <c r="T35" t="n">
         <v>23.1</v>
       </c>
-      <c r="V35" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W35" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y35" t="n">
         <v>7</v>
       </c>
@@ -4028,15 +3425,6 @@
       </c>
       <c r="AA35" t="n">
         <v>10.1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.8</v>
       </c>
       <c r="AF35" t="n">
         <v>219.99</v>
@@ -4136,15 +3524,6 @@
       <c r="T36" t="n">
         <v>23.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W36" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>8</v>
       </c>
@@ -4153,15 +3532,6 @@
       </c>
       <c r="AA36" t="n">
         <v>12.2</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>5.5</v>
       </c>
       <c r="AF36" t="n">
         <v>219.22</v>
@@ -4261,15 +3631,6 @@
       <c r="T37" t="n">
         <v>23.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4278,15 +3639,6 @@
       </c>
       <c r="AA37" t="n">
         <v>14</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>5.7</v>
       </c>
       <c r="AF37" t="n">
         <v>220.73</v>
@@ -4386,15 +3738,6 @@
       <c r="T38" t="n">
         <v>23.2</v>
       </c>
-      <c r="V38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y38" t="n">
         <v>10</v>
       </c>
@@ -4403,15 +3746,6 @@
       </c>
       <c r="AA38" t="n">
         <v>13.1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>6.7</v>
       </c>
       <c r="AF38" t="n">
         <v>220.58</v>
@@ -4472,15 +3806,6 @@
       <c r="F39" t="n">
         <v>6.1</v>
       </c>
-      <c r="V39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y39" t="n">
         <v>9</v>
       </c>
@@ -4489,15 +3814,6 @@
       </c>
       <c r="AA39" t="n">
         <v>13</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.5</v>
       </c>
       <c r="AF39" t="n">
         <v>223.43</v>
@@ -4552,15 +3868,6 @@
       <c r="F40" t="n">
         <v>3.4</v>
       </c>
-      <c r="V40" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y40" t="n">
         <v>8</v>
       </c>
@@ -4569,15 +3876,6 @@
       </c>
       <c r="AA40" t="n">
         <v>13</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.4</v>
       </c>
       <c r="AF40" t="n">
         <v>229.48</v>
@@ -4671,15 +3969,6 @@
       <c r="T41" t="n">
         <v>21.4</v>
       </c>
-      <c r="V41" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X41" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y41" t="n">
         <v>8</v>
       </c>
@@ -4688,15 +3977,6 @@
       </c>
       <c r="AA41" t="n">
         <v>16.1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4</v>
       </c>
       <c r="AF41" t="n">
         <v>241.48</v>
@@ -4796,15 +4076,6 @@
       <c r="T42" t="n">
         <v>19.7</v>
       </c>
-      <c r="V42" t="n">
-        <v>12</v>
-      </c>
-      <c r="W42" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X42" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>12</v>
       </c>
@@ -4813,15 +4084,6 @@
       </c>
       <c r="AA42" t="n">
         <v>15</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.9</v>
       </c>
       <c r="AF42" t="n">
         <v>238.69</v>
@@ -4921,15 +4183,6 @@
       <c r="T43" t="n">
         <v>20.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X43" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y43" t="n">
         <v>10</v>
       </c>
@@ -4938,15 +4191,6 @@
       </c>
       <c r="AA43" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.7</v>
       </c>
       <c r="AF43" t="n">
         <v>233.48</v>
@@ -5046,15 +4290,6 @@
       <c r="T44" t="n">
         <v>21.6</v>
       </c>
-      <c r="V44" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W44" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>11</v>
       </c>
@@ -5063,15 +4298,6 @@
       </c>
       <c r="AA44" t="n">
         <v>17.9</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>3.6</v>
       </c>
       <c r="AF44" t="n">
         <v>235.13</v>
@@ -5171,15 +4397,6 @@
       <c r="T45" t="n">
         <v>21</v>
       </c>
-      <c r="V45" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y45" t="n">
         <v>12</v>
       </c>
@@ -5188,15 +4405,6 @@
       </c>
       <c r="AA45" t="n">
         <v>16.3</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF45" t="n">
         <v>234.87</v>
@@ -5257,15 +4465,6 @@
       <c r="F46" t="n">
         <v>4</v>
       </c>
-      <c r="V46" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X46" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y46" t="n">
         <v>7</v>
       </c>
@@ -5274,15 +4473,6 @@
       </c>
       <c r="AA46" t="n">
         <v>13</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.2</v>
       </c>
       <c r="AF46" t="n">
         <v>234.78</v>
@@ -5337,15 +4527,6 @@
       <c r="F47" t="n">
         <v>3.3</v>
       </c>
-      <c r="V47" t="n">
-        <v>11</v>
-      </c>
-      <c r="W47" t="n">
-        <v>22</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y47" t="n">
         <v>7</v>
       </c>
@@ -5354,15 +4535,6 @@
       </c>
       <c r="AA47" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.4</v>
       </c>
       <c r="AF47" t="n">
         <v>229.75</v>
@@ -5456,15 +4628,6 @@
       <c r="T48" t="n">
         <v>23.7</v>
       </c>
-      <c r="V48" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W48" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -5473,15 +4636,6 @@
       </c>
       <c r="AA48" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.5</v>
       </c>
       <c r="AF48" t="n">
         <v>222.86</v>
@@ -6040,6 +5194,12 @@
       </c>
       <c r="AI54" t="n">
         <v>235</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>-3.65</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -685,7 +685,7 @@
         <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
         <v>216.02</v>
@@ -780,7 +780,7 @@
         <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.7</v>
+        <v>10.5</v>
       </c>
       <c r="AF3" t="n">
         <v>216.02</v>
@@ -987,7 +987,7 @@
         <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
         <v>237.43</v>
@@ -1138,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF8" t="n">
         <v>236.13</v>
@@ -1233,7 +1233,7 @@
         <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
         <v>218.6</v>
@@ -1328,7 +1328,7 @@
         <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="AF10" t="n">
         <v>218.84</v>
@@ -1535,7 +1535,7 @@
         <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF13" t="n">
         <v>232.22</v>
@@ -1630,7 +1630,7 @@
         <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF14" t="n">
         <v>229.69</v>
@@ -1725,7 +1725,7 @@
         <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
         <v>228.57</v>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="AF16" t="n">
         <v>225.08</v>
@@ -1915,7 +1915,7 @@
         <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AF17" t="n">
         <v>225</v>
@@ -2172,7 +2172,7 @@
         <v>12</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AF21" t="n">
         <v>218.63</v>
@@ -2267,7 +2267,7 @@
         <v>12</v>
       </c>
       <c r="AA22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
         <v>216.39</v>
@@ -2374,7 +2374,7 @@
         <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AF23" t="n">
         <v>217.16</v>
@@ -2753,7 +2753,7 @@
         <v>14</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AF28" t="n">
         <v>229.96</v>
@@ -2860,7 +2860,7 @@
         <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>227.01</v>
@@ -2967,7 +2967,7 @@
         <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AF30" t="n">
         <v>228.35</v>
@@ -3074,7 +3074,7 @@
         <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="AF31" t="n">
         <v>231.16</v>
@@ -3317,7 +3317,7 @@
         <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AF34" t="n">
         <v>228.55</v>
@@ -3424,7 +3424,7 @@
         <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="AF35" t="n">
         <v>219.99</v>
@@ -3531,7 +3531,7 @@
         <v>14</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.2</v>
+        <v>11</v>
       </c>
       <c r="AF36" t="n">
         <v>219.22</v>
@@ -3745,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="AF38" t="n">
         <v>220.58</v>
@@ -3976,7 +3976,7 @@
         <v>20</v>
       </c>
       <c r="AA41" t="n">
-        <v>16.1</v>
+        <v>14</v>
       </c>
       <c r="AF41" t="n">
         <v>241.48</v>
@@ -4083,7 +4083,7 @@
         <v>19</v>
       </c>
       <c r="AA42" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AF42" t="n">
         <v>238.69</v>
@@ -4190,7 +4190,7 @@
         <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF43" t="n">
         <v>233.48</v>
@@ -4297,7 +4297,7 @@
         <v>23</v>
       </c>
       <c r="AA44" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="AF44" t="n">
         <v>235.13</v>
@@ -4404,7 +4404,7 @@
         <v>19</v>
       </c>
       <c r="AA45" t="n">
-        <v>16.3</v>
+        <v>15.5</v>
       </c>
       <c r="AF45" t="n">
         <v>234.87</v>
@@ -4581,7 +4581,7 @@
         <v>46271</v>
       </c>
       <c r="B48" t="n">
-        <v>166.2</v>
+        <v>148.7</v>
       </c>
       <c r="C48" t="n">
         <v>72.40000000000001</v>
@@ -4635,7 +4635,7 @@
         <v>10</v>
       </c>
       <c r="AA48" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AF48" t="n">
         <v>222.86</v>
@@ -4688,7 +4688,7 @@
         <v>46272</v>
       </c>
       <c r="B49" t="n">
-        <v>166.3</v>
+        <v>149.3</v>
       </c>
       <c r="C49" t="n">
         <v>74.90000000000001</v>
@@ -4742,7 +4742,7 @@
         <v>14</v>
       </c>
       <c r="AA49" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AF49" t="n">
         <v>218.37</v>
@@ -4795,7 +4795,7 @@
         <v>46273</v>
       </c>
       <c r="B50" t="n">
-        <v>154.1</v>
+        <v>137</v>
       </c>
       <c r="C50" t="n">
         <v>65</v>
@@ -4849,7 +4849,7 @@
         <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF50" t="n">
         <v>220.85</v>
@@ -4902,7 +4902,7 @@
         <v>46274</v>
       </c>
       <c r="B51" t="n">
-        <v>148.8</v>
+        <v>131.5</v>
       </c>
       <c r="C51" t="n">
         <v>57.6</v>
@@ -4956,7 +4956,7 @@
         <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="AF51" t="n">
         <v>220.84</v>
@@ -5009,7 +5009,7 @@
         <v>46275</v>
       </c>
       <c r="B52" t="n">
-        <v>146.8</v>
+        <v>129.4</v>
       </c>
       <c r="C52" t="n">
         <v>52.8</v>
@@ -5063,7 +5063,7 @@
         <v>20</v>
       </c>
       <c r="AA52" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="AF52" t="n">
         <v>225.87</v>
@@ -5160,6 +5160,18 @@
       <c r="BL53" s="1" t="n">
         <v>46276</v>
       </c>
+      <c r="BM53" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>2545.1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5210,6 +5222,18 @@
       <c r="BL54" s="1" t="n">
         <v>46277</v>
       </c>
+      <c r="BM54" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>73</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>16</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>2697.4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5254,10 +5278,46 @@
       <c r="BL55" s="1" t="n">
         <v>46278</v>
       </c>
+      <c r="BM55" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>2603.2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>46279</v>
+      </c>
+      <c r="B56" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="C56" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="D56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>29</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>10.5</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -1964,6 +1964,21 @@
       <c r="F18" t="n">
         <v>5.4</v>
       </c>
+      <c r="K18" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y18" t="n">
         <v>5</v>
       </c>
@@ -3806,6 +3821,21 @@
       <c r="F39" t="n">
         <v>6.1</v>
       </c>
+      <c r="K39" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T39" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y39" t="n">
         <v>9</v>
       </c>
@@ -3868,6 +3898,21 @@
       <c r="F40" t="n">
         <v>3.4</v>
       </c>
+      <c r="K40" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="O40" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y40" t="n">
         <v>8</v>
       </c>
@@ -4465,6 +4510,21 @@
       <c r="F46" t="n">
         <v>4</v>
       </c>
+      <c r="K46" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="O46" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y46" t="n">
         <v>7</v>
       </c>
@@ -4527,6 +4587,21 @@
       <c r="F47" t="n">
         <v>3.3</v>
       </c>
+      <c r="K47" t="n">
+        <v>73</v>
+      </c>
+      <c r="O47" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T47" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y47" t="n">
         <v>7</v>
       </c>
@@ -5130,6 +5205,21 @@
       <c r="F53" t="n">
         <v>3.3</v>
       </c>
+      <c r="K53" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="O53" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T53" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y53" t="n">
         <v>12</v>
       </c>
@@ -5192,6 +5282,21 @@
       <c r="F54" t="n">
         <v>2.3</v>
       </c>
+      <c r="K54" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T54" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y54" t="n">
         <v>10</v>
       </c>
@@ -5254,6 +5359,21 @@
       <c r="F55" t="n">
         <v>2.3</v>
       </c>
+      <c r="K55" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="O55" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y55" t="n">
         <v>3</v>
       </c>
@@ -5309,6 +5429,21 @@
       </c>
       <c r="F56" t="n">
         <v>2.3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="O56" t="n">
+        <v>43</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T56" t="n">
+        <v>22.2</v>
       </c>
       <c r="Y56" t="n">
         <v>5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>22.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -773,6 +782,15 @@
       <c r="T3" t="n">
         <v>23.3</v>
       </c>
+      <c r="V3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -835,6 +853,15 @@
       <c r="O4" t="n">
         <v>39.2</v>
       </c>
+      <c r="V4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
@@ -891,6 +918,15 @@
       <c r="O5" t="n">
         <v>39.3</v>
       </c>
+      <c r="V5" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y5" t="n">
         <v>11</v>
       </c>
@@ -980,6 +1016,15 @@
       <c r="T6" t="n">
         <v>21.7</v>
       </c>
+      <c r="V6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1042,6 +1087,15 @@
       <c r="O7" t="n">
         <v>37.9</v>
       </c>
+      <c r="V7" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17.8</v>
+      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1131,6 +1185,15 @@
       <c r="T8" t="n">
         <v>20.3</v>
       </c>
+      <c r="V8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1226,6 +1289,15 @@
       <c r="T9" t="n">
         <v>19</v>
       </c>
+      <c r="V9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
@@ -1321,6 +1393,15 @@
       <c r="T10" t="n">
         <v>21.6</v>
       </c>
+      <c r="V10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y10" t="n">
         <v>11</v>
       </c>
@@ -1383,6 +1464,15 @@
       <c r="O11" t="n">
         <v>35.1</v>
       </c>
+      <c r="V11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19</v>
+      </c>
       <c r="Y11" t="n">
         <v>14</v>
       </c>
@@ -1439,6 +1529,15 @@
       <c r="O12" t="n">
         <v>31.6</v>
       </c>
+      <c r="V12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y12" t="n">
         <v>14</v>
       </c>
@@ -1528,6 +1627,15 @@
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
+      <c r="V13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1623,6 +1731,15 @@
       <c r="T14" t="n">
         <v>21.1</v>
       </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
@@ -1718,6 +1835,15 @@
       <c r="T15" t="n">
         <v>21.3</v>
       </c>
+      <c r="V15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>20</v>
+      </c>
       <c r="Y15" t="n">
         <v>11</v>
       </c>
@@ -1813,6 +1939,15 @@
       <c r="T16" t="n">
         <v>20.9</v>
       </c>
+      <c r="V16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
@@ -1908,6 +2043,15 @@
       <c r="T17" t="n">
         <v>21</v>
       </c>
+      <c r="V17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y17" t="n">
         <v>9</v>
       </c>
@@ -1979,6 +2123,15 @@
       <c r="T18" t="n">
         <v>22.2</v>
       </c>
+      <c r="V18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14</v>
+      </c>
       <c r="Y18" t="n">
         <v>5</v>
       </c>
@@ -2035,6 +2188,15 @@
       <c r="O19" t="n">
         <v>35.5</v>
       </c>
+      <c r="V19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
@@ -2091,6 +2253,15 @@
       <c r="O20" t="n">
         <v>35.1</v>
       </c>
+      <c r="V20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y20" t="n">
         <v>3</v>
       </c>
@@ -2180,6 +2351,15 @@
       <c r="T21" t="n">
         <v>22.4</v>
       </c>
+      <c r="V21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
@@ -2275,6 +2455,15 @@
       <c r="T22" t="n">
         <v>23</v>
       </c>
+      <c r="V22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y22" t="n">
         <v>6</v>
       </c>
@@ -2382,6 +2571,15 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y23" t="n">
         <v>8</v>
       </c>
@@ -2456,6 +2654,15 @@
       <c r="O24" t="n">
         <v>40.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2524,6 +2731,15 @@
       <c r="O25" t="n">
         <v>38.5</v>
       </c>
+      <c r="V25" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>10</v>
       </c>
@@ -2592,6 +2808,15 @@
       <c r="O26" t="n">
         <v>39.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y26" t="n">
         <v>13</v>
       </c>
@@ -2660,6 +2885,15 @@
       <c r="O27" t="n">
         <v>35.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y27" t="n">
         <v>12</v>
       </c>
@@ -2761,6 +2995,15 @@
       <c r="T28" t="n">
         <v>23.2</v>
       </c>
+      <c r="V28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -2868,6 +3111,15 @@
       <c r="T29" t="n">
         <v>23.8</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y29" t="n">
         <v>7</v>
       </c>
@@ -2975,6 +3227,15 @@
       <c r="T30" t="n">
         <v>23.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y30" t="n">
         <v>6</v>
       </c>
@@ -3082,6 +3343,15 @@
       <c r="T31" t="n">
         <v>23.7</v>
       </c>
+      <c r="V31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y31" t="n">
         <v>8</v>
       </c>
@@ -3156,6 +3426,15 @@
       <c r="O32" t="n">
         <v>34.4</v>
       </c>
+      <c r="V32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y32" t="n">
         <v>6</v>
       </c>
@@ -3224,6 +3503,15 @@
       <c r="O33" t="n">
         <v>35.2</v>
       </c>
+      <c r="V33" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y33" t="n">
         <v>4</v>
       </c>
@@ -3325,6 +3613,15 @@
       <c r="T34" t="n">
         <v>23.5</v>
       </c>
+      <c r="V34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>4</v>
       </c>
@@ -3432,6 +3729,15 @@
       <c r="T35" t="n">
         <v>23.1</v>
       </c>
+      <c r="V35" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W35" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y35" t="n">
         <v>7</v>
       </c>
@@ -3539,6 +3845,15 @@
       <c r="T36" t="n">
         <v>23.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>8</v>
       </c>
@@ -3646,6 +3961,15 @@
       <c r="T37" t="n">
         <v>23.2</v>
       </c>
+      <c r="V37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3753,6 +4077,15 @@
       <c r="T38" t="n">
         <v>23.2</v>
       </c>
+      <c r="V38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y38" t="n">
         <v>10</v>
       </c>
@@ -3836,6 +4169,15 @@
       <c r="T39" t="n">
         <v>22.2</v>
       </c>
+      <c r="V39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y39" t="n">
         <v>9</v>
       </c>
@@ -3913,6 +4255,15 @@
       <c r="T40" t="n">
         <v>22.2</v>
       </c>
+      <c r="V40" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y40" t="n">
         <v>8</v>
       </c>
@@ -4014,6 +4365,15 @@
       <c r="T41" t="n">
         <v>21.4</v>
       </c>
+      <c r="V41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y41" t="n">
         <v>8</v>
       </c>
@@ -4121,6 +4481,15 @@
       <c r="T42" t="n">
         <v>19.7</v>
       </c>
+      <c r="V42" t="n">
+        <v>12</v>
+      </c>
+      <c r="W42" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>12</v>
       </c>
@@ -4228,6 +4597,15 @@
       <c r="T43" t="n">
         <v>20.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y43" t="n">
         <v>10</v>
       </c>
@@ -4335,6 +4713,15 @@
       <c r="T44" t="n">
         <v>21.6</v>
       </c>
+      <c r="V44" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X44" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>11</v>
       </c>
@@ -4442,6 +4829,15 @@
       <c r="T45" t="n">
         <v>21</v>
       </c>
+      <c r="V45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y45" t="n">
         <v>12</v>
       </c>
@@ -4525,6 +4921,15 @@
       <c r="T46" t="n">
         <v>22.2</v>
       </c>
+      <c r="V46" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X46" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y46" t="n">
         <v>7</v>
       </c>
@@ -4602,6 +5007,15 @@
       <c r="T47" t="n">
         <v>22.2</v>
       </c>
+      <c r="V47" t="n">
+        <v>11</v>
+      </c>
+      <c r="W47" t="n">
+        <v>22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y47" t="n">
         <v>7</v>
       </c>
@@ -4703,6 +5117,15 @@
       <c r="T48" t="n">
         <v>23.7</v>
       </c>
+      <c r="V48" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -4809,6 +5232,15 @@
       </c>
       <c r="T49" t="n">
         <v>23.9</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W49" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y49" t="n">
         <v>5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,6 +696,15 @@
       <c r="AA2" t="n">
         <v>11</v>
       </c>
+      <c r="AB2" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AF2" t="n">
         <v>216.02</v>
       </c>
@@ -800,6 +809,15 @@
       <c r="AA3" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AF3" t="n">
         <v>216.02</v>
       </c>
@@ -871,6 +889,15 @@
       <c r="AA4" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AF4" t="n">
         <v>224.53</v>
       </c>
@@ -936,6 +963,15 @@
       <c r="AA5" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AF5" t="n">
         <v>230.27</v>
       </c>
@@ -1034,6 +1070,15 @@
       <c r="AA6" t="n">
         <v>16</v>
       </c>
+      <c r="AB6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="AF6" t="n">
         <v>237.43</v>
       </c>
@@ -1105,6 +1150,15 @@
       <c r="AA7" t="n">
         <v>16</v>
       </c>
+      <c r="AB7" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AF7" t="n">
         <v>236.14</v>
       </c>
@@ -1203,6 +1257,15 @@
       <c r="AA8" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="AF8" t="n">
         <v>236.13</v>
       </c>
@@ -1307,6 +1370,15 @@
       <c r="AA9" t="n">
         <v>12</v>
       </c>
+      <c r="AB9" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="AF9" t="n">
         <v>218.6</v>
       </c>
@@ -1411,6 +1483,15 @@
       <c r="AA10" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AF10" t="n">
         <v>218.84</v>
       </c>
@@ -1482,6 +1563,15 @@
       <c r="AA11" t="n">
         <v>17.5</v>
       </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF11" t="n">
         <v>221.78</v>
       </c>
@@ -1547,6 +1637,15 @@
       <c r="AA12" t="n">
         <v>16.5</v>
       </c>
+      <c r="AB12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AF12" t="n">
         <v>224.78</v>
       </c>
@@ -1645,6 +1744,15 @@
       <c r="AA13" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AF13" t="n">
         <v>232.22</v>
       </c>
@@ -1749,6 +1857,15 @@
       <c r="AA14" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB14" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2</v>
+      </c>
       <c r="AF14" t="n">
         <v>229.69</v>
       </c>
@@ -1853,6 +1970,15 @@
       <c r="AA15" t="n">
         <v>13</v>
       </c>
+      <c r="AB15" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
       <c r="AF15" t="n">
         <v>228.57</v>
       </c>
@@ -1957,6 +2083,15 @@
       <c r="AA16" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB16" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF16" t="n">
         <v>225.08</v>
       </c>
@@ -2061,6 +2196,15 @@
       <c r="AA17" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB17" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="AF17" t="n">
         <v>225</v>
       </c>
@@ -2141,6 +2285,15 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
+      <c r="AB18" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF18" t="n">
         <v>221.37</v>
       </c>
@@ -2206,6 +2359,15 @@
       <c r="AA19" t="n">
         <v>10</v>
       </c>
+      <c r="AB19" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AF19" t="n">
         <v>224.37</v>
       </c>
@@ -2271,6 +2433,15 @@
       <c r="AA20" t="n">
         <v>9</v>
       </c>
+      <c r="AB20" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="AF20" t="n">
         <v>225.93</v>
       </c>
@@ -2369,6 +2540,15 @@
       <c r="AA21" t="n">
         <v>8</v>
       </c>
+      <c r="AB21" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="AF21" t="n">
         <v>218.63</v>
       </c>
@@ -2473,6 +2653,15 @@
       <c r="AA22" t="n">
         <v>9</v>
       </c>
+      <c r="AB22" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF22" t="n">
         <v>216.39</v>
       </c>
@@ -2589,6 +2778,15 @@
       <c r="AA23" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AF23" t="n">
         <v>217.16</v>
       </c>
@@ -2672,6 +2870,15 @@
       <c r="AA24" t="n">
         <v>10</v>
       </c>
+      <c r="AB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF24" t="n">
         <v>220.31</v>
       </c>
@@ -2749,6 +2956,15 @@
       <c r="AA25" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AF25" t="n">
         <v>221.99</v>
       </c>
@@ -2826,6 +3042,15 @@
       <c r="AA26" t="n">
         <v>14</v>
       </c>
+      <c r="AB26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF26" t="n">
         <v>225.14</v>
       </c>
@@ -2903,6 +3128,15 @@
       <c r="AA27" t="n">
         <v>15</v>
       </c>
+      <c r="AB27" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="AF27" t="n">
         <v>229.98</v>
       </c>
@@ -3013,6 +3247,15 @@
       <c r="AA28" t="n">
         <v>13</v>
       </c>
+      <c r="AB28" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AF28" t="n">
         <v>229.96</v>
       </c>
@@ -3129,6 +3372,15 @@
       <c r="AA29" t="n">
         <v>10</v>
       </c>
+      <c r="AB29" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>4.4</v>
+      </c>
       <c r="AF29" t="n">
         <v>227.01</v>
       </c>
@@ -3245,6 +3497,15 @@
       <c r="AA30" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AF30" t="n">
         <v>228.35</v>
       </c>
@@ -3361,6 +3622,15 @@
       <c r="AA31" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF31" t="n">
         <v>231.16</v>
       </c>
@@ -3444,6 +3714,15 @@
       <c r="AA32" t="n">
         <v>9</v>
       </c>
+      <c r="AB32" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AF32" t="n">
         <v>228.13</v>
       </c>
@@ -3521,6 +3800,15 @@
       <c r="AA33" t="n">
         <v>9</v>
       </c>
+      <c r="AB33" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4</v>
+      </c>
       <c r="AF33" t="n">
         <v>229.16</v>
       </c>
@@ -3631,6 +3919,15 @@
       <c r="AA34" t="n">
         <v>8.5</v>
       </c>
+      <c r="AB34" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF34" t="n">
         <v>228.55</v>
       </c>
@@ -3747,6 +4044,15 @@
       <c r="AA35" t="n">
         <v>10</v>
       </c>
+      <c r="AB35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF35" t="n">
         <v>219.99</v>
       </c>
@@ -3863,6 +4169,15 @@
       <c r="AA36" t="n">
         <v>11</v>
       </c>
+      <c r="AB36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>5.5</v>
+      </c>
       <c r="AF36" t="n">
         <v>219.22</v>
       </c>
@@ -3979,6 +4294,15 @@
       <c r="AA37" t="n">
         <v>14</v>
       </c>
+      <c r="AB37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF37" t="n">
         <v>220.73</v>
       </c>
@@ -4095,6 +4419,15 @@
       <c r="AA38" t="n">
         <v>14</v>
       </c>
+      <c r="AB38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF38" t="n">
         <v>220.58</v>
       </c>
@@ -4187,6 +4520,15 @@
       <c r="AA39" t="n">
         <v>13</v>
       </c>
+      <c r="AB39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF39" t="n">
         <v>223.43</v>
       </c>
@@ -4273,6 +4615,15 @@
       <c r="AA40" t="n">
         <v>13</v>
       </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AF40" t="n">
         <v>229.48</v>
       </c>
@@ -4383,6 +4734,15 @@
       <c r="AA41" t="n">
         <v>14</v>
       </c>
+      <c r="AB41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>4</v>
+      </c>
       <c r="AF41" t="n">
         <v>241.48</v>
       </c>
@@ -4499,6 +4859,15 @@
       <c r="AA42" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB42" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AF42" t="n">
         <v>238.69</v>
       </c>
@@ -4615,6 +4984,15 @@
       <c r="AA43" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AF43" t="n">
         <v>233.48</v>
       </c>
@@ -4731,6 +5109,15 @@
       <c r="AA44" t="n">
         <v>17</v>
       </c>
+      <c r="AB44" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AF44" t="n">
         <v>235.13</v>
       </c>
@@ -4847,6 +5234,15 @@
       <c r="AA45" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB45" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF45" t="n">
         <v>234.87</v>
       </c>
@@ -4939,6 +5335,15 @@
       <c r="AA46" t="n">
         <v>13</v>
       </c>
+      <c r="AB46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.2</v>
+      </c>
       <c r="AF46" t="n">
         <v>234.78</v>
       </c>
@@ -5025,6 +5430,15 @@
       <c r="AA47" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB47" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AF47" t="n">
         <v>229.75</v>
       </c>
@@ -5135,6 +5549,15 @@
       <c r="AA48" t="n">
         <v>6.5</v>
       </c>
+      <c r="AB48" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AF48" t="n">
         <v>222.86</v>
       </c>
@@ -5250,6 +5673,15 @@
       </c>
       <c r="AA49" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF49" t="n">
         <v>218.37</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -2253,19 +2253,19 @@
         <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>82.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O18" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S18" t="n">
         <v>0.6</v>
       </c>
       <c r="T18" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="V18" t="n">
         <v>8.699999999999999</v>
@@ -4488,19 +4488,19 @@
         <v>6.1</v>
       </c>
       <c r="K39" t="n">
-        <v>73.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S39" t="n">
         <v>0.6</v>
       </c>
       <c r="T39" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="V39" t="n">
         <v>15.5</v>
@@ -4583,19 +4583,19 @@
         <v>3.4</v>
       </c>
       <c r="K40" t="n">
-        <v>66.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="O40" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="R40" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S40" t="n">
         <v>0.6</v>
       </c>
       <c r="T40" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="V40" t="n">
         <v>12.6</v>
@@ -5303,19 +5303,19 @@
         <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>69.8</v>
+        <v>68.7</v>
       </c>
       <c r="O46" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
       <c r="R46" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S46" t="n">
         <v>0.6</v>
       </c>
       <c r="T46" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="V46" t="n">
         <v>11.6</v>
@@ -5398,19 +5398,19 @@
         <v>3.3</v>
       </c>
       <c r="K47" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="R47" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S47" t="n">
         <v>0.6</v>
       </c>
       <c r="T47" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="V47" t="n">
         <v>11</v>
@@ -5781,6 +5781,15 @@
       <c r="T50" t="n">
         <v>21.7</v>
       </c>
+      <c r="V50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>21</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y50" t="n">
         <v>9</v>
       </c>
@@ -5789,6 +5798,15 @@
       </c>
       <c r="AA50" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF50" t="n">
         <v>220.85</v>
@@ -6070,19 +6088,19 @@
         <v>3.3</v>
       </c>
       <c r="K53" t="n">
-        <v>70.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="O53" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="R53" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S53" t="n">
         <v>0.6</v>
       </c>
       <c r="T53" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Y53" t="n">
         <v>12</v>
@@ -6147,19 +6165,19 @@
         <v>2.3</v>
       </c>
       <c r="K54" t="n">
-        <v>73.3</v>
+        <v>72.2</v>
       </c>
       <c r="O54" t="n">
-        <v>38.5</v>
+        <v>38.8</v>
       </c>
       <c r="R54" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S54" t="n">
         <v>0.6</v>
       </c>
       <c r="T54" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Y54" t="n">
         <v>10</v>
@@ -6209,34 +6227,52 @@
         <v>46278</v>
       </c>
       <c r="B55" t="n">
-        <v>141</v>
+        <v>140.8</v>
       </c>
       <c r="C55" t="n">
-        <v>71.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="E55" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="F55" t="n">
-        <v>2.3</v>
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I55" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J55" t="n">
+        <v>40.5</v>
       </c>
       <c r="K55" t="n">
-        <v>75.59999999999999</v>
+        <v>73.5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>33.4</v>
       </c>
       <c r="O55" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>23.8</v>
       </c>
       <c r="R55" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="S55" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>22.2</v>
+        <v>23.8</v>
       </c>
       <c r="Y55" t="n">
         <v>3</v>
@@ -6247,17 +6283,35 @@
       <c r="AA55" t="n">
         <v>7.5</v>
       </c>
+      <c r="AF55" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-1.67</v>
+      </c>
       <c r="AH55" t="n">
         <v>215</v>
       </c>
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>127.19</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>14.06</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46278</v>
@@ -6295,19 +6349,19 @@
         <v>2.3</v>
       </c>
       <c r="K56" t="n">
-        <v>81.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="O56" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="R56" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="S56" t="n">
         <v>0.6</v>
       </c>
       <c r="T56" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Y56" t="n">
         <v>5</v>
@@ -6332,11 +6386,62 @@
       </c>
       <c r="BL56" s="1" t="n">
         <v>46279</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>297.8</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>2677.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>46280</v>
+      </c>
+      <c r="B57" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="O57" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T57" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>16</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>22.6</v>
       </c>
-      <c r="V2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -791,15 +782,6 @@
       <c r="T3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -871,15 +853,6 @@
       <c r="O4" t="n">
         <v>39.2</v>
       </c>
-      <c r="V4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
@@ -945,15 +918,6 @@
       <c r="O5" t="n">
         <v>39.3</v>
       </c>
-      <c r="V5" t="n">
-        <v>8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y5" t="n">
         <v>11</v>
       </c>
@@ -1052,15 +1016,6 @@
       <c r="T6" t="n">
         <v>21.7</v>
       </c>
-      <c r="V6" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1132,15 +1087,6 @@
       <c r="O7" t="n">
         <v>37.9</v>
       </c>
-      <c r="V7" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X7" t="n">
-        <v>17.8</v>
-      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1239,15 +1185,6 @@
       <c r="T8" t="n">
         <v>20.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>27</v>
-      </c>
-      <c r="X8" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1352,15 +1289,6 @@
       <c r="T9" t="n">
         <v>19</v>
       </c>
-      <c r="V9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
@@ -1465,15 +1393,6 @@
       <c r="T10" t="n">
         <v>21.6</v>
       </c>
-      <c r="V10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y10" t="n">
         <v>11</v>
       </c>
@@ -1545,15 +1464,6 @@
       <c r="O11" t="n">
         <v>35.1</v>
       </c>
-      <c r="V11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>19</v>
-      </c>
       <c r="Y11" t="n">
         <v>14</v>
       </c>
@@ -1619,15 +1529,6 @@
       <c r="O12" t="n">
         <v>31.6</v>
       </c>
-      <c r="V12" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y12" t="n">
         <v>14</v>
       </c>
@@ -1726,15 +1627,6 @@
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1839,15 +1731,6 @@
       <c r="T14" t="n">
         <v>21.1</v>
       </c>
-      <c r="V14" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
@@ -1952,15 +1835,6 @@
       <c r="T15" t="n">
         <v>21.3</v>
       </c>
-      <c r="V15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>20</v>
-      </c>
       <c r="Y15" t="n">
         <v>11</v>
       </c>
@@ -2065,15 +1939,6 @@
       <c r="T16" t="n">
         <v>20.9</v>
       </c>
-      <c r="V16" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
@@ -2178,15 +2043,6 @@
       <c r="T17" t="n">
         <v>21</v>
       </c>
-      <c r="V17" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>27</v>
-      </c>
-      <c r="X17" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y17" t="n">
         <v>9</v>
       </c>
@@ -2253,28 +2109,19 @@
         <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>81.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="R18" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>14</v>
+        <v>22.9</v>
       </c>
       <c r="Y18" t="n">
         <v>5</v>
@@ -2341,15 +2188,6 @@
       <c r="O19" t="n">
         <v>35.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
@@ -2415,15 +2253,6 @@
       <c r="O20" t="n">
         <v>35.1</v>
       </c>
-      <c r="V20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y20" t="n">
         <v>3</v>
       </c>
@@ -2522,15 +2351,6 @@
       <c r="T21" t="n">
         <v>22.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
@@ -2635,15 +2455,6 @@
       <c r="T22" t="n">
         <v>23</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X22" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y22" t="n">
         <v>6</v>
       </c>
@@ -2760,15 +2571,6 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y23" t="n">
         <v>8</v>
       </c>
@@ -2852,15 +2654,6 @@
       <c r="O24" t="n">
         <v>40.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2938,15 +2731,6 @@
       <c r="O25" t="n">
         <v>38.5</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X25" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>10</v>
       </c>
@@ -3024,15 +2808,6 @@
       <c r="O26" t="n">
         <v>39.8</v>
       </c>
-      <c r="V26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X26" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y26" t="n">
         <v>13</v>
       </c>
@@ -3110,15 +2885,6 @@
       <c r="O27" t="n">
         <v>35.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y27" t="n">
         <v>12</v>
       </c>
@@ -3229,15 +2995,6 @@
       <c r="T28" t="n">
         <v>23.2</v>
       </c>
-      <c r="V28" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>13</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3354,15 +3111,6 @@
       <c r="T29" t="n">
         <v>23.8</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y29" t="n">
         <v>7</v>
       </c>
@@ -3479,15 +3227,6 @@
       <c r="T30" t="n">
         <v>23.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>6</v>
       </c>
@@ -3604,15 +3343,6 @@
       <c r="T31" t="n">
         <v>23.7</v>
       </c>
-      <c r="V31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y31" t="n">
         <v>8</v>
       </c>
@@ -3696,15 +3426,6 @@
       <c r="O32" t="n">
         <v>34.4</v>
       </c>
-      <c r="V32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y32" t="n">
         <v>6</v>
       </c>
@@ -3782,15 +3503,6 @@
       <c r="O33" t="n">
         <v>35.2</v>
       </c>
-      <c r="V33" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W33" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X33" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y33" t="n">
         <v>4</v>
       </c>
@@ -3901,15 +3613,6 @@
       <c r="T34" t="n">
         <v>23.5</v>
       </c>
-      <c r="V34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>4</v>
       </c>
@@ -4026,15 +3729,6 @@
       <c r="T35" t="n">
         <v>23.1</v>
       </c>
-      <c r="V35" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W35" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y35" t="n">
         <v>7</v>
       </c>
@@ -4151,15 +3845,6 @@
       <c r="T36" t="n">
         <v>23.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W36" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>8</v>
       </c>
@@ -4276,15 +3961,6 @@
       <c r="T37" t="n">
         <v>23.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4401,15 +4077,6 @@
       <c r="T38" t="n">
         <v>23.2</v>
       </c>
-      <c r="V38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y38" t="n">
         <v>10</v>
       </c>
@@ -4488,28 +4155,19 @@
         <v>6.1</v>
       </c>
       <c r="K39" t="n">
-        <v>72.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>39.1</v>
       </c>
       <c r="R39" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S39" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T39" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>19.4</v>
+        <v>22.9</v>
       </c>
       <c r="Y39" t="n">
         <v>9</v>
@@ -4583,28 +4241,19 @@
         <v>3.4</v>
       </c>
       <c r="K40" t="n">
-        <v>65</v>
+        <v>63.5</v>
       </c>
       <c r="O40" t="n">
         <v>35</v>
       </c>
       <c r="R40" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S40" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T40" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>17.4</v>
+        <v>22.9</v>
       </c>
       <c r="Y40" t="n">
         <v>8</v>
@@ -4716,15 +4365,6 @@
       <c r="T41" t="n">
         <v>21.4</v>
       </c>
-      <c r="V41" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X41" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y41" t="n">
         <v>8</v>
       </c>
@@ -4841,15 +4481,6 @@
       <c r="T42" t="n">
         <v>19.7</v>
       </c>
-      <c r="V42" t="n">
-        <v>12</v>
-      </c>
-      <c r="W42" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X42" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>12</v>
       </c>
@@ -4966,15 +4597,6 @@
       <c r="T43" t="n">
         <v>20.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X43" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y43" t="n">
         <v>10</v>
       </c>
@@ -5091,15 +4713,6 @@
       <c r="T44" t="n">
         <v>21.6</v>
       </c>
-      <c r="V44" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W44" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>11</v>
       </c>
@@ -5216,15 +4829,6 @@
       <c r="T45" t="n">
         <v>21</v>
       </c>
-      <c r="V45" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y45" t="n">
         <v>12</v>
       </c>
@@ -5303,28 +4907,19 @@
         <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="O46" t="n">
         <v>37</v>
       </c>
       <c r="R46" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S46" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T46" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V46" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X46" t="n">
-        <v>17.4</v>
+        <v>22.9</v>
       </c>
       <c r="Y46" t="n">
         <v>7</v>
@@ -5398,28 +4993,19 @@
         <v>3.3</v>
       </c>
       <c r="K47" t="n">
-        <v>71.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="O47" t="n">
         <v>38.7</v>
       </c>
       <c r="R47" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S47" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T47" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V47" t="n">
-        <v>11</v>
-      </c>
-      <c r="W47" t="n">
-        <v>22</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.5</v>
+        <v>22.9</v>
       </c>
       <c r="Y47" t="n">
         <v>7</v>
@@ -5531,15 +5117,6 @@
       <c r="T48" t="n">
         <v>23.7</v>
       </c>
-      <c r="V48" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W48" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -5656,15 +5233,6 @@
       <c r="T49" t="n">
         <v>23.9</v>
       </c>
-      <c r="V49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W49" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y49" t="n">
         <v>5</v>
       </c>
@@ -5781,15 +5349,6 @@
       <c r="T50" t="n">
         <v>21.7</v>
       </c>
-      <c r="V50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>21</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y50" t="n">
         <v>9</v>
       </c>
@@ -5915,6 +5474,15 @@
       <c r="AA51" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>6.3</v>
+      </c>
       <c r="AF51" t="n">
         <v>220.84</v>
       </c>
@@ -6088,19 +5656,19 @@
         <v>3.3</v>
       </c>
       <c r="K53" t="n">
-        <v>69.8</v>
+        <v>68.3</v>
       </c>
       <c r="O53" t="n">
         <v>37.6</v>
       </c>
       <c r="R53" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S53" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T53" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="Y53" t="n">
         <v>12</v>
@@ -6165,19 +5733,19 @@
         <v>2.3</v>
       </c>
       <c r="K54" t="n">
-        <v>72.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="R54" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S54" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="Y54" t="n">
         <v>10</v>
@@ -6334,34 +5902,52 @@
         <v>46279</v>
       </c>
       <c r="B56" t="n">
-        <v>150.3</v>
+        <v>139.6</v>
       </c>
       <c r="C56" t="n">
-        <v>75.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>33.3</v>
+        <v>32.2</v>
       </c>
       <c r="E56" t="n">
-        <v>29</v>
+        <v>25.9</v>
       </c>
       <c r="F56" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J56" t="n">
+        <v>39.6</v>
       </c>
       <c r="K56" t="n">
-        <v>80.5</v>
+        <v>73.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N56" t="n">
+        <v>34.4</v>
       </c>
       <c r="O56" t="n">
-        <v>43.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>23.8</v>
       </c>
       <c r="R56" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S56" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="Y56" t="n">
         <v>5</v>
@@ -6372,17 +5958,35 @@
       <c r="AA56" t="n">
         <v>10.5</v>
       </c>
+      <c r="AF56" t="n">
+        <v>223.35</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-0.85</v>
+      </c>
       <c r="AH56" t="n">
         <v>215</v>
       </c>
       <c r="AI56" t="n">
         <v>235</v>
       </c>
+      <c r="AK56" t="n">
+        <v>129.17</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.98</v>
+      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>13.63</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46279</v>
@@ -6420,19 +6024,19 @@
         <v>2.3</v>
       </c>
       <c r="K57" t="n">
-        <v>69.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O57" t="n">
         <v>37.2</v>
       </c>
       <c r="R57" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="S57" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="T57" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="Y57" t="n">
         <v>11</v>
@@ -6457,11 +6061,62 @@
       </c>
       <c r="BL57" s="1" t="n">
         <v>46280</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>2801.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>46281</v>
+      </c>
+      <c r="B58" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>10.5</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>22.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -782,6 +791,15 @@
       <c r="T3" t="n">
         <v>23.3</v>
       </c>
+      <c r="V3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -853,6 +871,15 @@
       <c r="O4" t="n">
         <v>39.2</v>
       </c>
+      <c r="V4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
@@ -918,6 +945,15 @@
       <c r="O5" t="n">
         <v>39.3</v>
       </c>
+      <c r="V5" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y5" t="n">
         <v>11</v>
       </c>
@@ -1016,6 +1052,15 @@
       <c r="T6" t="n">
         <v>21.7</v>
       </c>
+      <c r="V6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1087,6 +1132,15 @@
       <c r="O7" t="n">
         <v>37.9</v>
       </c>
+      <c r="V7" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17.8</v>
+      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1185,6 +1239,15 @@
       <c r="T8" t="n">
         <v>20.3</v>
       </c>
+      <c r="V8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1289,6 +1352,15 @@
       <c r="T9" t="n">
         <v>19</v>
       </c>
+      <c r="V9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
@@ -1393,6 +1465,15 @@
       <c r="T10" t="n">
         <v>21.6</v>
       </c>
+      <c r="V10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y10" t="n">
         <v>11</v>
       </c>
@@ -1464,6 +1545,15 @@
       <c r="O11" t="n">
         <v>35.1</v>
       </c>
+      <c r="V11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19</v>
+      </c>
       <c r="Y11" t="n">
         <v>14</v>
       </c>
@@ -1529,6 +1619,15 @@
       <c r="O12" t="n">
         <v>31.6</v>
       </c>
+      <c r="V12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y12" t="n">
         <v>14</v>
       </c>
@@ -1627,6 +1726,15 @@
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
+      <c r="V13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1731,6 +1839,15 @@
       <c r="T14" t="n">
         <v>21.1</v>
       </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
@@ -1835,6 +1952,15 @@
       <c r="T15" t="n">
         <v>21.3</v>
       </c>
+      <c r="V15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>20</v>
+      </c>
       <c r="Y15" t="n">
         <v>11</v>
       </c>
@@ -1939,6 +2065,15 @@
       <c r="T16" t="n">
         <v>20.9</v>
       </c>
+      <c r="V16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
@@ -2043,6 +2178,15 @@
       <c r="T17" t="n">
         <v>21</v>
       </c>
+      <c r="V17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y17" t="n">
         <v>9</v>
       </c>
@@ -2109,19 +2253,28 @@
         <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>79.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="R18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S18" t="n">
         <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
         <v>5</v>
@@ -2188,6 +2341,15 @@
       <c r="O19" t="n">
         <v>35.5</v>
       </c>
+      <c r="V19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
@@ -2253,6 +2415,15 @@
       <c r="O20" t="n">
         <v>35.1</v>
       </c>
+      <c r="V20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y20" t="n">
         <v>3</v>
       </c>
@@ -2351,6 +2522,15 @@
       <c r="T21" t="n">
         <v>22.4</v>
       </c>
+      <c r="V21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
@@ -2455,6 +2635,15 @@
       <c r="T22" t="n">
         <v>23</v>
       </c>
+      <c r="V22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y22" t="n">
         <v>6</v>
       </c>
@@ -2571,6 +2760,15 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y23" t="n">
         <v>8</v>
       </c>
@@ -2654,6 +2852,15 @@
       <c r="O24" t="n">
         <v>40.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2731,6 +2938,15 @@
       <c r="O25" t="n">
         <v>38.5</v>
       </c>
+      <c r="V25" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>10</v>
       </c>
@@ -2808,6 +3024,15 @@
       <c r="O26" t="n">
         <v>39.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y26" t="n">
         <v>13</v>
       </c>
@@ -2885,6 +3110,15 @@
       <c r="O27" t="n">
         <v>35.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y27" t="n">
         <v>12</v>
       </c>
@@ -2995,6 +3229,15 @@
       <c r="T28" t="n">
         <v>23.2</v>
       </c>
+      <c r="V28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3111,6 +3354,15 @@
       <c r="T29" t="n">
         <v>23.8</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y29" t="n">
         <v>7</v>
       </c>
@@ -3227,6 +3479,15 @@
       <c r="T30" t="n">
         <v>23.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y30" t="n">
         <v>6</v>
       </c>
@@ -3343,6 +3604,15 @@
       <c r="T31" t="n">
         <v>23.7</v>
       </c>
+      <c r="V31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y31" t="n">
         <v>8</v>
       </c>
@@ -3426,6 +3696,15 @@
       <c r="O32" t="n">
         <v>34.4</v>
       </c>
+      <c r="V32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y32" t="n">
         <v>6</v>
       </c>
@@ -3503,6 +3782,15 @@
       <c r="O33" t="n">
         <v>35.2</v>
       </c>
+      <c r="V33" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y33" t="n">
         <v>4</v>
       </c>
@@ -3613,6 +3901,15 @@
       <c r="T34" t="n">
         <v>23.5</v>
       </c>
+      <c r="V34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>4</v>
       </c>
@@ -3729,6 +4026,15 @@
       <c r="T35" t="n">
         <v>23.1</v>
       </c>
+      <c r="V35" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W35" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y35" t="n">
         <v>7</v>
       </c>
@@ -3845,6 +4151,15 @@
       <c r="T36" t="n">
         <v>23.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>8</v>
       </c>
@@ -3961,6 +4276,15 @@
       <c r="T37" t="n">
         <v>23.2</v>
       </c>
+      <c r="V37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4077,6 +4401,15 @@
       <c r="T38" t="n">
         <v>23.2</v>
       </c>
+      <c r="V38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y38" t="n">
         <v>10</v>
       </c>
@@ -4155,19 +4488,28 @@
         <v>6.1</v>
       </c>
       <c r="K39" t="n">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="O39" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="R39" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S39" t="n">
         <v>1.2</v>
       </c>
       <c r="T39" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
+      </c>
+      <c r="V39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y39" t="n">
         <v>9</v>
@@ -4241,19 +4583,28 @@
         <v>3.4</v>
       </c>
       <c r="K40" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="O40" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="R40" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S40" t="n">
         <v>1.2</v>
       </c>
       <c r="T40" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y40" t="n">
         <v>8</v>
@@ -4365,6 +4716,15 @@
       <c r="T41" t="n">
         <v>21.4</v>
       </c>
+      <c r="V41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y41" t="n">
         <v>8</v>
       </c>
@@ -4481,6 +4841,15 @@
       <c r="T42" t="n">
         <v>19.7</v>
       </c>
+      <c r="V42" t="n">
+        <v>12</v>
+      </c>
+      <c r="W42" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>12</v>
       </c>
@@ -4597,6 +4966,15 @@
       <c r="T43" t="n">
         <v>20.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y43" t="n">
         <v>10</v>
       </c>
@@ -4713,6 +5091,15 @@
       <c r="T44" t="n">
         <v>21.6</v>
       </c>
+      <c r="V44" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X44" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>11</v>
       </c>
@@ -4829,6 +5216,15 @@
       <c r="T45" t="n">
         <v>21</v>
       </c>
+      <c r="V45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y45" t="n">
         <v>12</v>
       </c>
@@ -4907,19 +5303,28 @@
         <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="R46" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S46" t="n">
         <v>1.2</v>
       </c>
       <c r="T46" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X46" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y46" t="n">
         <v>7</v>
@@ -4993,19 +5398,28 @@
         <v>3.3</v>
       </c>
       <c r="K47" t="n">
-        <v>70.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="R47" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S47" t="n">
         <v>1.2</v>
       </c>
       <c r="T47" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11</v>
+      </c>
+      <c r="W47" t="n">
+        <v>22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y47" t="n">
         <v>7</v>
@@ -5117,6 +5531,15 @@
       <c r="T48" t="n">
         <v>23.7</v>
       </c>
+      <c r="V48" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -5233,6 +5656,15 @@
       <c r="T49" t="n">
         <v>23.9</v>
       </c>
+      <c r="V49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W49" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y49" t="n">
         <v>5</v>
       </c>
@@ -5349,6 +5781,15 @@
       <c r="T50" t="n">
         <v>21.7</v>
       </c>
+      <c r="V50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>21</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y50" t="n">
         <v>9</v>
       </c>
@@ -5465,6 +5906,15 @@
       <c r="T51" t="n">
         <v>21.7</v>
       </c>
+      <c r="V51" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W51" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y51" t="n">
         <v>10</v>
       </c>
@@ -5581,6 +6031,15 @@
       <c r="T52" t="n">
         <v>22</v>
       </c>
+      <c r="V52" t="n">
+        <v>11</v>
+      </c>
+      <c r="W52" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y52" t="n">
         <v>11</v>
       </c>
@@ -5589,6 +6048,15 @@
       </c>
       <c r="AA52" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF52" t="n">
         <v>225.87</v>
@@ -5656,19 +6124,19 @@
         <v>3.3</v>
       </c>
       <c r="K53" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="O53" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="R53" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S53" t="n">
         <v>1.2</v>
       </c>
       <c r="T53" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Y53" t="n">
         <v>12</v>
@@ -5733,19 +6201,19 @@
         <v>2.3</v>
       </c>
       <c r="K54" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="O54" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="R54" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S54" t="n">
         <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Y54" t="n">
         <v>10</v>
@@ -6009,34 +6477,52 @@
         <v>46280</v>
       </c>
       <c r="B57" t="n">
-        <v>132.8</v>
+        <v>133.5</v>
       </c>
       <c r="C57" t="n">
-        <v>66.5</v>
+        <v>62.3</v>
       </c>
       <c r="D57" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="E57" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40.8</v>
       </c>
       <c r="K57" t="n">
-        <v>67.59999999999999</v>
+        <v>75</v>
+      </c>
+      <c r="M57" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>30.4</v>
       </c>
       <c r="O57" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>22.1</v>
       </c>
       <c r="R57" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="Y57" t="n">
         <v>11</v>
@@ -6047,17 +6533,35 @@
       <c r="AA57" t="n">
         <v>16</v>
       </c>
+      <c r="AF57" t="n">
+        <v>223.06</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-0.29</v>
+      </c>
       <c r="AH57" t="n">
         <v>215</v>
       </c>
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>130.42</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.25</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>82.36</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>13.91</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46280</v>
@@ -6095,19 +6599,19 @@
         <v>2.3</v>
       </c>
       <c r="K58" t="n">
-        <v>67.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="R58" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="S58" t="n">
         <v>1.2</v>
       </c>
       <c r="T58" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Y58" t="n">
         <v>6</v>
@@ -6132,11 +6636,62 @@
       </c>
       <c r="BL58" s="1" t="n">
         <v>46281</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>235.3</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>52.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>46282</v>
+      </c>
+      <c r="B59" t="n">
+        <v>125</v>
+      </c>
+      <c r="C59" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K59" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T59" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>16.5</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>20.5</v>
       </c>
+      <c r="V2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -758,6 +767,15 @@
       <c r="T3" t="n">
         <v>22.3</v>
       </c>
+      <c r="V3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -844,6 +862,15 @@
       <c r="T4" t="n">
         <v>22.5</v>
       </c>
+      <c r="V4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>13</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -924,6 +951,15 @@
       <c r="T5" t="n">
         <v>22.6</v>
       </c>
+      <c r="V5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y5" t="n">
         <v>9</v>
       </c>
@@ -1010,6 +1046,15 @@
       <c r="T6" t="n">
         <v>23.3</v>
       </c>
+      <c r="V6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y6" t="n">
         <v>8</v>
       </c>
@@ -1069,6 +1114,15 @@
       <c r="T7" t="n">
         <v>22.7</v>
       </c>
+      <c r="V7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>14</v>
+      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1134,6 +1188,15 @@
       <c r="T8" t="n">
         <v>22.7</v>
       </c>
+      <c r="V8" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1220,6 +1283,15 @@
       <c r="T9" t="n">
         <v>21.7</v>
       </c>
+      <c r="V9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y9" t="n">
         <v>12</v>
       </c>
@@ -1285,6 +1357,15 @@
       <c r="T10" t="n">
         <v>22.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>13</v>
       </c>
@@ -1371,6 +1452,15 @@
       <c r="T11" t="n">
         <v>20.3</v>
       </c>
+      <c r="V11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>27</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
@@ -1451,6 +1541,15 @@
       <c r="T12" t="n">
         <v>19</v>
       </c>
+      <c r="V12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>9</v>
       </c>
@@ -1537,6 +1636,15 @@
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
+      <c r="V13" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y13" t="n">
         <v>11</v>
       </c>
@@ -1602,6 +1710,15 @@
       <c r="T14" t="n">
         <v>22.7</v>
       </c>
+      <c r="V14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>19</v>
+      </c>
       <c r="Y14" t="n">
         <v>14</v>
       </c>
@@ -1667,6 +1784,15 @@
       <c r="T15" t="n">
         <v>22.7</v>
       </c>
+      <c r="V15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y15" t="n">
         <v>14</v>
       </c>
@@ -1753,6 +1879,15 @@
       <c r="T16" t="n">
         <v>21.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y16" t="n">
         <v>12</v>
       </c>
@@ -1839,6 +1974,15 @@
       <c r="T17" t="n">
         <v>21.1</v>
       </c>
+      <c r="V17" t="n">
+        <v>13</v>
+      </c>
+      <c r="W17" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y17" t="n">
         <v>13</v>
       </c>
@@ -1925,6 +2069,15 @@
       <c r="T18" t="n">
         <v>21.3</v>
       </c>
+      <c r="V18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20</v>
+      </c>
       <c r="Y18" t="n">
         <v>11</v>
       </c>
@@ -2011,6 +2164,15 @@
       <c r="T19" t="n">
         <v>20.9</v>
       </c>
+      <c r="V19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2097,6 +2259,15 @@
       <c r="T20" t="n">
         <v>21</v>
       </c>
+      <c r="V20" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>27</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y20" t="n">
         <v>9</v>
       </c>
@@ -2156,6 +2327,15 @@
       <c r="T21" t="n">
         <v>22.7</v>
       </c>
+      <c r="V21" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W21" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14</v>
+      </c>
       <c r="Y21" t="n">
         <v>5</v>
       </c>
@@ -2221,6 +2401,15 @@
       <c r="T22" t="n">
         <v>22.7</v>
       </c>
+      <c r="V22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2286,6 +2475,15 @@
       <c r="T23" t="n">
         <v>22.7</v>
       </c>
+      <c r="V23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y23" t="n">
         <v>3</v>
       </c>
@@ -2372,6 +2570,15 @@
       <c r="T24" t="n">
         <v>22.4</v>
       </c>
+      <c r="V24" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>15</v>
+      </c>
+      <c r="X24" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y24" t="n">
         <v>4</v>
       </c>
@@ -2458,6 +2665,15 @@
       <c r="T25" t="n">
         <v>23</v>
       </c>
+      <c r="V25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2556,6 +2772,15 @@
       <c r="T26" t="n">
         <v>23.6</v>
       </c>
+      <c r="V26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2633,6 +2858,15 @@
       <c r="T27" t="n">
         <v>22.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2710,6 +2944,15 @@
       <c r="T28" t="n">
         <v>22.7</v>
       </c>
+      <c r="V28" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y28" t="n">
         <v>10</v>
       </c>
@@ -2787,6 +3030,15 @@
       <c r="T29" t="n">
         <v>22.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y29" t="n">
         <v>13</v>
       </c>
@@ -2864,6 +3116,15 @@
       <c r="T30" t="n">
         <v>22.7</v>
       </c>
+      <c r="V30" t="n">
+        <v>9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X30" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y30" t="n">
         <v>12</v>
       </c>
@@ -2962,6 +3223,15 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
+      <c r="V31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W31" t="n">
+        <v>13</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3060,6 +3330,15 @@
       <c r="T32" t="n">
         <v>23.8</v>
       </c>
+      <c r="V32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3158,6 +3437,15 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
+      <c r="V33" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y33" t="n">
         <v>6</v>
       </c>
@@ -3256,6 +3544,15 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3333,6 +3630,15 @@
       <c r="T35" t="n">
         <v>22.7</v>
       </c>
+      <c r="V35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -3410,6 +3716,15 @@
       <c r="T36" t="n">
         <v>22.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X36" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y36" t="n">
         <v>4</v>
       </c>
@@ -3508,6 +3823,15 @@
       <c r="T37" t="n">
         <v>23.5</v>
       </c>
+      <c r="V37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y37" t="n">
         <v>4</v>
       </c>
@@ -3606,6 +3930,15 @@
       <c r="T38" t="n">
         <v>23.1</v>
       </c>
+      <c r="V38" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W38" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y38" t="n">
         <v>7</v>
       </c>
@@ -3704,6 +4037,15 @@
       <c r="T39" t="n">
         <v>23.1</v>
       </c>
+      <c r="V39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X39" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y39" t="n">
         <v>8</v>
       </c>
@@ -3802,6 +4144,15 @@
       <c r="T40" t="n">
         <v>23.2</v>
       </c>
+      <c r="V40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y40" t="n">
         <v>10</v>
       </c>
@@ -3900,6 +4251,15 @@
       <c r="T41" t="n">
         <v>23.2</v>
       </c>
+      <c r="V41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y41" t="n">
         <v>10</v>
       </c>
@@ -3977,6 +4337,15 @@
       <c r="T42" t="n">
         <v>22.7</v>
       </c>
+      <c r="V42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X42" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y42" t="n">
         <v>9</v>
       </c>
@@ -4054,6 +4423,15 @@
       <c r="T43" t="n">
         <v>22.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>8</v>
       </c>
@@ -4152,6 +4530,15 @@
       <c r="T44" t="n">
         <v>21.4</v>
       </c>
+      <c r="V44" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W44" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X44" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y44" t="n">
         <v>8</v>
       </c>
@@ -4250,6 +4637,15 @@
       <c r="T45" t="n">
         <v>19.7</v>
       </c>
+      <c r="V45" t="n">
+        <v>12</v>
+      </c>
+      <c r="W45" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X45" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y45" t="n">
         <v>12</v>
       </c>
@@ -4348,6 +4744,15 @@
       <c r="T46" t="n">
         <v>20.7</v>
       </c>
+      <c r="V46" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y46" t="n">
         <v>10</v>
       </c>
@@ -4446,6 +4851,15 @@
       <c r="T47" t="n">
         <v>21.6</v>
       </c>
+      <c r="V47" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X47" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y47" t="n">
         <v>11</v>
       </c>
@@ -4544,6 +4958,15 @@
       <c r="T48" t="n">
         <v>21</v>
       </c>
+      <c r="V48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W48" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X48" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y48" t="n">
         <v>12</v>
       </c>
@@ -4621,6 +5044,15 @@
       <c r="T49" t="n">
         <v>22.7</v>
       </c>
+      <c r="V49" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X49" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y49" t="n">
         <v>7</v>
       </c>
@@ -4698,6 +5130,15 @@
       <c r="T50" t="n">
         <v>22.7</v>
       </c>
+      <c r="V50" t="n">
+        <v>11</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y50" t="n">
         <v>7</v>
       </c>
@@ -4796,6 +5237,15 @@
       <c r="T51" t="n">
         <v>23.7</v>
       </c>
+      <c r="V51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W51" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X51" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y51" t="n">
         <v>3</v>
       </c>
@@ -4894,6 +5344,15 @@
       <c r="T52" t="n">
         <v>23.9</v>
       </c>
+      <c r="V52" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y52" t="n">
         <v>5</v>
       </c>
@@ -4992,6 +5451,15 @@
       <c r="T53" t="n">
         <v>21.7</v>
       </c>
+      <c r="V53" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W53" t="n">
+        <v>21</v>
+      </c>
+      <c r="X53" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y53" t="n">
         <v>9</v>
       </c>
@@ -5090,6 +5558,15 @@
       <c r="T54" t="n">
         <v>21.7</v>
       </c>
+      <c r="V54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W54" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y54" t="n">
         <v>10</v>
       </c>
@@ -5181,6 +5658,15 @@
       </c>
       <c r="T55" t="n">
         <v>22</v>
+      </c>
+      <c r="V55" t="n">
+        <v>11</v>
+      </c>
+      <c r="W55" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X55" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y55" t="n">
         <v>11</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.5</v>
       </c>
-      <c r="V2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -767,15 +758,6 @@
       <c r="T3" t="n">
         <v>22.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -862,15 +844,6 @@
       <c r="T4" t="n">
         <v>22.5</v>
       </c>
-      <c r="V4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>13</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -951,15 +924,6 @@
       <c r="T5" t="n">
         <v>22.6</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y5" t="n">
         <v>9</v>
       </c>
@@ -1046,15 +1010,6 @@
       <c r="T6" t="n">
         <v>23.3</v>
       </c>
-      <c r="V6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X6" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>8</v>
       </c>
@@ -1114,15 +1069,6 @@
       <c r="T7" t="n">
         <v>22.7</v>
       </c>
-      <c r="V7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X7" t="n">
-        <v>14</v>
-      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1188,15 +1134,6 @@
       <c r="T8" t="n">
         <v>22.7</v>
       </c>
-      <c r="V8" t="n">
-        <v>8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1283,15 +1220,6 @@
       <c r="T9" t="n">
         <v>21.7</v>
       </c>
-      <c r="V9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y9" t="n">
         <v>12</v>
       </c>
@@ -1357,15 +1285,6 @@
       <c r="T10" t="n">
         <v>22.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>10</v>
-      </c>
-      <c r="W10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>17.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>13</v>
       </c>
@@ -1452,15 +1371,6 @@
       <c r="T11" t="n">
         <v>20.3</v>
       </c>
-      <c r="V11" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>27</v>
-      </c>
-      <c r="X11" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
@@ -1541,15 +1451,6 @@
       <c r="T12" t="n">
         <v>19</v>
       </c>
-      <c r="V12" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>9</v>
       </c>
@@ -1636,15 +1537,6 @@
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y13" t="n">
         <v>11</v>
       </c>
@@ -1710,15 +1602,6 @@
       <c r="T14" t="n">
         <v>22.7</v>
       </c>
-      <c r="V14" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>19</v>
-      </c>
       <c r="Y14" t="n">
         <v>14</v>
       </c>
@@ -1784,15 +1667,6 @@
       <c r="T15" t="n">
         <v>22.7</v>
       </c>
-      <c r="V15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X15" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y15" t="n">
         <v>14</v>
       </c>
@@ -1879,15 +1753,6 @@
       <c r="T16" t="n">
         <v>21.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y16" t="n">
         <v>12</v>
       </c>
@@ -1974,15 +1839,6 @@
       <c r="T17" t="n">
         <v>21.1</v>
       </c>
-      <c r="V17" t="n">
-        <v>13</v>
-      </c>
-      <c r="W17" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y17" t="n">
         <v>13</v>
       </c>
@@ -2069,15 +1925,6 @@
       <c r="T18" t="n">
         <v>21.3</v>
       </c>
-      <c r="V18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>20</v>
-      </c>
       <c r="Y18" t="n">
         <v>11</v>
       </c>
@@ -2164,15 +2011,6 @@
       <c r="T19" t="n">
         <v>20.9</v>
       </c>
-      <c r="V19" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2259,15 +2097,6 @@
       <c r="T20" t="n">
         <v>21</v>
       </c>
-      <c r="V20" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>27</v>
-      </c>
-      <c r="X20" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y20" t="n">
         <v>9</v>
       </c>
@@ -2327,15 +2156,6 @@
       <c r="T21" t="n">
         <v>22.7</v>
       </c>
-      <c r="V21" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W21" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>14</v>
-      </c>
       <c r="Y21" t="n">
         <v>5</v>
       </c>
@@ -2401,15 +2221,6 @@
       <c r="T22" t="n">
         <v>22.7</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2475,15 +2286,6 @@
       <c r="T23" t="n">
         <v>22.7</v>
       </c>
-      <c r="V23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X23" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y23" t="n">
         <v>3</v>
       </c>
@@ -2570,15 +2372,6 @@
       <c r="T24" t="n">
         <v>22.4</v>
       </c>
-      <c r="V24" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y24" t="n">
         <v>4</v>
       </c>
@@ -2665,15 +2458,6 @@
       <c r="T25" t="n">
         <v>23</v>
       </c>
-      <c r="V25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X25" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2772,15 +2556,6 @@
       <c r="T26" t="n">
         <v>23.6</v>
       </c>
-      <c r="V26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2858,15 +2633,6 @@
       <c r="T27" t="n">
         <v>22.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2944,15 +2710,6 @@
       <c r="T28" t="n">
         <v>22.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W28" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y28" t="n">
         <v>10</v>
       </c>
@@ -3030,15 +2787,6 @@
       <c r="T29" t="n">
         <v>22.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y29" t="n">
         <v>13</v>
       </c>
@@ -3116,15 +2864,6 @@
       <c r="T30" t="n">
         <v>22.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X30" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y30" t="n">
         <v>12</v>
       </c>
@@ -3223,15 +2962,6 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W31" t="n">
-        <v>13</v>
-      </c>
-      <c r="X31" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3330,15 +3060,6 @@
       <c r="T32" t="n">
         <v>23.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3437,15 +3158,6 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
-      <c r="V33" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W33" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y33" t="n">
         <v>6</v>
       </c>
@@ -3544,15 +3256,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X34" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3630,15 +3333,6 @@
       <c r="T35" t="n">
         <v>22.7</v>
       </c>
-      <c r="V35" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X35" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -3716,15 +3410,6 @@
       <c r="T36" t="n">
         <v>22.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W36" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X36" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>4</v>
       </c>
@@ -3823,15 +3508,6 @@
       <c r="T37" t="n">
         <v>23.5</v>
       </c>
-      <c r="V37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y37" t="n">
         <v>4</v>
       </c>
@@ -3930,15 +3606,6 @@
       <c r="T38" t="n">
         <v>23.1</v>
       </c>
-      <c r="V38" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y38" t="n">
         <v>7</v>
       </c>
@@ -4037,15 +3704,6 @@
       <c r="T39" t="n">
         <v>23.1</v>
       </c>
-      <c r="V39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y39" t="n">
         <v>8</v>
       </c>
@@ -4144,15 +3802,6 @@
       <c r="T40" t="n">
         <v>23.2</v>
       </c>
-      <c r="V40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y40" t="n">
         <v>10</v>
       </c>
@@ -4251,15 +3900,6 @@
       <c r="T41" t="n">
         <v>23.2</v>
       </c>
-      <c r="V41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W41" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X41" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y41" t="n">
         <v>10</v>
       </c>
@@ -4337,15 +3977,6 @@
       <c r="T42" t="n">
         <v>22.7</v>
       </c>
-      <c r="V42" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X42" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y42" t="n">
         <v>9</v>
       </c>
@@ -4423,15 +4054,6 @@
       <c r="T43" t="n">
         <v>22.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X43" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>8</v>
       </c>
@@ -4530,15 +4152,6 @@
       <c r="T44" t="n">
         <v>21.4</v>
       </c>
-      <c r="V44" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W44" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X44" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y44" t="n">
         <v>8</v>
       </c>
@@ -4637,15 +4250,6 @@
       <c r="T45" t="n">
         <v>19.7</v>
       </c>
-      <c r="V45" t="n">
-        <v>12</v>
-      </c>
-      <c r="W45" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X45" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y45" t="n">
         <v>12</v>
       </c>
@@ -4744,15 +4348,6 @@
       <c r="T46" t="n">
         <v>20.7</v>
       </c>
-      <c r="V46" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X46" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y46" t="n">
         <v>10</v>
       </c>
@@ -4851,15 +4446,6 @@
       <c r="T47" t="n">
         <v>21.6</v>
       </c>
-      <c r="V47" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X47" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y47" t="n">
         <v>11</v>
       </c>
@@ -4958,15 +4544,6 @@
       <c r="T48" t="n">
         <v>21</v>
       </c>
-      <c r="V48" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W48" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X48" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y48" t="n">
         <v>12</v>
       </c>
@@ -5044,15 +4621,6 @@
       <c r="T49" t="n">
         <v>22.7</v>
       </c>
-      <c r="V49" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X49" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y49" t="n">
         <v>7</v>
       </c>
@@ -5130,15 +4698,6 @@
       <c r="T50" t="n">
         <v>22.7</v>
       </c>
-      <c r="V50" t="n">
-        <v>11</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22</v>
-      </c>
-      <c r="X50" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y50" t="n">
         <v>7</v>
       </c>
@@ -5237,15 +4796,6 @@
       <c r="T51" t="n">
         <v>23.7</v>
       </c>
-      <c r="V51" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W51" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X51" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y51" t="n">
         <v>3</v>
       </c>
@@ -5344,15 +4894,6 @@
       <c r="T52" t="n">
         <v>23.9</v>
       </c>
-      <c r="V52" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X52" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y52" t="n">
         <v>5</v>
       </c>
@@ -5451,15 +4992,6 @@
       <c r="T53" t="n">
         <v>21.7</v>
       </c>
-      <c r="V53" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W53" t="n">
-        <v>21</v>
-      </c>
-      <c r="X53" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y53" t="n">
         <v>9</v>
       </c>
@@ -5558,15 +5090,6 @@
       <c r="T54" t="n">
         <v>21.7</v>
       </c>
-      <c r="V54" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W54" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X54" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y54" t="n">
         <v>10</v>
       </c>
@@ -5658,15 +5181,6 @@
       </c>
       <c r="T55" t="n">
         <v>22</v>
-      </c>
-      <c r="V55" t="n">
-        <v>11</v>
-      </c>
-      <c r="W55" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X55" t="n">
-        <v>16.9</v>
       </c>
       <c r="Y55" t="n">
         <v>11</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -628,511 +628,559 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="B2" t="n">
-        <v>161.1</v>
+        <v>179.6</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="I2" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J2" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K2" t="n">
-        <v>75.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>37.1</v>
       </c>
       <c r="O2" t="n">
-        <v>37.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>21.2</v>
       </c>
       <c r="T2" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>225.51</v>
+        <v>216.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>133.83</v>
+        <v>127.85</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46222</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B3" t="n">
-        <v>176.4</v>
+        <v>170.4</v>
       </c>
       <c r="C3" t="n">
-        <v>77.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="D3" t="n">
-        <v>32.7</v>
+        <v>29.8</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>29.7</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="I3" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="J3" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="K3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="O3" t="n">
-        <v>39.1</v>
+        <v>41.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>21.1</v>
       </c>
       <c r="T3" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
         <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-5.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>220.92</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-4.59</v>
+        <v>4.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>131.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B4" t="n">
-        <v>181</v>
-      </c>
-      <c r="C4" t="n">
-        <v>80.7</v>
+        <v>156</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
-      </c>
-      <c r="E4" t="n">
-        <v>35.1</v>
+        <v>30.1</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41.9</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>36.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>39.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="S4" t="n">
-        <v>20.5</v>
+        <v>0.6</v>
       </c>
       <c r="T4" t="n">
-        <v>22.5</v>
+        <v>19.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-6.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>224.53</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>8.51</v>
       </c>
       <c r="AK4" t="n">
-        <v>130.06</v>
+        <v>130.92</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.79</v>
+        <v>2.38</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="B5" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>81.90000000000001</v>
+        <v>147.8</v>
       </c>
       <c r="D5" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
         <v>6.8</v>
       </c>
-      <c r="H5" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42.3</v>
-      </c>
       <c r="K5" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>37.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>41.4</v>
+        <v>40</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>21.2</v>
+        <v>0.6</v>
       </c>
       <c r="T5" t="n">
-        <v>22.6</v>
+        <v>19.9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>216.02</v>
+        <v>230.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.9</v>
+        <v>5.74</v>
       </c>
       <c r="AK5" t="n">
-        <v>127.85</v>
+        <v>132.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>-2.21</v>
+        <v>1.84</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="B6" t="n">
-        <v>170.4</v>
+        <v>149.1</v>
       </c>
       <c r="C6" t="n">
-        <v>78.5</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
-        <v>29.7</v>
+        <v>25.9</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="J6" t="n">
-        <v>41.4</v>
+        <v>38.8</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="O6" t="n">
-        <v>41.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.3</v>
+        <v>21.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>21.1</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>23.3</v>
+        <v>21.7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.7</v>
+        <v>-0.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>237.43</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>128.54</v>
+        <v>134.95</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.19</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>143.9</v>
       </c>
       <c r="D7" t="n">
-        <v>30.1</v>
+        <v>32.9</v>
       </c>
       <c r="F7" t="n">
         <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="O7" t="n">
-        <v>45.2</v>
+        <v>38.8</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="T7" t="n">
-        <v>22.7</v>
+        <v>19.9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>224.53</v>
+        <v>236.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>8.51</v>
+        <v>-1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>130.92</v>
+        <v>136.28</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="B8" t="n">
-        <v>147.8</v>
+        <v>166.4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>63.7</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>34.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>36.4</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39.9</v>
       </c>
       <c r="K8" t="n">
-        <v>77.5</v>
+        <v>75.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>35.9</v>
       </c>
       <c r="O8" t="n">
-        <v>42.3</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="R8" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>22.7</v>
+        <v>20.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
@@ -1144,2954 +1192,3326 @@
         <v>13.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>230.27</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5.74</v>
+        <v>-0.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>132.76</v>
+        <v>134.54</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.84</v>
+        <v>-1.74</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46229</v>
+        <v>46232</v>
       </c>
       <c r="B9" t="n">
-        <v>149.1</v>
+        <v>172.9</v>
       </c>
       <c r="C9" t="n">
-        <v>60</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>34.9</v>
       </c>
       <c r="E9" t="n">
-        <v>25.9</v>
+        <v>35.2</v>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="I9" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="J9" t="n">
-        <v>38.8</v>
+        <v>41.7</v>
       </c>
       <c r="K9" t="n">
-        <v>74.5</v>
+        <v>76.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="N9" t="n">
-        <v>36.7</v>
+        <v>34.8</v>
       </c>
       <c r="O9" t="n">
-        <v>40.1</v>
+        <v>37.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.7</v>
+        <v>19</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>21.7</v>
+        <v>19</v>
+      </c>
+      <c r="V9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>16</v>
-      </c>
       <c r="AB9" t="n">
-        <v>-2.4</v>
+        <v>-4.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>237.43</v>
+        <v>218.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.16</v>
+        <v>-17.54</v>
       </c>
       <c r="AK9" t="n">
-        <v>134.95</v>
+        <v>130.39</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.19</v>
+        <v>-4.15</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46229</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B10" t="n">
-        <v>143.9</v>
+        <v>157.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>68.5</v>
       </c>
       <c r="D10" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.7</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.4</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34.9</v>
       </c>
       <c r="O10" t="n">
-        <v>40.9</v>
+        <v>37.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="R10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.4</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>236.14</v>
+        <v>218.84</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.29</v>
+        <v>0.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>136.28</v>
+        <v>133.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B11" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>63.7</v>
+        <v>137.6</v>
       </c>
       <c r="D11" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>36.4</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>39.9</v>
+        <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>35.9</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>39</v>
+        <v>36.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="T11" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.5</v>
+        <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.4</v>
+        <v>2.8</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>221.78</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.94</v>
       </c>
       <c r="AK11" t="n">
-        <v>134.54</v>
+        <v>138.76</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.74</v>
+        <v>5.67</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="B12" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="C12" t="n">
-        <v>67.59999999999999</v>
+        <v>132.5</v>
       </c>
       <c r="D12" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>35.2</v>
+        <v>33.6</v>
       </c>
       <c r="F12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.7</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>34.8</v>
+        <v>75</v>
       </c>
       <c r="O12" t="n">
-        <v>37.2</v>
+        <v>35.1</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z12" t="n">
         <v>19</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>15</v>
-      </c>
       <c r="AA12" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>-4.9</v>
+        <v>0.6</v>
       </c>
       <c r="AC12" t="n">
         <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>218.6</v>
+        <v>224.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>-17.54</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>130.39</v>
+        <v>143.55</v>
       </c>
       <c r="AL12" t="n">
-        <v>-4.15</v>
+        <v>4.79</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46232</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="B13" t="n">
-        <v>157.5</v>
+        <v>137.2</v>
       </c>
       <c r="C13" t="n">
-        <v>68.5</v>
+        <v>56.3</v>
       </c>
       <c r="D13" t="n">
-        <v>33.2</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
-        <v>27.7</v>
+        <v>21.2</v>
       </c>
       <c r="F13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M13" t="n">
         <v>3.6</v>
       </c>
-      <c r="H13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N13" t="n">
-        <v>34.9</v>
+        <v>29</v>
       </c>
       <c r="O13" t="n">
-        <v>37.4</v>
+        <v>32.6</v>
       </c>
       <c r="Q13" t="n">
         <v>21.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>21.6</v>
       </c>
+      <c r="V13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>218.84</v>
+        <v>232.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.24</v>
+        <v>7.44</v>
       </c>
       <c r="AK13" t="n">
-        <v>133.09</v>
+        <v>143.61</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.7</v>
+        <v>0.06</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B14" t="n">
-        <v>137.6</v>
+        <v>157.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>59.6</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
       </c>
+      <c r="E14" t="n">
+        <v>30.6</v>
+      </c>
       <c r="F14" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>38.9</v>
       </c>
       <c r="K14" t="n">
-        <v>70.90000000000001</v>
+        <v>74.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>33.4</v>
       </c>
       <c r="O14" t="n">
-        <v>38.7</v>
+        <v>37.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="R14" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>22.7</v>
+        <v>21.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>19.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>-2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>221.78</v>
+        <v>229.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.94</v>
+        <v>-2.53</v>
       </c>
       <c r="AK14" t="n">
-        <v>138.76</v>
+        <v>136.96</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.67</v>
+        <v>-6.65</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="B15" t="n">
-        <v>132.5</v>
+        <v>159.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>33.6</v>
+        <v>34.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>31.1</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40.5</v>
       </c>
       <c r="K15" t="n">
-        <v>67.59999999999999</v>
+        <v>75.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>34.3</v>
       </c>
       <c r="O15" t="n">
-        <v>36.9</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>224.78</v>
+        <v>228.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>-1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>143.55</v>
+        <v>133.01</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.79</v>
+        <v>-3.95</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
       <c r="B16" t="n">
-        <v>137.2</v>
+        <v>160.4</v>
       </c>
       <c r="C16" t="n">
-        <v>56.3</v>
+        <v>62.6</v>
       </c>
       <c r="D16" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>21.2</v>
+        <v>32.2</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="I16" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="J16" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="K16" t="n">
         <v>75.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="N16" t="n">
-        <v>29</v>
+        <v>32.6</v>
       </c>
       <c r="O16" t="n">
-        <v>32.6</v>
+        <v>38</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>232.22</v>
+        <v>225.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.44</v>
+        <v>-3.49</v>
       </c>
       <c r="AK16" t="n">
-        <v>143.61</v>
+        <v>135.24</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.06</v>
+        <v>2.23</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B17" t="n">
-        <v>157.5</v>
+        <v>161.7</v>
       </c>
       <c r="C17" t="n">
-        <v>59.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E17" t="n">
-        <v>30.6</v>
+        <v>27.3</v>
       </c>
       <c r="F17" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="H17" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="J17" t="n">
-        <v>38.9</v>
+        <v>42.6</v>
       </c>
       <c r="K17" t="n">
-        <v>74.3</v>
+        <v>77</v>
       </c>
       <c r="M17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21</v>
+      </c>
+      <c r="R17" t="n">
         <v>3.7</v>
       </c>
-      <c r="N17" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>21.1</v>
+        <v>21</v>
+      </c>
+      <c r="V17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>229.69</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-2.53</v>
+        <v>-0.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>136.96</v>
+        <v>134.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>-6.65</v>
+        <v>-0.62</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B18" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>63</v>
+        <v>151.5</v>
       </c>
       <c r="D18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>31.1</v>
+        <v>35.1</v>
       </c>
       <c r="F18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>40.5</v>
+        <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>34.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="T18" t="n">
-        <v>21.3</v>
+        <v>19.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>228.57</v>
+        <v>221.37</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.12</v>
+        <v>-3.71</v>
       </c>
       <c r="AK18" t="n">
-        <v>133.01</v>
+        <v>135.21</v>
       </c>
       <c r="AL18" t="n">
-        <v>-3.95</v>
+        <v>0.59</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="B19" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>62.6</v>
+        <v>145.2</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
-      </c>
-      <c r="E19" t="n">
-        <v>32.2</v>
+        <v>33.5</v>
       </c>
       <c r="F19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>41.1</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>32.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>38</v>
+        <v>39.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="T19" t="n">
-        <v>20.9</v>
+        <v>19.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" t="n">
         <v>13</v>
       </c>
-      <c r="Z19" t="n">
-        <v>16</v>
-      </c>
       <c r="AA19" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>225.08</v>
+        <v>224.37</v>
       </c>
       <c r="AG19" t="n">
-        <v>-3.49</v>
+        <v>3</v>
       </c>
       <c r="AK19" t="n">
-        <v>135.24</v>
+        <v>135.61</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.23</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B20" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C20" t="n">
-        <v>71.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="D20" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>27.3</v>
+        <v>33.4</v>
       </c>
       <c r="F20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>42.6</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>77</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>31.5</v>
+        <v>84.3</v>
       </c>
       <c r="O20" t="n">
-        <v>37.3</v>
+        <v>39.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="T20" t="n">
-        <v>21</v>
+        <v>19.9</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA20" t="n">
         <v>9</v>
       </c>
-      <c r="Z20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AB20" t="n">
-        <v>-5.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.3</v>
+        <v>-3.3</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>225.93</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.56</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.62</v>
+        <v>135.28</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.62</v>
+        <v>-0.33</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B21" t="n">
-        <v>151.5</v>
+        <v>182.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>86.8</v>
       </c>
       <c r="D21" t="n">
-        <v>35.1</v>
+        <v>31.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41.1</v>
       </c>
       <c r="K21" t="n">
-        <v>79.90000000000001</v>
+        <v>74.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>33.5</v>
       </c>
       <c r="O21" t="n">
-        <v>43.6</v>
+        <v>38.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="R21" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="T21" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.7</v>
+        <v>-10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>-1.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>221.37</v>
+        <v>218.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>-3.71</v>
+        <v>-7.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>135.21</v>
+        <v>126.27</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.59</v>
+        <v>-9.01</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="B22" t="n">
-        <v>145.2</v>
+        <v>181.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>86.5</v>
       </c>
       <c r="D22" t="n">
-        <v>33.5</v>
+        <v>31.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>34.2</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>5.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>41.9</v>
       </c>
       <c r="K22" t="n">
-        <v>75.8</v>
+        <v>76.8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>35.7</v>
       </c>
       <c r="O22" t="n">
-        <v>41.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R22" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>20.1</v>
       </c>
       <c r="T22" t="n">
-        <v>22.7</v>
+        <v>23</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22" t="n">
-        <v>-5.4</v>
+        <v>-4.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.37</v>
+        <v>216.39</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>-2.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>135.61</v>
+        <v>123.32</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.4</v>
+        <v>-2.95</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46242</v>
+        <v>46245</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4649.3</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2021.1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>3016.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="B23" t="n">
-        <v>146.3</v>
+        <v>183</v>
+      </c>
+      <c r="C23" t="n">
+        <v>84.7</v>
       </c>
       <c r="D23" t="n">
-        <v>33.4</v>
+        <v>30.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33.7</v>
       </c>
       <c r="F23" t="n">
-        <v>5.5</v>
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>42.3</v>
       </c>
       <c r="K23" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>36.7</v>
       </c>
       <c r="O23" t="n">
-        <v>41.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="R23" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2</v>
+        <v>20.8</v>
       </c>
       <c r="T23" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-6.4</v>
+        <v>0.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>-3.3</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.93</v>
+        <v>217.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>0.77</v>
       </c>
       <c r="AK23" t="n">
-        <v>135.28</v>
+        <v>117.87</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.33</v>
+        <v>-5.45</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46243</v>
+        <v>46246</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6995.8</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2380.8</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>3192.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B24" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>86.8</v>
+        <v>163.8</v>
       </c>
       <c r="D24" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>41.1</v>
+        <v>6.5</v>
       </c>
       <c r="K24" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>33.5</v>
+        <v>96.3</v>
       </c>
       <c r="O24" t="n">
-        <v>38.4</v>
+        <v>45.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>0.6</v>
       </c>
       <c r="T24" t="n">
-        <v>22.4</v>
+        <v>19.9</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
         <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB24" t="n">
-        <v>-10.5</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>-5.1</v>
+        <v>2.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>218.63</v>
+        <v>220.31</v>
       </c>
       <c r="AG24" t="n">
-        <v>-7.3</v>
+        <v>3.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>126.27</v>
+        <v>116.52</v>
       </c>
       <c r="AL24" t="n">
-        <v>-9.01</v>
+        <v>-1.35</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>2827.2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>3152.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B25" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="C25" t="n">
-        <v>86.5</v>
+        <v>155.9</v>
       </c>
       <c r="D25" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E25" t="n">
-        <v>34.2</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>41.9</v>
+        <v>6.5</v>
       </c>
       <c r="K25" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>35.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>39.8</v>
+        <v>42.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S25" t="n">
-        <v>20.1</v>
+        <v>0.6</v>
       </c>
       <c r="T25" t="n">
-        <v>23</v>
+        <v>19.9</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-4.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>216.39</v>
+        <v>221.99</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.24</v>
+        <v>1.68</v>
       </c>
       <c r="AK25" t="n">
-        <v>123.32</v>
+        <v>116.37</v>
       </c>
       <c r="AL25" t="n">
-        <v>-2.95</v>
+        <v>-0.15</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="BM25" t="n">
-        <v>40.72</v>
+        <v>34.79</v>
       </c>
       <c r="BN25" t="n">
-        <v>4649.3</v>
+        <v>3609.5</v>
       </c>
       <c r="BO25" t="n">
-        <v>2021.1</v>
+        <v>1161.2</v>
       </c>
       <c r="BP25" t="n">
-        <v>3016.3</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="B26" t="n">
-        <v>183</v>
-      </c>
-      <c r="C26" t="n">
-        <v>84.7</v>
+        <v>141.3</v>
       </c>
       <c r="D26" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>33.7</v>
+        <v>26.3</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>42.3</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>36.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>40.8</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>20.8</v>
+        <v>0.6</v>
       </c>
       <c r="T26" t="n">
-        <v>23.6</v>
+        <v>19.9</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>217.16</v>
+        <v>225.14</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.77</v>
+        <v>3.15</v>
       </c>
       <c r="AK26" t="n">
-        <v>117.87</v>
+        <v>120.64</v>
       </c>
       <c r="AL26" t="n">
-        <v>-5.45</v>
+        <v>4.27</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="BM26" t="n">
-        <v>40.4</v>
+        <v>31.22</v>
       </c>
       <c r="BN26" t="n">
-        <v>6995.8</v>
+        <v>1884.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>2380.8</v>
+        <v>785.2</v>
       </c>
       <c r="BP26" t="n">
-        <v>3192.8</v>
+        <v>2636.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B27" t="n">
-        <v>163.8</v>
+        <v>131.5</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>27.3</v>
       </c>
       <c r="F27" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K27" t="n">
-        <v>87.8</v>
+        <v>74.3</v>
       </c>
       <c r="O27" t="n">
-        <v>48</v>
+        <v>34.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="T27" t="n">
-        <v>22.7</v>
+        <v>19.9</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.8</v>
+        <v>-0.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>220.31</v>
+        <v>229.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.15</v>
+        <v>4.84</v>
       </c>
       <c r="AK27" t="n">
-        <v>116.52</v>
+        <v>128.14</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.35</v>
+        <v>7.5</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="BM27" t="n">
-        <v>39.65</v>
+        <v>26.41</v>
       </c>
       <c r="BN27" t="n">
-        <v>2827.2</v>
+        <v>1894.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>2051.2</v>
+        <v>223.6</v>
       </c>
       <c r="BP27" t="n">
-        <v>3152.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B28" t="n">
-        <v>155.9</v>
+        <v>153</v>
+      </c>
+      <c r="C28" t="n">
+        <v>71.8</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>28.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>24.7</v>
       </c>
       <c r="F28" t="n">
-        <v>6.5</v>
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>41.1</v>
       </c>
       <c r="K28" t="n">
-        <v>82.7</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33.5</v>
       </c>
       <c r="O28" t="n">
-        <v>45.2</v>
+        <v>38.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="R28" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA28" t="n">
         <v>13</v>
       </c>
-      <c r="AA28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>221.99</v>
+        <v>229.96</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.68</v>
+        <v>-0.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>116.37</v>
+        <v>128.15</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="BM28" t="n">
-        <v>34.79</v>
+        <v>29.83</v>
       </c>
       <c r="BN28" t="n">
-        <v>3609.5</v>
+        <v>2723.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>1161.2</v>
+        <v>271.1</v>
       </c>
       <c r="BP28" t="n">
-        <v>3077.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="B29" t="n">
-        <v>141.3</v>
+        <v>165.8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>77.3</v>
       </c>
       <c r="D29" t="n">
-        <v>26.3</v>
+        <v>29.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>27.7</v>
       </c>
       <c r="F29" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>41.6</v>
       </c>
       <c r="K29" t="n">
-        <v>73.3</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>35.1</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="R29" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.4</v>
       </c>
       <c r="Y29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z29" t="n">
         <v>13</v>
       </c>
-      <c r="Z29" t="n">
-        <v>15</v>
-      </c>
       <c r="AA29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>225.14</v>
+        <v>227.01</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.15</v>
+        <v>-2.95</v>
       </c>
       <c r="AK29" t="n">
-        <v>120.64</v>
+        <v>128.86</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.27</v>
+        <v>0.71</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="BM29" t="n">
-        <v>31.22</v>
+        <v>33.62</v>
       </c>
       <c r="BN29" t="n">
-        <v>1884.4</v>
+        <v>6652.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>785.2</v>
+        <v>1412.3</v>
       </c>
       <c r="BP29" t="n">
-        <v>2636.2</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="B30" t="n">
-        <v>131.5</v>
+        <v>158.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>73.7</v>
       </c>
       <c r="D30" t="n">
-        <v>27.3</v>
+        <v>30.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J30" t="n">
+        <v>40.9</v>
       </c>
       <c r="K30" t="n">
-        <v>66.90000000000001</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>35.3</v>
       </c>
       <c r="O30" t="n">
-        <v>36.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="R30" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>229.98</v>
+        <v>228.35</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.84</v>
+        <v>1.34</v>
       </c>
       <c r="AK30" t="n">
-        <v>128.14</v>
+        <v>130.88</v>
       </c>
       <c r="AL30" t="n">
-        <v>7.5</v>
+        <v>2.02</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="BM30" t="n">
-        <v>26.41</v>
+        <v>32.38</v>
       </c>
       <c r="BN30" t="n">
-        <v>1894.8</v>
+        <v>4993.3</v>
       </c>
       <c r="BO30" t="n">
-        <v>223.6</v>
+        <v>958.6</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>2899.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B31" t="n">
-        <v>153</v>
+        <v>154.9</v>
       </c>
       <c r="C31" t="n">
-        <v>71.8</v>
+        <v>70.2</v>
       </c>
       <c r="D31" t="n">
-        <v>28.6</v>
+        <v>31.5</v>
       </c>
       <c r="E31" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="H31" t="n">
         <v>24.1</v>
       </c>
       <c r="I31" t="n">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="J31" t="n">
-        <v>41.1</v>
+        <v>40.3</v>
       </c>
       <c r="K31" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="N31" t="n">
-        <v>33.5</v>
+        <v>32.9</v>
       </c>
       <c r="O31" t="n">
-        <v>38.3</v>
+        <v>39</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T31" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-6.6</v>
+        <v>2.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.6</v>
+        <v>5.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>229.96</v>
+        <v>231.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.02</v>
+        <v>2.81</v>
       </c>
       <c r="AK31" t="n">
-        <v>128.15</v>
+        <v>132.55</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.01</v>
+        <v>1.67</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="BM31" t="n">
-        <v>29.83</v>
+        <v>33.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>2723.2</v>
+        <v>1514.9</v>
       </c>
       <c r="BO31" t="n">
-        <v>271.1</v>
+        <v>799.7</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B32" t="n">
-        <v>165.8</v>
-      </c>
-      <c r="C32" t="n">
-        <v>77.3</v>
+        <v>152.2</v>
       </c>
       <c r="D32" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H32" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J32" t="n">
-        <v>41.6</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N32" t="n">
-        <v>35.1</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="T32" t="n">
-        <v>23.8</v>
+        <v>19.9</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>227.01</v>
+        <v>228.13</v>
       </c>
       <c r="AG32" t="n">
-        <v>-2.95</v>
+        <v>-3.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>128.86</v>
+        <v>128.02</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.71</v>
+        <v>-4.53</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="BM32" t="n">
-        <v>33.62</v>
+        <v>35.62</v>
       </c>
       <c r="BN32" t="n">
-        <v>6652.6</v>
+        <v>1526.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>1412.3</v>
+        <v>957.4</v>
       </c>
       <c r="BP32" t="n">
-        <v>408</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="B33" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>73.7</v>
+        <v>143.9</v>
       </c>
       <c r="D33" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E33" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="F33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J33" t="n">
-        <v>40.9</v>
+        <v>2.5</v>
       </c>
       <c r="K33" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>35.3</v>
+        <v>82.7</v>
       </c>
       <c r="O33" t="n">
-        <v>40.3</v>
+        <v>38.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="T33" t="n">
-        <v>23.6</v>
+        <v>19.9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA33" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.4</v>
+        <v>-0.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AF33" t="n">
-        <v>228.35</v>
+        <v>229.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>130.88</v>
+        <v>127.06</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.02</v>
+        <v>-0.96</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="BM33" t="n">
-        <v>32.38</v>
+        <v>34.56</v>
       </c>
       <c r="BN33" t="n">
-        <v>4993.3</v>
+        <v>170.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>958.6</v>
+        <v>130.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>2899.8</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B34" t="n">
-        <v>154.9</v>
+        <v>163.2</v>
       </c>
       <c r="C34" t="n">
-        <v>70.2</v>
+        <v>73.7</v>
       </c>
       <c r="D34" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="E34" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="H34" t="n">
         <v>24.1</v>
       </c>
       <c r="I34" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="J34" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="K34" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="N34" t="n">
         <v>32.9</v>
       </c>
       <c r="O34" t="n">
-        <v>39</v>
+        <v>39.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R34" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="S34" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>14.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z34" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.9</v>
+        <v>-0.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>231.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.81</v>
+        <v>-0.61</v>
       </c>
       <c r="AK34" t="n">
-        <v>132.55</v>
+        <v>125.61</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.67</v>
+        <v>-1.45</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="BM34" t="n">
-        <v>33.01</v>
+        <v>34.78</v>
       </c>
       <c r="BN34" t="n">
-        <v>1514.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO34" t="n">
-        <v>799.7</v>
+        <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2923.4</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B35" t="n">
-        <v>152.2</v>
+        <v>174.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>31</v>
+        <v>32.1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>30.8</v>
       </c>
       <c r="F35" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>39.5</v>
       </c>
       <c r="K35" t="n">
-        <v>80.3</v>
+        <v>74</v>
+      </c>
+      <c r="M35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.8</v>
       </c>
       <c r="O35" t="n">
-        <v>43.9</v>
+        <v>42.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="R35" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="S35" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="T35" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W35" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB35" t="n">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>228.13</v>
+        <v>219.99</v>
       </c>
       <c r="AG35" t="n">
-        <v>-3.03</v>
+        <v>-8.56</v>
       </c>
       <c r="AK35" t="n">
-        <v>128.02</v>
+        <v>124.36</v>
       </c>
       <c r="AL35" t="n">
-        <v>-4.53</v>
+        <v>-1.25</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="BM35" t="n">
-        <v>35.62</v>
+        <v>36.78</v>
       </c>
       <c r="BN35" t="n">
-        <v>1526.5</v>
+        <v>108.8</v>
       </c>
       <c r="BO35" t="n">
-        <v>957.4</v>
+        <v>204.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>2928.4</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B36" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>30.8</v>
+        <v>32.9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26</v>
       </c>
       <c r="F36" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>40.1</v>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>71.3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>34.3</v>
       </c>
       <c r="O36" t="n">
-        <v>40.9</v>
+        <v>41.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="R36" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="T36" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
         <v>14</v>
       </c>
       <c r="AA36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>229.16</v>
+        <v>219.22</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.03</v>
+        <v>-0.77</v>
       </c>
       <c r="AK36" t="n">
-        <v>127.06</v>
+        <v>120.93</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.96</v>
+        <v>-3.43</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="BM36" t="n">
-        <v>34.56</v>
+        <v>32.64</v>
       </c>
       <c r="BN36" t="n">
-        <v>170.6</v>
+        <v>42.3</v>
       </c>
       <c r="BO36" t="n">
-        <v>130.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP36" t="n">
-        <v>2825.6</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B37" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C37" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="E37" t="n">
-        <v>28.2</v>
+        <v>24.6</v>
       </c>
       <c r="F37" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H37" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I37" t="n">
-        <v>11.4</v>
+        <v>7.2</v>
       </c>
       <c r="J37" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O37" t="n">
         <v>40.1</v>
       </c>
-      <c r="K37" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N37" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O37" t="n">
-        <v>39.7</v>
-      </c>
       <c r="Q37" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="R37" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>228.55</v>
+        <v>220.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.61</v>
+        <v>1.51</v>
       </c>
       <c r="AK37" t="n">
-        <v>125.61</v>
+        <v>120.28</v>
       </c>
       <c r="AL37" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="BM37" t="n">
-        <v>34.78</v>
+        <v>29.61</v>
       </c>
       <c r="BN37" t="n">
-        <v>69.59999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="BO37" t="n">
         <v>0</v>
       </c>
       <c r="BP37" t="n">
-        <v>2769.3</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B38" t="n">
-        <v>174.4</v>
+        <v>150.7</v>
       </c>
       <c r="C38" t="n">
-        <v>75.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="D38" t="n">
-        <v>32.1</v>
+        <v>33.7</v>
       </c>
       <c r="E38" t="n">
-        <v>30.8</v>
+        <v>27.1</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I38" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="J38" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="K38" t="n">
-        <v>74</v>
+        <v>70.5</v>
       </c>
       <c r="M38" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="N38" t="n">
-        <v>35.8</v>
+        <v>33</v>
       </c>
       <c r="O38" t="n">
-        <v>42.6</v>
+        <v>38.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R38" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="S38" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.7</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z38" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>219.99</v>
+        <v>220.58</v>
       </c>
       <c r="AG38" t="n">
-        <v>-8.56</v>
+        <v>-0.15</v>
       </c>
       <c r="AK38" t="n">
-        <v>124.36</v>
+        <v>119.29</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1.25</v>
+        <v>-0.99</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="BM38" t="n">
-        <v>36.78</v>
+        <v>31.11</v>
       </c>
       <c r="BN38" t="n">
-        <v>108.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO38" t="n">
-        <v>204.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP38" t="n">
-        <v>2982.8</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B39" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="C39" t="n">
-        <v>70.90000000000001</v>
+        <v>138.2</v>
       </c>
       <c r="D39" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E39" t="n">
-        <v>26</v>
+        <v>33.6</v>
       </c>
       <c r="F39" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H39" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>40.1</v>
+        <v>6.1</v>
       </c>
       <c r="K39" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>34.3</v>
+        <v>78.8</v>
       </c>
       <c r="O39" t="n">
-        <v>41.5</v>
+        <v>37</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="S39" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
       <c r="T39" t="n">
-        <v>23.1</v>
+        <v>19.9</v>
+      </c>
+      <c r="V39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="AC39" t="n">
         <v>8.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>219.22</v>
+        <v>223.43</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.77</v>
+        <v>2.85</v>
       </c>
       <c r="AK39" t="n">
-        <v>120.93</v>
+        <v>121.35</v>
       </c>
       <c r="AL39" t="n">
-        <v>-3.43</v>
+        <v>2.06</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="BM39" t="n">
-        <v>32.64</v>
+        <v>30.59</v>
       </c>
       <c r="BN39" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="BO39" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP39" t="n">
-        <v>3194.6</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B40" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="C40" t="n">
-        <v>62.6</v>
+        <v>126.5</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E40" t="n">
-        <v>24.6</v>
+        <v>33.2</v>
       </c>
       <c r="F40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I40" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>38.9</v>
+        <v>3.4</v>
       </c>
       <c r="K40" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N40" t="n">
-        <v>33.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>40.1</v>
+        <v>33.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="T40" t="n">
-        <v>23.2</v>
+        <v>19.9</v>
+      </c>
+      <c r="V40" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z40" t="n">
         <v>18</v>
       </c>
       <c r="AA40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>220.73</v>
+        <v>229.48</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.51</v>
+        <v>6.05</v>
       </c>
       <c r="AK40" t="n">
-        <v>120.28</v>
+        <v>128.37</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.65</v>
+        <v>7.02</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="BM40" t="n">
-        <v>29.61</v>
+        <v>30.05</v>
       </c>
       <c r="BN40" t="n">
-        <v>60.1</v>
+        <v>34</v>
       </c>
       <c r="BO40" t="n">
         <v>0</v>
       </c>
       <c r="BP40" t="n">
-        <v>2717.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B41" t="n">
-        <v>150.7</v>
+        <v>129.4</v>
       </c>
       <c r="C41" t="n">
-        <v>64.8</v>
+        <v>50.6</v>
       </c>
       <c r="D41" t="n">
-        <v>33.7</v>
+        <v>31.5</v>
       </c>
       <c r="E41" t="n">
-        <v>27.1</v>
+        <v>19.4</v>
       </c>
       <c r="F41" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="H41" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="I41" t="n">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="J41" t="n">
-        <v>39.9</v>
+        <v>38.9</v>
       </c>
       <c r="K41" t="n">
-        <v>70.5</v>
+        <v>73.3</v>
       </c>
       <c r="M41" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="N41" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="O41" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="R41" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="n">
         <v>14</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="AF41" t="n">
-        <v>220.58</v>
+        <v>241.48</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.15</v>
+        <v>12</v>
       </c>
       <c r="AK41" t="n">
-        <v>119.29</v>
+        <v>134.59</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.99</v>
+        <v>6.22</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="BM41" t="n">
-        <v>31.11</v>
+        <v>24.86</v>
       </c>
       <c r="BN41" t="n">
-        <v>87.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP41" t="n">
-        <v>3028.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B42" t="n">
-        <v>138.2</v>
+        <v>142.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>52.7</v>
       </c>
       <c r="D42" t="n">
-        <v>33.6</v>
+        <v>34.7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>24.8</v>
       </c>
       <c r="F42" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>22</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>38.2</v>
       </c>
       <c r="K42" t="n">
-        <v>71.3</v>
+        <v>70</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>31.9</v>
       </c>
       <c r="O42" t="n">
-        <v>38.9</v>
+        <v>35.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="R42" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="S42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>22.7</v>
+        <v>19.7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>12</v>
+      </c>
+      <c r="W42" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA42" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="AF42" t="n">
-        <v>223.43</v>
+        <v>238.69</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.85</v>
+        <v>-2.79</v>
       </c>
       <c r="AK42" t="n">
-        <v>121.35</v>
+        <v>136.6</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="BM42" t="n">
-        <v>30.59</v>
+        <v>29.8</v>
       </c>
       <c r="BN42" t="n">
-        <v>40.8</v>
+        <v>61.9</v>
       </c>
       <c r="BO42" t="n">
         <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>2959.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="B43" t="n">
-        <v>126.5</v>
+        <v>148.1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>51.9</v>
       </c>
       <c r="D43" t="n">
-        <v>33.2</v>
+        <v>35.4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31.5</v>
       </c>
       <c r="F43" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>39.6</v>
       </c>
       <c r="K43" t="n">
-        <v>63.7</v>
+        <v>71</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N43" t="n">
+        <v>30.8</v>
       </c>
       <c r="O43" t="n">
-        <v>34.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="R43" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="S43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
+      </c>
+      <c r="V43" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>19.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>229.48</v>
+        <v>233.48</v>
       </c>
       <c r="AG43" t="n">
-        <v>6.05</v>
+        <v>-5.21</v>
       </c>
       <c r="AK43" t="n">
-        <v>128.37</v>
+        <v>135.66</v>
       </c>
       <c r="AL43" t="n">
-        <v>7.02</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="BM43" t="n">
-        <v>30.05</v>
+        <v>36.03</v>
       </c>
       <c r="BN43" t="n">
-        <v>34</v>
+        <v>76.5</v>
       </c>
       <c r="BO43" t="n">
         <v>0</v>
@@ -4102,94 +4522,103 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="B44" t="n">
-        <v>129.4</v>
+        <v>143.4</v>
       </c>
       <c r="C44" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="D44" t="n">
-        <v>31.5</v>
+        <v>35.7</v>
       </c>
       <c r="E44" t="n">
-        <v>19.4</v>
+        <v>26.2</v>
       </c>
       <c r="F44" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I44" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K44" t="n">
-        <v>73.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="O44" t="n">
-        <v>38</v>
+        <v>33.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
+      </c>
+      <c r="V44" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X44" t="n">
+        <v>20.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA44" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AF44" t="n">
-        <v>241.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>1.65</v>
       </c>
       <c r="AK44" t="n">
-        <v>134.59</v>
+        <v>136.33</v>
       </c>
       <c r="AL44" t="n">
-        <v>6.22</v>
+        <v>0.67</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="BM44" t="n">
-        <v>24.86</v>
+        <v>32</v>
       </c>
       <c r="BN44" t="n">
-        <v>80.2</v>
+        <v>29.5</v>
       </c>
       <c r="BO44" t="n">
         <v>0</v>
@@ -4200,55 +4629,64 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B45" t="n">
-        <v>142.9</v>
+        <v>144.9</v>
       </c>
       <c r="C45" t="n">
-        <v>52.7</v>
+        <v>53</v>
       </c>
       <c r="D45" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="E45" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="J45" t="n">
-        <v>38.2</v>
+        <v>40.3</v>
       </c>
       <c r="K45" t="n">
-        <v>70</v>
+        <v>73.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="N45" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="O45" t="n">
-        <v>35.8</v>
+        <v>33.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="R45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>19.7</v>
+        <v>21</v>
+      </c>
+      <c r="V45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.1</v>
       </c>
       <c r="Y45" t="n">
         <v>12</v>
@@ -4260,34 +4698,34 @@
         <v>15.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>238.69</v>
+        <v>234.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>-2.79</v>
+        <v>-0.26</v>
       </c>
       <c r="AK45" t="n">
-        <v>136.6</v>
+        <v>137.17</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.01</v>
+        <v>0.84</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="BM45" t="n">
-        <v>29.8</v>
+        <v>32.57</v>
       </c>
       <c r="BN45" t="n">
-        <v>61.9</v>
+        <v>23.4</v>
       </c>
       <c r="BO45" t="n">
         <v>0</v>
@@ -4298,94 +4736,82 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B46" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="C46" t="n">
-        <v>51.9</v>
+        <v>132.2</v>
       </c>
       <c r="D46" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="E46" t="n">
-        <v>31.5</v>
+        <v>35.6</v>
       </c>
       <c r="F46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>39.6</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>71</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N46" t="n">
-        <v>30.8</v>
+        <v>74.7</v>
       </c>
       <c r="O46" t="n">
-        <v>33.7</v>
+        <v>35.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V46" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X46" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB46" t="n">
         <v>0.9</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-1</v>
-      </c>
       <c r="AC46" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AF46" t="n">
-        <v>233.48</v>
+        <v>234.78</v>
       </c>
       <c r="AG46" t="n">
-        <v>-5.21</v>
+        <v>-0.09</v>
       </c>
       <c r="AK46" t="n">
-        <v>135.66</v>
+        <v>136.08</v>
       </c>
       <c r="AL46" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="BM46" t="n">
-        <v>36.03</v>
+        <v>29.64</v>
       </c>
       <c r="BN46" t="n">
-        <v>76.5</v>
+        <v>36.4</v>
       </c>
       <c r="BO46" t="n">
         <v>0</v>
@@ -4396,94 +4822,82 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B47" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="C47" t="n">
-        <v>50.9</v>
+        <v>137.1</v>
       </c>
       <c r="D47" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E47" t="n">
-        <v>26.2</v>
+        <v>35.1</v>
       </c>
       <c r="F47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I47" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J47" t="n">
-        <v>39.9</v>
+        <v>3.3</v>
       </c>
       <c r="K47" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>31.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>33.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T47" t="n">
-        <v>21.6</v>
+        <v>19.9</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11</v>
+      </c>
+      <c r="W47" t="n">
+        <v>22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z47" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AA47" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.8</v>
+        <v>-5.3</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="AF47" t="n">
-        <v>235.13</v>
+        <v>229.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.65</v>
+        <v>-5.03</v>
       </c>
       <c r="AK47" t="n">
-        <v>136.33</v>
+        <v>135.42</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="BM47" t="n">
-        <v>32</v>
+        <v>31.45</v>
       </c>
       <c r="BN47" t="n">
-        <v>29.5</v>
+        <v>35.9</v>
       </c>
       <c r="BO47" t="n">
         <v>0</v>
@@ -4494,1229 +4908,1175 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="B48" t="n">
-        <v>144.9</v>
+        <v>148.7</v>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>35.6</v>
+        <v>32.7</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>28.1</v>
       </c>
       <c r="F48" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H48" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I48" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J48" t="n">
-        <v>40.3</v>
+        <v>42.1</v>
       </c>
       <c r="K48" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="M48" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="N48" t="n">
-        <v>31.6</v>
+        <v>33.7</v>
       </c>
       <c r="O48" t="n">
-        <v>33.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>21</v>
+        <v>23.7</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>21</v>
+        <v>23.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AA48" t="n">
-        <v>15.5</v>
+        <v>6.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1.1</v>
+        <v>-3.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF48" t="n">
-        <v>234.87</v>
+        <v>222.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.26</v>
+        <v>-6.89</v>
       </c>
       <c r="AK48" t="n">
-        <v>137.17</v>
+        <v>131.24</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.84</v>
+        <v>-4.18</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="BM48" t="n">
-        <v>32.57</v>
+        <v>34.46</v>
       </c>
       <c r="BN48" t="n">
-        <v>23.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP48" t="n">
-        <v>0</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B49" t="n">
-        <v>132.2</v>
+        <v>149.3</v>
+      </c>
+      <c r="C49" t="n">
+        <v>74.90000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>35.6</v>
+        <v>32.8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>28.8</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>4.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J49" t="n">
+        <v>41.2</v>
       </c>
       <c r="K49" t="n">
-        <v>67.40000000000001</v>
+        <v>73.8</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>35.4</v>
       </c>
       <c r="O49" t="n">
-        <v>36.8</v>
+        <v>42.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="R49" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="S49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>22.7</v>
+        <v>23.9</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W49" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z49" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.9</v>
+        <v>-2.9</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AF49" t="n">
-        <v>234.78</v>
+        <v>218.37</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.09</v>
+        <v>-4.49</v>
       </c>
       <c r="AK49" t="n">
-        <v>136.08</v>
+        <v>129.21</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.09</v>
+        <v>-2.03</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="BM49" t="n">
-        <v>29.64</v>
+        <v>35.4</v>
       </c>
       <c r="BN49" t="n">
-        <v>36.4</v>
+        <v>294.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="BP49" t="n">
-        <v>0</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B50" t="n">
-        <v>137.1</v>
+        <v>137</v>
+      </c>
+      <c r="C50" t="n">
+        <v>65</v>
       </c>
       <c r="D50" t="n">
-        <v>35.1</v>
+        <v>32</v>
+      </c>
+      <c r="E50" t="n">
+        <v>25.2</v>
       </c>
       <c r="F50" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>38.5</v>
       </c>
       <c r="K50" t="n">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="M50" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>32.3</v>
       </c>
       <c r="O50" t="n">
-        <v>38.5</v>
+        <v>40.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="R50" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="S50" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="T50" t="n">
-        <v>22.7</v>
+        <v>21.7</v>
+      </c>
+      <c r="V50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>21</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.2</v>
       </c>
       <c r="Y50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>-5.3</v>
+        <v>0.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>229.75</v>
+        <v>220.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>-5.03</v>
+        <v>2.48</v>
       </c>
       <c r="AK50" t="n">
-        <v>135.42</v>
+        <v>129.07</v>
       </c>
       <c r="AL50" t="n">
-        <v>-0.66</v>
+        <v>-0.14</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="BM50" t="n">
-        <v>31.45</v>
+        <v>32.31</v>
       </c>
       <c r="BN50" t="n">
-        <v>35.9</v>
+        <v>547</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BP50" t="n">
-        <v>0</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="B51" t="n">
-        <v>148.7</v>
+        <v>131.5</v>
       </c>
       <c r="C51" t="n">
-        <v>72.40000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="D51" t="n">
         <v>32.7</v>
       </c>
       <c r="E51" t="n">
-        <v>28.1</v>
+        <v>26.3</v>
       </c>
       <c r="F51" t="n">
         <v>3.3</v>
       </c>
       <c r="H51" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J51" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="K51" t="n">
-        <v>74.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="N51" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="O51" t="n">
-        <v>39.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="R51" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
+      </c>
+      <c r="V51" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W51" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>-3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>222.86</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>-6.89</v>
+        <v>6.3</v>
       </c>
       <c r="AK51" t="n">
-        <v>131.24</v>
+        <v>130.73</v>
       </c>
       <c r="AL51" t="n">
-        <v>-4.18</v>
+        <v>1.66</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="BM51" t="n">
-        <v>34.46</v>
+        <v>31.51</v>
       </c>
       <c r="BN51" t="n">
-        <v>80.40000000000001</v>
+        <v>124</v>
       </c>
       <c r="BO51" t="n">
-        <v>373.6</v>
+        <v>164.4</v>
       </c>
       <c r="BP51" t="n">
-        <v>249.4</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B52" t="n">
-        <v>149.3</v>
+        <v>129.4</v>
       </c>
       <c r="C52" t="n">
-        <v>74.90000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="D52" t="n">
-        <v>32.8</v>
+        <v>33.6</v>
       </c>
       <c r="E52" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="F52" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="H52" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="I52" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J52" t="n">
-        <v>41.2</v>
+        <v>40.8</v>
       </c>
       <c r="K52" t="n">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="N52" t="n">
-        <v>35.4</v>
+        <v>33.1</v>
       </c>
       <c r="O52" t="n">
-        <v>42.6</v>
+        <v>38.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.9</v>
+        <v>22</v>
       </c>
       <c r="R52" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>23.9</v>
+        <v>22</v>
+      </c>
+      <c r="V52" t="n">
+        <v>11</v>
+      </c>
+      <c r="W52" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y52" t="n">
-        <v>5</v>
+        <v>10.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>9.5</v>
+        <v>16.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>-2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>218.37</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>-4.49</v>
+        <v>4.5</v>
       </c>
       <c r="AK52" t="n">
-        <v>129.21</v>
+        <v>132</v>
       </c>
       <c r="AL52" t="n">
-        <v>-2.03</v>
+        <v>1.27</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="BM52" t="n">
-        <v>35.4</v>
+        <v>34.36</v>
       </c>
       <c r="BN52" t="n">
-        <v>294.2</v>
+        <v>62.8</v>
       </c>
       <c r="BO52" t="n">
-        <v>227</v>
+        <v>60.6</v>
       </c>
       <c r="BP52" t="n">
-        <v>2758.6</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B53" t="n">
-        <v>137</v>
+        <v>130.2</v>
       </c>
       <c r="C53" t="n">
-        <v>65</v>
+        <v>56.9</v>
       </c>
       <c r="D53" t="n">
-        <v>32</v>
+        <v>33.9</v>
       </c>
       <c r="E53" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>3.4</v>
+        <v>26.4</v>
       </c>
       <c r="H53" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J53" t="n">
-        <v>38.5</v>
+        <v>42.3</v>
       </c>
       <c r="K53" t="n">
-        <v>70.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="M53" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="N53" t="n">
         <v>32.3</v>
       </c>
       <c r="O53" t="n">
-        <v>40.3</v>
+        <v>37.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="R53" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>220.85</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.48</v>
+        <v>22.3</v>
       </c>
       <c r="AK53" t="n">
-        <v>129.07</v>
+        <v>132.25</v>
       </c>
       <c r="AL53" t="n">
-        <v>-0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="BM53" t="n">
-        <v>32.31</v>
+        <v>32.26</v>
       </c>
       <c r="BN53" t="n">
-        <v>547</v>
+        <v>28.3</v>
       </c>
       <c r="BO53" t="n">
-        <v>85</v>
+        <v>18.8</v>
       </c>
       <c r="BP53" t="n">
-        <v>2654.5</v>
+        <v>2545.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46274</v>
+        <v>46277</v>
       </c>
       <c r="B54" t="n">
-        <v>131.5</v>
+        <v>138.4</v>
       </c>
       <c r="C54" t="n">
-        <v>57.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E54" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3.3</v>
+        <v>25.9</v>
       </c>
       <c r="H54" t="n">
         <v>23.6</v>
       </c>
       <c r="I54" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="J54" t="n">
-        <v>41.6</v>
+        <v>42.8</v>
       </c>
       <c r="K54" t="n">
-        <v>74.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="M54" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="N54" t="n">
-        <v>35</v>
+        <v>32.3</v>
       </c>
       <c r="O54" t="n">
-        <v>42.4</v>
+        <v>35.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>21.7</v>
+        <v>23.6</v>
       </c>
       <c r="R54" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>6.3</v>
+        <v>23.6</v>
       </c>
       <c r="AK54" t="n">
-        <v>130.73</v>
+        <v>128.6</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.66</v>
+        <v>-3.65</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46274</v>
+        <v>46277</v>
       </c>
       <c r="BM54" t="n">
-        <v>31.51</v>
+        <v>33.93</v>
       </c>
       <c r="BN54" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="BO54" t="n">
-        <v>164.4</v>
+        <v>16</v>
       </c>
       <c r="BP54" t="n">
-        <v>2635.8</v>
+        <v>2697.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46275</v>
+        <v>46278</v>
       </c>
       <c r="B55" t="n">
-        <v>129.4</v>
+        <v>140.8</v>
       </c>
       <c r="C55" t="n">
-        <v>52.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>33.6</v>
+        <v>31.7</v>
       </c>
       <c r="E55" t="n">
-        <v>28.9</v>
+        <v>26.1</v>
       </c>
       <c r="F55" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I55" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="K55" t="n">
-        <v>73.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="M55" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="O55" t="n">
-        <v>38.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>22</v>
+        <v>23.8</v>
       </c>
       <c r="R55" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>20</v>
+        <v>23.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="AK55" t="n">
-        <v>132</v>
+        <v>127.19</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.27</v>
+        <v>-1.41</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46275</v>
+        <v>46278</v>
       </c>
       <c r="BM55" t="n">
-        <v>34.36</v>
+        <v>31.16</v>
       </c>
       <c r="BN55" t="n">
-        <v>62.8</v>
+        <v>21.2</v>
       </c>
       <c r="BO55" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="BP55" t="n">
-        <v>2693.4</v>
+        <v>2603.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B56" t="n">
-        <v>133.9</v>
+        <v>139.6</v>
       </c>
       <c r="C56" t="n">
-        <v>59.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>34.7</v>
+        <v>32.2</v>
       </c>
       <c r="E56" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
       </c>
       <c r="F56" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J56" t="n">
+        <v>39.6</v>
       </c>
       <c r="K56" t="n">
-        <v>68.5</v>
+        <v>73.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N56" t="n">
+        <v>34.4</v>
       </c>
       <c r="O56" t="n">
-        <v>37.4</v>
+        <v>40.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="R56" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="S56" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y56" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AA56" t="n">
         <v>12</v>
       </c>
-      <c r="Z56" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>15</v>
-      </c>
       <c r="AK56" t="n">
-        <v>132.25</v>
+        <v>129.17</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.25</v>
+        <v>1.98</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="BM56" t="n">
-        <v>32.26</v>
+        <v>32.41</v>
       </c>
       <c r="BN56" t="n">
-        <v>28.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BO56" t="n">
-        <v>18.8</v>
+        <v>297.8</v>
       </c>
       <c r="BP56" t="n">
-        <v>2545.1</v>
+        <v>2677.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B57" t="n">
-        <v>137.5</v>
+        <v>133.5</v>
       </c>
       <c r="C57" t="n">
-        <v>66.90000000000001</v>
+        <v>62.3</v>
       </c>
       <c r="D57" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
       <c r="E57" t="n">
-        <v>25.7</v>
+        <v>22.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40.8</v>
       </c>
       <c r="K57" t="n">
-        <v>70.8</v>
+        <v>75</v>
+      </c>
+      <c r="M57" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>30.4</v>
       </c>
       <c r="O57" t="n">
-        <v>38.7</v>
+        <v>37.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="R57" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="S57" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>11</v>
+        <v>22.1</v>
       </c>
       <c r="AA57" t="n">
-        <v>10.5</v>
+        <v>12.9</v>
       </c>
       <c r="AK57" t="n">
-        <v>128.6</v>
+        <v>130.42</v>
       </c>
       <c r="AL57" t="n">
-        <v>-3.65</v>
+        <v>1.25</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="BM57" t="n">
-        <v>33.93</v>
+        <v>26.56</v>
       </c>
       <c r="BN57" t="n">
-        <v>73</v>
+        <v>46.1</v>
       </c>
       <c r="BO57" t="n">
-        <v>16</v>
+        <v>266.8</v>
       </c>
       <c r="BP57" t="n">
-        <v>2697.4</v>
+        <v>2801.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="B58" t="n">
-        <v>140.8</v>
+        <v>136.6</v>
       </c>
       <c r="C58" t="n">
-        <v>73.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>31.7</v>
+        <v>34.7</v>
       </c>
       <c r="E58" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
+        <v>25.2</v>
       </c>
       <c r="H58" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="I58" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J58" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="K58" t="n">
-        <v>73.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="N58" t="n">
-        <v>33.4</v>
+        <v>28</v>
       </c>
       <c r="O58" t="n">
-        <v>39.5</v>
+        <v>33.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="R58" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>127.19</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-1.41</v>
+        <v>23.1</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="BM58" t="n">
-        <v>31.16</v>
+        <v>31.32</v>
       </c>
       <c r="BN58" t="n">
-        <v>21.2</v>
+        <v>54.7</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>235.3</v>
       </c>
       <c r="BP58" t="n">
-        <v>2603.2</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B59" t="n">
-        <v>139.6</v>
+        <v>127.5</v>
       </c>
       <c r="C59" t="n">
-        <v>69.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="D59" t="n">
-        <v>32.2</v>
+        <v>34.2</v>
       </c>
       <c r="E59" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F59" t="n">
-        <v>2.2</v>
+        <v>27</v>
       </c>
       <c r="H59" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="I59" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J59" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="K59" t="n">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>34.4</v>
+        <v>28.5</v>
       </c>
       <c r="O59" t="n">
-        <v>40.1</v>
+        <v>32.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.8</v>
+        <v>22</v>
       </c>
       <c r="R59" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>129.17</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1.98</v>
+        <v>22</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="BM59" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="BN59" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="BO59" t="n">
-        <v>297.8</v>
-      </c>
-      <c r="BP59" t="n">
-        <v>2677.8</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B60" t="n">
-        <v>133.5</v>
+        <v>119.2</v>
       </c>
       <c r="C60" t="n">
-        <v>62.3</v>
+        <v>45.9</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="E60" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F60" t="n">
-        <v>3.1</v>
+        <v>25.1</v>
       </c>
       <c r="H60" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="I60" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J60" t="n">
-        <v>40.8</v>
+        <v>37</v>
       </c>
       <c r="K60" t="n">
-        <v>75</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="N60" t="n">
-        <v>30.4</v>
+        <v>29</v>
       </c>
       <c r="O60" t="n">
-        <v>37.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.1</v>
+        <v>18</v>
       </c>
       <c r="R60" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>130.42</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>1.25</v>
+        <v>18</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="BM60" t="n">
-        <v>26.56</v>
-      </c>
-      <c r="BN60" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="BO60" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="BP60" t="n">
-        <v>2801.1</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B61" t="n">
-        <v>132.5</v>
+        <v>106.9</v>
       </c>
       <c r="C61" t="n">
-        <v>62.4</v>
+        <v>40.8</v>
       </c>
       <c r="D61" t="n">
         <v>33.4</v>
       </c>
       <c r="E61" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2.3</v>
+        <v>19.8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J61" t="n">
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>67.59999999999999</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>30</v>
       </c>
       <c r="O61" t="n">
-        <v>36.9</v>
+        <v>32.1</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z61" t="n">
         <v>15</v>
       </c>
-      <c r="AA61" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BL61" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>235.3</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>52.9</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="B62" t="n">
-        <v>125</v>
+        <v>100.3</v>
       </c>
       <c r="C62" t="n">
-        <v>53.6</v>
+        <v>38.2</v>
       </c>
       <c r="D62" t="n">
-        <v>34.2</v>
+        <v>33</v>
       </c>
       <c r="E62" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2.8</v>
+        <v>17</v>
+      </c>
+      <c r="H62" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>35</v>
       </c>
       <c r="K62" t="n">
-        <v>62.7</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>30</v>
       </c>
       <c r="O62" t="n">
-        <v>34.3</v>
+        <v>32.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R62" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46282</v>
+        <v>46285</v>
       </c>
     </row>
   </sheetData>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5443,7 +5443,7 @@
         <v>33.9</v>
       </c>
       <c r="E53" t="n">
-        <v>26.4</v>
+        <v>30.85</v>
       </c>
       <c r="H53" t="n">
         <v>23.6</v>
@@ -5514,7 +5514,7 @@
         <v>32.8</v>
       </c>
       <c r="E54" t="n">
-        <v>25.9</v>
+        <v>28.44</v>
       </c>
       <c r="H54" t="n">
         <v>23.6</v>
@@ -5816,7 +5816,7 @@
         <v>34.7</v>
       </c>
       <c r="E58" t="n">
-        <v>25.2</v>
+        <v>33</v>
       </c>
       <c r="H58" t="n">
         <v>24.5</v>
@@ -5850,6 +5850,12 @@
       </c>
       <c r="T58" t="n">
         <v>23.1</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>129.71</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-0.71</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46281</v>
@@ -5881,7 +5887,7 @@
         <v>34.2</v>
       </c>
       <c r="E59" t="n">
-        <v>27</v>
+        <v>34.83</v>
       </c>
       <c r="H59" t="n">
         <v>24.5</v>
@@ -5934,7 +5940,7 @@
         <v>34.9</v>
       </c>
       <c r="E60" t="n">
-        <v>25.1</v>
+        <v>34.73</v>
       </c>
       <c r="H60" t="n">
         <v>24.5</v>
@@ -5987,7 +5993,7 @@
         <v>33.4</v>
       </c>
       <c r="E61" t="n">
-        <v>19.8</v>
+        <v>26.47</v>
       </c>
       <c r="H61" t="n">
         <v>24.5</v>
@@ -6040,7 +6046,7 @@
         <v>33</v>
       </c>
       <c r="E62" t="n">
-        <v>17</v>
+        <v>25.47</v>
       </c>
       <c r="H62" t="n">
         <v>24.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -628,200 +628,206 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B2" t="n">
-        <v>179.6</v>
+        <v>172.9</v>
       </c>
       <c r="C2" t="n">
-        <v>81.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="E2" t="n">
-        <v>31.1</v>
+        <v>35.2</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="I2" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="J2" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="K2" t="n">
-        <v>74.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="n">
-        <v>37.1</v>
+        <v>34.8</v>
       </c>
       <c r="O2" t="n">
-        <v>41.4</v>
+        <v>37.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.6</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>21.2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>22.6</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>15.6</v>
+        <v>18.7</v>
       </c>
       <c r="X2" t="n">
-        <v>12.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.4</v>
+        <v>-4.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>216.02</v>
+        <v>218.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>127.85</v>
+        <v>130.39</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="B3" t="n">
-        <v>170.4</v>
+        <v>157.5</v>
       </c>
       <c r="C3" t="n">
-        <v>78.5</v>
+        <v>68.5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.8</v>
+        <v>33.2</v>
       </c>
       <c r="E3" t="n">
-        <v>29.7</v>
+        <v>27.7</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="I3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="J3" t="n">
         <v>41.4</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>36.6</v>
+        <v>34.9</v>
       </c>
       <c r="O3" t="n">
-        <v>41.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>21.1</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="V3" t="n">
-        <v>9.5</v>
+        <v>15.1</v>
       </c>
       <c r="W3" t="n">
-        <v>15.7</v>
+        <v>23.1</v>
       </c>
       <c r="X3" t="n">
-        <v>12.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>218.84</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>128.54</v>
+        <v>133.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46226</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B4" t="n">
-        <v>156</v>
+        <v>137.6</v>
       </c>
       <c r="D4" t="n">
-        <v>30.1</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>90.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>42.7</v>
+        <v>36.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -836,66 +842,66 @@
         <v>19.9</v>
       </c>
       <c r="V4" t="n">
-        <v>7.1</v>
+        <v>13.6</v>
       </c>
       <c r="W4" t="n">
-        <v>20.9</v>
+        <v>24.4</v>
       </c>
       <c r="X4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="n">
         <v>14</v>
       </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>224.53</v>
+        <v>221.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>8.51</v>
+        <v>2.94</v>
       </c>
       <c r="AK4" t="n">
-        <v>130.92</v>
+        <v>138.76</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.38</v>
+        <v>5.67</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B5" t="n">
-        <v>147.8</v>
+        <v>132.5</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>85.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>40</v>
+        <v>35.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -910,514 +916,535 @@
         <v>19.9</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
-        <v>22.4</v>
+        <v>24.7</v>
       </c>
       <c r="X5" t="n">
-        <v>15.2</v>
+        <v>19.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD5" t="n">
         <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>230.27</v>
+        <v>224.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.74</v>
+        <v>3</v>
       </c>
       <c r="AK5" t="n">
-        <v>132.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.84</v>
+        <v>4.79</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B6" t="n">
-        <v>149.1</v>
+        <v>137.2</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>56.3</v>
       </c>
       <c r="D6" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N6" t="n">
         <v>29</v>
       </c>
-      <c r="E6" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>24</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>36.7</v>
-      </c>
       <c r="O6" t="n">
-        <v>40.1</v>
+        <v>32.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="W6" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="X6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.4</v>
+        <v>0.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>237.43</v>
+        <v>232.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.16</v>
+        <v>7.44</v>
       </c>
       <c r="AK6" t="n">
-        <v>134.95</v>
+        <v>143.61</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.19</v>
+        <v>0.06</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B7" t="n">
-        <v>143.9</v>
+        <v>157.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>59.6</v>
       </c>
       <c r="D7" t="n">
-        <v>32.9</v>
+        <v>35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.6</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38.9</v>
       </c>
       <c r="K7" t="n">
-        <v>82.7</v>
+        <v>74.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>33.4</v>
       </c>
       <c r="O7" t="n">
-        <v>38.8</v>
+        <v>37.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="X7" t="n">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>236.14</v>
+        <v>229.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.29</v>
+        <v>-2.53</v>
       </c>
       <c r="AK7" t="n">
-        <v>136.28</v>
+        <v>136.96</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.33</v>
+        <v>-6.65</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46231</v>
+        <v>46238</v>
       </c>
       <c r="B8" t="n">
-        <v>166.4</v>
+        <v>159.6</v>
       </c>
       <c r="C8" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
         <v>34.5</v>
       </c>
       <c r="E8" t="n">
-        <v>36.4</v>
+        <v>31.1</v>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="J8" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="K8" t="n">
         <v>75.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>35.9</v>
+        <v>34.3</v>
       </c>
       <c r="O8" t="n">
-        <v>39</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="V8" t="n">
-        <v>11.9</v>
+        <v>17.5</v>
       </c>
       <c r="W8" t="n">
-        <v>27</v>
+        <v>22.5</v>
       </c>
       <c r="X8" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>228.57</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>134.54</v>
+        <v>133.01</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.74</v>
+        <v>-3.95</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46231</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B9" t="n">
-        <v>172.9</v>
+        <v>160.4</v>
       </c>
       <c r="C9" t="n">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="D9" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>35.2</v>
+        <v>32.2</v>
       </c>
       <c r="F9" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="I9" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="J9" t="n">
-        <v>41.7</v>
+        <v>41.1</v>
       </c>
       <c r="K9" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="N9" t="n">
-        <v>34.8</v>
+        <v>32.6</v>
       </c>
       <c r="O9" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>14.4</v>
+        <v>16.4</v>
       </c>
       <c r="W9" t="n">
-        <v>18.7</v>
+        <v>22.8</v>
       </c>
       <c r="X9" t="n">
-        <v>16.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>218.6</v>
+        <v>225.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>-17.54</v>
+        <v>-3.49</v>
       </c>
       <c r="AK9" t="n">
-        <v>130.39</v>
+        <v>135.24</v>
       </c>
       <c r="AL9" t="n">
-        <v>-4.15</v>
+        <v>2.23</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B10" t="n">
-        <v>157.5</v>
+        <v>161.7</v>
       </c>
       <c r="C10" t="n">
-        <v>68.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>33.2</v>
+        <v>34.9</v>
       </c>
       <c r="E10" t="n">
-        <v>27.7</v>
+        <v>27.3</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="I10" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="J10" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="K10" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="N10" t="n">
-        <v>34.9</v>
+        <v>31.5</v>
       </c>
       <c r="O10" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>11</v>
-      </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>-5.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>218.84</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.24</v>
+        <v>-0.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>133.09</v>
+        <v>134.62</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.7</v>
+        <v>-0.62</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B11" t="n">
-        <v>137.6</v>
+        <v>151.5</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>78.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>36.8</v>
+        <v>41.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1432,66 +1459,66 @@
         <v>19.9</v>
       </c>
       <c r="V11" t="n">
-        <v>13.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>24.4</v>
+        <v>19.4</v>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>-4.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.8</v>
+        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.78</v>
+        <v>221.37</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.94</v>
+        <v>-3.71</v>
       </c>
       <c r="AK11" t="n">
-        <v>138.76</v>
+        <v>135.21</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.67</v>
+        <v>0.59</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B12" t="n">
-        <v>132.5</v>
+        <v>145.2</v>
       </c>
       <c r="D12" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>75</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>35.1</v>
+        <v>39.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1506,535 +1533,535 @@
         <v>19.9</v>
       </c>
       <c r="V12" t="n">
-        <v>14.8</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>24.7</v>
+        <v>19.2</v>
       </c>
       <c r="X12" t="n">
-        <v>19.8</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>224.78</v>
+        <v>224.37</v>
       </c>
       <c r="AG12" t="n">
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>143.55</v>
+        <v>135.61</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.79</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B13" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>56.3</v>
+        <v>146.3</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>21.2</v>
+        <v>33.4</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>40.4</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>29</v>
+        <v>84.3</v>
       </c>
       <c r="O13" t="n">
-        <v>32.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T13" t="n">
-        <v>21.6</v>
+        <v>19.9</v>
       </c>
       <c r="V13" t="n">
-        <v>10.7</v>
+        <v>4.9</v>
       </c>
       <c r="W13" t="n">
-        <v>24.3</v>
+        <v>16.4</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>10.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z13" t="n">
         <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9</v>
+        <v>-6.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>232.22</v>
+        <v>225.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>7.44</v>
+        <v>1.56</v>
       </c>
       <c r="AK13" t="n">
-        <v>143.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.06</v>
+        <v>-0.33</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B14" t="n">
-        <v>157.5</v>
+        <v>182.8</v>
       </c>
       <c r="C14" t="n">
-        <v>59.6</v>
+        <v>86.8</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="E14" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="I14" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="J14" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="K14" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="N14" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="O14" t="n">
-        <v>37.1</v>
+        <v>38.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T14" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>26.3</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>19.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.1</v>
+        <v>-10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>-5.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>229.69</v>
+        <v>218.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>-2.53</v>
+        <v>-7.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>136.96</v>
+        <v>126.27</v>
       </c>
       <c r="AL14" t="n">
-        <v>-6.65</v>
+        <v>-9.01</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="B15" t="n">
-        <v>159.6</v>
+        <v>181.8</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>86.5</v>
       </c>
       <c r="D15" t="n">
-        <v>34.5</v>
+        <v>31.4</v>
       </c>
       <c r="E15" t="n">
-        <v>31.1</v>
+        <v>34.2</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="I15" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="J15" t="n">
-        <v>40.5</v>
+        <v>41.9</v>
       </c>
       <c r="K15" t="n">
-        <v>75.2</v>
+        <v>76.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>34.3</v>
+        <v>35.7</v>
       </c>
       <c r="O15" t="n">
-        <v>38.2</v>
+        <v>39.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>20.1</v>
       </c>
       <c r="T15" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>17.5</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>22.5</v>
+        <v>14.8</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>10.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>228.57</v>
+        <v>216.39</v>
       </c>
       <c r="AG15" t="n">
-        <v>-1.12</v>
+        <v>-2.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>133.01</v>
+        <v>123.32</v>
       </c>
       <c r="AL15" t="n">
-        <v>-3.95</v>
+        <v>-2.95</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4649.3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2021.1</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>3016.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="B16" t="n">
-        <v>160.4</v>
+        <v>183</v>
       </c>
       <c r="C16" t="n">
-        <v>62.6</v>
+        <v>84.7</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>30.9</v>
       </c>
       <c r="E16" t="n">
-        <v>32.2</v>
+        <v>33.7</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="I16" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="J16" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K16" t="n">
-        <v>75.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>32.6</v>
+        <v>36.7</v>
       </c>
       <c r="O16" t="n">
-        <v>38</v>
+        <v>40.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y16" t="n">
         <v>8</v>
       </c>
-      <c r="T16" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>13</v>
       </c>
-      <c r="Z16" t="n">
-        <v>16</v>
-      </c>
       <c r="AA16" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-3.1</v>
+        <v>0.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>225.08</v>
+        <v>217.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>-3.49</v>
+        <v>0.77</v>
       </c>
       <c r="AK16" t="n">
-        <v>135.24</v>
+        <v>117.87</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.23</v>
+        <v>-5.45</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6995.8</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2380.8</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3192.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B17" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>71.09999999999999</v>
+        <v>163.8</v>
       </c>
       <c r="D17" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>27.3</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>42.6</v>
+        <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>77</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>31.5</v>
+        <v>96.3</v>
       </c>
       <c r="O17" t="n">
-        <v>37.3</v>
+        <v>45.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="T17" t="n">
-        <v>21</v>
+        <v>19.9</v>
       </c>
       <c r="V17" t="n">
-        <v>12.7</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>27</v>
+        <v>17.2</v>
       </c>
       <c r="X17" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>-5.2</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.3</v>
+        <v>2.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>134.62</v>
+        <v>116.52</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.62</v>
+        <v>-1.35</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>2827.2</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>3152.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B18" t="n">
-        <v>151.5</v>
+        <v>155.9</v>
       </c>
       <c r="D18" t="n">
-        <v>35.1</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>41.2</v>
+        <v>42.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2049,66 +2076,78 @@
         <v>19.9</v>
       </c>
       <c r="V18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W18" t="n">
-        <v>19.4</v>
+        <v>15.8</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
         <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>-4.7</v>
+        <v>1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>-1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>221.37</v>
+        <v>221.99</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.71</v>
+        <v>1.68</v>
       </c>
       <c r="AK18" t="n">
-        <v>135.21</v>
+        <v>116.37</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.59</v>
+        <v>-0.15</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>3609.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1161.2</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>3077.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B19" t="n">
-        <v>145.2</v>
+        <v>141.3</v>
       </c>
       <c r="D19" t="n">
-        <v>33.5</v>
+        <v>26.3</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>83.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>39.2</v>
+        <v>38</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2123,66 +2162,78 @@
         <v>19.9</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
       <c r="X19" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB19" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>-1.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>224.37</v>
+        <v>225.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AK19" t="n">
-        <v>135.61</v>
+        <v>120.64</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.4</v>
+        <v>4.27</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1884.4</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>2636.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B20" t="n">
-        <v>146.3</v>
+        <v>131.5</v>
       </c>
       <c r="D20" t="n">
-        <v>33.4</v>
+        <v>27.3</v>
       </c>
       <c r="F20" t="n">
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>84.3</v>
+        <v>74.3</v>
       </c>
       <c r="O20" t="n">
-        <v>39.6</v>
+        <v>34.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2197,461 +2248,506 @@
         <v>19.9</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>16.4</v>
+        <v>13.9</v>
       </c>
       <c r="X20" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA20" t="n">
         <v>15</v>
       </c>
-      <c r="AA20" t="n">
-        <v>9</v>
-      </c>
       <c r="AB20" t="n">
-        <v>-6.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>-3.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>225.93</v>
+        <v>229.98</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.56</v>
+        <v>4.84</v>
       </c>
       <c r="AK20" t="n">
-        <v>135.28</v>
+        <v>128.14</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.33</v>
+        <v>7.5</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1894.8</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B21" t="n">
-        <v>182.8</v>
+        <v>153</v>
       </c>
       <c r="C21" t="n">
-        <v>86.8</v>
+        <v>71.8</v>
       </c>
       <c r="D21" t="n">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>24.7</v>
       </c>
       <c r="F21" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="I21" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="J21" t="n">
         <v>41.1</v>
       </c>
       <c r="K21" t="n">
-        <v>74.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
         <v>33.5</v>
       </c>
       <c r="O21" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="V21" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X21" t="n">
         <v>12.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB21" t="n">
-        <v>-10.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>218.63</v>
+        <v>229.96</v>
       </c>
       <c r="AG21" t="n">
-        <v>-7.3</v>
+        <v>-0.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>126.27</v>
+        <v>128.15</v>
       </c>
       <c r="AL21" t="n">
-        <v>-9.01</v>
+        <v>0.01</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>2723.2</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B22" t="n">
-        <v>181.8</v>
+        <v>165.8</v>
       </c>
       <c r="C22" t="n">
-        <v>86.5</v>
+        <v>77.3</v>
       </c>
       <c r="D22" t="n">
-        <v>31.4</v>
+        <v>29.3</v>
       </c>
       <c r="E22" t="n">
-        <v>34.2</v>
+        <v>27.7</v>
       </c>
       <c r="F22" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="K22" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="N22" t="n">
-        <v>35.7</v>
+        <v>35.1</v>
       </c>
       <c r="O22" t="n">
         <v>39.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>20.1</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="W22" t="n">
-        <v>14.8</v>
+        <v>17.4</v>
       </c>
       <c r="X22" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22" t="n">
-        <v>-4.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>-1.4</v>
+        <v>4.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>216.39</v>
+        <v>227.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.24</v>
+        <v>-2.95</v>
       </c>
       <c r="AK22" t="n">
-        <v>123.32</v>
+        <v>128.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>-2.95</v>
+        <v>0.71</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="BM22" t="n">
-        <v>40.72</v>
+        <v>33.62</v>
       </c>
       <c r="BN22" t="n">
-        <v>4649.3</v>
+        <v>6652.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>2021.1</v>
+        <v>1412.3</v>
       </c>
       <c r="BP22" t="n">
-        <v>3016.3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B23" t="n">
-        <v>183</v>
+        <v>158.1</v>
       </c>
       <c r="C23" t="n">
-        <v>84.7</v>
+        <v>73.7</v>
       </c>
       <c r="D23" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="E23" t="n">
-        <v>33.7</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="K23" t="n">
-        <v>76.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>36.7</v>
+        <v>35.3</v>
       </c>
       <c r="O23" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q23" t="n">
         <v>23.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
       <c r="V23" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="W23" t="n">
-        <v>16.1</v>
+        <v>19.3</v>
       </c>
       <c r="X23" t="n">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
         <v>10.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>217.16</v>
+        <v>228.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.77</v>
+        <v>1.34</v>
       </c>
       <c r="AK23" t="n">
-        <v>117.87</v>
+        <v>130.88</v>
       </c>
       <c r="AL23" t="n">
-        <v>-5.45</v>
+        <v>2.02</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="BM23" t="n">
-        <v>40.4</v>
+        <v>32.38</v>
       </c>
       <c r="BN23" t="n">
-        <v>6995.8</v>
+        <v>4993.3</v>
       </c>
       <c r="BO23" t="n">
-        <v>2380.8</v>
+        <v>958.6</v>
       </c>
       <c r="BP23" t="n">
-        <v>3192.8</v>
+        <v>2899.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B24" t="n">
-        <v>163.8</v>
+        <v>154.9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>70.2</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>31.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>27.7</v>
       </c>
       <c r="F24" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40.3</v>
       </c>
       <c r="K24" t="n">
-        <v>96.3</v>
+        <v>75.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>32.9</v>
       </c>
       <c r="O24" t="n">
-        <v>45.1</v>
+        <v>39</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="T24" t="n">
-        <v>19.9</v>
+        <v>23.7</v>
       </c>
       <c r="V24" t="n">
         <v>6.3</v>
       </c>
       <c r="W24" t="n">
-        <v>17.2</v>
+        <v>25.2</v>
       </c>
       <c r="X24" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>220.31</v>
+        <v>231.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="AK24" t="n">
-        <v>116.52</v>
+        <v>132.55</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="BM24" t="n">
-        <v>39.65</v>
+        <v>33.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>2827.2</v>
+        <v>1514.9</v>
       </c>
       <c r="BO24" t="n">
-        <v>2051.2</v>
+        <v>799.7</v>
       </c>
       <c r="BP24" t="n">
-        <v>3152.1</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B25" t="n">
-        <v>155.9</v>
+        <v>152.2</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>90.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>42.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2666,78 +2762,78 @@
         <v>19.9</v>
       </c>
       <c r="V25" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
-        <v>15.8</v>
+        <v>25.5</v>
       </c>
       <c r="X25" t="n">
-        <v>12.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>221.99</v>
+        <v>228.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.68</v>
+        <v>-3.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>116.37</v>
+        <v>128.02</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.15</v>
+        <v>-4.53</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="BM25" t="n">
-        <v>34.79</v>
+        <v>35.62</v>
       </c>
       <c r="BN25" t="n">
-        <v>3609.5</v>
+        <v>1526.5</v>
       </c>
       <c r="BO25" t="n">
-        <v>1161.2</v>
+        <v>957.4</v>
       </c>
       <c r="BP25" t="n">
-        <v>3077.1</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B26" t="n">
-        <v>141.3</v>
+        <v>143.9</v>
       </c>
       <c r="D26" t="n">
-        <v>26.3</v>
+        <v>30.8</v>
       </c>
       <c r="F26" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>80.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="O26" t="n">
-        <v>38</v>
+        <v>38.8</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2752,592 +2848,613 @@
         <v>19.9</v>
       </c>
       <c r="V26" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W26" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="X26" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.14</v>
+        <v>229.16</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK26" t="n">
-        <v>120.64</v>
+        <v>127.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.27</v>
+        <v>-0.96</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="BM26" t="n">
-        <v>31.22</v>
+        <v>34.56</v>
       </c>
       <c r="BN26" t="n">
-        <v>1884.4</v>
+        <v>170.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>785.2</v>
+        <v>130.4</v>
       </c>
       <c r="BP26" t="n">
-        <v>2636.2</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B27" t="n">
-        <v>131.5</v>
+        <v>163.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>73.7</v>
       </c>
       <c r="D27" t="n">
-        <v>27.3</v>
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28.2</v>
       </c>
       <c r="F27" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>40.1</v>
       </c>
       <c r="K27" t="n">
-        <v>74.3</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32.9</v>
       </c>
       <c r="O27" t="n">
-        <v>34.8</v>
+        <v>39.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>19.9</v>
+        <v>23.5</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W27" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="X27" t="n">
-        <v>11.4</v>
+        <v>14.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>-3.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.4</v>
+        <v>4.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>229.98</v>
+        <v>228.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.84</v>
+        <v>-0.61</v>
       </c>
       <c r="AK27" t="n">
-        <v>128.14</v>
+        <v>125.61</v>
       </c>
       <c r="AL27" t="n">
-        <v>7.5</v>
+        <v>-1.45</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="BM27" t="n">
-        <v>26.41</v>
+        <v>34.78</v>
       </c>
       <c r="BN27" t="n">
-        <v>1894.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO27" t="n">
-        <v>223.6</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B28" t="n">
-        <v>153</v>
+        <v>174.4</v>
       </c>
       <c r="C28" t="n">
-        <v>71.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>28.6</v>
+        <v>32.1</v>
       </c>
       <c r="E28" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="H28" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I28" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="K28" t="n">
-        <v>75.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="M28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD28" t="n">
         <v>4.8</v>
       </c>
-      <c r="N28" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V28" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>13</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF28" t="n">
-        <v>229.96</v>
+        <v>219.99</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.02</v>
+        <v>-8.56</v>
       </c>
       <c r="AK28" t="n">
-        <v>128.15</v>
+        <v>124.36</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.01</v>
+        <v>-1.25</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="BM28" t="n">
-        <v>29.83</v>
+        <v>36.78</v>
       </c>
       <c r="BN28" t="n">
-        <v>2723.2</v>
+        <v>108.8</v>
       </c>
       <c r="BO28" t="n">
-        <v>271.1</v>
+        <v>204.3</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B29" t="n">
-        <v>165.8</v>
+        <v>163.2</v>
       </c>
       <c r="C29" t="n">
-        <v>77.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>29.3</v>
+        <v>32.9</v>
       </c>
       <c r="E29" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="H29" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I29" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>41.6</v>
+        <v>40.1</v>
       </c>
       <c r="K29" t="n">
-        <v>76.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="N29" t="n">
-        <v>35.1</v>
+        <v>34.3</v>
       </c>
       <c r="O29" t="n">
-        <v>39.8</v>
+        <v>41.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="R29" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="T29" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W29" t="n">
-        <v>17.4</v>
+        <v>23.3</v>
       </c>
       <c r="X29" t="n">
-        <v>13.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>227.01</v>
+        <v>219.22</v>
       </c>
       <c r="AG29" t="n">
-        <v>-2.95</v>
+        <v>-0.77</v>
       </c>
       <c r="AK29" t="n">
-        <v>128.86</v>
+        <v>120.93</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.71</v>
+        <v>-3.43</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="BM29" t="n">
-        <v>33.62</v>
+        <v>32.64</v>
       </c>
       <c r="BN29" t="n">
-        <v>6652.6</v>
+        <v>42.3</v>
       </c>
       <c r="BO29" t="n">
-        <v>1412.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP29" t="n">
-        <v>408</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B30" t="n">
-        <v>158.1</v>
+        <v>152.7</v>
       </c>
       <c r="C30" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D30" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="H30" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I30" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="K30" t="n">
-        <v>74.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="N30" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="O30" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="V30" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="W30" t="n">
-        <v>19.3</v>
+        <v>27.3</v>
       </c>
       <c r="X30" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>228.35</v>
+        <v>220.73</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AK30" t="n">
-        <v>130.88</v>
+        <v>120.28</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.02</v>
+        <v>-0.65</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="BM30" t="n">
-        <v>32.38</v>
+        <v>29.61</v>
       </c>
       <c r="BN30" t="n">
-        <v>4993.3</v>
+        <v>60.1</v>
       </c>
       <c r="BO30" t="n">
-        <v>958.6</v>
+        <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>2899.8</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B31" t="n">
-        <v>154.9</v>
+        <v>150.7</v>
       </c>
       <c r="C31" t="n">
-        <v>70.2</v>
+        <v>64.8</v>
       </c>
       <c r="D31" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="E31" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F31" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H31" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I31" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="K31" t="n">
-        <v>75.8</v>
+        <v>70.5</v>
       </c>
       <c r="M31" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="N31" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="O31" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="R31" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S31" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="W31" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="X31" t="n">
-        <v>15.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>231.16</v>
+        <v>220.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.81</v>
+        <v>-0.15</v>
       </c>
       <c r="AK31" t="n">
-        <v>132.55</v>
+        <v>119.29</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.67</v>
+        <v>-0.99</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="BM31" t="n">
-        <v>33.01</v>
+        <v>31.11</v>
       </c>
       <c r="BN31" t="n">
-        <v>1514.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO31" t="n">
-        <v>799.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP31" t="n">
-        <v>2923.4</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B32" t="n">
-        <v>152.2</v>
+        <v>138.2</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>33.6</v>
       </c>
       <c r="F32" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>88.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="O32" t="n">
-        <v>41.4</v>
+        <v>37</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3352,78 +3469,78 @@
         <v>19.9</v>
       </c>
       <c r="V32" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="W32" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="X32" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z32" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB32" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>228.13</v>
+        <v>223.43</v>
       </c>
       <c r="AG32" t="n">
-        <v>-3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AK32" t="n">
-        <v>128.02</v>
+        <v>121.35</v>
       </c>
       <c r="AL32" t="n">
-        <v>-4.53</v>
+        <v>2.06</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="BM32" t="n">
-        <v>35.62</v>
+        <v>30.59</v>
       </c>
       <c r="BN32" t="n">
-        <v>1526.5</v>
+        <v>40.8</v>
       </c>
       <c r="BO32" t="n">
-        <v>957.4</v>
+        <v>0</v>
       </c>
       <c r="BP32" t="n">
-        <v>2928.4</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B33" t="n">
-        <v>143.9</v>
+        <v>126.5</v>
       </c>
       <c r="D33" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F33" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>82.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>38.8</v>
+        <v>33.2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3438,613 +3555,613 @@
         <v>19.9</v>
       </c>
       <c r="V33" t="n">
-        <v>10.7</v>
+        <v>12.6</v>
       </c>
       <c r="W33" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="X33" t="n">
-        <v>14.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>229.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.03</v>
+        <v>6.05</v>
       </c>
       <c r="AK33" t="n">
-        <v>127.06</v>
+        <v>128.37</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.96</v>
+        <v>7.02</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="BM33" t="n">
-        <v>34.56</v>
+        <v>30.05</v>
       </c>
       <c r="BN33" t="n">
-        <v>170.6</v>
+        <v>34</v>
       </c>
       <c r="BO33" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2825.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B34" t="n">
-        <v>163.2</v>
+        <v>129.4</v>
       </c>
       <c r="C34" t="n">
-        <v>73.7</v>
+        <v>50.6</v>
       </c>
       <c r="D34" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E34" t="n">
-        <v>28.2</v>
+        <v>19.4</v>
       </c>
       <c r="F34" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H34" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I34" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="J34" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
       <c r="K34" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M34" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="N34" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="O34" t="n">
-        <v>39.7</v>
+        <v>38</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="R34" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="V34" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="W34" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="X34" t="n">
-        <v>14.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD34" t="n">
         <v>4</v>
       </c>
-      <c r="Z34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF34" t="n">
-        <v>228.55</v>
+        <v>241.48</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.61</v>
+        <v>12</v>
       </c>
       <c r="AK34" t="n">
-        <v>125.61</v>
+        <v>134.59</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.45</v>
+        <v>6.22</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="BM34" t="n">
-        <v>34.78</v>
+        <v>24.86</v>
       </c>
       <c r="BN34" t="n">
-        <v>69.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2769.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B35" t="n">
-        <v>174.4</v>
+        <v>142.9</v>
       </c>
       <c r="C35" t="n">
-        <v>75.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="D35" t="n">
-        <v>32.1</v>
+        <v>34.7</v>
       </c>
       <c r="E35" t="n">
-        <v>30.8</v>
+        <v>24.8</v>
       </c>
       <c r="F35" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I35" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="J35" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="K35" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M35" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O35" t="n">
         <v>35.8</v>
       </c>
-      <c r="O35" t="n">
-        <v>42.6</v>
-      </c>
       <c r="Q35" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="R35" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="S35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="V35" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="W35" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
       <c r="X35" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>219.99</v>
+        <v>238.69</v>
       </c>
       <c r="AG35" t="n">
-        <v>-8.56</v>
+        <v>-2.79</v>
       </c>
       <c r="AK35" t="n">
-        <v>124.36</v>
+        <v>136.6</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.25</v>
+        <v>2.01</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="BM35" t="n">
-        <v>36.78</v>
+        <v>29.8</v>
       </c>
       <c r="BN35" t="n">
-        <v>108.8</v>
+        <v>61.9</v>
       </c>
       <c r="BO35" t="n">
-        <v>204.3</v>
+        <v>0</v>
       </c>
       <c r="BP35" t="n">
-        <v>2982.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B36" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C36" t="n">
-        <v>70.90000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D36" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="F36" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="n">
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
       <c r="I36" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J36" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K36" t="n">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="O36" t="n">
-        <v>41.5</v>
+        <v>33.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="S36" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="V36" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="W36" t="n">
-        <v>23.3</v>
+        <v>25.5</v>
       </c>
       <c r="X36" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA36" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>219.22</v>
+        <v>233.48</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.77</v>
+        <v>-5.21</v>
       </c>
       <c r="AK36" t="n">
-        <v>120.93</v>
+        <v>135.66</v>
       </c>
       <c r="AL36" t="n">
-        <v>-3.43</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="BM36" t="n">
-        <v>32.64</v>
+        <v>36.03</v>
       </c>
       <c r="BN36" t="n">
-        <v>42.3</v>
+        <v>76.5</v>
       </c>
       <c r="BO36" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP36" t="n">
-        <v>3194.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B37" t="n">
-        <v>152.7</v>
+        <v>143.4</v>
       </c>
       <c r="C37" t="n">
-        <v>62.6</v>
+        <v>50.9</v>
       </c>
       <c r="D37" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="E37" t="n">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="F37" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="I37" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K37" t="n">
-        <v>69.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>33.5</v>
+        <v>31.2</v>
       </c>
       <c r="O37" t="n">
-        <v>40.1</v>
+        <v>33.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="R37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="V37" t="n">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="W37" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="X37" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA37" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>220.73</v>
+        <v>235.13</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AK37" t="n">
-        <v>120.28</v>
+        <v>136.33</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="BM37" t="n">
-        <v>29.61</v>
+        <v>32</v>
       </c>
       <c r="BN37" t="n">
-        <v>60.1</v>
+        <v>29.5</v>
       </c>
       <c r="BO37" t="n">
         <v>0</v>
       </c>
       <c r="BP37" t="n">
-        <v>2717.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B38" t="n">
-        <v>150.7</v>
+        <v>144.9</v>
       </c>
       <c r="C38" t="n">
-        <v>64.8</v>
+        <v>53</v>
       </c>
       <c r="D38" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
       <c r="E38" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="n">
+        <v>24</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O38" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>21</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>21</v>
+      </c>
+      <c r="V38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>234.87</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>137.17</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BL38" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="BN38" t="n">
         <v>23.4</v>
       </c>
-      <c r="I38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K38" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N38" t="n">
-        <v>33</v>
-      </c>
-      <c r="O38" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>119.29</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="BL38" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>87.90000000000001</v>
-      </c>
       <c r="BO38" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP38" t="n">
-        <v>3028.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B39" t="n">
-        <v>138.2</v>
+        <v>132.2</v>
       </c>
       <c r="D39" t="n">
-        <v>33.6</v>
+        <v>35.6</v>
       </c>
       <c r="F39" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>78.8</v>
+        <v>74.7</v>
       </c>
       <c r="O39" t="n">
-        <v>37</v>
+        <v>35.1</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4059,78 +4176,78 @@
         <v>19.9</v>
       </c>
       <c r="V39" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="W39" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="X39" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="n">
         <v>13</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AF39" t="n">
-        <v>223.43</v>
+        <v>234.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.85</v>
+        <v>-0.09</v>
       </c>
       <c r="AK39" t="n">
-        <v>121.35</v>
+        <v>136.08</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.06</v>
+        <v>-1.09</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="BM39" t="n">
-        <v>30.59</v>
+        <v>29.64</v>
       </c>
       <c r="BN39" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="BO39" t="n">
         <v>0</v>
       </c>
       <c r="BP39" t="n">
-        <v>2959.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B40" t="n">
-        <v>126.5</v>
+        <v>137.1</v>
       </c>
       <c r="D40" t="n">
-        <v>33.2</v>
+        <v>35.1</v>
       </c>
       <c r="F40" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>70.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>33.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4145,52 +4262,52 @@
         <v>19.9</v>
       </c>
       <c r="V40" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="X40" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z40" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.48</v>
+        <v>229.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>6.05</v>
+        <v>-5.03</v>
       </c>
       <c r="AK40" t="n">
-        <v>128.37</v>
+        <v>135.42</v>
       </c>
       <c r="AL40" t="n">
-        <v>7.02</v>
+        <v>-0.66</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="BM40" t="n">
-        <v>30.05</v>
+        <v>31.45</v>
       </c>
       <c r="BN40" t="n">
-        <v>34</v>
+        <v>35.9</v>
       </c>
       <c r="BO40" t="n">
         <v>0</v>
@@ -4201,1178 +4318,1013 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B41" t="n">
-        <v>129.4</v>
+        <v>148.7</v>
       </c>
       <c r="C41" t="n">
-        <v>50.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E41" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I41" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="K41" t="n">
-        <v>73.3</v>
+        <v>74.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="N41" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="O41" t="n">
-        <v>38</v>
+        <v>39.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="V41" t="n">
-        <v>14.3</v>
+        <v>7.9</v>
       </c>
       <c r="W41" t="n">
-        <v>23.9</v>
+        <v>15.6</v>
       </c>
       <c r="X41" t="n">
-        <v>19.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>241.48</v>
+        <v>222.86</v>
       </c>
       <c r="AG41" t="n">
-        <v>12</v>
+        <v>-6.89</v>
       </c>
       <c r="AK41" t="n">
-        <v>134.59</v>
+        <v>131.24</v>
       </c>
       <c r="AL41" t="n">
-        <v>6.22</v>
+        <v>-4.18</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="BM41" t="n">
-        <v>24.86</v>
+        <v>34.46</v>
       </c>
       <c r="BN41" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP41" t="n">
-        <v>0</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B42" t="n">
-        <v>142.9</v>
+        <v>149.3</v>
       </c>
       <c r="C42" t="n">
-        <v>52.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="E42" t="n">
-        <v>24.8</v>
+        <v>28.8</v>
       </c>
       <c r="F42" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="H42" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="I42" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="K42" t="n">
-        <v>70</v>
+        <v>73.8</v>
       </c>
       <c r="M42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R42" t="n">
         <v>3.9</v>
       </c>
-      <c r="N42" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="O42" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.7</v>
-      </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>19.7</v>
+        <v>23.9</v>
       </c>
       <c r="V42" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="W42" t="n">
-        <v>25.8</v>
+        <v>18.1</v>
       </c>
       <c r="X42" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z42" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>238.69</v>
+        <v>218.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>-2.79</v>
+        <v>-4.49</v>
       </c>
       <c r="AK42" t="n">
-        <v>136.6</v>
+        <v>129.21</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.01</v>
+        <v>-2.03</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="BM42" t="n">
-        <v>29.8</v>
+        <v>35.4</v>
       </c>
       <c r="BN42" t="n">
-        <v>61.9</v>
+        <v>294.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="BP42" t="n">
-        <v>0</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B43" t="n">
-        <v>148.1</v>
+        <v>137</v>
       </c>
       <c r="C43" t="n">
-        <v>51.9</v>
+        <v>65</v>
       </c>
       <c r="D43" t="n">
-        <v>35.4</v>
+        <v>32</v>
       </c>
       <c r="E43" t="n">
-        <v>31.5</v>
+        <v>25.2</v>
       </c>
       <c r="F43" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H43" t="n">
-        <v>21.8</v>
+        <v>23.5</v>
       </c>
       <c r="I43" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>39.6</v>
+        <v>38.5</v>
       </c>
       <c r="K43" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>30.8</v>
+        <v>32.3</v>
       </c>
       <c r="O43" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="R43" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T43" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="V43" t="n">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="W43" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="X43" t="n">
-        <v>19.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="n">
         <v>13.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="AF43" t="n">
-        <v>233.48</v>
+        <v>220.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>-5.21</v>
+        <v>2.48</v>
       </c>
       <c r="AK43" t="n">
-        <v>135.66</v>
+        <v>129.07</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="BM43" t="n">
-        <v>36.03</v>
+        <v>32.31</v>
       </c>
       <c r="BN43" t="n">
-        <v>76.5</v>
+        <v>547</v>
       </c>
       <c r="BO43" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BP43" t="n">
-        <v>0</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B44" t="n">
-        <v>143.4</v>
+        <v>131.5</v>
       </c>
       <c r="C44" t="n">
-        <v>50.9</v>
+        <v>57.6</v>
       </c>
       <c r="D44" t="n">
-        <v>35.7</v>
+        <v>32.7</v>
       </c>
       <c r="E44" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="F44" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="I44" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J44" t="n">
-        <v>39.9</v>
+        <v>41.6</v>
       </c>
       <c r="K44" t="n">
-        <v>72.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="N44" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="O44" t="n">
-        <v>33.1</v>
+        <v>42.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V44" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>28.3</v>
+        <v>24.1</v>
       </c>
       <c r="X44" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>235.13</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.65</v>
+        <v>6.3</v>
       </c>
       <c r="AK44" t="n">
-        <v>136.33</v>
+        <v>130.73</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="BM44" t="n">
-        <v>32</v>
+        <v>31.51</v>
       </c>
       <c r="BN44" t="n">
-        <v>29.5</v>
+        <v>124</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>164.4</v>
       </c>
       <c r="BP44" t="n">
-        <v>0</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B45" t="n">
-        <v>144.9</v>
+        <v>129.4</v>
       </c>
       <c r="C45" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="D45" t="n">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="F45" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I45" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J45" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="K45" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="N45" t="n">
-        <v>31.6</v>
+        <v>33.1</v>
       </c>
       <c r="O45" t="n">
-        <v>33.6</v>
+        <v>38.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V45" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="W45" t="n">
-        <v>27.7</v>
+        <v>22.9</v>
       </c>
       <c r="X45" t="n">
-        <v>21.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y45" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="Z45" t="n">
         <v>19</v>
       </c>
       <c r="AA45" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-1.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>234.87</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>-0.26</v>
+        <v>4.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>137.17</v>
+        <v>132</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.84</v>
+        <v>1.27</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="BM45" t="n">
-        <v>32.57</v>
+        <v>34.36</v>
       </c>
       <c r="BN45" t="n">
-        <v>23.4</v>
+        <v>62.8</v>
       </c>
       <c r="BO45" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="BP45" t="n">
-        <v>0</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B46" t="n">
-        <v>132.2</v>
+        <v>130.2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>56.9</v>
       </c>
       <c r="D46" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="F46" t="n">
-        <v>4</v>
+        <v>33.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>42.3</v>
       </c>
       <c r="K46" t="n">
-        <v>74.7</v>
+        <v>75.3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N46" t="n">
+        <v>32.3</v>
       </c>
       <c r="O46" t="n">
-        <v>35.1</v>
+        <v>37.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="R46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V46" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X46" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>234.78</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>-0.09</v>
+        <v>22.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>136.08</v>
+        <v>132.25</v>
       </c>
       <c r="AL46" t="n">
-        <v>-1.09</v>
+        <v>0.25</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="BM46" t="n">
-        <v>29.64</v>
+        <v>32.26</v>
       </c>
       <c r="BN46" t="n">
-        <v>36.4</v>
+        <v>28.3</v>
       </c>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="BP46" t="n">
-        <v>0</v>
+        <v>2545.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B47" t="n">
-        <v>137.1</v>
+        <v>138.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3.3</v>
+        <v>32.8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H47" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>42.8</v>
       </c>
       <c r="K47" t="n">
-        <v>78.09999999999999</v>
+        <v>75.8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>32.3</v>
       </c>
       <c r="O47" t="n">
-        <v>36.6</v>
+        <v>35.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V47" t="n">
-        <v>11</v>
-      </c>
-      <c r="W47" t="n">
-        <v>22</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>229.75</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>-5.03</v>
+        <v>23.6</v>
       </c>
       <c r="AK47" t="n">
-        <v>135.42</v>
+        <v>128.6</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.66</v>
+        <v>-3.65</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="BM47" t="n">
-        <v>31.45</v>
+        <v>33.93</v>
       </c>
       <c r="BN47" t="n">
-        <v>35.9</v>
+        <v>73</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BP47" t="n">
-        <v>0</v>
+        <v>2697.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B48" t="n">
-        <v>148.7</v>
+        <v>140.8</v>
       </c>
       <c r="C48" t="n">
-        <v>72.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>32.7</v>
+        <v>31.7</v>
       </c>
       <c r="E48" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="F48" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="K48" t="n">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
       <c r="M48" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N48" t="n">
-        <v>33.7</v>
+        <v>33.4</v>
       </c>
       <c r="O48" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="R48" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V48" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AA48" t="n">
         <v>7.9</v>
       </c>
-      <c r="W48" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>222.86</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>-6.89</v>
-      </c>
       <c r="AK48" t="n">
-        <v>131.24</v>
+        <v>127.19</v>
       </c>
       <c r="AL48" t="n">
-        <v>-4.18</v>
+        <v>-1.41</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="BM48" t="n">
-        <v>34.46</v>
+        <v>31.16</v>
       </c>
       <c r="BN48" t="n">
-        <v>80.40000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="BO48" t="n">
-        <v>373.6</v>
+        <v>0</v>
       </c>
       <c r="BP48" t="n">
-        <v>249.4</v>
+        <v>2603.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B49" t="n">
-        <v>149.3</v>
+        <v>139.6</v>
       </c>
       <c r="C49" t="n">
-        <v>74.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E49" t="n">
-        <v>28.8</v>
+        <v>25.9</v>
       </c>
       <c r="F49" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="H49" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="I49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>41.2</v>
+        <v>39.6</v>
       </c>
       <c r="K49" t="n">
-        <v>73.8</v>
+        <v>73.3</v>
       </c>
       <c r="M49" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="N49" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="O49" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="R49" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W49" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>14</v>
+        <v>23.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>218.37</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>-4.49</v>
+        <v>12</v>
       </c>
       <c r="AK49" t="n">
-        <v>129.21</v>
+        <v>129.17</v>
       </c>
       <c r="AL49" t="n">
-        <v>-2.03</v>
+        <v>1.98</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="BM49" t="n">
-        <v>35.4</v>
+        <v>32.41</v>
       </c>
       <c r="BN49" t="n">
-        <v>294.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BO49" t="n">
-        <v>227</v>
+        <v>297.8</v>
       </c>
       <c r="BP49" t="n">
-        <v>2758.6</v>
+        <v>2677.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B50" t="n">
-        <v>137</v>
+        <v>133.5</v>
       </c>
       <c r="C50" t="n">
-        <v>65</v>
+        <v>62.3</v>
       </c>
       <c r="D50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E50" t="n">
-        <v>25.2</v>
+        <v>22.5</v>
       </c>
       <c r="F50" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H50" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J50" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="K50" t="n">
-        <v>70.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="N50" t="n">
-        <v>32.3</v>
+        <v>30.4</v>
       </c>
       <c r="O50" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="R50" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="S50" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>21</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>18</v>
+        <v>22.1</v>
       </c>
       <c r="AA50" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>220.85</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.48</v>
+        <v>12.9</v>
       </c>
       <c r="AK50" t="n">
-        <v>129.07</v>
+        <v>130.42</v>
       </c>
       <c r="AL50" t="n">
-        <v>-0.14</v>
+        <v>1.25</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="BM50" t="n">
-        <v>32.31</v>
+        <v>26.56</v>
       </c>
       <c r="BN50" t="n">
-        <v>547</v>
+        <v>46.1</v>
       </c>
       <c r="BO50" t="n">
-        <v>85</v>
+        <v>266.8</v>
       </c>
       <c r="BP50" t="n">
-        <v>2654.5</v>
+        <v>2801.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B51" t="n">
-        <v>131.5</v>
+        <v>136.6</v>
       </c>
       <c r="C51" t="n">
-        <v>57.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>32.7</v>
+        <v>34.7</v>
       </c>
       <c r="E51" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3.3</v>
+        <v>33</v>
       </c>
       <c r="H51" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="I51" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="J51" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="K51" t="n">
-        <v>74.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="N51" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O51" t="n">
-        <v>42.4</v>
+        <v>33.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="R51" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="V51" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W51" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>6.3</v>
+        <v>23.1</v>
       </c>
       <c r="AK51" t="n">
-        <v>130.73</v>
+        <v>129.71</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.66</v>
+        <v>-0.71</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="BM51" t="n">
-        <v>31.51</v>
+        <v>31.32</v>
       </c>
       <c r="BN51" t="n">
-        <v>124</v>
+        <v>54.7</v>
       </c>
       <c r="BO51" t="n">
-        <v>164.4</v>
+        <v>235.3</v>
       </c>
       <c r="BP51" t="n">
-        <v>2635.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="B52" t="n">
-        <v>129.4</v>
+        <v>127.5</v>
       </c>
       <c r="C52" t="n">
-        <v>52.8</v>
+        <v>53.6</v>
       </c>
       <c r="D52" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="E52" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.3</v>
+        <v>34.83</v>
       </c>
       <c r="H52" t="n">
-        <v>23.7</v>
+        <v>24.5</v>
       </c>
       <c r="I52" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="J52" t="n">
-        <v>40.8</v>
+        <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>73.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>33.1</v>
+        <v>28.5</v>
       </c>
       <c r="O52" t="n">
-        <v>38.7</v>
+        <v>32.1</v>
       </c>
       <c r="Q52" t="n">
         <v>22</v>
       </c>
       <c r="R52" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -5380,591 +5332,300 @@
       <c r="T52" t="n">
         <v>22</v>
       </c>
-      <c r="V52" t="n">
-        <v>11</v>
-      </c>
-      <c r="W52" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X52" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>132</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="BM52" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>2693.4</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B53" t="n">
-        <v>130.2</v>
+        <v>119.2</v>
       </c>
       <c r="C53" t="n">
-        <v>56.9</v>
+        <v>45.9</v>
       </c>
       <c r="D53" t="n">
-        <v>33.9</v>
+        <v>34.9</v>
       </c>
       <c r="E53" t="n">
-        <v>30.85</v>
+        <v>34.73</v>
       </c>
       <c r="H53" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="I53" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J53" t="n">
-        <v>42.3</v>
+        <v>37</v>
       </c>
       <c r="K53" t="n">
-        <v>75.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="N53" t="n">
-        <v>32.3</v>
+        <v>29</v>
       </c>
       <c r="O53" t="n">
-        <v>37.1</v>
+        <v>31.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>22.3</v>
+        <v>18</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>132.25</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0.25</v>
+        <v>18</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>2545.1</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B54" t="n">
-        <v>138.4</v>
+        <v>106.9</v>
       </c>
       <c r="C54" t="n">
-        <v>66.90000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="D54" t="n">
-        <v>32.8</v>
+        <v>33.4</v>
       </c>
       <c r="E54" t="n">
-        <v>28.44</v>
+        <v>26.47</v>
       </c>
       <c r="H54" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="I54" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J54" t="n">
-        <v>42.8</v>
+        <v>35</v>
       </c>
       <c r="K54" t="n">
-        <v>75.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="N54" t="n">
-        <v>32.3</v>
+        <v>30</v>
       </c>
       <c r="O54" t="n">
-        <v>35.9</v>
+        <v>32.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="R54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>-3.65</v>
+        <v>15</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46277</v>
-      </c>
-      <c r="BM54" t="n">
-        <v>33.93</v>
-      </c>
-      <c r="BN54" t="n">
-        <v>73</v>
-      </c>
-      <c r="BO54" t="n">
-        <v>16</v>
-      </c>
-      <c r="BP54" t="n">
-        <v>2697.4</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>140.8</v>
+        <v>100.3</v>
       </c>
       <c r="C55" t="n">
-        <v>73.09999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="D55" t="n">
-        <v>31.7</v>
+        <v>33</v>
       </c>
       <c r="E55" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2</v>
+        <v>25.47</v>
       </c>
       <c r="H55" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="I55" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J55" t="n">
-        <v>40.5</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>73.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="N55" t="n">
-        <v>33.4</v>
+        <v>30</v>
       </c>
       <c r="O55" t="n">
-        <v>39.5</v>
+        <v>32.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.8</v>
+        <v>15</v>
       </c>
       <c r="R55" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>127.19</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>-1.41</v>
+        <v>15</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>2603.2</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B56" t="n">
-        <v>139.6</v>
-      </c>
-      <c r="C56" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="D56" t="n">
-        <v>32.2</v>
+        <v>46286</v>
       </c>
       <c r="E56" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H56" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J56" t="n">
-        <v>39.6</v>
+        <v>28.7</v>
       </c>
       <c r="K56" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="M56" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N56" t="n">
-        <v>34.4</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>40.1</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.8</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>129.17</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>297.8</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>2677.8</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B57" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="C57" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="D57" t="n">
-        <v>34</v>
+        <v>46287</v>
       </c>
       <c r="E57" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>40.8</v>
+        <v>28.7</v>
       </c>
       <c r="K57" t="n">
-        <v>75</v>
-      </c>
-      <c r="M57" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="N57" t="n">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>37.3</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>130.42</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>26.56</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="BO57" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="BP57" t="n">
-        <v>2801.1</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B58" t="n">
-        <v>136.6</v>
-      </c>
-      <c r="C58" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="D58" t="n">
-        <v>34.7</v>
+        <v>46288</v>
       </c>
       <c r="E58" t="n">
-        <v>33</v>
-      </c>
-      <c r="H58" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>41.5</v>
+        <v>28.7</v>
       </c>
       <c r="K58" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>33.1</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>129.71</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="BN58" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="BO58" t="n">
-        <v>235.3</v>
-      </c>
-      <c r="BP58" t="n">
-        <v>52.9</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B59" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="C59" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="D59" t="n">
-        <v>34.2</v>
+        <v>46289</v>
       </c>
       <c r="E59" t="n">
-        <v>34.83</v>
-      </c>
-      <c r="H59" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J59" t="n">
-        <v>40</v>
+        <v>27.62</v>
       </c>
       <c r="K59" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M59" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N59" t="n">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B60" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="C60" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="D60" t="n">
-        <v>34.9</v>
+        <v>46290</v>
       </c>
       <c r="E60" t="n">
-        <v>34.73</v>
-      </c>
-      <c r="H60" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J60" t="n">
-        <v>37</v>
+        <v>28.79</v>
       </c>
       <c r="K60" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="M60" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -5973,51 +5634,27 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B61" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="C61" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="D61" t="n">
-        <v>33.4</v>
+        <v>46291</v>
       </c>
       <c r="E61" t="n">
-        <v>26.47</v>
-      </c>
-      <c r="H61" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I61" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J61" t="n">
-        <v>35</v>
+        <v>27.23</v>
       </c>
       <c r="K61" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6026,51 +5663,27 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B62" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="C62" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="D62" t="n">
-        <v>33</v>
+        <v>46292</v>
       </c>
       <c r="E62" t="n">
-        <v>25.47</v>
-      </c>
-      <c r="H62" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I62" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>35</v>
+        <v>25.96</v>
       </c>
       <c r="K62" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6079,10 +5692,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
     </row>
   </sheetData>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
-      <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -695,15 +686,6 @@
       </c>
       <c r="AA2" t="n">
         <v>12</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.7</v>
       </c>
       <c r="AF2" t="n">
         <v>218.6</v>
@@ -767,15 +749,6 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -784,15 +757,6 @@
       </c>
       <c r="AA3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
         <v>218.84</v>
@@ -841,15 +805,6 @@
       <c r="T4" t="n">
         <v>19.9</v>
       </c>
-      <c r="V4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19</v>
-      </c>
       <c r="Y4" t="n">
         <v>14</v>
       </c>
@@ -858,15 +813,6 @@
       </c>
       <c r="AA4" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
         <v>221.78</v>
@@ -915,15 +861,6 @@
       <c r="T5" t="n">
         <v>19.9</v>
       </c>
-      <c r="V5" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
@@ -932,15 +869,6 @@
       </c>
       <c r="AA5" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
         <v>224.78</v>
@@ -1010,15 +938,6 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
-      <c r="V6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1027,15 +946,6 @@
       </c>
       <c r="AA6" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
         <v>232.22</v>
@@ -1105,15 +1015,6 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1122,15 +1023,6 @@
       </c>
       <c r="AA7" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>229.69</v>
@@ -1200,15 +1092,6 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>20</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1217,15 +1100,6 @@
       </c>
       <c r="AA8" t="n">
         <v>13</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
         <v>228.57</v>
@@ -1295,15 +1169,6 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
-      <c r="V9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1312,15 +1177,6 @@
       </c>
       <c r="AA9" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.6</v>
       </c>
       <c r="AF9" t="n">
         <v>225.08</v>
@@ -1390,15 +1246,6 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="V10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>27</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1407,15 +1254,6 @@
       </c>
       <c r="AA10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.3</v>
       </c>
       <c r="AK10" t="n">
         <v>134.62</v>
@@ -1458,15 +1296,6 @@
       <c r="T11" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>14</v>
-      </c>
       <c r="Y11" t="n">
         <v>5</v>
       </c>
@@ -1475,15 +1304,6 @@
       </c>
       <c r="AA11" t="n">
         <v>9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
         <v>221.37</v>
@@ -1532,15 +1352,6 @@
       <c r="T12" t="n">
         <v>19.9</v>
       </c>
-      <c r="V12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1549,15 +1360,6 @@
       </c>
       <c r="AA12" t="n">
         <v>10</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>224.37</v>
@@ -1606,15 +1408,6 @@
       <c r="T13" t="n">
         <v>19.9</v>
       </c>
-      <c r="V13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y13" t="n">
         <v>3</v>
       </c>
@@ -1623,15 +1416,6 @@
       </c>
       <c r="AA13" t="n">
         <v>9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-3.3</v>
       </c>
       <c r="AF13" t="n">
         <v>225.93</v>
@@ -1701,15 +1485,6 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1718,15 +1493,6 @@
       </c>
       <c r="AA14" t="n">
         <v>8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-5.1</v>
       </c>
       <c r="AF14" t="n">
         <v>218.63</v>
@@ -1796,15 +1562,6 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1813,15 +1570,6 @@
       </c>
       <c r="AA15" t="n">
         <v>9</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-1.4</v>
       </c>
       <c r="AF15" t="n">
         <v>216.39</v>
@@ -1903,15 +1651,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1920,15 +1659,6 @@
       </c>
       <c r="AA16" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>217.16</v>
@@ -1989,15 +1719,6 @@
       <c r="T17" t="n">
         <v>19.9</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2006,15 +1727,6 @@
       </c>
       <c r="AA17" t="n">
         <v>10</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF17" t="n">
         <v>220.31</v>
@@ -2075,15 +1787,6 @@
       <c r="T18" t="n">
         <v>19.9</v>
       </c>
-      <c r="V18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
@@ -2092,15 +1795,6 @@
       </c>
       <c r="AA18" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
         <v>221.99</v>
@@ -2161,15 +1855,6 @@
       <c r="T19" t="n">
         <v>19.9</v>
       </c>
-      <c r="V19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2178,15 +1863,6 @@
       </c>
       <c r="AA19" t="n">
         <v>14</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.9</v>
       </c>
       <c r="AF19" t="n">
         <v>225.14</v>
@@ -2247,15 +1923,6 @@
       <c r="T20" t="n">
         <v>19.9</v>
       </c>
-      <c r="V20" t="n">
-        <v>9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y20" t="n">
         <v>12</v>
       </c>
@@ -2264,15 +1931,6 @@
       </c>
       <c r="AA20" t="n">
         <v>15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-0.4</v>
       </c>
       <c r="AF20" t="n">
         <v>229.98</v>
@@ -2354,15 +2012,6 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
-      <c r="V21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2371,15 +2020,6 @@
       </c>
       <c r="AA21" t="n">
         <v>13</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-0.6</v>
       </c>
       <c r="AF21" t="n">
         <v>229.96</v>
@@ -2461,15 +2101,6 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2478,15 +2109,6 @@
       </c>
       <c r="AA22" t="n">
         <v>10</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.4</v>
       </c>
       <c r="AF22" t="n">
         <v>227.01</v>
@@ -2568,15 +2190,6 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2585,15 +2198,6 @@
       </c>
       <c r="AA23" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>6.5</v>
       </c>
       <c r="AF23" t="n">
         <v>228.35</v>
@@ -2675,15 +2279,6 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2692,15 +2287,6 @@
       </c>
       <c r="AA24" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>5.8</v>
       </c>
       <c r="AF24" t="n">
         <v>231.16</v>
@@ -2761,15 +2347,6 @@
       <c r="T25" t="n">
         <v>19.9</v>
       </c>
-      <c r="V25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2778,15 +2355,6 @@
       </c>
       <c r="AA25" t="n">
         <v>9</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.8</v>
       </c>
       <c r="AF25" t="n">
         <v>228.13</v>
@@ -2847,15 +2415,6 @@
       <c r="T26" t="n">
         <v>19.9</v>
       </c>
-      <c r="V26" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y26" t="n">
         <v>4</v>
       </c>
@@ -2864,15 +2423,6 @@
       </c>
       <c r="AA26" t="n">
         <v>9</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.16</v>
@@ -2954,15 +2504,6 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
-      <c r="V27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -2971,15 +2512,6 @@
       </c>
       <c r="AA27" t="n">
         <v>8.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.3</v>
       </c>
       <c r="AF27" t="n">
         <v>228.55</v>
@@ -3061,15 +2593,6 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
-      <c r="V28" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -3078,15 +2601,6 @@
       </c>
       <c r="AA28" t="n">
         <v>10</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.8</v>
       </c>
       <c r="AF28" t="n">
         <v>219.99</v>
@@ -3168,15 +2682,6 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3185,15 +2690,6 @@
       </c>
       <c r="AA29" t="n">
         <v>11</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>5.5</v>
       </c>
       <c r="AF29" t="n">
         <v>219.22</v>
@@ -3275,15 +2771,6 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
-      <c r="V30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3292,15 +2779,6 @@
       </c>
       <c r="AA30" t="n">
         <v>14</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
         <v>220.73</v>
@@ -3382,15 +2860,6 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3399,15 +2868,6 @@
       </c>
       <c r="AA31" t="n">
         <v>14</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>6.7</v>
       </c>
       <c r="AF31" t="n">
         <v>220.58</v>
@@ -3468,15 +2928,6 @@
       <c r="T32" t="n">
         <v>19.9</v>
       </c>
-      <c r="V32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
@@ -3485,15 +2936,6 @@
       </c>
       <c r="AA32" t="n">
         <v>13</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.5</v>
       </c>
       <c r="AF32" t="n">
         <v>223.43</v>
@@ -3554,15 +2996,6 @@
       <c r="T33" t="n">
         <v>19.9</v>
       </c>
-      <c r="V33" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
@@ -3571,15 +3004,6 @@
       </c>
       <c r="AA33" t="n">
         <v>13</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.4</v>
       </c>
       <c r="AF33" t="n">
         <v>229.48</v>
@@ -3661,15 +3085,6 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
-      <c r="V34" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X34" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3678,15 +3093,6 @@
       </c>
       <c r="AA34" t="n">
         <v>14</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4</v>
       </c>
       <c r="AF34" t="n">
         <v>241.48</v>
@@ -3768,15 +3174,6 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
-      <c r="V35" t="n">
-        <v>12</v>
-      </c>
-      <c r="W35" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X35" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3785,15 +3182,6 @@
       </c>
       <c r="AA35" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.9</v>
       </c>
       <c r="AF35" t="n">
         <v>238.69</v>
@@ -3875,15 +3263,6 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3892,15 +3271,6 @@
       </c>
       <c r="AA36" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
         <v>233.48</v>
@@ -3982,15 +3352,6 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
-      <c r="V37" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W37" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -3999,15 +3360,6 @@
       </c>
       <c r="AA37" t="n">
         <v>17</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.6</v>
       </c>
       <c r="AF37" t="n">
         <v>235.13</v>
@@ -4089,15 +3441,6 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
-      <c r="V38" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -4106,15 +3449,6 @@
       </c>
       <c r="AA38" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
         <v>234.87</v>
@@ -4175,15 +3509,6 @@
       <c r="T39" t="n">
         <v>19.9</v>
       </c>
-      <c r="V39" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y39" t="n">
         <v>7</v>
       </c>
@@ -4192,15 +3517,6 @@
       </c>
       <c r="AA39" t="n">
         <v>13</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.2</v>
       </c>
       <c r="AF39" t="n">
         <v>234.78</v>
@@ -4261,15 +3577,6 @@
       <c r="T40" t="n">
         <v>19.9</v>
       </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22</v>
-      </c>
-      <c r="X40" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
@@ -4278,15 +3585,6 @@
       </c>
       <c r="AA40" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.4</v>
       </c>
       <c r="AF40" t="n">
         <v>229.75</v>
@@ -4368,15 +3666,6 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
-      <c r="V41" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4385,15 +3674,6 @@
       </c>
       <c r="AA41" t="n">
         <v>6.5</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.5</v>
       </c>
       <c r="AF41" t="n">
         <v>222.86</v>
@@ -4475,15 +3755,6 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W42" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4492,15 +3763,6 @@
       </c>
       <c r="AA42" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
         <v>218.37</v>
@@ -4582,15 +3844,6 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>21</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4599,15 +3852,6 @@
       </c>
       <c r="AA43" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>3.9</v>
       </c>
       <c r="AF43" t="n">
         <v>220.85</v>
@@ -4689,15 +3933,6 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
-      <c r="V44" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4706,15 +3941,6 @@
       </c>
       <c r="AA44" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>6.3</v>
       </c>
       <c r="AK44" t="n">
         <v>130.73</v>
@@ -4790,15 +4016,6 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
-      <c r="V45" t="n">
-        <v>11</v>
-      </c>
-      <c r="W45" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X45" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4807,15 +4024,6 @@
       </c>
       <c r="AA45" t="n">
         <v>16.1</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>4.5</v>
       </c>
       <c r="AK45" t="n">
         <v>132</v>
@@ -4888,6 +4096,15 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
+      <c r="Y46" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>15.1</v>
+      </c>
       <c r="AK46" t="n">
         <v>132.25</v>
       </c>
@@ -5217,7 +4434,7 @@
         <v>46281</v>
       </c>
       <c r="B51" t="n">
-        <v>136.6</v>
+        <v>137.8</v>
       </c>
       <c r="C51" t="n">
         <v>64.59999999999999</v>
@@ -5288,7 +4505,7 @@
         <v>46282</v>
       </c>
       <c r="B52" t="n">
-        <v>127.5</v>
+        <v>128.3</v>
       </c>
       <c r="C52" t="n">
         <v>53.6</v>
@@ -5341,7 +4558,7 @@
         <v>46283</v>
       </c>
       <c r="B53" t="n">
-        <v>119.2</v>
+        <v>121.5</v>
       </c>
       <c r="C53" t="n">
         <v>45.9</v>
@@ -5394,7 +4611,7 @@
         <v>46284</v>
       </c>
       <c r="B54" t="n">
-        <v>106.9</v>
+        <v>106.5</v>
       </c>
       <c r="C54" t="n">
         <v>40.8</v>
@@ -5447,7 +4664,7 @@
         <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>100.3</v>
+        <v>101.8</v>
       </c>
       <c r="C55" t="n">
         <v>38.2</v>
@@ -5499,26 +4716,29 @@
       <c r="A56" s="1" t="n">
         <v>46286</v>
       </c>
+      <c r="B56" t="n">
+        <v>28.7</v>
+      </c>
       <c r="E56" t="n">
         <v>28.7</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46286</v>
@@ -5528,26 +4748,29 @@
       <c r="A57" s="1" t="n">
         <v>46287</v>
       </c>
+      <c r="B57" t="n">
+        <v>28.7</v>
+      </c>
       <c r="E57" t="n">
         <v>28.7</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
@@ -5557,26 +4780,29 @@
       <c r="A58" s="1" t="n">
         <v>46288</v>
       </c>
+      <c r="B58" t="n">
+        <v>28.7</v>
+      </c>
       <c r="E58" t="n">
         <v>28.7</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
@@ -5586,26 +4812,29 @@
       <c r="A59" s="1" t="n">
         <v>46289</v>
       </c>
+      <c r="B59" t="n">
+        <v>27.6</v>
+      </c>
       <c r="E59" t="n">
         <v>27.62</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
@@ -5615,26 +4844,29 @@
       <c r="A60" s="1" t="n">
         <v>46290</v>
       </c>
+      <c r="B60" t="n">
+        <v>28.8</v>
+      </c>
       <c r="E60" t="n">
         <v>28.79</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46290</v>
@@ -5644,26 +4876,29 @@
       <c r="A61" s="1" t="n">
         <v>46291</v>
       </c>
+      <c r="B61" t="n">
+        <v>27.2</v>
+      </c>
       <c r="E61" t="n">
         <v>27.23</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46291</v>
@@ -5673,26 +4908,29 @@
       <c r="A62" s="1" t="n">
         <v>46292</v>
       </c>
+      <c r="B62" t="n">
+        <v>26</v>
+      </c>
       <c r="E62" t="n">
         <v>25.96</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
+      <c r="V2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -686,6 +695,15 @@
       </c>
       <c r="AA2" t="n">
         <v>12</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AF2" t="n">
         <v>218.6</v>
@@ -749,6 +767,15 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
+      <c r="V3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -757,6 +784,15 @@
       </c>
       <c r="AA3" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
         <v>218.84</v>
@@ -788,22 +824,31 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="O4" t="n">
-        <v>36.8</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>0.6</v>
       </c>
       <c r="T4" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>14</v>
@@ -813,6 +858,15 @@
       </c>
       <c r="AA4" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
         <v>221.78</v>
@@ -844,22 +898,31 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="O5" t="n">
-        <v>35.1</v>
+        <v>34.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>0.6</v>
       </c>
       <c r="T5" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y5" t="n">
         <v>14</v>
@@ -869,6 +932,15 @@
       </c>
       <c r="AA5" t="n">
         <v>16.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
         <v>224.78</v>
@@ -938,6 +1010,15 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
+      <c r="V6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -946,6 +1027,15 @@
       </c>
       <c r="AA6" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
         <v>232.22</v>
@@ -1015,6 +1105,15 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1023,6 +1122,15 @@
       </c>
       <c r="AA7" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>229.69</v>
@@ -1092,6 +1200,15 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
+      <c r="V8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1100,6 +1217,15 @@
       </c>
       <c r="AA8" t="n">
         <v>13</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
         <v>228.57</v>
@@ -1169,6 +1295,15 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
+      <c r="V9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1177,6 +1312,15 @@
       </c>
       <c r="AA9" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6</v>
       </c>
       <c r="AF9" t="n">
         <v>225.08</v>
@@ -1246,6 +1390,15 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
+      <c r="V10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1254,6 +1407,15 @@
       </c>
       <c r="AA10" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AK10" t="n">
         <v>134.62</v>
@@ -1279,22 +1441,31 @@
         <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>87.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="O11" t="n">
-        <v>41.2</v>
+        <v>40.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>0.6</v>
       </c>
       <c r="T11" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
         <v>5</v>
@@ -1304,6 +1475,15 @@
       </c>
       <c r="AA11" t="n">
         <v>9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
         <v>221.37</v>
@@ -1335,22 +1515,31 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>83.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="O12" t="n">
-        <v>39.2</v>
+        <v>38.4</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>0.6</v>
       </c>
       <c r="T12" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
@@ -1360,6 +1549,15 @@
       </c>
       <c r="AA12" t="n">
         <v>10</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>224.37</v>
@@ -1391,22 +1589,31 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>84.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>39.6</v>
+        <v>38.8</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>0.6</v>
       </c>
       <c r="T13" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y13" t="n">
         <v>3</v>
@@ -1416,6 +1623,15 @@
       </c>
       <c r="AA13" t="n">
         <v>9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF13" t="n">
         <v>225.93</v>
@@ -1485,6 +1701,15 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
+      <c r="V14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1493,6 +1718,15 @@
       </c>
       <c r="AA14" t="n">
         <v>8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-5.1</v>
       </c>
       <c r="AF14" t="n">
         <v>218.63</v>
@@ -1562,6 +1796,15 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1570,6 +1813,15 @@
       </c>
       <c r="AA15" t="n">
         <v>9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF15" t="n">
         <v>216.39</v>
@@ -1651,6 +1903,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1659,6 +1920,15 @@
       </c>
       <c r="AA16" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>217.16</v>
@@ -1702,22 +1972,31 @@
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>96.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>45.1</v>
+        <v>44.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>0.6</v>
       </c>
       <c r="T17" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y17" t="n">
         <v>8</v>
@@ -1727,6 +2006,15 @@
       </c>
       <c r="AA17" t="n">
         <v>10</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF17" t="n">
         <v>220.31</v>
@@ -1770,22 +2058,31 @@
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>90.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="O18" t="n">
-        <v>42.6</v>
+        <v>41.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>0.6</v>
       </c>
       <c r="T18" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y18" t="n">
         <v>10</v>
@@ -1795,6 +2092,15 @@
       </c>
       <c r="AA18" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
         <v>221.99</v>
@@ -1838,22 +2144,31 @@
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>80.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="O19" t="n">
-        <v>38</v>
+        <v>37.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>0.6</v>
       </c>
       <c r="T19" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -1863,6 +2178,15 @@
       </c>
       <c r="AA19" t="n">
         <v>14</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF19" t="n">
         <v>225.14</v>
@@ -1906,22 +2230,31 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
       <c r="O20" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>0.6</v>
       </c>
       <c r="T20" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -1931,6 +2264,15 @@
       </c>
       <c r="AA20" t="n">
         <v>15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF20" t="n">
         <v>229.98</v>
@@ -2012,6 +2354,15 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
+      <c r="V21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2020,6 +2371,15 @@
       </c>
       <c r="AA21" t="n">
         <v>13</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AF21" t="n">
         <v>229.96</v>
@@ -2101,6 +2461,15 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2109,6 +2478,15 @@
       </c>
       <c r="AA22" t="n">
         <v>10</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF22" t="n">
         <v>227.01</v>
@@ -2190,6 +2568,15 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2198,6 +2585,15 @@
       </c>
       <c r="AA23" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF23" t="n">
         <v>228.35</v>
@@ -2279,6 +2675,15 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2287,6 +2692,15 @@
       </c>
       <c r="AA24" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF24" t="n">
         <v>231.16</v>
@@ -2330,22 +2744,31 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="O25" t="n">
-        <v>41.4</v>
+        <v>40.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
         <v>0.6</v>
       </c>
       <c r="T25" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
         <v>6</v>
@@ -2355,6 +2778,15 @@
       </c>
       <c r="AA25" t="n">
         <v>9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF25" t="n">
         <v>228.13</v>
@@ -2398,22 +2830,31 @@
         <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="O26" t="n">
-        <v>38.8</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>0.6</v>
       </c>
       <c r="T26" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y26" t="n">
         <v>4</v>
@@ -2423,6 +2864,15 @@
       </c>
       <c r="AA26" t="n">
         <v>9</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.16</v>
@@ -2504,6 +2954,15 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
+      <c r="V27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -2512,6 +2971,15 @@
       </c>
       <c r="AA27" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF27" t="n">
         <v>228.55</v>
@@ -2593,6 +3061,15 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
+      <c r="V28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -2601,6 +3078,15 @@
       </c>
       <c r="AA28" t="n">
         <v>10</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF28" t="n">
         <v>219.99</v>
@@ -2682,6 +3168,15 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -2690,6 +3185,15 @@
       </c>
       <c r="AA29" t="n">
         <v>11</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF29" t="n">
         <v>219.22</v>
@@ -2771,6 +3275,15 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
+      <c r="V30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -2779,6 +3292,15 @@
       </c>
       <c r="AA30" t="n">
         <v>14</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
         <v>220.73</v>
@@ -2860,6 +3382,15 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -2868,6 +3399,15 @@
       </c>
       <c r="AA31" t="n">
         <v>14</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF31" t="n">
         <v>220.58</v>
@@ -2911,22 +3451,31 @@
         <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>37</v>
+        <v>36.2</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
         <v>0.6</v>
       </c>
       <c r="T32" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y32" t="n">
         <v>9</v>
@@ -2936,6 +3485,15 @@
       </c>
       <c r="AA32" t="n">
         <v>13</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF32" t="n">
         <v>223.43</v>
@@ -2979,22 +3537,31 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>33.2</v>
+        <v>32.5</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
         <v>0.6</v>
       </c>
       <c r="T33" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V33" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
@@ -3004,6 +3571,15 @@
       </c>
       <c r="AA33" t="n">
         <v>13</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF33" t="n">
         <v>229.48</v>
@@ -3085,6 +3661,15 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
+      <c r="V34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3093,6 +3678,15 @@
       </c>
       <c r="AA34" t="n">
         <v>14</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4</v>
       </c>
       <c r="AF34" t="n">
         <v>241.48</v>
@@ -3174,6 +3768,15 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3182,6 +3785,15 @@
       </c>
       <c r="AA35" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF35" t="n">
         <v>238.69</v>
@@ -3263,6 +3875,15 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3271,6 +3892,15 @@
       </c>
       <c r="AA36" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
         <v>233.48</v>
@@ -3352,6 +3982,15 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
+      <c r="V37" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -3360,6 +3999,15 @@
       </c>
       <c r="AA37" t="n">
         <v>17</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF37" t="n">
         <v>235.13</v>
@@ -3441,6 +4089,15 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
+      <c r="V38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -3449,6 +4106,15 @@
       </c>
       <c r="AA38" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
         <v>234.87</v>
@@ -3492,22 +4158,31 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="O39" t="n">
-        <v>35.1</v>
+        <v>34.3</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
         <v>0.6</v>
       </c>
       <c r="T39" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y39" t="n">
         <v>7</v>
@@ -3517,6 +4192,15 @@
       </c>
       <c r="AA39" t="n">
         <v>13</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.2</v>
       </c>
       <c r="AF39" t="n">
         <v>234.78</v>
@@ -3560,22 +4244,31 @@
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>78.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>36.6</v>
+        <v>35.9</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
         <v>0.6</v>
       </c>
       <c r="T40" t="n">
-        <v>19.9</v>
+        <v>21</v>
+      </c>
+      <c r="V40" t="n">
+        <v>11</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22</v>
+      </c>
+      <c r="X40" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y40" t="n">
         <v>7</v>
@@ -3585,6 +4278,15 @@
       </c>
       <c r="AA40" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF40" t="n">
         <v>229.75</v>
@@ -3666,6 +4368,15 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
+      <c r="V41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -3674,6 +4385,15 @@
       </c>
       <c r="AA41" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF41" t="n">
         <v>222.86</v>
@@ -3755,6 +4475,15 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -3763,6 +4492,15 @@
       </c>
       <c r="AA42" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
         <v>218.37</v>
@@ -3844,6 +4582,15 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>21</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -3852,6 +4599,15 @@
       </c>
       <c r="AA43" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF43" t="n">
         <v>220.85</v>
@@ -3933,6 +4689,15 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
+      <c r="V44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W44" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -3941,6 +4706,15 @@
       </c>
       <c r="AA44" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>6.3</v>
       </c>
       <c r="AK44" t="n">
         <v>130.73</v>
@@ -4016,6 +4790,15 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
+      <c r="V45" t="n">
+        <v>11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4024,6 +4807,15 @@
       </c>
       <c r="AA45" t="n">
         <v>16.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>4.5</v>
       </c>
       <c r="AK45" t="n">
         <v>132</v>
@@ -4096,6 +4888,15 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X46" t="n">
+        <v>18</v>
+      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -4104,6 +4905,15 @@
       </c>
       <c r="AA46" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AK46" t="n">
         <v>132.25</v>
@@ -4434,49 +5244,55 @@
         <v>46281</v>
       </c>
       <c r="B51" t="n">
-        <v>137.8</v>
+        <v>133.5</v>
       </c>
       <c r="C51" t="n">
-        <v>64.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="D51" t="n">
-        <v>34.7</v>
+        <v>33.9</v>
       </c>
       <c r="E51" t="n">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.2</v>
       </c>
       <c r="H51" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="I51" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J51" t="n">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="K51" t="n">
-        <v>75.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="N51" t="n">
-        <v>28</v>
+        <v>28.6</v>
       </c>
       <c r="O51" t="n">
-        <v>33.1</v>
+        <v>34.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>11.6</v>
       </c>
       <c r="AK51" t="n">
         <v>129.71</v>
@@ -4505,28 +5321,28 @@
         <v>46282</v>
       </c>
       <c r="B52" t="n">
-        <v>128.3</v>
+        <v>130.2</v>
       </c>
       <c r="C52" t="n">
-        <v>53.6</v>
+        <v>55.3</v>
       </c>
       <c r="D52" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="E52" t="n">
         <v>34.83</v>
       </c>
       <c r="H52" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="I52" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="J52" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="K52" t="n">
-        <v>74.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="M52" t="n">
         <v>3.6</v>
@@ -4538,7 +5354,7 @@
         <v>32.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R52" t="n">
         <v>1.5</v>
@@ -4547,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BL52" s="1" t="n">
         <v>46282</v>
@@ -4558,28 +5374,28 @@
         <v>46283</v>
       </c>
       <c r="B53" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="C53" t="n">
-        <v>45.9</v>
+        <v>47.1</v>
       </c>
       <c r="D53" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="E53" t="n">
         <v>34.73</v>
       </c>
       <c r="H53" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="I53" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="J53" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K53" t="n">
-        <v>71.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="M53" t="n">
         <v>2.1</v>
@@ -4591,7 +5407,7 @@
         <v>31.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -4600,7 +5416,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BL53" s="1" t="n">
         <v>46283</v>
@@ -4611,40 +5427,40 @@
         <v>46284</v>
       </c>
       <c r="B54" t="n">
-        <v>106.5</v>
+        <v>105.8</v>
       </c>
       <c r="C54" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="D54" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="E54" t="n">
         <v>26.47</v>
       </c>
       <c r="H54" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="I54" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="J54" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K54" t="n">
-        <v>69.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="M54" t="n">
         <v>2.1</v>
       </c>
       <c r="N54" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O54" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4653,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46284</v>
@@ -4664,40 +5480,40 @@
         <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>101.8</v>
+        <v>100.1</v>
       </c>
       <c r="C55" t="n">
-        <v>38.2</v>
+        <v>36.3</v>
       </c>
       <c r="D55" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="E55" t="n">
         <v>25.47</v>
       </c>
       <c r="H55" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="I55" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="J55" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>69.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="M55" t="n">
         <v>2.1</v>
       </c>
       <c r="N55" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O55" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4706,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46285</v>
@@ -4723,22 +5539,22 @@
         <v>28.7</v>
       </c>
       <c r="K56" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O56" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
         <v>2</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.9</v>
       </c>
       <c r="S56" t="n">
         <v>0.6</v>
       </c>
       <c r="T56" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46286</v>
@@ -4755,22 +5571,22 @@
         <v>28.7</v>
       </c>
       <c r="K57" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
         <v>2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.9</v>
       </c>
       <c r="S57" t="n">
         <v>0.6</v>
       </c>
       <c r="T57" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
@@ -4787,22 +5603,22 @@
         <v>28.7</v>
       </c>
       <c r="K58" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
         <v>2</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.9</v>
       </c>
       <c r="S58" t="n">
         <v>0.6</v>
       </c>
       <c r="T58" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
@@ -4819,22 +5635,22 @@
         <v>27.62</v>
       </c>
       <c r="K59" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O59" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
         <v>0.6</v>
       </c>
       <c r="T59" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
@@ -4851,22 +5667,22 @@
         <v>28.79</v>
       </c>
       <c r="K60" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="O60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
         <v>2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.9</v>
       </c>
       <c r="S60" t="n">
         <v>0.6</v>
       </c>
       <c r="T60" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46290</v>
@@ -4883,22 +5699,22 @@
         <v>27.23</v>
       </c>
       <c r="K61" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S61" t="n">
         <v>0.6</v>
       </c>
       <c r="T61" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46291</v>
@@ -4915,22 +5731,22 @@
         <v>25.96</v>
       </c>
       <c r="K62" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O62" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
         <v>0.6</v>
       </c>
       <c r="T62" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
-      <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -767,15 +758,6 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -824,31 +806,22 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>78</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>36</v>
+        <v>36.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>21</v>
-      </c>
-      <c r="V4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y4" t="n">
         <v>14</v>
@@ -898,30 +871,21 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>74.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>34.4</v>
+        <v>34.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>21</v>
-      </c>
-      <c r="V5" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X5" t="n">
         <v>19.8</v>
       </c>
       <c r="Y5" t="n">
@@ -1010,15 +974,6 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
-      <c r="V6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1105,15 +1060,6 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1200,15 +1146,6 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>20</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1295,15 +1232,6 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
-      <c r="V9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1390,15 +1318,6 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="V10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>27</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1441,31 +1360,22 @@
         <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>87.5</v>
+        <v>89.7</v>
       </c>
       <c r="O11" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>21</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>14</v>
+        <v>19.8</v>
       </c>
       <c r="Y11" t="n">
         <v>5</v>
@@ -1515,31 +1425,22 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>83.2</v>
+        <v>85.3</v>
       </c>
       <c r="O12" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>21</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.1</v>
+        <v>19.8</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
@@ -1589,31 +1490,22 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>83.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>21</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.6</v>
+        <v>19.8</v>
       </c>
       <c r="Y13" t="n">
         <v>3</v>
@@ -1701,15 +1593,6 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1796,15 +1679,6 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1903,15 +1777,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1972,31 +1837,22 @@
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>95.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>21</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>11.8</v>
+        <v>19.8</v>
       </c>
       <c r="Y17" t="n">
         <v>8</v>
@@ -2058,31 +1914,22 @@
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>90.5</v>
+        <v>92.7</v>
       </c>
       <c r="O18" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>21</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.4</v>
+        <v>19.8</v>
       </c>
       <c r="Y18" t="n">
         <v>10</v>
@@ -2144,31 +1991,22 @@
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>80.5</v>
+        <v>82.7</v>
       </c>
       <c r="O19" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>21</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13.6</v>
+        <v>19.8</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -2230,31 +2068,22 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>73.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>21</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>11.4</v>
+        <v>19.8</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -2354,15 +2183,6 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
-      <c r="V21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2461,15 +2281,6 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2568,15 +2379,6 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2675,15 +2477,6 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2744,31 +2537,22 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>88</v>
+        <v>90.2</v>
       </c>
       <c r="O25" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>21</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y25" t="n">
         <v>6</v>
@@ -2830,31 +2614,22 @@
         <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>82.3</v>
+        <v>84.5</v>
       </c>
       <c r="O26" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>21</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>14.2</v>
+        <v>19.8</v>
       </c>
       <c r="Y26" t="n">
         <v>4</v>
@@ -2954,15 +2729,6 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
-      <c r="V27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -3061,15 +2827,6 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
-      <c r="V28" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -3168,15 +2925,6 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3275,15 +3023,6 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
-      <c r="V30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3382,15 +3121,6 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3451,31 +3181,22 @@
         <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>78.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="O32" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>21</v>
-      </c>
-      <c r="V32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="Y32" t="n">
         <v>9</v>
@@ -3537,31 +3258,22 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>70.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="O33" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>21</v>
-      </c>
-      <c r="V33" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>17.4</v>
+        <v>19.8</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
@@ -3661,15 +3373,6 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
-      <c r="V34" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X34" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3768,15 +3471,6 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
-      <c r="V35" t="n">
-        <v>12</v>
-      </c>
-      <c r="W35" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X35" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3875,15 +3569,6 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3982,15 +3667,6 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
-      <c r="V37" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W37" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -4089,15 +3765,6 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
-      <c r="V38" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -4158,31 +3825,22 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>74.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>21</v>
-      </c>
-      <c r="V39" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>17.4</v>
+        <v>19.8</v>
       </c>
       <c r="Y39" t="n">
         <v>7</v>
@@ -4244,31 +3902,22 @@
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>77.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="O40" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>21</v>
-      </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22</v>
-      </c>
-      <c r="X40" t="n">
-        <v>16.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y40" t="n">
         <v>7</v>
@@ -4368,15 +4017,6 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
-      <c r="V41" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4475,15 +4115,6 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W42" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4582,15 +4213,6 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>21</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4689,15 +4311,6 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
-      <c r="V44" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4790,15 +4403,6 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
-      <c r="V45" t="n">
-        <v>11</v>
-      </c>
-      <c r="W45" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X45" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4888,15 +4492,6 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W46" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X46" t="n">
-        <v>18</v>
-      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -4986,6 +4581,24 @@
       <c r="T47" t="n">
         <v>23.6</v>
       </c>
+      <c r="Y47" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AK47" t="n">
         <v>128.6</v>
       </c>
@@ -5321,52 +4934,76 @@
         <v>46282</v>
       </c>
       <c r="B52" t="n">
-        <v>130.2</v>
+        <v>120.6</v>
       </c>
       <c r="C52" t="n">
-        <v>55.3</v>
+        <v>47.7</v>
       </c>
       <c r="D52" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="E52" t="n">
-        <v>34.83</v>
+        <v>24.1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.5</v>
       </c>
       <c r="H52" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="I52" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>39.5</v>
+        <v>38.4</v>
       </c>
       <c r="K52" t="n">
-        <v>74.5</v>
+        <v>73.2</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>28.5</v>
+        <v>30.3</v>
       </c>
       <c r="O52" t="n">
-        <v>32.1</v>
+        <v>33.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>23</v>
+        <v>23.3</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>133.39</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>3.68</v>
       </c>
       <c r="BL52" s="1" t="n">
         <v>46282</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5374,40 +5011,40 @@
         <v>46283</v>
       </c>
       <c r="B53" t="n">
-        <v>122.5</v>
+        <v>121.2</v>
       </c>
       <c r="C53" t="n">
-        <v>47.1</v>
+        <v>45.4</v>
       </c>
       <c r="D53" t="n">
-        <v>34.7</v>
+        <v>35.3</v>
       </c>
       <c r="E53" t="n">
         <v>34.73</v>
       </c>
       <c r="H53" t="n">
-        <v>25.1</v>
+        <v>22.3</v>
       </c>
       <c r="I53" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>38</v>
       </c>
       <c r="K53" t="n">
-        <v>73</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M53" t="n">
         <v>2.1</v>
       </c>
       <c r="N53" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="O53" t="n">
-        <v>31.1</v>
+        <v>30.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5416,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BL53" s="1" t="n">
         <v>46283</v>
@@ -5427,40 +5064,40 @@
         <v>46284</v>
       </c>
       <c r="B54" t="n">
-        <v>105.8</v>
+        <v>103</v>
       </c>
       <c r="C54" t="n">
-        <v>40.3</v>
+        <v>36.8</v>
       </c>
       <c r="D54" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="E54" t="n">
         <v>26.47</v>
       </c>
       <c r="H54" t="n">
-        <v>25.1</v>
+        <v>21.7</v>
       </c>
       <c r="I54" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K54" t="n">
-        <v>72</v>
+        <v>65.5</v>
       </c>
       <c r="M54" t="n">
         <v>2.1</v>
       </c>
       <c r="N54" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O54" t="n">
-        <v>31.1</v>
+        <v>29.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5469,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46284</v>
@@ -5480,40 +5117,40 @@
         <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>100.1</v>
+        <v>101.3</v>
       </c>
       <c r="C55" t="n">
-        <v>36.3</v>
+        <v>36.8</v>
       </c>
       <c r="D55" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="E55" t="n">
         <v>25.47</v>
       </c>
       <c r="H55" t="n">
-        <v>25.1</v>
+        <v>21.7</v>
       </c>
       <c r="I55" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>72</v>
+        <v>65.5</v>
       </c>
       <c r="M55" t="n">
         <v>2.1</v>
       </c>
       <c r="N55" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>31.1</v>
+        <v>29.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5522,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46285</v>
@@ -5533,28 +5170,49 @@
         <v>46286</v>
       </c>
       <c r="B56" t="n">
-        <v>28.7</v>
+        <v>118.7</v>
+      </c>
+      <c r="C56" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>35.3</v>
       </c>
       <c r="E56" t="n">
         <v>28.7</v>
       </c>
+      <c r="H56" t="n">
+        <v>23</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>38</v>
+      </c>
       <c r="K56" t="n">
-        <v>3.5</v>
+        <v>70.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>28</v>
       </c>
       <c r="O56" t="n">
-        <v>1.6</v>
+        <v>30.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46286</v>
@@ -5571,22 +5229,22 @@
         <v>28.7</v>
       </c>
       <c r="K57" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="O57" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S57" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
@@ -5603,22 +5261,22 @@
         <v>28.7</v>
       </c>
       <c r="K58" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S58" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
@@ -5635,22 +5293,22 @@
         <v>27.62</v>
       </c>
       <c r="K59" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="O59" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S59" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
@@ -5667,22 +5325,22 @@
         <v>28.79</v>
       </c>
       <c r="K60" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="O60" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S60" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46290</v>
@@ -5699,22 +5357,22 @@
         <v>27.23</v>
       </c>
       <c r="K61" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="O61" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46291</v>
@@ -5731,22 +5389,22 @@
         <v>25.96</v>
       </c>
       <c r="K62" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="S62" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
+      <c r="V2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -758,6 +767,15 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
+      <c r="V3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -823,6 +841,15 @@
       <c r="T4" t="n">
         <v>19.8</v>
       </c>
+      <c r="V4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>19</v>
+      </c>
       <c r="Y4" t="n">
         <v>14</v>
       </c>
@@ -888,6 +915,15 @@
       <c r="T5" t="n">
         <v>19.8</v>
       </c>
+      <c r="V5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
@@ -974,6 +1010,15 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
+      <c r="V6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1060,6 +1105,15 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1146,6 +1200,15 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
+      <c r="V8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1232,6 +1295,15 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
+      <c r="V9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1318,6 +1390,15 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
+      <c r="V10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1377,6 +1458,15 @@
       <c r="T11" t="n">
         <v>19.8</v>
       </c>
+      <c r="V11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
+      </c>
       <c r="Y11" t="n">
         <v>5</v>
       </c>
@@ -1442,6 +1532,15 @@
       <c r="T12" t="n">
         <v>19.8</v>
       </c>
+      <c r="V12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1507,6 +1606,15 @@
       <c r="T13" t="n">
         <v>19.8</v>
       </c>
+      <c r="V13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y13" t="n">
         <v>3</v>
       </c>
@@ -1593,6 +1701,15 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
+      <c r="V14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1679,6 +1796,15 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1777,6 +1903,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1854,6 +1989,15 @@
       <c r="T17" t="n">
         <v>19.8</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1931,6 +2075,15 @@
       <c r="T18" t="n">
         <v>19.8</v>
       </c>
+      <c r="V18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
@@ -2008,6 +2161,15 @@
       <c r="T19" t="n">
         <v>19.8</v>
       </c>
+      <c r="V19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2085,6 +2247,15 @@
       <c r="T20" t="n">
         <v>19.8</v>
       </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y20" t="n">
         <v>12</v>
       </c>
@@ -2183,6 +2354,15 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
+      <c r="V21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2281,6 +2461,15 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2379,6 +2568,15 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2477,6 +2675,15 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2554,6 +2761,15 @@
       <c r="T25" t="n">
         <v>19.8</v>
       </c>
+      <c r="V25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2631,6 +2847,15 @@
       <c r="T26" t="n">
         <v>19.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y26" t="n">
         <v>4</v>
       </c>
@@ -2729,6 +2954,15 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
+      <c r="V27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -2827,6 +3061,15 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
+      <c r="V28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -2925,6 +3168,15 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3023,6 +3275,15 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
+      <c r="V30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3121,6 +3382,15 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3198,6 +3468,15 @@
       <c r="T32" t="n">
         <v>19.8</v>
       </c>
+      <c r="V32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
@@ -3275,6 +3554,15 @@
       <c r="T33" t="n">
         <v>19.8</v>
       </c>
+      <c r="V33" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
@@ -3373,6 +3661,15 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
+      <c r="V34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3471,6 +3768,15 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3569,6 +3875,15 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3667,6 +3982,15 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
+      <c r="V37" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -3765,6 +4089,15 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
+      <c r="V38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -3842,6 +4175,15 @@
       <c r="T39" t="n">
         <v>19.8</v>
       </c>
+      <c r="V39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y39" t="n">
         <v>7</v>
       </c>
@@ -3919,6 +4261,15 @@
       <c r="T40" t="n">
         <v>19.8</v>
       </c>
+      <c r="V40" t="n">
+        <v>11</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22</v>
+      </c>
+      <c r="X40" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
@@ -4017,6 +4368,15 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
+      <c r="V41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4115,6 +4475,15 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4213,6 +4582,15 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>21</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4311,6 +4689,15 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
+      <c r="V44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W44" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4403,6 +4790,15 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
+      <c r="V45" t="n">
+        <v>11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4492,6 +4888,15 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X46" t="n">
+        <v>18</v>
+      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -4581,6 +4986,15 @@
       <c r="T47" t="n">
         <v>23.6</v>
       </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>7.7</v>
       </c>
@@ -4673,8 +5087,32 @@
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
+      <c r="V48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>11</v>
+      </c>
+      <c r="X48" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>11.2</v>
+      </c>
       <c r="AA48" t="n">
         <v>7.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>5.7</v>
       </c>
       <c r="AK48" t="n">
         <v>127.19</v>
@@ -5054,6 +5492,12 @@
       </c>
       <c r="T53" t="n">
         <v>20</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>137.14</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>3.75</v>
       </c>
       <c r="BL53" s="1" t="n">
         <v>46283</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5188,8 +5188,32 @@
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
+      <c r="V49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X49" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>13.6</v>
+      </c>
       <c r="AA49" t="n">
         <v>12</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.8</v>
       </c>
       <c r="AK49" t="n">
         <v>129.17</v>
@@ -5551,6 +5575,12 @@
       </c>
       <c r="T54" t="n">
         <v>15</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.37</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46284</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5526,6 +5526,18 @@
       <c r="BL53" s="1" t="n">
         <v>46283</v>
       </c>
+      <c r="BM53" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5585,6 +5597,18 @@
       <c r="BL54" s="1" t="n">
         <v>46284</v>
       </c>
+      <c r="BM54" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5637,6 +5661,18 @@
       </c>
       <c r="BL55" s="1" t="n">
         <v>46285</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -824,22 +824,22 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>80.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="O4" t="n">
-        <v>36.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V4" t="n">
         <v>13.6</v>
@@ -898,22 +898,22 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>76.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="O5" t="n">
-        <v>34.7</v>
+        <v>35.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V5" t="n">
         <v>14.8</v>
@@ -1441,22 +1441,22 @@
         <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>89.7</v>
+        <v>91.5</v>
       </c>
       <c r="O11" t="n">
-        <v>40.6</v>
+        <v>41.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V11" t="n">
         <v>8.699999999999999</v>
@@ -1515,22 +1515,22 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>85.3</v>
+        <v>87.2</v>
       </c>
       <c r="O12" t="n">
-        <v>38.7</v>
+        <v>39.8</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V12" t="n">
         <v>7.1</v>
@@ -1589,22 +1589,22 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>86.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="O13" t="n">
-        <v>39</v>
+        <v>40.1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V13" t="n">
         <v>4.9</v>
@@ -1972,22 +1972,22 @@
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>44.5</v>
+        <v>45.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V17" t="n">
         <v>6.3</v>
@@ -2058,22 +2058,22 @@
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>92.7</v>
+        <v>94.5</v>
       </c>
       <c r="O18" t="n">
-        <v>42</v>
+        <v>43.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V18" t="n">
         <v>8.9</v>
@@ -2144,22 +2144,22 @@
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>82.7</v>
+        <v>84.5</v>
       </c>
       <c r="O19" t="n">
-        <v>37.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V19" t="n">
         <v>9.5</v>
@@ -2230,22 +2230,22 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>75.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="O20" t="n">
-        <v>34.4</v>
+        <v>35.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V20" t="n">
         <v>9</v>
@@ -2744,22 +2744,22 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>90.2</v>
+        <v>92</v>
       </c>
       <c r="O25" t="n">
-        <v>40.8</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V25" t="n">
         <v>9.5</v>
@@ -2830,22 +2830,22 @@
         <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>84.5</v>
+        <v>86.3</v>
       </c>
       <c r="O26" t="n">
-        <v>38.2</v>
+        <v>39.4</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V26" t="n">
         <v>10.7</v>
@@ -3451,22 +3451,22 @@
         <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>80.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V32" t="n">
         <v>15.5</v>
@@ -3537,22 +3537,22 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>72.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>32.8</v>
+        <v>33.9</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V33" t="n">
         <v>12.6</v>
@@ -4158,22 +4158,22 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>76.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="O39" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V39" t="n">
         <v>11.6</v>
@@ -4244,22 +4244,22 @@
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>79.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>36.1</v>
+        <v>37.3</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="V40" t="n">
         <v>11</v>
@@ -5289,8 +5289,32 @@
       <c r="T50" t="n">
         <v>22.1</v>
       </c>
+      <c r="V50" t="n">
+        <v>4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>20.2</v>
+      </c>
       <c r="AA50" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>6.7</v>
       </c>
       <c r="AK50" t="n">
         <v>130.42</v>
@@ -5615,40 +5639,43 @@
         <v>46285</v>
       </c>
       <c r="B55" t="n">
-        <v>101.3</v>
+        <v>93.2</v>
       </c>
       <c r="C55" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="D55" t="n">
-        <v>34</v>
+        <v>32.7</v>
       </c>
       <c r="E55" t="n">
-        <v>25.47</v>
+        <v>17</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.6</v>
       </c>
       <c r="H55" t="n">
-        <v>21.7</v>
+        <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J55" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>65.5</v>
+        <v>51.2</v>
       </c>
       <c r="M55" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="N55" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="O55" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5657,7 +5684,16 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>15</v>
+        <v>10.5</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>138.98</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.47</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46285</v>
@@ -5680,28 +5716,28 @@
         <v>46286</v>
       </c>
       <c r="B56" t="n">
-        <v>118.7</v>
+        <v>120.4</v>
       </c>
       <c r="C56" t="n">
-        <v>49.1</v>
+        <v>51.3</v>
       </c>
       <c r="D56" t="n">
-        <v>35.3</v>
+        <v>34.9</v>
       </c>
       <c r="E56" t="n">
         <v>28.7</v>
       </c>
       <c r="H56" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I56" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="J56" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>70.5</v>
+        <v>63.1</v>
       </c>
       <c r="M56" t="n">
         <v>2.1</v>
@@ -5713,7 +5749,7 @@
         <v>30.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5722,10 +5758,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46286</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5733,28 +5781,49 @@
         <v>46287</v>
       </c>
       <c r="B57" t="n">
-        <v>28.7</v>
+        <v>126</v>
+      </c>
+      <c r="C57" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35.3</v>
       </c>
       <c r="E57" t="n">
         <v>28.7</v>
       </c>
+      <c r="H57" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>36</v>
+      </c>
       <c r="K57" t="n">
-        <v>5.2</v>
+        <v>67.3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>28.5</v>
       </c>
       <c r="O57" t="n">
-        <v>2.3</v>
+        <v>30.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
@@ -5765,28 +5834,49 @@
         <v>46288</v>
       </c>
       <c r="B58" t="n">
-        <v>28.7</v>
+        <v>120</v>
+      </c>
+      <c r="C58" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>34.9</v>
       </c>
       <c r="E58" t="n">
         <v>28.7</v>
       </c>
+      <c r="H58" t="n">
+        <v>22</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>37</v>
+      </c>
       <c r="K58" t="n">
-        <v>5.2</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>28.5</v>
       </c>
       <c r="O58" t="n">
-        <v>2.3</v>
+        <v>30.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R58" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
@@ -5797,28 +5887,49 @@
         <v>46289</v>
       </c>
       <c r="B59" t="n">
-        <v>27.6</v>
+        <v>110.7</v>
+      </c>
+      <c r="C59" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>34.9</v>
       </c>
       <c r="E59" t="n">
         <v>27.62</v>
       </c>
+      <c r="H59" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>37</v>
+      </c>
       <c r="K59" t="n">
-        <v>4.4</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>28.5</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>30.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R59" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
@@ -5829,28 +5940,49 @@
         <v>46290</v>
       </c>
       <c r="B60" t="n">
-        <v>28.8</v>
+        <v>110.3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>34.7</v>
       </c>
       <c r="E60" t="n">
         <v>28.79</v>
       </c>
+      <c r="H60" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>37</v>
+      </c>
       <c r="K60" t="n">
-        <v>5.2</v>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>28.5</v>
       </c>
       <c r="O60" t="n">
-        <v>2.4</v>
+        <v>30.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R60" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46290</v>
@@ -5867,22 +5999,22 @@
         <v>27.23</v>
       </c>
       <c r="K61" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="O61" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46291</v>
@@ -5899,22 +6031,22 @@
         <v>25.96</v>
       </c>
       <c r="K62" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O62" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -824,10 +824,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>82</v>
+        <v>82.7</v>
       </c>
       <c r="O4" t="n">
-        <v>37.4</v>
+        <v>35.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V4" t="n">
         <v>13.6</v>
@@ -898,10 +898,10 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>78.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>35.8</v>
+        <v>33.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V5" t="n">
         <v>14.8</v>
@@ -1441,10 +1441,10 @@
         <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>91.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>41.8</v>
+        <v>39.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V11" t="n">
         <v>8.699999999999999</v>
@@ -1515,10 +1515,10 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>87.2</v>
+        <v>88</v>
       </c>
       <c r="O12" t="n">
-        <v>39.8</v>
+        <v>37.4</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V12" t="n">
         <v>7.1</v>
@@ -1589,10 +1589,10 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="O13" t="n">
-        <v>40.1</v>
+        <v>37.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V13" t="n">
         <v>4.9</v>
@@ -1972,10 +1972,10 @@
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O17" t="n">
-        <v>45.6</v>
+        <v>43</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V17" t="n">
         <v>6.3</v>
@@ -2058,10 +2058,10 @@
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
       <c r="O18" t="n">
-        <v>43.2</v>
+        <v>40.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
         <v>8.9</v>
@@ -2144,10 +2144,10 @@
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>84.5</v>
+        <v>85.3</v>
       </c>
       <c r="O19" t="n">
-        <v>38.6</v>
+        <v>36.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V19" t="n">
         <v>9.5</v>
@@ -2230,10 +2230,10 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>77.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>35.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V20" t="n">
         <v>9</v>
@@ -2744,10 +2744,10 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>92</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>42</v>
+        <v>39.5</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V25" t="n">
         <v>9.5</v>
@@ -2830,10 +2830,10 @@
         <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>86.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>39.4</v>
+        <v>37</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V26" t="n">
         <v>10.7</v>
@@ -3451,10 +3451,10 @@
         <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>82.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>37.6</v>
+        <v>35.3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V32" t="n">
         <v>15.5</v>
@@ -3537,10 +3537,10 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>74.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>33.9</v>
+        <v>31.8</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V33" t="n">
         <v>12.6</v>
@@ -4158,10 +4158,10 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>78.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>35.7</v>
+        <v>33.5</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V39" t="n">
         <v>11.6</v>
@@ -4244,10 +4244,10 @@
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>81.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="O40" t="n">
-        <v>37.3</v>
+        <v>35</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="V40" t="n">
         <v>11</v>
@@ -5390,8 +5390,32 @@
       <c r="T51" t="n">
         <v>23.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>12.9</v>
+      </c>
       <c r="AA51" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>7.8</v>
       </c>
       <c r="AK51" t="n">
         <v>129.71</v>
@@ -5716,40 +5740,43 @@
         <v>46286</v>
       </c>
       <c r="B56" t="n">
-        <v>120.4</v>
+        <v>120.3</v>
       </c>
       <c r="C56" t="n">
-        <v>51.3</v>
+        <v>53.3</v>
       </c>
       <c r="D56" t="n">
-        <v>34.9</v>
+        <v>36.3</v>
       </c>
       <c r="E56" t="n">
-        <v>28.7</v>
+        <v>20.6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.6</v>
       </c>
       <c r="H56" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="I56" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
-        <v>32</v>
+        <v>35.4</v>
       </c>
       <c r="K56" t="n">
-        <v>63.1</v>
+        <v>66</v>
       </c>
       <c r="M56" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N56" t="n">
-        <v>28</v>
+        <v>24.8</v>
       </c>
       <c r="O56" t="n">
-        <v>30.1</v>
+        <v>26.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5758,7 +5785,16 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>19</v>
+        <v>18.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>134.04</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>-4.94</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46286</v>
@@ -5781,37 +5817,37 @@
         <v>46287</v>
       </c>
       <c r="B57" t="n">
-        <v>126</v>
+        <v>134.7</v>
       </c>
       <c r="C57" t="n">
-        <v>56.2</v>
+        <v>64</v>
       </c>
       <c r="D57" t="n">
-        <v>35.3</v>
+        <v>36.4</v>
       </c>
       <c r="E57" t="n">
         <v>28.7</v>
       </c>
       <c r="H57" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="I57" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="J57" t="n">
         <v>36</v>
       </c>
       <c r="K57" t="n">
-        <v>67.3</v>
+        <v>67.8</v>
       </c>
       <c r="M57" t="n">
         <v>2.1</v>
       </c>
       <c r="N57" t="n">
-        <v>28.5</v>
+        <v>27</v>
       </c>
       <c r="O57" t="n">
-        <v>30.6</v>
+        <v>29.1</v>
       </c>
       <c r="Q57" t="n">
         <v>22</v>
@@ -5834,13 +5870,13 @@
         <v>46288</v>
       </c>
       <c r="B58" t="n">
-        <v>120</v>
+        <v>125.6</v>
       </c>
       <c r="C58" t="n">
-        <v>50.7</v>
+        <v>54.8</v>
       </c>
       <c r="D58" t="n">
-        <v>34.9</v>
+        <v>36.4</v>
       </c>
       <c r="E58" t="n">
         <v>28.7</v>
@@ -5849,22 +5885,22 @@
         <v>22</v>
       </c>
       <c r="I58" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="J58" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K58" t="n">
-        <v>69.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="M58" t="n">
         <v>2.1</v>
       </c>
       <c r="N58" t="n">
-        <v>28.5</v>
+        <v>27</v>
       </c>
       <c r="O58" t="n">
-        <v>30.6</v>
+        <v>29.1</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -5887,13 +5923,13 @@
         <v>46289</v>
       </c>
       <c r="B59" t="n">
-        <v>110.7</v>
+        <v>114.9</v>
       </c>
       <c r="C59" t="n">
-        <v>42.5</v>
+        <v>45.1</v>
       </c>
       <c r="D59" t="n">
-        <v>34.9</v>
+        <v>36.4</v>
       </c>
       <c r="E59" t="n">
         <v>27.62</v>
@@ -5902,25 +5938,25 @@
         <v>22.8</v>
       </c>
       <c r="I59" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="J59" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K59" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="M59" t="n">
         <v>2.1</v>
       </c>
       <c r="N59" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="O59" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -5929,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
@@ -5940,13 +5976,13 @@
         <v>46290</v>
       </c>
       <c r="B60" t="n">
-        <v>110.3</v>
+        <v>113.1</v>
       </c>
       <c r="C60" t="n">
-        <v>40.8</v>
+        <v>41.9</v>
       </c>
       <c r="D60" t="n">
-        <v>34.7</v>
+        <v>36.3</v>
       </c>
       <c r="E60" t="n">
         <v>28.79</v>
@@ -5955,25 +5991,25 @@
         <v>24.5</v>
       </c>
       <c r="I60" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="J60" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K60" t="n">
-        <v>71.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M60" t="n">
         <v>2.1</v>
       </c>
       <c r="N60" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="O60" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -5982,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46290</v>
@@ -5993,19 +6029,40 @@
         <v>46291</v>
       </c>
       <c r="B61" t="n">
-        <v>27.2</v>
+        <v>107.3</v>
+      </c>
+      <c r="C61" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>34.8</v>
       </c>
       <c r="E61" t="n">
         <v>27.23</v>
       </c>
+      <c r="H61" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>39</v>
+      </c>
       <c r="K61" t="n">
-        <v>6.2</v>
+        <v>73</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>27.5</v>
       </c>
       <c r="O61" t="n">
-        <v>2.8</v>
+        <v>29.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6014,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>18.2</v>
+        <v>22</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46291</v>
@@ -6031,10 +6088,10 @@
         <v>25.96</v>
       </c>
       <c r="K62" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O62" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6046,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5491,8 +5491,32 @@
       <c r="T52" t="n">
         <v>23.3</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>23.2</v>
+      </c>
       <c r="AA52" t="n">
         <v>18.8</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AK52" t="n">
         <v>133.39</v>
@@ -5565,6 +5589,33 @@
       <c r="T53" t="n">
         <v>20</v>
       </c>
+      <c r="V53" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="AK53" t="n">
         <v>137.14</v>
       </c>
@@ -5636,6 +5687,33 @@
       <c r="T54" t="n">
         <v>15</v>
       </c>
+      <c r="V54" t="n">
+        <v>16</v>
+      </c>
+      <c r="W54" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X54" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AK54" t="n">
         <v>137.51</v>
       </c>
@@ -5710,8 +5788,32 @@
       <c r="T55" t="n">
         <v>10.5</v>
       </c>
+      <c r="V55" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W55" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X55" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>23</v>
+      </c>
       <c r="AA55" t="n">
         <v>16.9</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>7</v>
       </c>
       <c r="AK55" t="n">
         <v>138.98</v>
@@ -5787,8 +5889,32 @@
       <c r="T56" t="n">
         <v>18.3</v>
       </c>
+      <c r="V56" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X56" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AA56" t="n">
         <v>13.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>5.4</v>
       </c>
       <c r="AK56" t="n">
         <v>134.04</v>
@@ -5860,6 +5986,33 @@
       </c>
       <c r="T57" t="n">
         <v>22</v>
+      </c>
+      <c r="V57" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X57" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4.8</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,15 +696,6 @@
       <c r="AA2" t="n">
         <v>12</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.7</v>
-      </c>
       <c r="AF2" t="n">
         <v>218.6</v>
       </c>
@@ -785,15 +776,6 @@
       <c r="AA3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF3" t="n">
         <v>218.84</v>
       </c>
@@ -859,15 +841,6 @@
       <c r="AA4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF4" t="n">
         <v>221.78</v>
       </c>
@@ -933,15 +906,6 @@
       <c r="AA5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF5" t="n">
         <v>224.78</v>
       </c>
@@ -1028,15 +992,6 @@
       <c r="AA6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AF6" t="n">
         <v>232.22</v>
       </c>
@@ -1123,15 +1078,6 @@
       <c r="AA7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2</v>
-      </c>
       <c r="AF7" t="n">
         <v>229.69</v>
       </c>
@@ -1218,15 +1164,6 @@
       <c r="AA8" t="n">
         <v>13</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF8" t="n">
         <v>228.57</v>
       </c>
@@ -1313,15 +1250,6 @@
       <c r="AA9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AF9" t="n">
         <v>225.08</v>
       </c>
@@ -1408,15 +1336,6 @@
       <c r="AA10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB10" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AK10" t="n">
         <v>134.62</v>
       </c>
@@ -1476,15 +1395,6 @@
       <c r="AA11" t="n">
         <v>9</v>
       </c>
-      <c r="AB11" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF11" t="n">
         <v>221.37</v>
       </c>
@@ -1550,15 +1460,6 @@
       <c r="AA12" t="n">
         <v>10</v>
       </c>
-      <c r="AB12" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AF12" t="n">
         <v>224.37</v>
       </c>
@@ -1624,15 +1525,6 @@
       <c r="AA13" t="n">
         <v>9</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="AF13" t="n">
         <v>225.93</v>
       </c>
@@ -1719,15 +1611,6 @@
       <c r="AA14" t="n">
         <v>8</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="AF14" t="n">
         <v>218.63</v>
       </c>
@@ -1814,15 +1697,6 @@
       <c r="AA15" t="n">
         <v>9</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF15" t="n">
         <v>216.39</v>
       </c>
@@ -1921,15 +1795,6 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF16" t="n">
         <v>217.16</v>
       </c>
@@ -2007,15 +1872,6 @@
       <c r="AA17" t="n">
         <v>10</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF17" t="n">
         <v>220.31</v>
       </c>
@@ -2093,15 +1949,6 @@
       <c r="AA18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AF18" t="n">
         <v>221.99</v>
       </c>
@@ -2179,15 +2026,6 @@
       <c r="AA19" t="n">
         <v>14</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF19" t="n">
         <v>225.14</v>
       </c>
@@ -2265,15 +2103,6 @@
       <c r="AA20" t="n">
         <v>15</v>
       </c>
-      <c r="AB20" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF20" t="n">
         <v>229.98</v>
       </c>
@@ -2372,15 +2201,6 @@
       <c r="AA21" t="n">
         <v>13</v>
       </c>
-      <c r="AB21" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF21" t="n">
         <v>229.96</v>
       </c>
@@ -2479,15 +2299,6 @@
       <c r="AA22" t="n">
         <v>10</v>
       </c>
-      <c r="AB22" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF22" t="n">
         <v>227.01</v>
       </c>
@@ -2586,15 +2397,6 @@
       <c r="AA23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF23" t="n">
         <v>228.35</v>
       </c>
@@ -2693,15 +2495,6 @@
       <c r="AA24" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF24" t="n">
         <v>231.16</v>
       </c>
@@ -2779,15 +2572,6 @@
       <c r="AA25" t="n">
         <v>9</v>
       </c>
-      <c r="AB25" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF25" t="n">
         <v>228.13</v>
       </c>
@@ -2865,15 +2649,6 @@
       <c r="AA26" t="n">
         <v>9</v>
       </c>
-      <c r="AB26" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4</v>
-      </c>
       <c r="AF26" t="n">
         <v>229.16</v>
       </c>
@@ -2972,15 +2747,6 @@
       <c r="AA27" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB27" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF27" t="n">
         <v>228.55</v>
       </c>
@@ -3079,15 +2845,6 @@
       <c r="AA28" t="n">
         <v>10</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF28" t="n">
         <v>219.99</v>
       </c>
@@ -3186,15 +2943,6 @@
       <c r="AA29" t="n">
         <v>11</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF29" t="n">
         <v>219.22</v>
       </c>
@@ -3293,15 +3041,6 @@
       <c r="AA30" t="n">
         <v>14</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF30" t="n">
         <v>220.73</v>
       </c>
@@ -3400,15 +3139,6 @@
       <c r="AA31" t="n">
         <v>14</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF31" t="n">
         <v>220.58</v>
       </c>
@@ -3486,15 +3216,6 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF32" t="n">
         <v>223.43</v>
       </c>
@@ -3572,15 +3293,6 @@
       <c r="AA33" t="n">
         <v>13</v>
       </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF33" t="n">
         <v>229.48</v>
       </c>
@@ -3679,15 +3391,6 @@
       <c r="AA34" t="n">
         <v>14</v>
       </c>
-      <c r="AB34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4</v>
-      </c>
       <c r="AF34" t="n">
         <v>241.48</v>
       </c>
@@ -3786,15 +3489,6 @@
       <c r="AA35" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF35" t="n">
         <v>238.69</v>
       </c>
@@ -3893,15 +3587,6 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AF36" t="n">
         <v>233.48</v>
       </c>
@@ -4000,15 +3685,6 @@
       <c r="AA37" t="n">
         <v>17</v>
       </c>
-      <c r="AB37" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF37" t="n">
         <v>235.13</v>
       </c>
@@ -4107,15 +3783,6 @@
       <c r="AA38" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB38" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF38" t="n">
         <v>234.87</v>
       </c>
@@ -4193,15 +3860,6 @@
       <c r="AA39" t="n">
         <v>13</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AF39" t="n">
         <v>234.78</v>
       </c>
@@ -4279,15 +3937,6 @@
       <c r="AA40" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF40" t="n">
         <v>229.75</v>
       </c>
@@ -4386,15 +4035,6 @@
       <c r="AA41" t="n">
         <v>6.5</v>
       </c>
-      <c r="AB41" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF41" t="n">
         <v>222.86</v>
       </c>
@@ -4493,15 +4133,6 @@
       <c r="AA42" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB42" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF42" t="n">
         <v>218.37</v>
       </c>
@@ -4600,15 +4231,6 @@
       <c r="AA43" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB43" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF43" t="n">
         <v>220.85</v>
       </c>
@@ -4707,15 +4329,6 @@
       <c r="AA44" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AK44" t="n">
         <v>130.73</v>
       </c>
@@ -4808,15 +4421,6 @@
       <c r="AA45" t="n">
         <v>16.1</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AK45" t="n">
         <v>132</v>
       </c>
@@ -4906,15 +4510,6 @@
       <c r="AA46" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB46" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AK46" t="n">
         <v>132.25</v>
       </c>
@@ -5004,15 +4599,6 @@
       <c r="AA47" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB47" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AK47" t="n">
         <v>128.6</v>
       </c>
@@ -5105,15 +4691,6 @@
       <c r="AA48" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB48" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AK48" t="n">
         <v>127.19</v>
       </c>
@@ -5206,15 +4783,6 @@
       <c r="AA49" t="n">
         <v>12</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AK49" t="n">
         <v>129.17</v>
       </c>
@@ -5307,15 +4875,6 @@
       <c r="AA50" t="n">
         <v>12.9</v>
       </c>
-      <c r="AB50" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AK50" t="n">
         <v>130.42</v>
       </c>
@@ -5408,15 +4967,6 @@
       <c r="AA51" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AK51" t="n">
         <v>129.71</v>
       </c>
@@ -5509,15 +5059,6 @@
       <c r="AA52" t="n">
         <v>18.8</v>
       </c>
-      <c r="AB52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AK52" t="n">
         <v>133.39</v>
       </c>
@@ -5607,15 +5148,6 @@
       <c r="AA53" t="n">
         <v>17.2</v>
       </c>
-      <c r="AB53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AK53" t="n">
         <v>137.14</v>
       </c>
@@ -5705,15 +5237,6 @@
       <c r="AA54" t="n">
         <v>18.1</v>
       </c>
-      <c r="AB54" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>12.8</v>
-      </c>
       <c r="AK54" t="n">
         <v>137.51</v>
       </c>
@@ -5806,15 +5329,6 @@
       <c r="AA55" t="n">
         <v>16.9</v>
       </c>
-      <c r="AB55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>7</v>
-      </c>
       <c r="AK55" t="n">
         <v>138.98</v>
       </c>
@@ -5907,15 +5421,6 @@
       <c r="AA56" t="n">
         <v>13.8</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AK56" t="n">
         <v>134.04</v>
       </c>
@@ -6005,17 +5510,20 @@
       <c r="AA57" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AB57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
-      <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -695,6 +686,15 @@
       </c>
       <c r="AA2" t="n">
         <v>12</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AF2" t="n">
         <v>218.6</v>
@@ -758,15 +758,6 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -775,6 +766,15 @@
       </c>
       <c r="AA3" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
         <v>218.84</v>
@@ -823,15 +823,6 @@
       <c r="T4" t="n">
         <v>19.8</v>
       </c>
-      <c r="V4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19</v>
-      </c>
       <c r="Y4" t="n">
         <v>14</v>
       </c>
@@ -840,6 +831,15 @@
       </c>
       <c r="AA4" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
         <v>221.78</v>
@@ -888,15 +888,6 @@
       <c r="T5" t="n">
         <v>19.8</v>
       </c>
-      <c r="V5" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
@@ -905,6 +896,15 @@
       </c>
       <c r="AA5" t="n">
         <v>16.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
         <v>224.78</v>
@@ -974,15 +974,6 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
-      <c r="V6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -991,6 +982,15 @@
       </c>
       <c r="AA6" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
         <v>232.22</v>
@@ -1060,15 +1060,6 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1077,6 +1068,15 @@
       </c>
       <c r="AA7" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>229.69</v>
@@ -1146,15 +1146,6 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>20</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1163,6 +1154,15 @@
       </c>
       <c r="AA8" t="n">
         <v>13</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
         <v>228.57</v>
@@ -1232,15 +1232,6 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
-      <c r="V9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1249,6 +1240,15 @@
       </c>
       <c r="AA9" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6</v>
       </c>
       <c r="AF9" t="n">
         <v>225.08</v>
@@ -1318,15 +1318,6 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="V10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>27</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1335,6 +1326,15 @@
       </c>
       <c r="AA10" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AK10" t="n">
         <v>134.62</v>
@@ -1377,15 +1377,6 @@
       <c r="T11" t="n">
         <v>19.8</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>14</v>
-      </c>
       <c r="Y11" t="n">
         <v>5</v>
       </c>
@@ -1394,6 +1385,15 @@
       </c>
       <c r="AA11" t="n">
         <v>9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF11" t="n">
         <v>221.37</v>
@@ -1442,15 +1442,6 @@
       <c r="T12" t="n">
         <v>19.8</v>
       </c>
-      <c r="V12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1459,6 +1450,15 @@
       </c>
       <c r="AA12" t="n">
         <v>10</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>224.37</v>
@@ -1507,15 +1507,6 @@
       <c r="T13" t="n">
         <v>19.8</v>
       </c>
-      <c r="V13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y13" t="n">
         <v>3</v>
       </c>
@@ -1524,6 +1515,15 @@
       </c>
       <c r="AA13" t="n">
         <v>9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF13" t="n">
         <v>225.93</v>
@@ -1593,15 +1593,6 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1610,6 +1601,15 @@
       </c>
       <c r="AA14" t="n">
         <v>8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-5.1</v>
       </c>
       <c r="AF14" t="n">
         <v>218.63</v>
@@ -1679,15 +1679,6 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1696,6 +1687,15 @@
       </c>
       <c r="AA15" t="n">
         <v>9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF15" t="n">
         <v>216.39</v>
@@ -1777,15 +1777,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1794,6 +1785,15 @@
       </c>
       <c r="AA16" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>217.16</v>
@@ -1854,15 +1854,6 @@
       <c r="T17" t="n">
         <v>19.8</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1871,6 +1862,15 @@
       </c>
       <c r="AA17" t="n">
         <v>10</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF17" t="n">
         <v>220.31</v>
@@ -1931,15 +1931,6 @@
       <c r="T18" t="n">
         <v>19.8</v>
       </c>
-      <c r="V18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
@@ -1948,6 +1939,15 @@
       </c>
       <c r="AA18" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
         <v>221.99</v>
@@ -2008,15 +2008,6 @@
       <c r="T19" t="n">
         <v>19.8</v>
       </c>
-      <c r="V19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2025,6 +2016,15 @@
       </c>
       <c r="AA19" t="n">
         <v>14</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF19" t="n">
         <v>225.14</v>
@@ -2085,15 +2085,6 @@
       <c r="T20" t="n">
         <v>19.8</v>
       </c>
-      <c r="V20" t="n">
-        <v>9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y20" t="n">
         <v>12</v>
       </c>
@@ -2102,6 +2093,15 @@
       </c>
       <c r="AA20" t="n">
         <v>15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF20" t="n">
         <v>229.98</v>
@@ -2183,15 +2183,6 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
-      <c r="V21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2200,6 +2191,15 @@
       </c>
       <c r="AA21" t="n">
         <v>13</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AF21" t="n">
         <v>229.96</v>
@@ -2281,15 +2281,6 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2298,6 +2289,15 @@
       </c>
       <c r="AA22" t="n">
         <v>10</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF22" t="n">
         <v>227.01</v>
@@ -2379,15 +2379,6 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2396,6 +2387,15 @@
       </c>
       <c r="AA23" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF23" t="n">
         <v>228.35</v>
@@ -2477,15 +2477,6 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2494,6 +2485,15 @@
       </c>
       <c r="AA24" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF24" t="n">
         <v>231.16</v>
@@ -2554,15 +2554,6 @@
       <c r="T25" t="n">
         <v>19.8</v>
       </c>
-      <c r="V25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2571,6 +2562,15 @@
       </c>
       <c r="AA25" t="n">
         <v>9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF25" t="n">
         <v>228.13</v>
@@ -2631,15 +2631,6 @@
       <c r="T26" t="n">
         <v>19.8</v>
       </c>
-      <c r="V26" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y26" t="n">
         <v>4</v>
       </c>
@@ -2648,6 +2639,15 @@
       </c>
       <c r="AA26" t="n">
         <v>9</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.16</v>
@@ -2729,15 +2729,6 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
-      <c r="V27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -2746,6 +2737,15 @@
       </c>
       <c r="AA27" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF27" t="n">
         <v>228.55</v>
@@ -2827,15 +2827,6 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
-      <c r="V28" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -2844,6 +2835,15 @@
       </c>
       <c r="AA28" t="n">
         <v>10</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF28" t="n">
         <v>219.99</v>
@@ -2925,15 +2925,6 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -2942,6 +2933,15 @@
       </c>
       <c r="AA29" t="n">
         <v>11</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF29" t="n">
         <v>219.22</v>
@@ -3023,15 +3023,6 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
-      <c r="V30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3040,6 +3031,15 @@
       </c>
       <c r="AA30" t="n">
         <v>14</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
         <v>220.73</v>
@@ -3121,15 +3121,6 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3138,6 +3129,15 @@
       </c>
       <c r="AA31" t="n">
         <v>14</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF31" t="n">
         <v>220.58</v>
@@ -3198,15 +3198,6 @@
       <c r="T32" t="n">
         <v>19.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
@@ -3215,6 +3206,15 @@
       </c>
       <c r="AA32" t="n">
         <v>13</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF32" t="n">
         <v>223.43</v>
@@ -3275,15 +3275,6 @@
       <c r="T33" t="n">
         <v>19.8</v>
       </c>
-      <c r="V33" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
@@ -3292,6 +3283,15 @@
       </c>
       <c r="AA33" t="n">
         <v>13</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF33" t="n">
         <v>229.48</v>
@@ -3373,15 +3373,6 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
-      <c r="V34" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X34" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3390,6 +3381,15 @@
       </c>
       <c r="AA34" t="n">
         <v>14</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4</v>
       </c>
       <c r="AF34" t="n">
         <v>241.48</v>
@@ -3471,15 +3471,6 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
-      <c r="V35" t="n">
-        <v>12</v>
-      </c>
-      <c r="W35" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X35" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3488,6 +3479,15 @@
       </c>
       <c r="AA35" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF35" t="n">
         <v>238.69</v>
@@ -3569,15 +3569,6 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3586,6 +3577,15 @@
       </c>
       <c r="AA36" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
         <v>233.48</v>
@@ -3667,15 +3667,6 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
-      <c r="V37" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W37" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -3684,6 +3675,15 @@
       </c>
       <c r="AA37" t="n">
         <v>17</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF37" t="n">
         <v>235.13</v>
@@ -3765,15 +3765,6 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
-      <c r="V38" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -3782,6 +3773,15 @@
       </c>
       <c r="AA38" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
         <v>234.87</v>
@@ -3842,15 +3842,6 @@
       <c r="T39" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y39" t="n">
         <v>7</v>
       </c>
@@ -3859,6 +3850,15 @@
       </c>
       <c r="AA39" t="n">
         <v>13</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.2</v>
       </c>
       <c r="AF39" t="n">
         <v>234.78</v>
@@ -3919,15 +3919,6 @@
       <c r="T40" t="n">
         <v>19.8</v>
       </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22</v>
-      </c>
-      <c r="X40" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
@@ -3936,6 +3927,15 @@
       </c>
       <c r="AA40" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF40" t="n">
         <v>229.75</v>
@@ -4017,15 +4017,6 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
-      <c r="V41" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4034,6 +4025,15 @@
       </c>
       <c r="AA41" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF41" t="n">
         <v>222.86</v>
@@ -4115,15 +4115,6 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W42" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4132,6 +4123,15 @@
       </c>
       <c r="AA42" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
         <v>218.37</v>
@@ -4213,15 +4213,6 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>21</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4230,6 +4221,15 @@
       </c>
       <c r="AA43" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF43" t="n">
         <v>220.85</v>
@@ -4311,15 +4311,6 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
-      <c r="V44" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4328,6 +4319,15 @@
       </c>
       <c r="AA44" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>6.3</v>
       </c>
       <c r="AK44" t="n">
         <v>130.73</v>
@@ -4403,15 +4403,6 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
-      <c r="V45" t="n">
-        <v>11</v>
-      </c>
-      <c r="W45" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X45" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4420,6 +4411,15 @@
       </c>
       <c r="AA45" t="n">
         <v>16.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>4.5</v>
       </c>
       <c r="AK45" t="n">
         <v>132</v>
@@ -4492,15 +4492,6 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W46" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X46" t="n">
-        <v>18</v>
-      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -4509,6 +4500,15 @@
       </c>
       <c r="AA46" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AK46" t="n">
         <v>132.25</v>
@@ -4581,15 +4581,6 @@
       <c r="T47" t="n">
         <v>23.6</v>
       </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X47" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>7.7</v>
       </c>
@@ -4598,6 +4589,15 @@
       </c>
       <c r="AA47" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8</v>
       </c>
       <c r="AK47" t="n">
         <v>128.6</v>
@@ -4673,15 +4673,6 @@
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
-      <c r="V48" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>11</v>
-      </c>
-      <c r="X48" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y48" t="n">
         <v>3.4</v>
       </c>
@@ -4690,6 +4681,15 @@
       </c>
       <c r="AA48" t="n">
         <v>7.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>5.7</v>
       </c>
       <c r="AK48" t="n">
         <v>127.19</v>
@@ -4765,15 +4765,6 @@
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
-      <c r="V49" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X49" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y49" t="n">
         <v>6</v>
       </c>
@@ -4782,6 +4773,15 @@
       </c>
       <c r="AA49" t="n">
         <v>12</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.8</v>
       </c>
       <c r="AK49" t="n">
         <v>129.17</v>
@@ -4857,15 +4857,6 @@
       <c r="T50" t="n">
         <v>22.1</v>
       </c>
-      <c r="V50" t="n">
-        <v>4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y50" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4874,6 +4865,15 @@
       </c>
       <c r="AA50" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>6.7</v>
       </c>
       <c r="AK50" t="n">
         <v>130.42</v>
@@ -4949,15 +4949,6 @@
       <c r="T51" t="n">
         <v>23.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26</v>
-      </c>
-      <c r="X51" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y51" t="n">
         <v>5.3</v>
       </c>
@@ -4966,6 +4957,15 @@
       </c>
       <c r="AA51" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>7.8</v>
       </c>
       <c r="AK51" t="n">
         <v>129.71</v>
@@ -5041,23 +5041,17 @@
       <c r="T52" t="n">
         <v>23.3</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W52" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>23.2</v>
-      </c>
       <c r="AA52" t="n">
         <v>18.8</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AK52" t="n">
         <v>133.39</v>
@@ -5130,23 +5124,14 @@
       <c r="T53" t="n">
         <v>20</v>
       </c>
-      <c r="V53" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X53" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>17.2</v>
+      <c r="AB53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AK53" t="n">
         <v>137.14</v>
@@ -5219,23 +5204,14 @@
       <c r="T54" t="n">
         <v>15</v>
       </c>
-      <c r="V54" t="n">
-        <v>16</v>
-      </c>
-      <c r="W54" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X54" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>18.1</v>
+      <c r="AB54" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>12.8</v>
       </c>
       <c r="AK54" t="n">
         <v>137.51</v>
@@ -5311,23 +5287,17 @@
       <c r="T55" t="n">
         <v>10.5</v>
       </c>
-      <c r="V55" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W55" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X55" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>23</v>
-      </c>
       <c r="AA55" t="n">
         <v>16.9</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>7</v>
       </c>
       <c r="AK55" t="n">
         <v>138.98</v>
@@ -5403,23 +5373,17 @@
       <c r="T56" t="n">
         <v>18.3</v>
       </c>
-      <c r="V56" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W56" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X56" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>16.1</v>
-      </c>
       <c r="AA56" t="n">
         <v>13.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>5.4</v>
       </c>
       <c r="AK56" t="n">
         <v>134.04</v>
@@ -5492,23 +5456,14 @@
       <c r="T57" t="n">
         <v>22</v>
       </c>
-      <c r="V57" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>8.699999999999999</v>
+      <c r="AB57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4.8</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5465,6 +5465,12 @@
       <c r="AD57" t="n">
         <v>4.8</v>
       </c>
+      <c r="AK57" t="n">
+        <v>131.01</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-3.03</v>
+      </c>
       <c r="BL57" s="1" t="n">
         <v>46287</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -4329,6 +4329,12 @@
       <c r="AD44" t="n">
         <v>6.3</v>
       </c>
+      <c r="AF44" t="n">
+        <v>225.87</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>5.02</v>
+      </c>
       <c r="AK44" t="n">
         <v>130.73</v>
       </c>
@@ -4421,6 +4427,12 @@
       <c r="AD45" t="n">
         <v>4.5</v>
       </c>
+      <c r="AF45" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.61</v>
+      </c>
       <c r="AK45" t="n">
         <v>132</v>
       </c>
@@ -4510,6 +4522,12 @@
       <c r="AD46" t="n">
         <v>-0.1</v>
       </c>
+      <c r="AF46" t="n">
+        <v>230.54</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.06</v>
+      </c>
       <c r="AK46" t="n">
         <v>132.25</v>
       </c>
@@ -4599,6 +4617,12 @@
       <c r="AD47" t="n">
         <v>0.8</v>
       </c>
+      <c r="AF47" t="n">
+        <v>224.23</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>-6.31</v>
+      </c>
       <c r="AK47" t="n">
         <v>128.6</v>
       </c>
@@ -4691,6 +4715,12 @@
       <c r="AD48" t="n">
         <v>5.7</v>
       </c>
+      <c r="AF48" t="n">
+        <v>223.36</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>-0.87</v>
+      </c>
       <c r="AK48" t="n">
         <v>127.19</v>
       </c>
@@ -4783,6 +4813,12 @@
       <c r="AD49" t="n">
         <v>5.8</v>
       </c>
+      <c r="AF49" t="n">
+        <v>222.92</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>-0.44</v>
+      </c>
       <c r="AK49" t="n">
         <v>129.17</v>
       </c>
@@ -4875,6 +4911,12 @@
       <c r="AD50" t="n">
         <v>6.7</v>
       </c>
+      <c r="AF50" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="AK50" t="n">
         <v>130.42</v>
       </c>
@@ -4967,6 +5009,12 @@
       <c r="AD51" t="n">
         <v>7.8</v>
       </c>
+      <c r="AF51" t="n">
+        <v>221.86</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AK51" t="n">
         <v>129.71</v>
       </c>
@@ -5053,6 +5101,12 @@
       <c r="AD52" t="n">
         <v>8.699999999999999</v>
       </c>
+      <c r="AF52" t="n">
+        <v>227.49</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>5.63</v>
+      </c>
       <c r="AK52" t="n">
         <v>133.39</v>
       </c>
@@ -5133,6 +5187,12 @@
       <c r="AD53" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="AF53" t="n">
+        <v>233.56</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>6.07</v>
+      </c>
       <c r="AK53" t="n">
         <v>137.14</v>
       </c>
@@ -5213,6 +5273,12 @@
       <c r="AD54" t="n">
         <v>12.8</v>
       </c>
+      <c r="AF54" t="n">
+        <v>234.94</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.38</v>
+      </c>
       <c r="AK54" t="n">
         <v>137.51</v>
       </c>
@@ -5299,6 +5365,12 @@
       <c r="AD55" t="n">
         <v>7</v>
       </c>
+      <c r="AF55" t="n">
+        <v>229.19</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-5.75</v>
+      </c>
       <c r="AK55" t="n">
         <v>138.98</v>
       </c>
@@ -5385,6 +5457,12 @@
       <c r="AD56" t="n">
         <v>5.4</v>
       </c>
+      <c r="AF56" t="n">
+        <v>224.91</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-4.28</v>
+      </c>
       <c r="AK56" t="n">
         <v>134.04</v>
       </c>
@@ -5464,6 +5542,12 @@
       </c>
       <c r="AD57" t="n">
         <v>4.8</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>220.83</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-4.08</v>
       </c>
       <c r="AK57" t="n">
         <v>131.01</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
+      <c r="V2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -758,6 +767,15 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
+      <c r="V3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -823,6 +841,15 @@
       <c r="T4" t="n">
         <v>19.8</v>
       </c>
+      <c r="V4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>19</v>
+      </c>
       <c r="Y4" t="n">
         <v>14</v>
       </c>
@@ -888,6 +915,15 @@
       <c r="T5" t="n">
         <v>19.8</v>
       </c>
+      <c r="V5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
@@ -974,6 +1010,15 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
+      <c r="V6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1060,6 +1105,15 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1146,6 +1200,15 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
+      <c r="V8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1232,6 +1295,15 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
+      <c r="V9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1318,6 +1390,15 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
+      <c r="V10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1377,6 +1458,15 @@
       <c r="T11" t="n">
         <v>19.8</v>
       </c>
+      <c r="V11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
+      </c>
       <c r="Y11" t="n">
         <v>5</v>
       </c>
@@ -1442,6 +1532,15 @@
       <c r="T12" t="n">
         <v>19.8</v>
       </c>
+      <c r="V12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1507,6 +1606,15 @@
       <c r="T13" t="n">
         <v>19.8</v>
       </c>
+      <c r="V13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y13" t="n">
         <v>3</v>
       </c>
@@ -1593,6 +1701,15 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
+      <c r="V14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1679,6 +1796,15 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1777,6 +1903,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1854,6 +1989,15 @@
       <c r="T17" t="n">
         <v>19.8</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1931,6 +2075,15 @@
       <c r="T18" t="n">
         <v>19.8</v>
       </c>
+      <c r="V18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
@@ -2008,6 +2161,15 @@
       <c r="T19" t="n">
         <v>19.8</v>
       </c>
+      <c r="V19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2085,6 +2247,15 @@
       <c r="T20" t="n">
         <v>19.8</v>
       </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y20" t="n">
         <v>12</v>
       </c>
@@ -2183,6 +2354,15 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
+      <c r="V21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2281,6 +2461,15 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2379,6 +2568,15 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2477,6 +2675,15 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2554,6 +2761,15 @@
       <c r="T25" t="n">
         <v>19.8</v>
       </c>
+      <c r="V25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2631,6 +2847,15 @@
       <c r="T26" t="n">
         <v>19.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y26" t="n">
         <v>4</v>
       </c>
@@ -2729,6 +2954,15 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
+      <c r="V27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -2827,6 +3061,15 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
+      <c r="V28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -2925,6 +3168,15 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3023,6 +3275,15 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
+      <c r="V30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3121,6 +3382,15 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3198,6 +3468,15 @@
       <c r="T32" t="n">
         <v>19.8</v>
       </c>
+      <c r="V32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
@@ -3275,6 +3554,15 @@
       <c r="T33" t="n">
         <v>19.8</v>
       </c>
+      <c r="V33" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
@@ -3373,6 +3661,15 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
+      <c r="V34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3471,6 +3768,15 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3569,6 +3875,15 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3667,6 +3982,15 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
+      <c r="V37" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -3765,6 +4089,15 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
+      <c r="V38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -3842,6 +4175,15 @@
       <c r="T39" t="n">
         <v>19.8</v>
       </c>
+      <c r="V39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y39" t="n">
         <v>7</v>
       </c>
@@ -3919,6 +4261,15 @@
       <c r="T40" t="n">
         <v>19.8</v>
       </c>
+      <c r="V40" t="n">
+        <v>11</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22</v>
+      </c>
+      <c r="X40" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
@@ -4017,6 +4368,15 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
+      <c r="V41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4115,6 +4475,15 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4213,6 +4582,15 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>21</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4311,6 +4689,15 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
+      <c r="V44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W44" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4409,6 +4796,15 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
+      <c r="V45" t="n">
+        <v>11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4504,6 +4900,15 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X46" t="n">
+        <v>18</v>
+      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -4599,6 +5004,15 @@
       <c r="T47" t="n">
         <v>23.6</v>
       </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>7.7</v>
       </c>
@@ -4697,6 +5111,15 @@
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
+      <c r="V48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>11</v>
+      </c>
+      <c r="X48" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y48" t="n">
         <v>3.4</v>
       </c>
@@ -4795,6 +5218,15 @@
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
+      <c r="V49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X49" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y49" t="n">
         <v>6</v>
       </c>
@@ -4893,6 +5325,15 @@
       <c r="T50" t="n">
         <v>22.1</v>
       </c>
+      <c r="V50" t="n">
+        <v>4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y50" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4991,6 +5432,15 @@
       <c r="T51" t="n">
         <v>23.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y51" t="n">
         <v>5.3</v>
       </c>
@@ -5089,6 +5539,21 @@
       <c r="T52" t="n">
         <v>23.3</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>23.2</v>
+      </c>
       <c r="AA52" t="n">
         <v>18.8</v>
       </c>
@@ -5178,6 +5643,24 @@
       <c r="T53" t="n">
         <v>20</v>
       </c>
+      <c r="V53" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>17.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>3.6</v>
       </c>
@@ -5264,6 +5747,24 @@
       <c r="T54" t="n">
         <v>15</v>
       </c>
+      <c r="V54" t="n">
+        <v>16</v>
+      </c>
+      <c r="W54" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X54" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>18.1</v>
+      </c>
       <c r="AB54" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -5353,6 +5854,21 @@
       <c r="T55" t="n">
         <v>10.5</v>
       </c>
+      <c r="V55" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W55" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X55" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>23</v>
+      </c>
       <c r="AA55" t="n">
         <v>16.9</v>
       </c>
@@ -5445,6 +5961,21 @@
       <c r="T56" t="n">
         <v>18.3</v>
       </c>
+      <c r="V56" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X56" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AA56" t="n">
         <v>13.8</v>
       </c>
@@ -5533,6 +6064,24 @@
       </c>
       <c r="T57" t="n">
         <v>22</v>
+      </c>
+      <c r="V57" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X57" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AB57" t="n">
         <v>-0</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6169,6 +6169,39 @@
       <c r="T58" t="n">
         <v>22</v>
       </c>
+      <c r="V58" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W58" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>228.06</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>7.23</v>
+      </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -824,10 +824,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="O4" t="n">
-        <v>35.1</v>
+        <v>33.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V4" t="n">
         <v>13.6</v>
@@ -898,10 +898,10 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>33.6</v>
+        <v>32.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
         <v>14.8</v>
@@ -1441,10 +1441,10 @@
         <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="O11" t="n">
-        <v>39.3</v>
+        <v>38</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V11" t="n">
         <v>8.699999999999999</v>
@@ -1515,10 +1515,10 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>37.4</v>
+        <v>36.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V12" t="n">
         <v>7.1</v>
@@ -1589,10 +1589,10 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
       <c r="O13" t="n">
-        <v>37.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V13" t="n">
         <v>4.9</v>
@@ -1972,10 +1972,10 @@
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="O17" t="n">
-        <v>43</v>
+        <v>41.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V17" t="n">
         <v>6.3</v>
@@ -2061,7 +2061,7 @@
         <v>95.5</v>
       </c>
       <c r="O18" t="n">
-        <v>40.6</v>
+        <v>39.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V18" t="n">
         <v>8.9</v>
@@ -2144,10 +2144,10 @@
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>36.2</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V19" t="n">
         <v>9.5</v>
@@ -2230,10 +2230,10 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="O20" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>9</v>
@@ -2744,10 +2744,10 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="O25" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V25" t="n">
         <v>9.5</v>
@@ -2830,10 +2830,10 @@
         <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="O26" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V26" t="n">
         <v>10.7</v>
@@ -3451,10 +3451,10 @@
         <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>35.3</v>
+        <v>34.1</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V32" t="n">
         <v>15.5</v>
@@ -3537,10 +3537,10 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>31.8</v>
+        <v>30.7</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V33" t="n">
         <v>12.6</v>
@@ -4158,10 +4158,10 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="O39" t="n">
-        <v>33.5</v>
+        <v>32.3</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V39" t="n">
         <v>11.6</v>
@@ -4244,10 +4244,10 @@
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>35</v>
+        <v>33.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="V40" t="n">
         <v>11</v>
@@ -5643,15 +5643,6 @@
       <c r="T53" t="n">
         <v>20</v>
       </c>
-      <c r="V53" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X53" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y53" t="n">
         <v>13.4</v>
       </c>
@@ -5747,15 +5738,6 @@
       <c r="T54" t="n">
         <v>15</v>
       </c>
-      <c r="V54" t="n">
-        <v>16</v>
-      </c>
-      <c r="W54" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X54" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y54" t="n">
         <v>15.2</v>
       </c>
@@ -5854,15 +5836,6 @@
       <c r="T55" t="n">
         <v>10.5</v>
       </c>
-      <c r="V55" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W55" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X55" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y55" t="n">
         <v>14.8</v>
       </c>
@@ -5961,15 +5934,6 @@
       <c r="T56" t="n">
         <v>18.3</v>
       </c>
-      <c r="V56" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W56" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X56" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y56" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -6021,40 +5985,43 @@
         <v>46287</v>
       </c>
       <c r="B57" t="n">
-        <v>134.7</v>
+        <v>131.1</v>
       </c>
       <c r="C57" t="n">
-        <v>64</v>
+        <v>60.2</v>
       </c>
       <c r="D57" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
       <c r="E57" t="n">
-        <v>28.7</v>
+        <v>24.2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.4</v>
       </c>
       <c r="H57" t="n">
-        <v>22.3</v>
+        <v>23</v>
       </c>
       <c r="I57" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>36</v>
+        <v>38.2</v>
       </c>
       <c r="K57" t="n">
-        <v>67.8</v>
+        <v>70</v>
       </c>
       <c r="M57" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="N57" t="n">
-        <v>27</v>
+        <v>30.2</v>
       </c>
       <c r="O57" t="n">
-        <v>29.1</v>
+        <v>31.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6063,16 +6030,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>22</v>
-      </c>
-      <c r="V57" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W57" t="n">
         <v>20.2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>17.1</v>
       </c>
       <c r="Y57" t="n">
         <v>4.9</v>
@@ -6081,7 +6039,7 @@
         <v>12.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>8.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AB57" t="n">
         <v>-0</v>
@@ -6125,28 +6083,28 @@
         <v>46288</v>
       </c>
       <c r="B58" t="n">
-        <v>125.6</v>
+        <v>128</v>
       </c>
       <c r="C58" t="n">
-        <v>54.8</v>
+        <v>58.3</v>
       </c>
       <c r="D58" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="E58" t="n">
         <v>28.7</v>
       </c>
       <c r="H58" t="n">
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="I58" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K58" t="n">
-        <v>70.5</v>
+        <v>73.2</v>
       </c>
       <c r="M58" t="n">
         <v>2.1</v>
@@ -6168,15 +6126,6 @@
       </c>
       <c r="T58" t="n">
         <v>22</v>
-      </c>
-      <c r="V58" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W58" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X58" t="n">
-        <v>17.6</v>
       </c>
       <c r="Y58" t="n">
         <v>6.8</v>
@@ -6211,28 +6160,28 @@
         <v>46289</v>
       </c>
       <c r="B59" t="n">
-        <v>114.9</v>
+        <v>120.8</v>
       </c>
       <c r="C59" t="n">
-        <v>45.1</v>
+        <v>51.3</v>
       </c>
       <c r="D59" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="E59" t="n">
         <v>27.62</v>
       </c>
       <c r="H59" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="I59" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K59" t="n">
-        <v>71.3</v>
+        <v>73.2</v>
       </c>
       <c r="M59" t="n">
         <v>2.1</v>
@@ -6264,25 +6213,25 @@
         <v>46290</v>
       </c>
       <c r="B60" t="n">
-        <v>113.1</v>
+        <v>116.9</v>
       </c>
       <c r="C60" t="n">
-        <v>41.9</v>
+        <v>46.4</v>
       </c>
       <c r="D60" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="E60" t="n">
         <v>28.79</v>
       </c>
       <c r="H60" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="I60" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
         <v>73</v>
@@ -6317,25 +6266,25 @@
         <v>46291</v>
       </c>
       <c r="B61" t="n">
-        <v>107.3</v>
+        <v>112.1</v>
       </c>
       <c r="C61" t="n">
-        <v>39.5</v>
+        <v>44.9</v>
       </c>
       <c r="D61" t="n">
-        <v>34.8</v>
+        <v>34.2</v>
       </c>
       <c r="E61" t="n">
         <v>27.23</v>
       </c>
       <c r="H61" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="I61" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J61" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K61" t="n">
         <v>73</v>
@@ -6370,19 +6319,40 @@
         <v>46292</v>
       </c>
       <c r="B62" t="n">
-        <v>26</v>
+        <v>107.6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>34</v>
       </c>
       <c r="E62" t="n">
         <v>25.96</v>
       </c>
+      <c r="H62" t="n">
+        <v>24</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9</v>
+      </c>
+      <c r="J62" t="n">
+        <v>40</v>
+      </c>
       <c r="K62" t="n">
-        <v>4.4</v>
+        <v>73</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>27.5</v>
       </c>
       <c r="O62" t="n">
-        <v>1.8</v>
+        <v>29.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6391,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
-      <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -767,15 +758,6 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -841,15 +823,6 @@
       <c r="T4" t="n">
         <v>21.2</v>
       </c>
-      <c r="V4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>19</v>
-      </c>
       <c r="Y4" t="n">
         <v>14</v>
       </c>
@@ -915,15 +888,6 @@
       <c r="T5" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
@@ -1010,15 +974,6 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
-      <c r="V6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1105,15 +1060,6 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1200,15 +1146,6 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
-      <c r="V8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>20</v>
-      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1295,15 +1232,6 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
-      <c r="V9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1390,15 +1318,6 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="V10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>27</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1458,15 +1377,6 @@
       <c r="T11" t="n">
         <v>21.2</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>14</v>
-      </c>
       <c r="Y11" t="n">
         <v>5</v>
       </c>
@@ -1532,15 +1442,6 @@
       <c r="T12" t="n">
         <v>21.2</v>
       </c>
-      <c r="V12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1606,15 +1507,6 @@
       <c r="T13" t="n">
         <v>21.2</v>
       </c>
-      <c r="V13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y13" t="n">
         <v>3</v>
       </c>
@@ -1701,15 +1593,6 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1796,15 +1679,6 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1903,15 +1777,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1989,15 +1854,6 @@
       <c r="T17" t="n">
         <v>21.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2075,15 +1931,6 @@
       <c r="T18" t="n">
         <v>21.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
@@ -2161,15 +2008,6 @@
       <c r="T19" t="n">
         <v>21.2</v>
       </c>
-      <c r="V19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y19" t="n">
         <v>13</v>
       </c>
@@ -2247,15 +2085,6 @@
       <c r="T20" t="n">
         <v>21.2</v>
       </c>
-      <c r="V20" t="n">
-        <v>9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y20" t="n">
         <v>12</v>
       </c>
@@ -2354,15 +2183,6 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
-      <c r="V21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2461,15 +2281,6 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2568,15 +2379,6 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2675,15 +2477,6 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
-      <c r="V24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2761,15 +2554,6 @@
       <c r="T25" t="n">
         <v>21.2</v>
       </c>
-      <c r="V25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y25" t="n">
         <v>6</v>
       </c>
@@ -2847,15 +2631,6 @@
       <c r="T26" t="n">
         <v>21.2</v>
       </c>
-      <c r="V26" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y26" t="n">
         <v>4</v>
       </c>
@@ -2954,15 +2729,6 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
-      <c r="V27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -3061,15 +2827,6 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
-      <c r="V28" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -3168,15 +2925,6 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3275,15 +3023,6 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
-      <c r="V30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3382,15 +3121,6 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3468,15 +3198,6 @@
       <c r="T32" t="n">
         <v>21.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>9</v>
       </c>
@@ -3554,15 +3275,6 @@
       <c r="T33" t="n">
         <v>21.2</v>
       </c>
-      <c r="V33" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
@@ -3661,15 +3373,6 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
-      <c r="V34" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X34" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3768,15 +3471,6 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
-      <c r="V35" t="n">
-        <v>12</v>
-      </c>
-      <c r="W35" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X35" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3875,15 +3569,6 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3982,15 +3667,6 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
-      <c r="V37" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W37" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -4089,15 +3765,6 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
-      <c r="V38" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -4175,15 +3842,6 @@
       <c r="T39" t="n">
         <v>21.2</v>
       </c>
-      <c r="V39" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y39" t="n">
         <v>7</v>
       </c>
@@ -4261,15 +3919,6 @@
       <c r="T40" t="n">
         <v>21.2</v>
       </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22</v>
-      </c>
-      <c r="X40" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
@@ -4368,15 +4017,6 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
-      <c r="V41" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4475,15 +4115,6 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W42" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4582,15 +4213,6 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
-      <c r="V43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>21</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4689,15 +4311,6 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
-      <c r="V44" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4796,15 +4409,6 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
-      <c r="V45" t="n">
-        <v>11</v>
-      </c>
-      <c r="W45" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X45" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4900,15 +4504,6 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W46" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X46" t="n">
-        <v>18</v>
-      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -5004,15 +4599,6 @@
       <c r="T47" t="n">
         <v>23.6</v>
       </c>
-      <c r="V47" t="n">
-        <v>9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X47" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>7.7</v>
       </c>
@@ -5111,15 +4697,6 @@
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
-      <c r="V48" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>11</v>
-      </c>
-      <c r="X48" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y48" t="n">
         <v>3.4</v>
       </c>
@@ -5218,15 +4795,6 @@
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
-      <c r="V49" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X49" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y49" t="n">
         <v>6</v>
       </c>
@@ -5325,15 +4893,6 @@
       <c r="T50" t="n">
         <v>22.1</v>
       </c>
-      <c r="V50" t="n">
-        <v>4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y50" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -5432,15 +4991,6 @@
       <c r="T51" t="n">
         <v>23.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26</v>
-      </c>
-      <c r="X51" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y51" t="n">
         <v>5.3</v>
       </c>
@@ -5539,15 +5089,6 @@
       <c r="T52" t="n">
         <v>23.3</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W52" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y52" t="n">
         <v>11.1</v>
       </c>
@@ -5643,15 +5184,6 @@
       <c r="T53" t="n">
         <v>20</v>
       </c>
-      <c r="Y53" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>17.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>3.6</v>
       </c>
@@ -5738,15 +5270,6 @@
       <c r="T54" t="n">
         <v>15</v>
       </c>
-      <c r="Y54" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>18.1</v>
-      </c>
       <c r="AB54" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -5836,12 +5359,6 @@
       <c r="T55" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y55" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>23</v>
-      </c>
       <c r="AA55" t="n">
         <v>16.9</v>
       </c>
@@ -5934,12 +5451,6 @@
       <c r="T56" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y56" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>16.1</v>
-      </c>
       <c r="AA56" t="n">
         <v>13.8</v>
       </c>
@@ -6032,12 +5543,6 @@
       <c r="T57" t="n">
         <v>20.2</v>
       </c>
-      <c r="Y57" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA57" t="n">
         <v>9.6</v>
       </c>
@@ -6127,15 +5632,6 @@
       <c r="T58" t="n">
         <v>22</v>
       </c>
-      <c r="Y58" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>11.8</v>
-      </c>
       <c r="AB58" t="n">
         <v>5.1</v>
       </c>
@@ -6153,6 +5649,18 @@
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>19</v>
       </c>
+      <c r="V2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>9</v>
       </c>
@@ -758,6 +767,15 @@
       <c r="T3" t="n">
         <v>21.6</v>
       </c>
+      <c r="V3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
@@ -806,10 +824,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>82.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -821,7 +839,16 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>14</v>
@@ -871,10 +898,10 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>78.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="O5" t="n">
-        <v>32.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -886,7 +913,16 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y5" t="n">
         <v>14</v>
@@ -974,6 +1010,15 @@
       <c r="T6" t="n">
         <v>21.6</v>
       </c>
+      <c r="V6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1060,6 +1105,15 @@
       <c r="T7" t="n">
         <v>21.1</v>
       </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
@@ -1146,6 +1200,15 @@
       <c r="T8" t="n">
         <v>21.3</v>
       </c>
+      <c r="V8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
@@ -1232,6 +1295,15 @@
       <c r="T9" t="n">
         <v>20.9</v>
       </c>
+      <c r="V9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
@@ -1318,6 +1390,15 @@
       <c r="T10" t="n">
         <v>21</v>
       </c>
+      <c r="V10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1360,10 +1441,10 @@
         <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>92.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>38</v>
+        <v>39.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1375,7 +1456,16 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
         <v>5</v>
@@ -1425,10 +1515,10 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>87.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="O12" t="n">
-        <v>36.1</v>
+        <v>37.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1440,7 +1530,16 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
@@ -1490,10 +1589,10 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>88.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1505,7 +1604,16 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y13" t="n">
         <v>3</v>
@@ -1593,6 +1701,15 @@
       <c r="T14" t="n">
         <v>22.4</v>
       </c>
+      <c r="V14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>4</v>
       </c>
@@ -1679,6 +1796,15 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y15" t="n">
         <v>6</v>
       </c>
@@ -1777,6 +1903,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1837,10 +1972,10 @@
         <v>6.5</v>
       </c>
       <c r="K17" t="n">
-        <v>101.1</v>
+        <v>100.1</v>
       </c>
       <c r="O17" t="n">
-        <v>41.5</v>
+        <v>43.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1852,7 +1987,16 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y17" t="n">
         <v>8</v>
@@ -1914,10 +2058,10 @@
         <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>95.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>39.2</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1929,7 +2073,16 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y18" t="n">
         <v>10</v>
@@ -1991,10 +2144,10 @@
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>85.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>35</v>
+        <v>36.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2006,7 +2159,16 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -2068,10 +2230,10 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>78.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>32.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2083,7 +2245,16 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -2183,6 +2354,15 @@
       <c r="T21" t="n">
         <v>23.2</v>
       </c>
+      <c r="V21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2281,6 +2461,15 @@
       <c r="T22" t="n">
         <v>23.8</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>7</v>
       </c>
@@ -2379,6 +2568,15 @@
       <c r="T23" t="n">
         <v>23.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y23" t="n">
         <v>6</v>
       </c>
@@ -2477,6 +2675,15 @@
       <c r="T24" t="n">
         <v>23.7</v>
       </c>
+      <c r="V24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2537,10 +2744,10 @@
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>92.8</v>
+        <v>92</v>
       </c>
       <c r="O25" t="n">
-        <v>38.2</v>
+        <v>39.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2552,7 +2759,16 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
         <v>6</v>
@@ -2614,10 +2830,10 @@
         <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>87</v>
+        <v>86.3</v>
       </c>
       <c r="O26" t="n">
-        <v>35.7</v>
+        <v>37.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2629,7 +2845,16 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y26" t="n">
         <v>4</v>
@@ -2729,6 +2954,15 @@
       <c r="T27" t="n">
         <v>23.5</v>
       </c>
+      <c r="V27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>4</v>
       </c>
@@ -2827,6 +3061,15 @@
       <c r="T28" t="n">
         <v>23.1</v>
       </c>
+      <c r="V28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y28" t="n">
         <v>7</v>
       </c>
@@ -2925,6 +3168,15 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3023,6 +3275,15 @@
       <c r="T30" t="n">
         <v>23.2</v>
       </c>
+      <c r="V30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3121,6 +3382,15 @@
       <c r="T31" t="n">
         <v>23.2</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y31" t="n">
         <v>10</v>
       </c>
@@ -3181,10 +3451,10 @@
         <v>6.1</v>
       </c>
       <c r="K32" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="O32" t="n">
-        <v>34.1</v>
+        <v>35.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3196,7 +3466,16 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X32" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y32" t="n">
         <v>9</v>
@@ -3258,10 +3537,10 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3273,7 +3552,16 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
@@ -3373,6 +3661,15 @@
       <c r="T34" t="n">
         <v>21.4</v>
       </c>
+      <c r="V34" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3471,6 +3768,15 @@
       <c r="T35" t="n">
         <v>19.7</v>
       </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>12</v>
       </c>
@@ -3569,6 +3875,15 @@
       <c r="T36" t="n">
         <v>20.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3667,6 +3982,15 @@
       <c r="T37" t="n">
         <v>21.6</v>
       </c>
+      <c r="V37" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>11</v>
       </c>
@@ -3765,6 +4089,15 @@
       <c r="T38" t="n">
         <v>21</v>
       </c>
+      <c r="V38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -3825,10 +4158,10 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>32.3</v>
+        <v>33.8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3840,7 +4173,16 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y39" t="n">
         <v>7</v>
@@ -3902,10 +4244,10 @@
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>82.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="O40" t="n">
-        <v>33.8</v>
+        <v>35.3</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3917,7 +4259,16 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="V40" t="n">
+        <v>11</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22</v>
+      </c>
+      <c r="X40" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y40" t="n">
         <v>7</v>
@@ -4017,6 +4368,15 @@
       <c r="T41" t="n">
         <v>23.7</v>
       </c>
+      <c r="V41" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y41" t="n">
         <v>3</v>
       </c>
@@ -4115,6 +4475,15 @@
       <c r="T42" t="n">
         <v>23.9</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y42" t="n">
         <v>5</v>
       </c>
@@ -4213,6 +4582,15 @@
       <c r="T43" t="n">
         <v>21.7</v>
       </c>
+      <c r="V43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>21</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y43" t="n">
         <v>9</v>
       </c>
@@ -4311,6 +4689,15 @@
       <c r="T44" t="n">
         <v>21.7</v>
       </c>
+      <c r="V44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W44" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y44" t="n">
         <v>10</v>
       </c>
@@ -4409,6 +4796,15 @@
       <c r="T45" t="n">
         <v>22</v>
       </c>
+      <c r="V45" t="n">
+        <v>11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y45" t="n">
         <v>10.4</v>
       </c>
@@ -4504,6 +4900,15 @@
       <c r="T46" t="n">
         <v>22.3</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X46" t="n">
+        <v>18</v>
+      </c>
       <c r="Y46" t="n">
         <v>12.1</v>
       </c>
@@ -4599,6 +5004,15 @@
       <c r="T47" t="n">
         <v>23.6</v>
       </c>
+      <c r="V47" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>7.7</v>
       </c>
@@ -4697,6 +5111,15 @@
       <c r="T48" t="n">
         <v>23.8</v>
       </c>
+      <c r="V48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>11</v>
+      </c>
+      <c r="X48" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y48" t="n">
         <v>3.4</v>
       </c>
@@ -4795,6 +5218,15 @@
       <c r="T49" t="n">
         <v>23.8</v>
       </c>
+      <c r="V49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X49" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y49" t="n">
         <v>6</v>
       </c>
@@ -4893,6 +5325,15 @@
       <c r="T50" t="n">
         <v>22.1</v>
       </c>
+      <c r="V50" t="n">
+        <v>4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X50" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y50" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4991,6 +5432,15 @@
       <c r="T51" t="n">
         <v>23.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26</v>
+      </c>
+      <c r="X51" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y51" t="n">
         <v>5.3</v>
       </c>
@@ -5089,6 +5539,15 @@
       <c r="T52" t="n">
         <v>23.3</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y52" t="n">
         <v>11.1</v>
       </c>
@@ -5184,6 +5643,24 @@
       <c r="T53" t="n">
         <v>20</v>
       </c>
+      <c r="V53" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>17.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>3.6</v>
       </c>
@@ -5270,6 +5747,24 @@
       <c r="T54" t="n">
         <v>15</v>
       </c>
+      <c r="V54" t="n">
+        <v>16</v>
+      </c>
+      <c r="W54" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X54" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>18.1</v>
+      </c>
       <c r="AB54" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -5359,6 +5854,21 @@
       <c r="T55" t="n">
         <v>10.5</v>
       </c>
+      <c r="V55" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W55" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X55" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>23</v>
+      </c>
       <c r="AA55" t="n">
         <v>16.9</v>
       </c>
@@ -5451,6 +5961,21 @@
       <c r="T56" t="n">
         <v>18.3</v>
       </c>
+      <c r="V56" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X56" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AA56" t="n">
         <v>13.8</v>
       </c>
@@ -5543,6 +6068,21 @@
       <c r="T57" t="n">
         <v>20.2</v>
       </c>
+      <c r="V57" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X57" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA57" t="n">
         <v>9.6</v>
       </c>
@@ -5588,40 +6128,43 @@
         <v>46288</v>
       </c>
       <c r="B58" t="n">
-        <v>128</v>
+        <v>117.2</v>
       </c>
       <c r="C58" t="n">
-        <v>58.3</v>
+        <v>53.7</v>
       </c>
       <c r="D58" t="n">
-        <v>35.5</v>
+        <v>34.7</v>
       </c>
       <c r="E58" t="n">
-        <v>28.7</v>
+        <v>20.1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.2</v>
       </c>
       <c r="H58" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J58" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K58" t="n">
-        <v>73.2</v>
+        <v>69.8</v>
       </c>
       <c r="M58" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N58" t="n">
-        <v>27</v>
+        <v>31.4</v>
       </c>
       <c r="O58" t="n">
-        <v>29.1</v>
+        <v>33.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -5630,7 +6173,25 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>22</v>
+        <v>22.3</v>
+      </c>
+      <c r="V58" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W58" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>14</v>
       </c>
       <c r="AB58" t="n">
         <v>5.1</v>
@@ -5646,6 +6207,12 @@
       </c>
       <c r="AG58" t="n">
         <v>7.23</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>131.96</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.95</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46288</v>
@@ -5668,37 +6235,37 @@
         <v>46289</v>
       </c>
       <c r="B59" t="n">
-        <v>120.8</v>
+        <v>118.1</v>
       </c>
       <c r="C59" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="D59" t="n">
-        <v>36.1</v>
+        <v>35.3</v>
       </c>
       <c r="E59" t="n">
         <v>27.62</v>
       </c>
       <c r="H59" t="n">
-        <v>24.2</v>
+        <v>21.7</v>
       </c>
       <c r="I59" t="n">
         <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K59" t="n">
-        <v>73.2</v>
+        <v>68.7</v>
       </c>
       <c r="M59" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N59" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="O59" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q59" t="n">
         <v>22</v>
@@ -5711,6 +6278,39 @@
       </c>
       <c r="T59" t="n">
         <v>22</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W59" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X59" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>233.59</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>5.53</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
@@ -5721,40 +6321,40 @@
         <v>46290</v>
       </c>
       <c r="B60" t="n">
-        <v>116.9</v>
+        <v>115.9</v>
       </c>
       <c r="C60" t="n">
-        <v>46.4</v>
+        <v>45.7</v>
       </c>
       <c r="D60" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="E60" t="n">
         <v>28.79</v>
       </c>
       <c r="H60" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="I60" t="n">
         <v>9</v>
       </c>
       <c r="J60" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K60" t="n">
-        <v>73</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N60" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="O60" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -5763,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46290</v>
@@ -5774,40 +6374,40 @@
         <v>46291</v>
       </c>
       <c r="B61" t="n">
-        <v>112.1</v>
+        <v>111.1</v>
       </c>
       <c r="C61" t="n">
-        <v>44.9</v>
+        <v>44.2</v>
       </c>
       <c r="D61" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="E61" t="n">
         <v>27.23</v>
       </c>
       <c r="H61" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="I61" t="n">
         <v>9</v>
       </c>
       <c r="J61" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>73</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N61" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="O61" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -5816,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46291</v>
@@ -5827,40 +6427,40 @@
         <v>46292</v>
       </c>
       <c r="B62" t="n">
-        <v>107.6</v>
+        <v>105.9</v>
       </c>
       <c r="C62" t="n">
-        <v>42.4</v>
+        <v>40.9</v>
       </c>
       <c r="D62" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E62" t="n">
         <v>25.96</v>
       </c>
       <c r="H62" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="I62" t="n">
         <v>9</v>
       </c>
       <c r="J62" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K62" t="n">
-        <v>73</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N62" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="O62" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -5869,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6315,6 +6315,18 @@
       <c r="BL59" s="1" t="n">
         <v>46289</v>
       </c>
+      <c r="BM59" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6312,6 +6312,12 @@
       <c r="AG59" t="n">
         <v>5.53</v>
       </c>
+      <c r="AK59" t="n">
+        <v>132.79</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.83</v>
+      </c>
       <c r="BL59" s="1" t="n">
         <v>46289</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -628,206 +628,200 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B2" t="n">
-        <v>172.9</v>
+        <v>160.4</v>
       </c>
       <c r="C2" t="n">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="D2" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>35.2</v>
+        <v>32.2</v>
       </c>
       <c r="F2" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="H2" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="I2" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="J2" t="n">
-        <v>41.7</v>
+        <v>41.1</v>
       </c>
       <c r="K2" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M2" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="N2" t="n">
-        <v>34.8</v>
+        <v>32.6</v>
       </c>
       <c r="O2" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>16.4</v>
       </c>
       <c r="W2" t="n">
-        <v>18.7</v>
+        <v>22.8</v>
       </c>
       <c r="X2" t="n">
-        <v>16.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-4.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>218.6</v>
+        <v>225.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>130.39</v>
+        <v>135.24</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B3" t="n">
-        <v>157.5</v>
+        <v>161.7</v>
       </c>
       <c r="C3" t="n">
-        <v>68.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>33.2</v>
+        <v>34.9</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7</v>
+        <v>27.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="I3" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="J3" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="K3" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="N3" t="n">
-        <v>34.9</v>
+        <v>31.5</v>
       </c>
       <c r="O3" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21</v>
+      </c>
+      <c r="V3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y3" t="n">
         <v>9</v>
       </c>
-      <c r="T3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>11</v>
-      </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>-5.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>218.84</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.24</v>
+        <v>-0.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.09</v>
+        <v>134.62</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.7</v>
+        <v>-0.62</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B4" t="n">
-        <v>137.6</v>
+        <v>151.5</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>81.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>35.4</v>
+        <v>39.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -842,66 +836,66 @@
         <v>20.3</v>
       </c>
       <c r="V4" t="n">
-        <v>13.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>24.4</v>
+        <v>19.4</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>-4.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.8</v>
+        <v>-1.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>221.78</v>
+        <v>221.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.94</v>
+        <v>-3.71</v>
       </c>
       <c r="AK4" t="n">
-        <v>138.76</v>
+        <v>135.21</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.67</v>
+        <v>0.59</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B5" t="n">
-        <v>132.5</v>
+        <v>145.2</v>
       </c>
       <c r="D5" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>78.3</v>
+        <v>87.2</v>
       </c>
       <c r="O5" t="n">
-        <v>33.9</v>
+        <v>37.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -916,535 +910,535 @@
         <v>20.3</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>24.7</v>
+        <v>19.2</v>
       </c>
       <c r="X5" t="n">
-        <v>19.8</v>
+        <v>13.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>224.78</v>
+        <v>224.37</v>
       </c>
       <c r="AG5" t="n">
         <v>3</v>
       </c>
       <c r="AK5" t="n">
-        <v>143.55</v>
+        <v>135.61</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.79</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B6" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>56.3</v>
+        <v>146.3</v>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>21.2</v>
+        <v>33.4</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>40.4</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>29</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>32.6</v>
+        <v>38.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>21.6</v>
+        <v>20.3</v>
       </c>
       <c r="V6" t="n">
-        <v>10.7</v>
+        <v>4.9</v>
       </c>
       <c r="W6" t="n">
-        <v>24.3</v>
+        <v>16.4</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>10.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="n">
         <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9</v>
+        <v>-6.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>232.22</v>
+        <v>225.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.44</v>
+        <v>1.56</v>
       </c>
       <c r="AK6" t="n">
-        <v>143.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.06</v>
+        <v>-0.33</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B7" t="n">
-        <v>157.5</v>
+        <v>182.8</v>
       </c>
       <c r="C7" t="n">
-        <v>59.6</v>
+        <v>86.8</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="E7" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="J7" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="K7" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="N7" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="O7" t="n">
-        <v>37.1</v>
+        <v>38.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="W7" t="n">
-        <v>26.3</v>
+        <v>15</v>
       </c>
       <c r="X7" t="n">
-        <v>19.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.1</v>
+        <v>-10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>-5.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>229.69</v>
+        <v>218.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.53</v>
+        <v>-7.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>136.96</v>
+        <v>126.27</v>
       </c>
       <c r="AL7" t="n">
-        <v>-6.65</v>
+        <v>-9.01</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="B8" t="n">
-        <v>159.6</v>
+        <v>181.8</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>86.5</v>
       </c>
       <c r="D8" t="n">
-        <v>34.5</v>
+        <v>31.4</v>
       </c>
       <c r="E8" t="n">
-        <v>31.1</v>
+        <v>34.2</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H8" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="J8" t="n">
-        <v>40.5</v>
+        <v>41.9</v>
       </c>
       <c r="K8" t="n">
-        <v>75.2</v>
+        <v>76.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3</v>
+        <v>35.7</v>
       </c>
       <c r="O8" t="n">
-        <v>38.2</v>
+        <v>39.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>20.1</v>
       </c>
       <c r="T8" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>17.5</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>22.5</v>
+        <v>14.8</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>10.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>228.57</v>
+        <v>216.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.12</v>
+        <v>-2.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.01</v>
+        <v>123.32</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3.95</v>
+        <v>-2.95</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4649.3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2021.1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>3016.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="B9" t="n">
-        <v>160.4</v>
+        <v>183</v>
       </c>
       <c r="C9" t="n">
-        <v>62.6</v>
+        <v>84.7</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>30.9</v>
       </c>
       <c r="E9" t="n">
-        <v>32.2</v>
+        <v>33.7</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="J9" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K9" t="n">
-        <v>75.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>32.6</v>
+        <v>36.7</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>40.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y9" t="n">
         <v>8</v>
       </c>
-      <c r="T9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="V9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>13</v>
       </c>
-      <c r="Z9" t="n">
-        <v>16</v>
-      </c>
       <c r="AA9" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.1</v>
+        <v>0.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>225.08</v>
+        <v>217.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.49</v>
+        <v>0.77</v>
       </c>
       <c r="AK9" t="n">
-        <v>135.24</v>
+        <v>117.87</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.23</v>
+        <v>-5.45</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6995.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2380.8</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>3192.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B10" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>71.09999999999999</v>
+        <v>163.8</v>
       </c>
       <c r="D10" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>27.3</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>42.6</v>
+        <v>6.5</v>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>31.5</v>
+        <v>100.1</v>
       </c>
       <c r="O10" t="n">
-        <v>37.3</v>
+        <v>43.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>21</v>
+        <v>20.3</v>
       </c>
       <c r="V10" t="n">
-        <v>12.7</v>
+        <v>6.3</v>
       </c>
       <c r="W10" t="n">
-        <v>27</v>
+        <v>17.2</v>
       </c>
       <c r="X10" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.2</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3</v>
+        <v>2.8</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.62</v>
+        <v>116.52</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.62</v>
+        <v>-1.35</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>2827.2</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>3152.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B11" t="n">
-        <v>151.5</v>
+        <v>155.9</v>
       </c>
       <c r="D11" t="n">
-        <v>35.1</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>91.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>39.6</v>
+        <v>41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1459,66 +1453,78 @@
         <v>20.3</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
-        <v>19.4</v>
+        <v>15.8</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
         <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.7</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.37</v>
+        <v>221.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>-3.71</v>
+        <v>1.68</v>
       </c>
       <c r="AK11" t="n">
-        <v>135.21</v>
+        <v>116.37</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.59</v>
+        <v>-0.15</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>3609.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1161.2</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>3077.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B12" t="n">
-        <v>145.2</v>
+        <v>141.3</v>
       </c>
       <c r="D12" t="n">
-        <v>33.5</v>
+        <v>26.3</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K12" t="n">
-        <v>87.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>37.7</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1533,66 +1539,78 @@
         <v>20.3</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="W12" t="n">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
       <c r="X12" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB12" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>224.37</v>
+        <v>225.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>135.61</v>
+        <v>120.64</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.4</v>
+        <v>4.27</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1884.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>2636.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B13" t="n">
-        <v>146.3</v>
+        <v>131.5</v>
       </c>
       <c r="D13" t="n">
-        <v>33.4</v>
+        <v>27.3</v>
       </c>
       <c r="F13" t="n">
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>87.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>38.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1607,461 +1625,506 @@
         <v>20.3</v>
       </c>
       <c r="V13" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>16.4</v>
+        <v>13.9</v>
       </c>
       <c r="X13" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA13" t="n">
         <v>15</v>
       </c>
-      <c r="AA13" t="n">
-        <v>9</v>
-      </c>
       <c r="AB13" t="n">
-        <v>-6.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>-3.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>225.93</v>
+        <v>229.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>4.84</v>
       </c>
       <c r="AK13" t="n">
-        <v>135.28</v>
+        <v>128.14</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.33</v>
+        <v>7.5</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1894.8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B14" t="n">
-        <v>182.8</v>
+        <v>153</v>
       </c>
       <c r="C14" t="n">
-        <v>86.8</v>
+        <v>71.8</v>
       </c>
       <c r="D14" t="n">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>24.7</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="I14" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="J14" t="n">
         <v>41.1</v>
       </c>
       <c r="K14" t="n">
-        <v>74.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
         <v>33.5</v>
       </c>
       <c r="O14" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X14" t="n">
         <v>12.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="n">
-        <v>-10.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>218.63</v>
+        <v>229.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>-7.3</v>
+        <v>-0.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>126.27</v>
+        <v>128.15</v>
       </c>
       <c r="AL14" t="n">
-        <v>-9.01</v>
+        <v>0.01</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>2723.2</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B15" t="n">
-        <v>181.8</v>
+        <v>165.8</v>
       </c>
       <c r="C15" t="n">
-        <v>86.5</v>
+        <v>77.3</v>
       </c>
       <c r="D15" t="n">
-        <v>31.4</v>
+        <v>29.3</v>
       </c>
       <c r="E15" t="n">
-        <v>34.2</v>
+        <v>27.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H15" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="I15" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="J15" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="K15" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>35.7</v>
+        <v>35.1</v>
       </c>
       <c r="O15" t="n">
         <v>39.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>20.1</v>
+        <v>7</v>
       </c>
       <c r="T15" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="W15" t="n">
-        <v>14.8</v>
+        <v>17.4</v>
       </c>
       <c r="X15" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>-1.4</v>
+        <v>4.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>216.39</v>
+        <v>227.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>-2.24</v>
+        <v>-2.95</v>
       </c>
       <c r="AK15" t="n">
-        <v>123.32</v>
+        <v>128.86</v>
       </c>
       <c r="AL15" t="n">
-        <v>-2.95</v>
+        <v>0.71</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="BM15" t="n">
-        <v>40.72</v>
+        <v>33.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>4649.3</v>
+        <v>6652.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>2021.1</v>
+        <v>1412.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>3016.3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B16" t="n">
-        <v>183</v>
+        <v>158.1</v>
       </c>
       <c r="C16" t="n">
-        <v>84.7</v>
+        <v>73.7</v>
       </c>
       <c r="D16" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="E16" t="n">
-        <v>33.7</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="H16" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="I16" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="K16" t="n">
-        <v>76.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>36.7</v>
+        <v>35.3</v>
       </c>
       <c r="O16" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q16" t="n">
         <v>23.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="W16" t="n">
-        <v>16.1</v>
+        <v>19.3</v>
       </c>
       <c r="X16" t="n">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>217.16</v>
+        <v>228.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.77</v>
+        <v>1.34</v>
       </c>
       <c r="AK16" t="n">
-        <v>117.87</v>
+        <v>130.88</v>
       </c>
       <c r="AL16" t="n">
-        <v>-5.45</v>
+        <v>2.02</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="BM16" t="n">
-        <v>40.4</v>
+        <v>32.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>6995.8</v>
+        <v>4993.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>2380.8</v>
+        <v>958.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>3192.8</v>
+        <v>2899.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B17" t="n">
-        <v>163.8</v>
+        <v>154.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>70.2</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>31.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>27.7</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.3</v>
       </c>
       <c r="K17" t="n">
-        <v>100.1</v>
+        <v>75.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>32.9</v>
       </c>
       <c r="O17" t="n">
-        <v>43.4</v>
+        <v>39</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T17" t="n">
-        <v>20.3</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
         <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>17.2</v>
+        <v>25.2</v>
       </c>
       <c r="X17" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>220.31</v>
+        <v>231.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="AK17" t="n">
-        <v>116.52</v>
+        <v>132.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="BM17" t="n">
-        <v>39.65</v>
+        <v>33.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>2827.2</v>
+        <v>1514.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>2051.2</v>
+        <v>799.7</v>
       </c>
       <c r="BP17" t="n">
-        <v>3152.1</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B18" t="n">
-        <v>155.9</v>
+        <v>152.2</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>94.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="O18" t="n">
-        <v>41</v>
+        <v>39.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2076,78 +2139,78 @@
         <v>20.3</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W18" t="n">
-        <v>15.8</v>
+        <v>25.5</v>
       </c>
       <c r="X18" t="n">
-        <v>12.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>221.99</v>
+        <v>228.13</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.68</v>
+        <v>-3.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>116.37</v>
+        <v>128.02</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.15</v>
+        <v>-4.53</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="BM18" t="n">
-        <v>34.79</v>
+        <v>35.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>3609.5</v>
+        <v>1526.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1161.2</v>
+        <v>957.4</v>
       </c>
       <c r="BP18" t="n">
-        <v>3077.1</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B19" t="n">
-        <v>141.3</v>
+        <v>143.9</v>
       </c>
       <c r="D19" t="n">
-        <v>26.3</v>
+        <v>30.8</v>
       </c>
       <c r="F19" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>84.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="O19" t="n">
-        <v>36.6</v>
+        <v>37.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2162,592 +2225,613 @@
         <v>20.3</v>
       </c>
       <c r="V19" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W19" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="X19" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AF19" t="n">
-        <v>225.14</v>
+        <v>229.16</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK19" t="n">
-        <v>120.64</v>
+        <v>127.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.27</v>
+        <v>-0.96</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="BM19" t="n">
-        <v>31.22</v>
+        <v>34.56</v>
       </c>
       <c r="BN19" t="n">
-        <v>1884.4</v>
+        <v>170.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>785.2</v>
+        <v>130.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>2636.2</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B20" t="n">
-        <v>131.5</v>
+        <v>163.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>73.7</v>
       </c>
       <c r="D20" t="n">
-        <v>27.3</v>
+        <v>30</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28.2</v>
       </c>
       <c r="F20" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>40.1</v>
       </c>
       <c r="K20" t="n">
-        <v>77.59999999999999</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>32.9</v>
       </c>
       <c r="O20" t="n">
-        <v>33.6</v>
+        <v>39.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>20.3</v>
+        <v>23.5</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W20" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="X20" t="n">
-        <v>11.4</v>
+        <v>14.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.4</v>
+        <v>4.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>229.98</v>
+        <v>228.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.84</v>
+        <v>-0.61</v>
       </c>
       <c r="AK20" t="n">
-        <v>128.14</v>
+        <v>125.61</v>
       </c>
       <c r="AL20" t="n">
-        <v>7.5</v>
+        <v>-1.45</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="BM20" t="n">
-        <v>26.41</v>
+        <v>34.78</v>
       </c>
       <c r="BN20" t="n">
-        <v>1894.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO20" t="n">
-        <v>223.6</v>
+        <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B21" t="n">
-        <v>153</v>
+        <v>174.4</v>
       </c>
       <c r="C21" t="n">
-        <v>71.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>28.6</v>
+        <v>32.1</v>
       </c>
       <c r="E21" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="H21" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I21" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="K21" t="n">
-        <v>75.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="M21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD21" t="n">
         <v>4.8</v>
       </c>
-      <c r="N21" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF21" t="n">
-        <v>229.96</v>
+        <v>219.99</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.02</v>
+        <v>-8.56</v>
       </c>
       <c r="AK21" t="n">
-        <v>128.15</v>
+        <v>124.36</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.01</v>
+        <v>-1.25</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="BM21" t="n">
-        <v>29.83</v>
+        <v>36.78</v>
       </c>
       <c r="BN21" t="n">
-        <v>2723.2</v>
+        <v>108.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>271.1</v>
+        <v>204.3</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B22" t="n">
-        <v>165.8</v>
+        <v>163.2</v>
       </c>
       <c r="C22" t="n">
-        <v>77.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>29.3</v>
+        <v>32.9</v>
       </c>
       <c r="E22" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="H22" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="J22" t="n">
-        <v>41.6</v>
+        <v>40.1</v>
       </c>
       <c r="K22" t="n">
-        <v>76.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="N22" t="n">
-        <v>35.1</v>
+        <v>34.3</v>
       </c>
       <c r="O22" t="n">
-        <v>39.8</v>
+        <v>41.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="V22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W22" t="n">
-        <v>17.4</v>
+        <v>23.3</v>
       </c>
       <c r="X22" t="n">
-        <v>13.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>227.01</v>
+        <v>219.22</v>
       </c>
       <c r="AG22" t="n">
-        <v>-2.95</v>
+        <v>-0.77</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.86</v>
+        <v>120.93</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.71</v>
+        <v>-3.43</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="BM22" t="n">
-        <v>33.62</v>
+        <v>32.64</v>
       </c>
       <c r="BN22" t="n">
-        <v>6652.6</v>
+        <v>42.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>1412.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP22" t="n">
-        <v>408</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B23" t="n">
-        <v>158.1</v>
+        <v>152.7</v>
       </c>
       <c r="C23" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D23" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I23" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J23" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="K23" t="n">
-        <v>74.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="N23" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="O23" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="V23" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="W23" t="n">
-        <v>19.3</v>
+        <v>27.3</v>
       </c>
       <c r="X23" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>228.35</v>
+        <v>220.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AK23" t="n">
-        <v>130.88</v>
+        <v>120.28</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.02</v>
+        <v>-0.65</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="BM23" t="n">
-        <v>32.38</v>
+        <v>29.61</v>
       </c>
       <c r="BN23" t="n">
-        <v>4993.3</v>
+        <v>60.1</v>
       </c>
       <c r="BO23" t="n">
-        <v>958.6</v>
+        <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2899.8</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B24" t="n">
-        <v>154.9</v>
+        <v>150.7</v>
       </c>
       <c r="C24" t="n">
-        <v>70.2</v>
+        <v>64.8</v>
       </c>
       <c r="D24" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="E24" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H24" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I24" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="K24" t="n">
-        <v>75.8</v>
+        <v>70.5</v>
       </c>
       <c r="M24" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="O24" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="V24" t="n">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="W24" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="X24" t="n">
-        <v>15.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>231.16</v>
+        <v>220.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.81</v>
+        <v>-0.15</v>
       </c>
       <c r="AK24" t="n">
-        <v>132.55</v>
+        <v>119.29</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.67</v>
+        <v>-0.99</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="BM24" t="n">
-        <v>33.01</v>
+        <v>31.11</v>
       </c>
       <c r="BN24" t="n">
-        <v>1514.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO24" t="n">
-        <v>799.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP24" t="n">
-        <v>2923.4</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B25" t="n">
-        <v>152.2</v>
+        <v>138.2</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>33.6</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="K25" t="n">
-        <v>92</v>
+        <v>82.3</v>
       </c>
       <c r="O25" t="n">
-        <v>39.9</v>
+        <v>35.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2762,78 +2846,78 @@
         <v>20.3</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="W25" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB25" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.13</v>
+        <v>223.43</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AK25" t="n">
-        <v>128.02</v>
+        <v>121.35</v>
       </c>
       <c r="AL25" t="n">
-        <v>-4.53</v>
+        <v>2.06</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="BM25" t="n">
-        <v>35.62</v>
+        <v>30.59</v>
       </c>
       <c r="BN25" t="n">
-        <v>1526.5</v>
+        <v>40.8</v>
       </c>
       <c r="BO25" t="n">
-        <v>957.4</v>
+        <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>2928.4</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B26" t="n">
-        <v>143.9</v>
+        <v>126.5</v>
       </c>
       <c r="D26" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>86.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>37.3</v>
+        <v>32.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2848,613 +2932,613 @@
         <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>10.7</v>
+        <v>12.6</v>
       </c>
       <c r="W26" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="X26" t="n">
-        <v>14.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>229.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.03</v>
+        <v>6.05</v>
       </c>
       <c r="AK26" t="n">
-        <v>127.06</v>
+        <v>128.37</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.96</v>
+        <v>7.02</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="BM26" t="n">
-        <v>34.56</v>
+        <v>30.05</v>
       </c>
       <c r="BN26" t="n">
-        <v>170.6</v>
+        <v>34</v>
       </c>
       <c r="BO26" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>2825.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B27" t="n">
-        <v>163.2</v>
+        <v>129.4</v>
       </c>
       <c r="C27" t="n">
-        <v>73.7</v>
+        <v>50.6</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E27" t="n">
-        <v>28.2</v>
+        <v>19.4</v>
       </c>
       <c r="F27" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H27" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I27" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="J27" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
       <c r="K27" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M27" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="N27" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="O27" t="n">
-        <v>39.7</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="R27" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="V27" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="W27" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="X27" t="n">
-        <v>14.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y27" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
         <v>4</v>
       </c>
-      <c r="Z27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF27" t="n">
-        <v>228.55</v>
+        <v>241.48</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.61</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>125.61</v>
+        <v>134.59</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.45</v>
+        <v>6.22</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="BM27" t="n">
-        <v>34.78</v>
+        <v>24.86</v>
       </c>
       <c r="BN27" t="n">
-        <v>69.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="BO27" t="n">
         <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>2769.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B28" t="n">
-        <v>174.4</v>
+        <v>142.9</v>
       </c>
       <c r="C28" t="n">
-        <v>75.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="D28" t="n">
-        <v>32.1</v>
+        <v>34.7</v>
       </c>
       <c r="E28" t="n">
-        <v>30.8</v>
+        <v>24.8</v>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="J28" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="K28" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M28" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O28" t="n">
         <v>35.8</v>
       </c>
-      <c r="O28" t="n">
-        <v>42.6</v>
-      </c>
       <c r="Q28" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="S28" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="V28" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
       <c r="X28" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>219.99</v>
+        <v>238.69</v>
       </c>
       <c r="AG28" t="n">
-        <v>-8.56</v>
+        <v>-2.79</v>
       </c>
       <c r="AK28" t="n">
-        <v>124.36</v>
+        <v>136.6</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.25</v>
+        <v>2.01</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="BM28" t="n">
-        <v>36.78</v>
+        <v>29.8</v>
       </c>
       <c r="BN28" t="n">
-        <v>108.8</v>
+        <v>61.9</v>
       </c>
       <c r="BO28" t="n">
-        <v>204.3</v>
+        <v>0</v>
       </c>
       <c r="BP28" t="n">
-        <v>2982.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B29" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C29" t="n">
-        <v>70.90000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D29" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="F29" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H29" t="n">
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J29" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K29" t="n">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="M29" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="O29" t="n">
-        <v>41.5</v>
+        <v>33.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="S29" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="V29" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
-        <v>23.3</v>
+        <v>25.5</v>
       </c>
       <c r="X29" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>219.22</v>
+        <v>233.48</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.77</v>
+        <v>-5.21</v>
       </c>
       <c r="AK29" t="n">
-        <v>120.93</v>
+        <v>135.66</v>
       </c>
       <c r="AL29" t="n">
-        <v>-3.43</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="BM29" t="n">
-        <v>32.64</v>
+        <v>36.03</v>
       </c>
       <c r="BN29" t="n">
-        <v>42.3</v>
+        <v>76.5</v>
       </c>
       <c r="BO29" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>3194.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B30" t="n">
-        <v>152.7</v>
+        <v>143.4</v>
       </c>
       <c r="C30" t="n">
-        <v>62.6</v>
+        <v>50.9</v>
       </c>
       <c r="D30" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="E30" t="n">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="F30" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="H30" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="I30" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K30" t="n">
-        <v>69.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>33.5</v>
+        <v>31.2</v>
       </c>
       <c r="O30" t="n">
-        <v>40.1</v>
+        <v>33.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="R30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="V30" t="n">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="W30" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="X30" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>220.73</v>
+        <v>235.13</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AK30" t="n">
-        <v>120.28</v>
+        <v>136.33</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="BM30" t="n">
-        <v>29.61</v>
+        <v>32</v>
       </c>
       <c r="BN30" t="n">
-        <v>60.1</v>
+        <v>29.5</v>
       </c>
       <c r="BO30" t="n">
         <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>2717.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B31" t="n">
-        <v>150.7</v>
+        <v>144.9</v>
       </c>
       <c r="C31" t="n">
-        <v>64.8</v>
+        <v>53</v>
       </c>
       <c r="D31" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
       <c r="E31" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>21</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>21</v>
+      </c>
+      <c r="V31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>234.87</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>137.17</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BL31" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="BN31" t="n">
         <v>23.4</v>
       </c>
-      <c r="I31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N31" t="n">
-        <v>33</v>
-      </c>
-      <c r="O31" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>119.29</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="BL31" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>87.90000000000001</v>
-      </c>
       <c r="BO31" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP31" t="n">
-        <v>3028.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B32" t="n">
-        <v>138.2</v>
+        <v>132.2</v>
       </c>
       <c r="D32" t="n">
-        <v>33.6</v>
+        <v>35.6</v>
       </c>
       <c r="F32" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>82.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>35.6</v>
+        <v>33.8</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3469,78 +3553,78 @@
         <v>20.3</v>
       </c>
       <c r="V32" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="W32" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="X32" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
         <v>13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>223.43</v>
+        <v>234.78</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.85</v>
+        <v>-0.09</v>
       </c>
       <c r="AK32" t="n">
-        <v>121.35</v>
+        <v>136.08</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.06</v>
+        <v>-1.09</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="BM32" t="n">
-        <v>30.59</v>
+        <v>29.64</v>
       </c>
       <c r="BN32" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="BO32" t="n">
         <v>0</v>
       </c>
       <c r="BP32" t="n">
-        <v>2959.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B33" t="n">
-        <v>126.5</v>
+        <v>137.1</v>
       </c>
       <c r="D33" t="n">
-        <v>33.2</v>
+        <v>35.1</v>
       </c>
       <c r="F33" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>74.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="O33" t="n">
-        <v>32.1</v>
+        <v>35.3</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3555,52 +3639,52 @@
         <v>20.3</v>
       </c>
       <c r="V33" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="W33" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="X33" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA33" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>229.48</v>
+        <v>229.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>6.05</v>
+        <v>-5.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>128.37</v>
+        <v>135.42</v>
       </c>
       <c r="AL33" t="n">
-        <v>7.02</v>
+        <v>-0.66</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="BM33" t="n">
-        <v>30.05</v>
+        <v>31.45</v>
       </c>
       <c r="BN33" t="n">
-        <v>34</v>
+        <v>35.9</v>
       </c>
       <c r="BO33" t="n">
         <v>0</v>
@@ -3611,1981 +3695,2014 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B34" t="n">
-        <v>129.4</v>
+        <v>148.7</v>
       </c>
       <c r="C34" t="n">
-        <v>50.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E34" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H34" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="J34" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="K34" t="n">
-        <v>73.3</v>
+        <v>74.5</v>
       </c>
       <c r="M34" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="N34" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="O34" t="n">
-        <v>38</v>
+        <v>39.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="V34" t="n">
-        <v>14.3</v>
+        <v>7.9</v>
       </c>
       <c r="W34" t="n">
-        <v>23.9</v>
+        <v>15.6</v>
       </c>
       <c r="X34" t="n">
-        <v>19.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA34" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>241.48</v>
+        <v>222.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>12</v>
+        <v>-6.89</v>
       </c>
       <c r="AK34" t="n">
-        <v>134.59</v>
+        <v>131.24</v>
       </c>
       <c r="AL34" t="n">
-        <v>6.22</v>
+        <v>-4.18</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="BM34" t="n">
-        <v>24.86</v>
+        <v>34.46</v>
       </c>
       <c r="BN34" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B35" t="n">
-        <v>142.9</v>
+        <v>149.3</v>
       </c>
       <c r="C35" t="n">
-        <v>52.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="E35" t="n">
-        <v>24.8</v>
+        <v>28.8</v>
       </c>
       <c r="F35" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="H35" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="I35" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>73.8</v>
       </c>
       <c r="M35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R35" t="n">
         <v>3.9</v>
       </c>
-      <c r="N35" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="O35" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.7</v>
-      </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>19.7</v>
+        <v>23.9</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="W35" t="n">
-        <v>25.8</v>
+        <v>18.1</v>
       </c>
       <c r="X35" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>238.69</v>
+        <v>218.37</v>
       </c>
       <c r="AG35" t="n">
-        <v>-2.79</v>
+        <v>-4.49</v>
       </c>
       <c r="AK35" t="n">
-        <v>136.6</v>
+        <v>129.21</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.01</v>
+        <v>-2.03</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="BM35" t="n">
-        <v>29.8</v>
+        <v>35.4</v>
       </c>
       <c r="BN35" t="n">
-        <v>61.9</v>
+        <v>294.2</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B36" t="n">
-        <v>148.1</v>
+        <v>137</v>
       </c>
       <c r="C36" t="n">
-        <v>51.9</v>
+        <v>65</v>
       </c>
       <c r="D36" t="n">
-        <v>35.4</v>
+        <v>32</v>
       </c>
       <c r="E36" t="n">
-        <v>31.5</v>
+        <v>25.2</v>
       </c>
       <c r="F36" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H36" t="n">
-        <v>21.8</v>
+        <v>23.5</v>
       </c>
       <c r="I36" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J36" t="n">
-        <v>39.6</v>
+        <v>38.5</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
-        <v>30.8</v>
+        <v>32.3</v>
       </c>
       <c r="O36" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="R36" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T36" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="V36" t="n">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="W36" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="X36" t="n">
-        <v>19.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>233.48</v>
+        <v>220.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>-5.21</v>
+        <v>2.48</v>
       </c>
       <c r="AK36" t="n">
-        <v>135.66</v>
+        <v>129.07</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="BM36" t="n">
-        <v>36.03</v>
+        <v>32.31</v>
       </c>
       <c r="BN36" t="n">
-        <v>76.5</v>
+        <v>547</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B37" t="n">
-        <v>143.4</v>
+        <v>131.5</v>
       </c>
       <c r="C37" t="n">
-        <v>50.9</v>
+        <v>57.6</v>
       </c>
       <c r="D37" t="n">
-        <v>35.7</v>
+        <v>32.7</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="F37" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="H37" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="I37" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J37" t="n">
-        <v>39.9</v>
+        <v>41.6</v>
       </c>
       <c r="K37" t="n">
-        <v>72.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="N37" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="O37" t="n">
-        <v>33.1</v>
+        <v>42.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V37" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W37" t="n">
-        <v>28.3</v>
+        <v>24.1</v>
       </c>
       <c r="X37" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="AF37" t="n">
-        <v>235.13</v>
+        <v>225.87</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.65</v>
+        <v>5.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>136.33</v>
+        <v>130.73</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="BM37" t="n">
-        <v>32</v>
+        <v>31.51</v>
       </c>
       <c r="BN37" t="n">
-        <v>29.5</v>
+        <v>124</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>164.4</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B38" t="n">
-        <v>144.9</v>
+        <v>129.4</v>
       </c>
       <c r="C38" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="D38" t="n">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="F38" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I38" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J38" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="K38" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="N38" t="n">
-        <v>31.6</v>
+        <v>33.1</v>
       </c>
       <c r="O38" t="n">
-        <v>33.6</v>
+        <v>38.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V38" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>27.7</v>
+        <v>22.9</v>
       </c>
       <c r="X38" t="n">
-        <v>21.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="Z38" t="n">
         <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-1.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>234.87</v>
+        <v>229.48</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.26</v>
+        <v>3.61</v>
       </c>
       <c r="AK38" t="n">
-        <v>137.17</v>
+        <v>132</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.84</v>
+        <v>1.27</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="BM38" t="n">
-        <v>32.57</v>
+        <v>34.36</v>
       </c>
       <c r="BN38" t="n">
-        <v>23.4</v>
+        <v>62.8</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B39" t="n">
-        <v>132.2</v>
+        <v>130.2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>56.9</v>
       </c>
       <c r="D39" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="F39" t="n">
-        <v>4</v>
+        <v>33.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>42.3</v>
       </c>
       <c r="K39" t="n">
-        <v>78.09999999999999</v>
+        <v>75.3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>32.3</v>
       </c>
       <c r="O39" t="n">
-        <v>33.8</v>
+        <v>37.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>20.3</v>
+        <v>22.3</v>
       </c>
       <c r="V39" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="W39" t="n">
-        <v>23.2</v>
+        <v>21.7</v>
       </c>
       <c r="X39" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>12.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>234.78</v>
+        <v>230.54</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK39" t="n">
-        <v>136.08</v>
+        <v>132.25</v>
       </c>
       <c r="AL39" t="n">
-        <v>-1.09</v>
+        <v>0.25</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="BM39" t="n">
-        <v>29.64</v>
+        <v>32.26</v>
       </c>
       <c r="BN39" t="n">
-        <v>36.4</v>
+        <v>28.3</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="BP39" t="n">
-        <v>0</v>
+        <v>2545.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B40" t="n">
-        <v>137.1</v>
+        <v>138.4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3.3</v>
+        <v>32.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>42.8</v>
       </c>
       <c r="K40" t="n">
-        <v>81.5</v>
+        <v>75.8</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>32.3</v>
       </c>
       <c r="O40" t="n">
-        <v>35.3</v>
+        <v>35.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>20.3</v>
+        <v>23.6</v>
       </c>
       <c r="V40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>22</v>
+        <v>15.7</v>
       </c>
       <c r="X40" t="n">
-        <v>16.5</v>
+        <v>12.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>-5.3</v>
+        <v>-6.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.75</v>
+        <v>224.23</v>
       </c>
       <c r="AG40" t="n">
-        <v>-5.03</v>
+        <v>-6.31</v>
       </c>
       <c r="AK40" t="n">
-        <v>135.42</v>
+        <v>128.6</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.66</v>
+        <v>-3.65</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="BM40" t="n">
-        <v>31.45</v>
+        <v>33.93</v>
       </c>
       <c r="BN40" t="n">
-        <v>35.9</v>
+        <v>73</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>2697.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B41" t="n">
-        <v>148.7</v>
+        <v>140.8</v>
       </c>
       <c r="C41" t="n">
-        <v>72.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>32.7</v>
+        <v>31.7</v>
       </c>
       <c r="E41" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="F41" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="K41" t="n">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
       <c r="M41" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>33.7</v>
+        <v>33.4</v>
       </c>
       <c r="O41" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="R41" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AA41" t="n">
         <v>7.9</v>
       </c>
-      <c r="W41" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AB41" t="n">
-        <v>-3.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>12.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF41" t="n">
-        <v>222.86</v>
+        <v>223.36</v>
       </c>
       <c r="AG41" t="n">
-        <v>-6.89</v>
+        <v>-0.87</v>
       </c>
       <c r="AK41" t="n">
-        <v>131.24</v>
+        <v>127.19</v>
       </c>
       <c r="AL41" t="n">
-        <v>-4.18</v>
+        <v>-1.41</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="BM41" t="n">
-        <v>34.46</v>
+        <v>31.16</v>
       </c>
       <c r="BN41" t="n">
-        <v>80.40000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>373.6</v>
+        <v>0</v>
       </c>
       <c r="BP41" t="n">
-        <v>249.4</v>
+        <v>2603.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B42" t="n">
-        <v>149.3</v>
+        <v>139.6</v>
       </c>
       <c r="C42" t="n">
-        <v>74.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8</v>
+        <v>25.9</v>
       </c>
       <c r="F42" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="H42" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="I42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>41.2</v>
+        <v>39.6</v>
       </c>
       <c r="K42" t="n">
-        <v>73.8</v>
+        <v>73.3</v>
       </c>
       <c r="M42" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="N42" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="O42" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="R42" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V42" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W42" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="X42" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AB42" t="n">
-        <v>-2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>218.37</v>
+        <v>222.92</v>
       </c>
       <c r="AG42" t="n">
-        <v>-4.49</v>
+        <v>-0.44</v>
       </c>
       <c r="AK42" t="n">
-        <v>129.21</v>
+        <v>129.17</v>
       </c>
       <c r="AL42" t="n">
-        <v>-2.03</v>
+        <v>1.98</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="BM42" t="n">
-        <v>35.4</v>
+        <v>32.41</v>
       </c>
       <c r="BN42" t="n">
-        <v>294.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BO42" t="n">
-        <v>227</v>
+        <v>297.8</v>
       </c>
       <c r="BP42" t="n">
-        <v>2758.6</v>
+        <v>2677.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B43" t="n">
-        <v>137</v>
+        <v>133.5</v>
       </c>
       <c r="C43" t="n">
-        <v>65</v>
+        <v>62.3</v>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E43" t="n">
-        <v>25.2</v>
+        <v>22.5</v>
       </c>
       <c r="F43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H43" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J43" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="K43" t="n">
-        <v>70.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="N43" t="n">
-        <v>32.3</v>
+        <v>30.4</v>
       </c>
       <c r="O43" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="R43" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="V43" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="W43" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="X43" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>18</v>
+        <v>20.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.3</v>
+        <v>12.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>220.85</v>
+        <v>222.77</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.48</v>
+        <v>-0.15</v>
       </c>
       <c r="AK43" t="n">
-        <v>129.07</v>
+        <v>130.42</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.14</v>
+        <v>1.25</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="BM43" t="n">
-        <v>32.31</v>
+        <v>26.56</v>
       </c>
       <c r="BN43" t="n">
-        <v>547</v>
+        <v>46.1</v>
       </c>
       <c r="BO43" t="n">
-        <v>85</v>
+        <v>266.8</v>
       </c>
       <c r="BP43" t="n">
-        <v>2654.5</v>
+        <v>2801.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B44" t="n">
-        <v>131.5</v>
+        <v>133.5</v>
       </c>
       <c r="C44" t="n">
-        <v>57.6</v>
+        <v>61.6</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>33.9</v>
       </c>
       <c r="E44" t="n">
-        <v>26.3</v>
+        <v>25</v>
       </c>
       <c r="F44" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="H44" t="n">
-        <v>23.6</v>
+        <v>25.1</v>
       </c>
       <c r="I44" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="J44" t="n">
-        <v>41.6</v>
+        <v>39.5</v>
       </c>
       <c r="K44" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="N44" t="n">
-        <v>35</v>
+        <v>28.6</v>
       </c>
       <c r="O44" t="n">
-        <v>42.4</v>
+        <v>34.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="R44" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="V44" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W44" t="n">
-        <v>24.1</v>
+        <v>26</v>
       </c>
       <c r="X44" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>19</v>
+        <v>12.9</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.5</v>
+        <v>11.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>225.87</v>
+        <v>221.86</v>
       </c>
       <c r="AG44" t="n">
-        <v>5.02</v>
+        <v>-0.91</v>
       </c>
       <c r="AK44" t="n">
-        <v>130.73</v>
+        <v>129.71</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.66</v>
+        <v>-0.71</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="BM44" t="n">
-        <v>31.51</v>
+        <v>31.32</v>
       </c>
       <c r="BN44" t="n">
-        <v>124</v>
+        <v>54.7</v>
       </c>
       <c r="BO44" t="n">
-        <v>164.4</v>
+        <v>235.3</v>
       </c>
       <c r="BP44" t="n">
-        <v>2635.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="B45" t="n">
-        <v>129.4</v>
+        <v>120.6</v>
       </c>
       <c r="C45" t="n">
-        <v>52.8</v>
+        <v>47.7</v>
       </c>
       <c r="D45" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="E45" t="n">
-        <v>28.9</v>
+        <v>24.1</v>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="H45" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="I45" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>40.8</v>
+        <v>38.4</v>
       </c>
       <c r="K45" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M45" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>33.1</v>
+        <v>30.3</v>
       </c>
       <c r="O45" t="n">
-        <v>38.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="R45" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V45" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="W45" t="n">
-        <v>22.9</v>
+        <v>27.6</v>
       </c>
       <c r="X45" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z45" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>16.1</v>
+        <v>18.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF45" t="n">
-        <v>229.48</v>
+        <v>227.49</v>
       </c>
       <c r="AG45" t="n">
-        <v>3.61</v>
+        <v>5.63</v>
       </c>
       <c r="AK45" t="n">
-        <v>132</v>
+        <v>133.39</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.27</v>
+        <v>3.68</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="BM45" t="n">
-        <v>34.36</v>
+        <v>29.84</v>
       </c>
       <c r="BN45" t="n">
-        <v>62.8</v>
+        <v>41.3</v>
       </c>
       <c r="BO45" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="BP45" t="n">
-        <v>2693.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B46" t="n">
-        <v>130.2</v>
+        <v>116.8</v>
       </c>
       <c r="C46" t="n">
-        <v>56.9</v>
+        <v>45.4</v>
       </c>
       <c r="D46" t="n">
-        <v>33.9</v>
+        <v>35.3</v>
       </c>
       <c r="E46" t="n">
-        <v>26.4</v>
+        <v>23.2</v>
       </c>
       <c r="H46" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="I46" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>42.3</v>
+        <v>38</v>
       </c>
       <c r="K46" t="n">
-        <v>75.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="N46" t="n">
-        <v>32.3</v>
+        <v>28.2</v>
       </c>
       <c r="O46" t="n">
-        <v>37.1</v>
+        <v>30.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="V46" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W46" t="n">
-        <v>21.7</v>
+        <v>27.6</v>
       </c>
       <c r="X46" t="n">
-        <v>18</v>
+        <v>20.9</v>
       </c>
       <c r="Y46" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="n">
-        <v>15.1</v>
+        <v>17.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>-3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.2</v>
+        <v>14.9</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF46" t="n">
-        <v>230.54</v>
+        <v>233.56</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.06</v>
+        <v>6.07</v>
       </c>
       <c r="AK46" t="n">
-        <v>132.25</v>
+        <v>137.14</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.25</v>
+        <v>3.75</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="BM46" t="n">
-        <v>32.26</v>
+        <v>26.51</v>
       </c>
       <c r="BN46" t="n">
-        <v>28.3</v>
+        <v>107.4</v>
       </c>
       <c r="BO46" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="BP46" t="n">
-        <v>2545.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B47" t="n">
-        <v>138.4</v>
+        <v>102.9</v>
       </c>
       <c r="C47" t="n">
-        <v>66.90000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="D47" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
       <c r="E47" t="n">
-        <v>25.9</v>
+        <v>19.8</v>
       </c>
       <c r="H47" t="n">
-        <v>23.6</v>
+        <v>21.7</v>
       </c>
       <c r="I47" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>42.8</v>
+        <v>34</v>
       </c>
       <c r="K47" t="n">
-        <v>75.8</v>
+        <v>65.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="N47" t="n">
-        <v>32.3</v>
+        <v>27</v>
       </c>
       <c r="O47" t="n">
-        <v>35.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="R47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W47" t="n">
-        <v>15.7</v>
+        <v>30.6</v>
       </c>
       <c r="X47" t="n">
-        <v>12.3</v>
+        <v>23.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>7.7</v>
+        <v>15.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="n">
-        <v>10.3</v>
+        <v>18.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.1</v>
+        <v>16.7</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.8</v>
+        <v>12.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>224.23</v>
+        <v>234.94</v>
       </c>
       <c r="AG47" t="n">
-        <v>-6.31</v>
+        <v>1.38</v>
       </c>
       <c r="AK47" t="n">
-        <v>128.6</v>
+        <v>137.51</v>
       </c>
       <c r="AL47" t="n">
-        <v>-3.65</v>
+        <v>0.37</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="BM47" t="n">
-        <v>33.93</v>
+        <v>20.4</v>
       </c>
       <c r="BN47" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="BO47" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BP47" t="n">
-        <v>2697.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="B48" t="n">
-        <v>140.8</v>
+        <v>93.2</v>
       </c>
       <c r="C48" t="n">
-        <v>73.09999999999999</v>
+        <v>36.3</v>
       </c>
       <c r="D48" t="n">
-        <v>31.7</v>
+        <v>32.7</v>
       </c>
       <c r="E48" t="n">
-        <v>26.1</v>
+        <v>17</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H48" t="n">
-        <v>23.6</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J48" t="n">
-        <v>40.5</v>
+        <v>25</v>
       </c>
       <c r="K48" t="n">
-        <v>73.5</v>
+        <v>51.2</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="N48" t="n">
-        <v>33.4</v>
+        <v>25.5</v>
       </c>
       <c r="O48" t="n">
-        <v>39.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="R48" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="V48" t="n">
-        <v>6.8</v>
+        <v>15.8</v>
       </c>
       <c r="W48" t="n">
-        <v>11</v>
+        <v>33.6</v>
       </c>
       <c r="X48" t="n">
-        <v>8.9</v>
+        <v>24.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
       <c r="AA48" t="n">
-        <v>7.9</v>
+        <v>16.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1.2</v>
+        <v>4</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AF48" t="n">
-        <v>223.36</v>
+        <v>229.19</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.87</v>
+        <v>-5.75</v>
       </c>
       <c r="AK48" t="n">
-        <v>127.19</v>
+        <v>138.98</v>
       </c>
       <c r="AL48" t="n">
-        <v>-1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="BM48" t="n">
-        <v>31.16</v>
+        <v>19.88</v>
       </c>
       <c r="BN48" t="n">
-        <v>21.2</v>
+        <v>35.1</v>
       </c>
       <c r="BO48" t="n">
         <v>0</v>
       </c>
       <c r="BP48" t="n">
-        <v>2603.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B49" t="n">
-        <v>139.6</v>
+        <v>120.3</v>
       </c>
       <c r="C49" t="n">
-        <v>69.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="D49" t="n">
-        <v>32.2</v>
+        <v>36.3</v>
       </c>
       <c r="E49" t="n">
-        <v>25.9</v>
+        <v>20.6</v>
       </c>
       <c r="F49" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H49" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J49" t="n">
-        <v>39.6</v>
+        <v>35.4</v>
       </c>
       <c r="K49" t="n">
-        <v>73.3</v>
+        <v>66</v>
       </c>
       <c r="M49" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="N49" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="O49" t="n">
-        <v>40.1</v>
+        <v>26.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.8</v>
+        <v>18.3</v>
       </c>
       <c r="R49" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>23.8</v>
+        <v>18.3</v>
       </c>
       <c r="V49" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="W49" t="n">
-        <v>15.2</v>
+        <v>22.5</v>
       </c>
       <c r="X49" t="n">
-        <v>10.9</v>
+        <v>20.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z49" t="n">
-        <v>13.6</v>
+        <v>16.1</v>
       </c>
       <c r="AA49" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AC49" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AF49" t="n">
-        <v>222.92</v>
+        <v>224.91</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.44</v>
+        <v>-4.28</v>
       </c>
       <c r="AK49" t="n">
-        <v>129.17</v>
+        <v>134.04</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.98</v>
+        <v>-4.94</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="BM49" t="n">
-        <v>32.41</v>
+        <v>22.59</v>
       </c>
       <c r="BN49" t="n">
-        <v>74.59999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="BO49" t="n">
-        <v>297.8</v>
+        <v>0</v>
       </c>
       <c r="BP49" t="n">
-        <v>2677.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B50" t="n">
-        <v>133.5</v>
+        <v>131.1</v>
       </c>
       <c r="C50" t="n">
-        <v>62.3</v>
+        <v>60.2</v>
       </c>
       <c r="D50" t="n">
-        <v>34</v>
+        <v>35.6</v>
       </c>
       <c r="E50" t="n">
-        <v>22.5</v>
+        <v>24.2</v>
       </c>
       <c r="F50" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="H50" t="n">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="I50" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>40.8</v>
+        <v>38.2</v>
       </c>
       <c r="K50" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M50" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="N50" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="O50" t="n">
-        <v>37.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q50" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V50" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y50" t="n">
         <v>4.9</v>
       </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z50" t="n">
-        <v>20.2</v>
+        <v>12.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="AC50" t="n">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD50" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>222.77</v>
+        <v>220.83</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.15</v>
+        <v>-4.08</v>
       </c>
       <c r="AK50" t="n">
-        <v>130.42</v>
+        <v>131.01</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.25</v>
+        <v>-3.03</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="BM50" t="n">
-        <v>26.56</v>
+        <v>29.62</v>
       </c>
       <c r="BN50" t="n">
-        <v>46.1</v>
+        <v>58.2</v>
       </c>
       <c r="BO50" t="n">
-        <v>266.8</v>
+        <v>0</v>
       </c>
       <c r="BP50" t="n">
-        <v>2801.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B51" t="n">
-        <v>133.5</v>
+        <v>117.2</v>
       </c>
       <c r="C51" t="n">
-        <v>61.6</v>
+        <v>53.7</v>
       </c>
       <c r="D51" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="F51" t="n">
         <v>2.2</v>
       </c>
       <c r="H51" t="n">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="I51" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="J51" t="n">
-        <v>39.5</v>
+        <v>37</v>
       </c>
       <c r="K51" t="n">
-        <v>74.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="M51" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="N51" t="n">
-        <v>28.6</v>
+        <v>31.4</v>
       </c>
       <c r="O51" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="R51" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="V51" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="W51" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="X51" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="Z51" t="n">
-        <v>12.9</v>
+        <v>16.8</v>
       </c>
       <c r="AA51" t="n">
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="AB51" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AC51" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
-        <v>221.86</v>
+        <v>228.06</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.91</v>
+        <v>7.23</v>
       </c>
       <c r="AK51" t="n">
-        <v>129.71</v>
+        <v>131.96</v>
       </c>
       <c r="AL51" t="n">
-        <v>-0.71</v>
+        <v>0.95</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="BM51" t="n">
-        <v>31.32</v>
+        <v>23.82</v>
       </c>
       <c r="BN51" t="n">
-        <v>54.7</v>
+        <v>49.9</v>
       </c>
       <c r="BO51" t="n">
-        <v>235.3</v>
+        <v>0</v>
       </c>
       <c r="BP51" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B52" t="n">
-        <v>120.6</v>
+        <v>118.1</v>
       </c>
       <c r="C52" t="n">
-        <v>47.7</v>
+        <v>49.6</v>
       </c>
       <c r="D52" t="n">
-        <v>34.2</v>
+        <v>35.3</v>
       </c>
       <c r="E52" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>3.5</v>
+        <v>27.62</v>
       </c>
       <c r="H52" t="n">
-        <v>24.9</v>
+        <v>21.7</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
-        <v>38.4</v>
+        <v>38</v>
       </c>
       <c r="K52" t="n">
-        <v>73.2</v>
+        <v>68.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="N52" t="n">
-        <v>30.3</v>
+        <v>27</v>
       </c>
       <c r="O52" t="n">
-        <v>33.3</v>
+        <v>28.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.3</v>
+        <v>22</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>23.3</v>
+        <v>22</v>
       </c>
       <c r="V52" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="W52" t="n">
-        <v>27.6</v>
+        <v>31.2</v>
       </c>
       <c r="X52" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="Y52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
         <v>11.1</v>
       </c>
-      <c r="Z52" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AD52" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
-        <v>227.49</v>
+        <v>233.59</v>
       </c>
       <c r="AG52" t="n">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="AK52" t="n">
-        <v>133.39</v>
+        <v>132.79</v>
       </c>
       <c r="AL52" t="n">
-        <v>3.68</v>
+        <v>0.83</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="BM52" t="n">
-        <v>29.84</v>
+        <v>23.43</v>
       </c>
       <c r="BN52" t="n">
-        <v>41.3</v>
+        <v>83.8</v>
       </c>
       <c r="BO52" t="n">
         <v>0</v>
@@ -5596,43 +5713,43 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B53" t="n">
-        <v>121.2</v>
+        <v>115.9</v>
       </c>
       <c r="C53" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="D53" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="E53" t="n">
-        <v>34.73</v>
+        <v>28.79</v>
       </c>
       <c r="H53" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="I53" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J53" t="n">
         <v>38</v>
       </c>
       <c r="K53" t="n">
-        <v>70.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N53" t="n">
-        <v>28.2</v>
+        <v>27</v>
       </c>
       <c r="O53" t="n">
-        <v>30.3</v>
+        <v>28.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5641,102 +5758,51 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>20</v>
-      </c>
-      <c r="V53" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X53" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>233.56</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>137.14</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>3.75</v>
+        <v>19.8</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>0</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B54" t="n">
-        <v>103</v>
+        <v>111.1</v>
       </c>
       <c r="C54" t="n">
-        <v>36.8</v>
+        <v>44.2</v>
       </c>
       <c r="D54" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E54" t="n">
-        <v>26.47</v>
+        <v>27.23</v>
       </c>
       <c r="H54" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="I54" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K54" t="n">
-        <v>65.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N54" t="n">
         <v>27</v>
       </c>
       <c r="O54" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>19.8</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5745,105 +5811,51 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>15</v>
-      </c>
-      <c r="V54" t="n">
-        <v>16</v>
-      </c>
-      <c r="W54" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X54" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>234.94</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>137.51</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.37</v>
+        <v>19.8</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="BM54" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="BN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP54" t="n">
-        <v>0</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B55" t="n">
-        <v>93.2</v>
+        <v>105.9</v>
       </c>
       <c r="C55" t="n">
-        <v>36.3</v>
+        <v>40.9</v>
       </c>
       <c r="D55" t="n">
-        <v>32.7</v>
+        <v>33.9</v>
       </c>
       <c r="E55" t="n">
-        <v>17</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.6</v>
+        <v>25.96</v>
       </c>
       <c r="H55" t="n">
-        <v>16</v>
+        <v>21.9</v>
       </c>
       <c r="I55" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>51.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>10.5</v>
+        <v>19.8</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5852,105 +5864,30 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="V55" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W55" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X55" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>229.19</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>138.98</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.47</v>
+        <v>19.8</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B56" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="C56" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D56" t="n">
-        <v>36.3</v>
+        <v>28.8</v>
       </c>
       <c r="E56" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H56" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J56" t="n">
-        <v>35.4</v>
+        <v>28.84</v>
       </c>
       <c r="K56" t="n">
-        <v>66</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>24.8</v>
+        <v>5.9</v>
       </c>
       <c r="O56" t="n">
-        <v>26.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5959,105 +5896,30 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W56" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X56" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>224.91</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>-4.28</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>134.04</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>-4.94</v>
+        <v>20.3</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B57" t="n">
-        <v>131.1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="D57" t="n">
-        <v>35.6</v>
+        <v>28.5</v>
       </c>
       <c r="E57" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H57" t="n">
-        <v>23</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J57" t="n">
-        <v>38.2</v>
+        <v>28.54</v>
       </c>
       <c r="K57" t="n">
-        <v>70</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N57" t="n">
-        <v>30.2</v>
+        <v>5.7</v>
       </c>
       <c r="O57" t="n">
-        <v>31.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6066,105 +5928,30 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="V57" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>220.83</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>131.01</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>-3.03</v>
+        <v>20.3</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="BO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP57" t="n">
-        <v>0</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B58" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="D58" t="n">
-        <v>34.7</v>
+        <v>27.9</v>
       </c>
       <c r="E58" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>37</v>
+        <v>27.93</v>
       </c>
       <c r="K58" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N58" t="n">
-        <v>31.4</v>
+        <v>5.3</v>
       </c>
       <c r="O58" t="n">
-        <v>33.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6173,102 +5960,30 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V58" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W58" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>228.06</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>131.96</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0.95</v>
+        <v>20.3</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>23.82</v>
-      </c>
-      <c r="BN58" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="BO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP58" t="n">
-        <v>0</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B59" t="n">
-        <v>118.1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D59" t="n">
-        <v>35.3</v>
+        <v>27.1</v>
       </c>
       <c r="E59" t="n">
-        <v>27.62</v>
-      </c>
-      <c r="H59" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9</v>
-      </c>
-      <c r="J59" t="n">
-        <v>38</v>
+        <v>27.12</v>
       </c>
       <c r="K59" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N59" t="n">
-        <v>27</v>
+        <v>4.7</v>
       </c>
       <c r="O59" t="n">
-        <v>28.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6277,102 +5992,30 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>22</v>
-      </c>
-      <c r="V59" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W59" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X59" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>233.59</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>132.79</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0.83</v>
+        <v>20.3</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="BM59" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="BN59" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="BO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP59" t="n">
-        <v>0</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B60" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="C60" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="D60" t="n">
-        <v>35.4</v>
+        <v>25.7</v>
       </c>
       <c r="E60" t="n">
-        <v>28.79</v>
-      </c>
-      <c r="H60" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" t="n">
-        <v>38</v>
+        <v>25.73</v>
       </c>
       <c r="K60" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N60" t="n">
-        <v>27</v>
+        <v>3.8</v>
       </c>
       <c r="O60" t="n">
-        <v>28.9</v>
+        <v>1.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6381,51 +6024,30 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="B61" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="C61" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="D61" t="n">
-        <v>33.9</v>
+        <v>24.4</v>
       </c>
       <c r="E61" t="n">
-        <v>27.23</v>
-      </c>
-      <c r="H61" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I61" t="n">
-        <v>9</v>
-      </c>
-      <c r="J61" t="n">
-        <v>37</v>
+        <v>24.44</v>
       </c>
       <c r="K61" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N61" t="n">
-        <v>27</v>
+        <v>2.9</v>
       </c>
       <c r="O61" t="n">
-        <v>28.9</v>
+        <v>1.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6434,51 +6056,30 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46292</v>
+        <v>46299</v>
       </c>
       <c r="B62" t="n">
-        <v>105.9</v>
-      </c>
-      <c r="C62" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="D62" t="n">
-        <v>33.9</v>
+        <v>23.9</v>
       </c>
       <c r="E62" t="n">
-        <v>25.96</v>
-      </c>
-      <c r="H62" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I62" t="n">
-        <v>9</v>
-      </c>
-      <c r="J62" t="n">
-        <v>37</v>
+        <v>23.87</v>
       </c>
       <c r="K62" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N62" t="n">
-        <v>27</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
-        <v>28.9</v>
+        <v>1.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6487,10 +6088,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46292</v>
+        <v>46299</v>
       </c>
     </row>
   </sheetData>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5760,6 +5760,33 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
+      </c>
       <c r="BL53" s="1" t="n">
         <v>46290</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -818,7 +818,7 @@
         <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>91.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>39.6</v>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V4" t="n">
         <v>8.699999999999999</v>
@@ -892,10 +892,10 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>87.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V5" t="n">
         <v>7.1</v>
@@ -966,7 +966,7 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>87.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="O6" t="n">
         <v>38.1</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V6" t="n">
         <v>4.9</v>
@@ -1349,10 +1349,10 @@
         <v>6.5</v>
       </c>
       <c r="K10" t="n">
-        <v>100.1</v>
+        <v>102.5</v>
       </c>
       <c r="O10" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V10" t="n">
         <v>6.3</v>
@@ -1435,7 +1435,7 @@
         <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>94.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>41</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V11" t="n">
         <v>8.9</v>
@@ -1521,7 +1521,7 @@
         <v>5.5</v>
       </c>
       <c r="K12" t="n">
-        <v>84.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="O12" t="n">
         <v>36.6</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V12" t="n">
         <v>9.5</v>
@@ -1607,10 +1607,10 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>77.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="O13" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V13" t="n">
         <v>9</v>
@@ -2121,7 +2121,7 @@
         <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>92</v>
+        <v>94.3</v>
       </c>
       <c r="O18" t="n">
         <v>39.9</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V18" t="n">
         <v>9.5</v>
@@ -2207,10 +2207,10 @@
         <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>86.3</v>
+        <v>88.5</v>
       </c>
       <c r="O19" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V19" t="n">
         <v>10.7</v>
@@ -2828,10 +2828,10 @@
         <v>6.1</v>
       </c>
       <c r="K25" t="n">
-        <v>82.3</v>
+        <v>84.5</v>
       </c>
       <c r="O25" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V25" t="n">
         <v>15.5</v>
@@ -2914,10 +2914,10 @@
         <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>74.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="O26" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
         <v>12.6</v>
@@ -3535,10 +3535,10 @@
         <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>78.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="O32" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V32" t="n">
         <v>11.6</v>
@@ -3621,10 +3621,10 @@
         <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>81.5</v>
+        <v>83.7</v>
       </c>
       <c r="O33" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="V33" t="n">
         <v>11</v>
@@ -5240,12 +5240,6 @@
       <c r="X48" t="n">
         <v>24.7</v>
       </c>
-      <c r="Y48" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>23</v>
-      </c>
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
@@ -5347,12 +5341,6 @@
       <c r="X49" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y49" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>16.1</v>
-      </c>
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
@@ -5454,12 +5442,6 @@
       <c r="X50" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y50" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
@@ -5561,12 +5543,6 @@
       <c r="X51" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5612,40 +5588,43 @@
         <v>46289</v>
       </c>
       <c r="B52" t="n">
-        <v>118.1</v>
+        <v>112.8</v>
       </c>
       <c r="C52" t="n">
-        <v>49.6</v>
+        <v>42.7</v>
       </c>
       <c r="D52" t="n">
-        <v>35.3</v>
+        <v>34.6</v>
       </c>
       <c r="E52" t="n">
-        <v>27.62</v>
+        <v>20.7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.5</v>
       </c>
       <c r="H52" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J52" t="n">
-        <v>38</v>
+        <v>36.8</v>
       </c>
       <c r="K52" t="n">
-        <v>68.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>27</v>
+        <v>27.9</v>
       </c>
       <c r="O52" t="n">
-        <v>28.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5654,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V52" t="n">
         <v>11.9</v>
@@ -5665,14 +5644,8 @@
       <c r="X52" t="n">
         <v>21.6</v>
       </c>
-      <c r="Y52" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21.4</v>
-      </c>
       <c r="AA52" t="n">
-        <v>16.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB52" t="n">
         <v>5.1</v>
@@ -5716,13 +5689,13 @@
         <v>46290</v>
       </c>
       <c r="B53" t="n">
-        <v>115.9</v>
+        <v>110.9</v>
       </c>
       <c r="C53" t="n">
-        <v>45.7</v>
+        <v>41.3</v>
       </c>
       <c r="D53" t="n">
-        <v>35.4</v>
+        <v>34.9</v>
       </c>
       <c r="E53" t="n">
         <v>28.79</v>
@@ -5734,19 +5707,19 @@
         <v>9</v>
       </c>
       <c r="J53" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K53" t="n">
-        <v>68.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M53" t="n">
         <v>1.9</v>
       </c>
       <c r="N53" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O53" t="n">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="Q53" t="n">
         <v>19.8</v>
@@ -5768,15 +5741,6 @@
       </c>
       <c r="X53" t="n">
         <v>25.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
       </c>
       <c r="AB53" t="n">
         <v>4.3</v>
@@ -5796,13 +5760,13 @@
         <v>46291</v>
       </c>
       <c r="B54" t="n">
-        <v>111.1</v>
+        <v>106.3</v>
       </c>
       <c r="C54" t="n">
-        <v>44.2</v>
+        <v>39.3</v>
       </c>
       <c r="D54" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="E54" t="n">
         <v>27.23</v>
@@ -5814,22 +5778,22 @@
         <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>67.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M54" t="n">
         <v>1.9</v>
       </c>
       <c r="N54" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O54" t="n">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>19.8</v>
+        <v>16</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5838,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>19.8</v>
+        <v>16</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46291</v>
@@ -5849,13 +5813,13 @@
         <v>46292</v>
       </c>
       <c r="B55" t="n">
-        <v>105.9</v>
+        <v>100.4</v>
       </c>
       <c r="C55" t="n">
-        <v>40.9</v>
+        <v>35.8</v>
       </c>
       <c r="D55" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="E55" t="n">
         <v>25.96</v>
@@ -5867,22 +5831,22 @@
         <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K55" t="n">
-        <v>67.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O55" t="n">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>19.8</v>
+        <v>13</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5891,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>19.8</v>
+        <v>13</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46292</v>
@@ -5902,19 +5866,40 @@
         <v>46293</v>
       </c>
       <c r="B56" t="n">
-        <v>28.8</v>
+        <v>111.9</v>
+      </c>
+      <c r="C56" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>35.3</v>
       </c>
       <c r="E56" t="n">
         <v>28.84</v>
       </c>
+      <c r="H56" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>38</v>
+      </c>
       <c r="K56" t="n">
-        <v>5.9</v>
+        <v>69.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N56" t="n">
+        <v>27</v>
       </c>
       <c r="O56" t="n">
-        <v>2.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5923,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>20.3</v>
+        <v>13</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46293</v>
@@ -5934,19 +5919,40 @@
         <v>46294</v>
       </c>
       <c r="B57" t="n">
-        <v>28.5</v>
+        <v>115</v>
+      </c>
+      <c r="C57" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35.6</v>
       </c>
       <c r="E57" t="n">
         <v>28.54</v>
       </c>
+      <c r="H57" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>39</v>
+      </c>
       <c r="K57" t="n">
-        <v>5.7</v>
+        <v>70.3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>27</v>
       </c>
       <c r="O57" t="n">
-        <v>2.5</v>
+        <v>28.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5955,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46294</v>
@@ -5972,10 +5978,10 @@
         <v>27.93</v>
       </c>
       <c r="K58" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -5987,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46295</v>
@@ -6004,10 +6010,10 @@
         <v>27.12</v>
       </c>
       <c r="K59" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="O59" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -6019,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46296</v>
@@ -6036,10 +6042,10 @@
         <v>25.73</v>
       </c>
       <c r="K60" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="O60" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -6051,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46297</v>
@@ -6068,10 +6074,10 @@
         <v>24.44</v>
       </c>
       <c r="K61" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6083,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46298</v>
@@ -6100,10 +6106,10 @@
         <v>23.87</v>
       </c>
       <c r="K62" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="O62" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6115,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46299</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5240,6 +5240,12 @@
       <c r="X48" t="n">
         <v>24.7</v>
       </c>
+      <c r="Y48" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>23</v>
+      </c>
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
@@ -5341,6 +5347,12 @@
       <c r="X49" t="n">
         <v>20.5</v>
       </c>
+      <c r="Y49" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
@@ -5442,6 +5454,12 @@
       <c r="X50" t="n">
         <v>17.1</v>
       </c>
+      <c r="Y50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
@@ -5543,6 +5561,12 @@
       <c r="X51" t="n">
         <v>17.6</v>
       </c>
+      <c r="Y51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5644,6 +5668,12 @@
       <c r="X52" t="n">
         <v>21.6</v>
       </c>
+      <c r="Y52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.4</v>
+      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5742,6 +5772,15 @@
       <c r="X53" t="n">
         <v>25.6</v>
       </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5750,6 +5789,18 @@
       </c>
       <c r="AD53" t="n">
         <v>7.3</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>231.92</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>136.54</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>3.75</v>
       </c>
       <c r="BL53" s="1" t="n">
         <v>46290</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,15 +696,6 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
       </c>
@@ -785,15 +776,6 @@
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AK3" t="n">
         <v>134.62</v>
       </c>
@@ -853,15 +835,6 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
@@ -927,15 +900,6 @@
       <c r="AA5" t="n">
         <v>10</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AF5" t="n">
         <v>224.37</v>
       </c>
@@ -1001,15 +965,6 @@
       <c r="AA6" t="n">
         <v>9</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="AF6" t="n">
         <v>225.93</v>
       </c>
@@ -1096,15 +1051,6 @@
       <c r="AA7" t="n">
         <v>8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="AF7" t="n">
         <v>218.63</v>
       </c>
@@ -1191,15 +1137,6 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
@@ -1298,15 +1235,6 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
@@ -1384,15 +1312,6 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
@@ -1470,15 +1389,6 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
@@ -1556,15 +1466,6 @@
       <c r="AA12" t="n">
         <v>14</v>
       </c>
-      <c r="AB12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF12" t="n">
         <v>225.14</v>
       </c>
@@ -1642,15 +1543,6 @@
       <c r="AA13" t="n">
         <v>15</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF13" t="n">
         <v>229.98</v>
       </c>
@@ -1749,15 +1641,6 @@
       <c r="AA14" t="n">
         <v>13</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF14" t="n">
         <v>229.96</v>
       </c>
@@ -1856,15 +1739,6 @@
       <c r="AA15" t="n">
         <v>10</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF15" t="n">
         <v>227.01</v>
       </c>
@@ -1963,15 +1837,6 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
@@ -2070,15 +1935,6 @@
       <c r="AA17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF17" t="n">
         <v>231.16</v>
       </c>
@@ -2156,15 +2012,6 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
-      <c r="AB18" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF18" t="n">
         <v>228.13</v>
       </c>
@@ -2242,15 +2089,6 @@
       <c r="AA19" t="n">
         <v>9</v>
       </c>
-      <c r="AB19" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4</v>
-      </c>
       <c r="AF19" t="n">
         <v>229.16</v>
       </c>
@@ -2349,15 +2187,6 @@
       <c r="AA20" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB20" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF20" t="n">
         <v>228.55</v>
       </c>
@@ -2456,15 +2285,6 @@
       <c r="AA21" t="n">
         <v>10</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF21" t="n">
         <v>219.99</v>
       </c>
@@ -2563,15 +2383,6 @@
       <c r="AA22" t="n">
         <v>11</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF22" t="n">
         <v>219.22</v>
       </c>
@@ -2670,15 +2481,6 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
@@ -2777,15 +2579,6 @@
       <c r="AA24" t="n">
         <v>14</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF24" t="n">
         <v>220.58</v>
       </c>
@@ -2863,15 +2656,6 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF25" t="n">
         <v>223.43</v>
       </c>
@@ -2949,15 +2733,6 @@
       <c r="AA26" t="n">
         <v>13</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF26" t="n">
         <v>229.48</v>
       </c>
@@ -3056,15 +2831,6 @@
       <c r="AA27" t="n">
         <v>14</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
-      </c>
       <c r="AF27" t="n">
         <v>241.48</v>
       </c>
@@ -3163,15 +2929,6 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB28" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
@@ -3270,15 +3027,6 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
@@ -3377,15 +3125,6 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
-      <c r="AB30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
@@ -3484,15 +3223,6 @@
       <c r="AA31" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB31" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF31" t="n">
         <v>234.87</v>
       </c>
@@ -3570,15 +3300,6 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AF32" t="n">
         <v>234.78</v>
       </c>
@@ -3656,15 +3377,6 @@
       <c r="AA33" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF33" t="n">
         <v>229.75</v>
       </c>
@@ -3763,15 +3475,6 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
@@ -3870,15 +3573,6 @@
       <c r="AA35" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF35" t="n">
         <v>218.37</v>
       </c>
@@ -3977,15 +3671,6 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF36" t="n">
         <v>220.85</v>
       </c>
@@ -4084,15 +3769,6 @@
       <c r="AA37" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AF37" t="n">
         <v>225.87</v>
       </c>
@@ -4191,15 +3867,6 @@
       <c r="AA38" t="n">
         <v>16.1</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF38" t="n">
         <v>229.48</v>
       </c>
@@ -4295,15 +3962,6 @@
       <c r="AA39" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF39" t="n">
         <v>230.54</v>
       </c>
@@ -4399,15 +4057,6 @@
       <c r="AA40" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB40" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AF40" t="n">
         <v>224.23</v>
       </c>
@@ -4506,15 +4155,6 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB41" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
@@ -4613,15 +4253,6 @@
       <c r="AA42" t="n">
         <v>12</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF42" t="n">
         <v>222.92</v>
       </c>
@@ -4720,15 +4351,6 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
-      <c r="AB43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
@@ -4827,15 +4449,6 @@
       <c r="AA44" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AF44" t="n">
         <v>221.86</v>
       </c>
@@ -4934,15 +4547,6 @@
       <c r="AA45" t="n">
         <v>18.8</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AF45" t="n">
         <v>227.49</v>
       </c>
@@ -5038,15 +4642,6 @@
       <c r="AA46" t="n">
         <v>17.2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AF46" t="n">
         <v>233.56</v>
       </c>
@@ -5142,15 +4737,6 @@
       <c r="AA47" t="n">
         <v>18.1</v>
       </c>
-      <c r="AB47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>12.8</v>
-      </c>
       <c r="AF47" t="n">
         <v>234.94</v>
       </c>
@@ -5249,15 +4835,6 @@
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
-      <c r="AB48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>7</v>
-      </c>
       <c r="AF48" t="n">
         <v>229.19</v>
       </c>
@@ -5356,15 +4933,6 @@
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AF49" t="n">
         <v>224.91</v>
       </c>
@@ -5463,15 +5031,6 @@
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
-      <c r="AB50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF50" t="n">
         <v>220.83</v>
       </c>
@@ -5570,15 +5129,6 @@
       <c r="AA51" t="n">
         <v>14</v>
       </c>
-      <c r="AB51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.1</v>
-      </c>
       <c r="AF51" t="n">
         <v>228.06</v>
       </c>
@@ -5677,15 +5227,6 @@
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
-      <c r="AB52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.1</v>
-      </c>
       <c r="AF52" t="n">
         <v>233.59</v>
       </c>
@@ -5780,15 +5321,6 @@
       </c>
       <c r="AA53" t="n">
         <v>21.2</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -696,8 +687,20 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB2" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-3.5</v>
       </c>
       <c r="AK2" t="n">
         <v>135.24</v>
@@ -758,15 +761,6 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -775,6 +769,15 @@
       </c>
       <c r="AA3" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AK3" t="n">
         <v>134.62</v>
@@ -817,15 +820,6 @@
       <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -835,11 +829,20 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
+      <c r="AB4" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3.71</v>
+        <v>0.05</v>
       </c>
       <c r="AK4" t="n">
         <v>135.21</v>
@@ -882,15 +885,6 @@
       <c r="T5" t="n">
         <v>18</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -899,6 +893,15 @@
       </c>
       <c r="AA5" t="n">
         <v>10</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>224.37</v>
@@ -947,15 +950,6 @@
       <c r="T6" t="n">
         <v>18</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -964,6 +958,15 @@
       </c>
       <c r="AA6" t="n">
         <v>9</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF6" t="n">
         <v>225.93</v>
@@ -1033,15 +1036,6 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1050,6 +1044,15 @@
       </c>
       <c r="AA7" t="n">
         <v>8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-5.1</v>
       </c>
       <c r="AF7" t="n">
         <v>218.63</v>
@@ -1119,15 +1122,6 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1137,11 +1131,20 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.24</v>
+        <v>-2.23</v>
       </c>
       <c r="AK8" t="n">
         <v>123.32</v>
@@ -1217,15 +1220,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1235,11 +1229,20 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AK9" t="n">
         <v>117.87</v>
@@ -1294,15 +1297,6 @@
       <c r="T10" t="n">
         <v>18</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1312,11 +1306,20 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="AK10" t="n">
         <v>116.52</v>
@@ -1371,15 +1374,6 @@
       <c r="T11" t="n">
         <v>18</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1389,11 +1383,20 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AK11" t="n">
         <v>116.37</v>
@@ -1448,15 +1451,6 @@
       <c r="T12" t="n">
         <v>18</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1465,6 +1459,15 @@
       </c>
       <c r="AA12" t="n">
         <v>14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF12" t="n">
         <v>225.14</v>
@@ -1525,15 +1528,6 @@
       <c r="T13" t="n">
         <v>18</v>
       </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1542,6 +1536,15 @@
       </c>
       <c r="AA13" t="n">
         <v>15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF13" t="n">
         <v>229.98</v>
@@ -1623,15 +1626,6 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1640,6 +1634,15 @@
       </c>
       <c r="AA14" t="n">
         <v>13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AF14" t="n">
         <v>229.96</v>
@@ -1721,15 +1724,6 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1738,6 +1732,15 @@
       </c>
       <c r="AA15" t="n">
         <v>10</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF15" t="n">
         <v>227.01</v>
@@ -1819,15 +1822,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -1837,11 +1831,20 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
         <v>130.88</v>
@@ -1917,15 +1920,6 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1934,6 +1928,15 @@
       </c>
       <c r="AA17" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF17" t="n">
         <v>231.16</v>
@@ -1994,15 +1997,6 @@
       <c r="T18" t="n">
         <v>18</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2011,6 +2005,15 @@
       </c>
       <c r="AA18" t="n">
         <v>9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF18" t="n">
         <v>228.13</v>
@@ -2071,15 +2074,6 @@
       <c r="T19" t="n">
         <v>18</v>
       </c>
-      <c r="V19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2088,6 +2082,15 @@
       </c>
       <c r="AA19" t="n">
         <v>9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
       </c>
       <c r="AF19" t="n">
         <v>229.16</v>
@@ -2169,15 +2172,6 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2186,6 +2180,15 @@
       </c>
       <c r="AA20" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF20" t="n">
         <v>228.55</v>
@@ -2267,15 +2270,6 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2284,6 +2278,15 @@
       </c>
       <c r="AA21" t="n">
         <v>10</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF21" t="n">
         <v>219.99</v>
@@ -2365,15 +2368,6 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2382,6 +2376,15 @@
       </c>
       <c r="AA22" t="n">
         <v>11</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF22" t="n">
         <v>219.22</v>
@@ -2463,15 +2466,6 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2481,11 +2475,20 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AK23" t="n">
         <v>120.28</v>
@@ -2561,15 +2564,6 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2578,6 +2572,15 @@
       </c>
       <c r="AA24" t="n">
         <v>14</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF24" t="n">
         <v>220.58</v>
@@ -2638,15 +2641,6 @@
       <c r="T25" t="n">
         <v>18</v>
       </c>
-      <c r="V25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2655,6 +2649,15 @@
       </c>
       <c r="AA25" t="n">
         <v>13</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF25" t="n">
         <v>223.43</v>
@@ -2715,15 +2718,6 @@
       <c r="T26" t="n">
         <v>18</v>
       </c>
-      <c r="V26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2732,6 +2726,15 @@
       </c>
       <c r="AA26" t="n">
         <v>13</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.48</v>
@@ -2813,15 +2816,6 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2830,6 +2824,15 @@
       </c>
       <c r="AA27" t="n">
         <v>14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>241.48</v>
@@ -2911,15 +2914,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -2929,11 +2923,20 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB28" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
       <c r="AG28" t="n">
-        <v>-2.79</v>
+        <v>-2.8</v>
       </c>
       <c r="AK28" t="n">
         <v>136.6</v>
@@ -3009,15 +3012,6 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3027,11 +3021,20 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
       <c r="AG29" t="n">
-        <v>-5.21</v>
+        <v>-4.86</v>
       </c>
       <c r="AK29" t="n">
         <v>135.66</v>
@@ -3107,15 +3110,6 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3125,11 +3119,20 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
+      <c r="AB30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AK30" t="n">
         <v>136.33</v>
@@ -3205,15 +3208,6 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3222,6 +3216,15 @@
       </c>
       <c r="AA31" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF31" t="n">
         <v>234.87</v>
@@ -3282,15 +3285,6 @@
       <c r="T32" t="n">
         <v>18</v>
       </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3299,6 +3293,15 @@
       </c>
       <c r="AA32" t="n">
         <v>13</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.2</v>
       </c>
       <c r="AF32" t="n">
         <v>234.78</v>
@@ -3359,15 +3362,6 @@
       <c r="T33" t="n">
         <v>18</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3376,6 +3370,15 @@
       </c>
       <c r="AA33" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF33" t="n">
         <v>229.75</v>
@@ -3457,15 +3460,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3475,11 +3469,20 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
+      <c r="AB34" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>-6.89</v>
+        <v>-6.9</v>
       </c>
       <c r="AK34" t="n">
         <v>131.24</v>
@@ -3555,15 +3558,6 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3572,6 +3566,15 @@
       </c>
       <c r="AA35" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF35" t="n">
         <v>218.37</v>
@@ -3653,15 +3656,6 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3670,6 +3664,15 @@
       </c>
       <c r="AA36" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF36" t="n">
         <v>220.85</v>
@@ -3751,15 +3754,6 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3768,6 +3762,15 @@
       </c>
       <c r="AA37" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>6.3</v>
       </c>
       <c r="AF37" t="n">
         <v>225.87</v>
@@ -3849,15 +3852,6 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -3866,6 +3860,15 @@
       </c>
       <c r="AA38" t="n">
         <v>16.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF38" t="n">
         <v>229.48</v>
@@ -3944,15 +3947,6 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -3961,6 +3955,15 @@
       </c>
       <c r="AA39" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF39" t="n">
         <v>230.54</v>
@@ -4039,15 +4042,6 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4057,11 +4051,20 @@
       <c r="AA40" t="n">
         <v>10.3</v>
       </c>
+      <c r="AB40" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF40" t="n">
         <v>224.23</v>
       </c>
       <c r="AG40" t="n">
-        <v>-6.31</v>
+        <v>-6.3</v>
       </c>
       <c r="AK40" t="n">
         <v>128.6</v>
@@ -4137,15 +4140,6 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4155,11 +4149,20 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
+      <c r="AB41" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.87</v>
+        <v>-0.88</v>
       </c>
       <c r="AK41" t="n">
         <v>127.19</v>
@@ -4235,15 +4238,6 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4252,6 +4246,15 @@
       </c>
       <c r="AA42" t="n">
         <v>12</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF42" t="n">
         <v>222.92</v>
@@ -4333,15 +4336,6 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4351,11 +4345,20 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
+      <c r="AB43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AK43" t="n">
         <v>130.42</v>
@@ -4431,15 +4434,6 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4448,6 +4442,15 @@
       </c>
       <c r="AA44" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF44" t="n">
         <v>221.86</v>
@@ -4529,15 +4532,6 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -4546,6 +4540,15 @@
       </c>
       <c r="AA45" t="n">
         <v>18.8</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AF45" t="n">
         <v>227.49</v>
@@ -4624,15 +4627,6 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -4641,6 +4635,15 @@
       </c>
       <c r="AA46" t="n">
         <v>17.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AF46" t="n">
         <v>233.56</v>
@@ -4719,15 +4722,6 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
-      <c r="V47" t="n">
-        <v>16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -4736,6 +4730,15 @@
       </c>
       <c r="AA47" t="n">
         <v>18.1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>12.8</v>
       </c>
       <c r="AF47" t="n">
         <v>234.94</v>
@@ -4817,23 +4820,17 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>23</v>
-      </c>
       <c r="AA48" t="n">
         <v>16.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>7</v>
       </c>
       <c r="AF48" t="n">
         <v>229.19</v>
@@ -4915,23 +4912,17 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>16.1</v>
-      </c>
       <c r="AA49" t="n">
         <v>13.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.4</v>
       </c>
       <c r="AF49" t="n">
         <v>224.91</v>
@@ -5013,23 +5004,17 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA50" t="n">
         <v>9.6</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF50" t="n">
         <v>220.83</v>
@@ -5111,23 +5096,17 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA51" t="n">
         <v>14</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
         <v>228.06</v>
@@ -5209,23 +5188,17 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21.4</v>
-      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
         <v>233.59</v>
@@ -5304,23 +5277,14 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -687,15 +687,6 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
       </c>
@@ -770,15 +761,6 @@
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AK3" t="n">
         <v>134.62</v>
       </c>
@@ -829,15 +811,6 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
@@ -894,15 +867,6 @@
       <c r="AA5" t="n">
         <v>10</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AF5" t="n">
         <v>224.37</v>
       </c>
@@ -959,15 +923,6 @@
       <c r="AA6" t="n">
         <v>9</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="AF6" t="n">
         <v>225.93</v>
       </c>
@@ -1045,15 +1000,6 @@
       <c r="AA7" t="n">
         <v>8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="AF7" t="n">
         <v>218.63</v>
       </c>
@@ -1131,15 +1077,6 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
@@ -1229,15 +1166,6 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
@@ -1306,15 +1234,6 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
@@ -1383,15 +1302,6 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
@@ -1460,15 +1370,6 @@
       <c r="AA12" t="n">
         <v>14</v>
       </c>
-      <c r="AB12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF12" t="n">
         <v>225.14</v>
       </c>
@@ -1537,15 +1438,6 @@
       <c r="AA13" t="n">
         <v>15</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF13" t="n">
         <v>229.98</v>
       </c>
@@ -1635,15 +1527,6 @@
       <c r="AA14" t="n">
         <v>13</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF14" t="n">
         <v>229.96</v>
       </c>
@@ -1733,15 +1616,6 @@
       <c r="AA15" t="n">
         <v>10</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF15" t="n">
         <v>227.01</v>
       </c>
@@ -1831,15 +1705,6 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
@@ -1929,15 +1794,6 @@
       <c r="AA17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF17" t="n">
         <v>231.16</v>
       </c>
@@ -2006,15 +1862,6 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
-      <c r="AB18" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF18" t="n">
         <v>228.13</v>
       </c>
@@ -2083,15 +1930,6 @@
       <c r="AA19" t="n">
         <v>9</v>
       </c>
-      <c r="AB19" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4</v>
-      </c>
       <c r="AF19" t="n">
         <v>229.16</v>
       </c>
@@ -2181,15 +2019,6 @@
       <c r="AA20" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB20" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF20" t="n">
         <v>228.55</v>
       </c>
@@ -2279,15 +2108,6 @@
       <c r="AA21" t="n">
         <v>10</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF21" t="n">
         <v>219.99</v>
       </c>
@@ -2377,15 +2197,6 @@
       <c r="AA22" t="n">
         <v>11</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF22" t="n">
         <v>219.22</v>
       </c>
@@ -2475,15 +2286,6 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
@@ -2573,15 +2375,6 @@
       <c r="AA24" t="n">
         <v>14</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF24" t="n">
         <v>220.58</v>
       </c>
@@ -2650,15 +2443,6 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF25" t="n">
         <v>223.43</v>
       </c>
@@ -2727,15 +2511,6 @@
       <c r="AA26" t="n">
         <v>13</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF26" t="n">
         <v>229.48</v>
       </c>
@@ -2825,15 +2600,6 @@
       <c r="AA27" t="n">
         <v>14</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
-      </c>
       <c r="AF27" t="n">
         <v>241.48</v>
       </c>
@@ -2923,15 +2689,6 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB28" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
@@ -3021,15 +2778,6 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
@@ -3119,15 +2867,6 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
-      <c r="AB30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
@@ -3217,15 +2956,6 @@
       <c r="AA31" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB31" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF31" t="n">
         <v>234.87</v>
       </c>
@@ -3294,15 +3024,6 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AF32" t="n">
         <v>234.78</v>
       </c>
@@ -3371,15 +3092,6 @@
       <c r="AA33" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF33" t="n">
         <v>229.75</v>
       </c>
@@ -3469,15 +3181,6 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
@@ -3567,15 +3270,6 @@
       <c r="AA35" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF35" t="n">
         <v>218.37</v>
       </c>
@@ -3665,15 +3359,6 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF36" t="n">
         <v>220.85</v>
       </c>
@@ -3763,15 +3448,6 @@
       <c r="AA37" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AF37" t="n">
         <v>225.87</v>
       </c>
@@ -3861,15 +3537,6 @@
       <c r="AA38" t="n">
         <v>16.1</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF38" t="n">
         <v>229.48</v>
       </c>
@@ -3956,15 +3623,6 @@
       <c r="AA39" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF39" t="n">
         <v>230.54</v>
       </c>
@@ -4051,15 +3709,6 @@
       <c r="AA40" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB40" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AF40" t="n">
         <v>224.23</v>
       </c>
@@ -4149,15 +3798,6 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB41" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
@@ -4247,15 +3887,6 @@
       <c r="AA42" t="n">
         <v>12</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF42" t="n">
         <v>222.92</v>
       </c>
@@ -4345,15 +3976,6 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
-      <c r="AB43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
@@ -4443,15 +4065,6 @@
       <c r="AA44" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AF44" t="n">
         <v>221.86</v>
       </c>
@@ -4541,15 +4154,6 @@
       <c r="AA45" t="n">
         <v>18.8</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AF45" t="n">
         <v>227.49</v>
       </c>
@@ -4636,15 +4240,6 @@
       <c r="AA46" t="n">
         <v>17.2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AF46" t="n">
         <v>233.56</v>
       </c>
@@ -4731,15 +4326,6 @@
       <c r="AA47" t="n">
         <v>18.1</v>
       </c>
-      <c r="AB47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>12.8</v>
-      </c>
       <c r="AF47" t="n">
         <v>234.94</v>
       </c>
@@ -4820,17 +4406,14 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
+      <c r="Y48" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>23</v>
+      </c>
       <c r="AA48" t="n">
         <v>16.9</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>7</v>
       </c>
       <c r="AF48" t="n">
         <v>229.19</v>
@@ -4912,17 +4495,14 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="Y49" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AA49" t="n">
         <v>13.8</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.4</v>
       </c>
       <c r="AF49" t="n">
         <v>224.91</v>
@@ -5004,17 +4584,14 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
+      <c r="Y50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA50" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.8</v>
       </c>
       <c r="AF50" t="n">
         <v>220.83</v>
@@ -5096,17 +4673,14 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="Y51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA51" t="n">
         <v>14</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
         <v>228.06</v>
@@ -5188,17 +4762,14 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="Y52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.4</v>
+      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
         <v>233.59</v>
@@ -5277,14 +4848,14 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
+      <c r="V2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -686,6 +695,15 @@
       </c>
       <c r="AA2" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6</v>
       </c>
       <c r="AF2" t="n">
         <v>225.08</v>
@@ -752,6 +770,15 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
+      <c r="V3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -760,6 +787,15 @@
       </c>
       <c r="AA3" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AK3" t="n">
         <v>134.62</v>
@@ -802,6 +838,15 @@
       <c r="T4" t="n">
         <v>18</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -810,6 +855,15 @@
       </c>
       <c r="AA4" t="n">
         <v>9</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF4" t="n">
         <v>221.37</v>
@@ -858,6 +912,15 @@
       <c r="T5" t="n">
         <v>18</v>
       </c>
+      <c r="V5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -866,6 +929,15 @@
       </c>
       <c r="AA5" t="n">
         <v>10</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>224.37</v>
@@ -914,6 +986,15 @@
       <c r="T6" t="n">
         <v>18</v>
       </c>
+      <c r="V6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -922,6 +1003,15 @@
       </c>
       <c r="AA6" t="n">
         <v>9</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF6" t="n">
         <v>225.93</v>
@@ -991,6 +1081,15 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
+      <c r="V7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -999,6 +1098,15 @@
       </c>
       <c r="AA7" t="n">
         <v>8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-5.1</v>
       </c>
       <c r="AF7" t="n">
         <v>218.63</v>
@@ -1068,6 +1176,15 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1076,6 +1193,15 @@
       </c>
       <c r="AA8" t="n">
         <v>9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF8" t="n">
         <v>216.39</v>
@@ -1157,6 +1283,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1165,6 +1300,15 @@
       </c>
       <c r="AA9" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
         <v>217.16</v>
@@ -1225,6 +1369,15 @@
       <c r="T10" t="n">
         <v>18</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1233,6 +1386,15 @@
       </c>
       <c r="AA10" t="n">
         <v>10</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF10" t="n">
         <v>220.31</v>
@@ -1293,6 +1455,15 @@
       <c r="T11" t="n">
         <v>18</v>
       </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1301,6 +1472,15 @@
       </c>
       <c r="AA11" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.5</v>
       </c>
       <c r="AF11" t="n">
         <v>221.99</v>
@@ -1361,6 +1541,15 @@
       <c r="T12" t="n">
         <v>18</v>
       </c>
+      <c r="V12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1369,6 +1558,15 @@
       </c>
       <c r="AA12" t="n">
         <v>14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF12" t="n">
         <v>225.14</v>
@@ -1429,6 +1627,15 @@
       <c r="T13" t="n">
         <v>18</v>
       </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1437,6 +1644,15 @@
       </c>
       <c r="AA13" t="n">
         <v>15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF13" t="n">
         <v>229.98</v>
@@ -1518,6 +1734,15 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
+      <c r="V14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1526,6 +1751,15 @@
       </c>
       <c r="AA14" t="n">
         <v>13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AF14" t="n">
         <v>229.96</v>
@@ -1607,6 +1841,15 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1615,6 +1858,15 @@
       </c>
       <c r="AA15" t="n">
         <v>10</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF15" t="n">
         <v>227.01</v>
@@ -1696,6 +1948,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -1704,6 +1965,15 @@
       </c>
       <c r="AA16" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF16" t="n">
         <v>228.35</v>
@@ -1785,6 +2055,15 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1793,6 +2072,15 @@
       </c>
       <c r="AA17" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF17" t="n">
         <v>231.16</v>
@@ -1853,6 +2141,15 @@
       <c r="T18" t="n">
         <v>18</v>
       </c>
+      <c r="V18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -1861,6 +2158,15 @@
       </c>
       <c r="AA18" t="n">
         <v>9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF18" t="n">
         <v>228.13</v>
@@ -1921,6 +2227,15 @@
       <c r="T19" t="n">
         <v>18</v>
       </c>
+      <c r="V19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -1929,6 +2244,15 @@
       </c>
       <c r="AA19" t="n">
         <v>9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
       </c>
       <c r="AF19" t="n">
         <v>229.16</v>
@@ -2010,6 +2334,15 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
+      <c r="V20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2018,6 +2351,15 @@
       </c>
       <c r="AA20" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF20" t="n">
         <v>228.55</v>
@@ -2099,6 +2441,15 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
+      <c r="V21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2107,6 +2458,15 @@
       </c>
       <c r="AA21" t="n">
         <v>10</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF21" t="n">
         <v>219.99</v>
@@ -2188,6 +2548,15 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2196,6 +2565,15 @@
       </c>
       <c r="AA22" t="n">
         <v>11</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF22" t="n">
         <v>219.22</v>
@@ -2277,6 +2655,15 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
+      <c r="V23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2285,6 +2672,15 @@
       </c>
       <c r="AA23" t="n">
         <v>14</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF23" t="n">
         <v>220.73</v>
@@ -2366,6 +2762,15 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2374,6 +2779,15 @@
       </c>
       <c r="AA24" t="n">
         <v>14</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF24" t="n">
         <v>220.58</v>
@@ -2434,6 +2848,15 @@
       <c r="T25" t="n">
         <v>18</v>
       </c>
+      <c r="V25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2442,6 +2865,15 @@
       </c>
       <c r="AA25" t="n">
         <v>13</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF25" t="n">
         <v>223.43</v>
@@ -2502,6 +2934,15 @@
       <c r="T26" t="n">
         <v>18</v>
       </c>
+      <c r="V26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2510,6 +2951,15 @@
       </c>
       <c r="AA26" t="n">
         <v>13</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.48</v>
@@ -2591,6 +3041,15 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
+      <c r="V27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2599,6 +3058,15 @@
       </c>
       <c r="AA27" t="n">
         <v>14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>241.48</v>
@@ -2680,6 +3148,15 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
+      <c r="V28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -2688,6 +3165,15 @@
       </c>
       <c r="AA28" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF28" t="n">
         <v>238.69</v>
@@ -2769,6 +3255,15 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -2777,6 +3272,15 @@
       </c>
       <c r="AA29" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.7</v>
       </c>
       <c r="AF29" t="n">
         <v>233.48</v>
@@ -2858,6 +3362,15 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -2866,6 +3379,15 @@
       </c>
       <c r="AA30" t="n">
         <v>17</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF30" t="n">
         <v>235.13</v>
@@ -2947,6 +3469,15 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -2955,6 +3486,15 @@
       </c>
       <c r="AA31" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF31" t="n">
         <v>234.87</v>
@@ -3015,6 +3555,15 @@
       <c r="T32" t="n">
         <v>18</v>
       </c>
+      <c r="V32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3023,6 +3572,15 @@
       </c>
       <c r="AA32" t="n">
         <v>13</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.2</v>
       </c>
       <c r="AF32" t="n">
         <v>234.78</v>
@@ -3083,6 +3641,15 @@
       <c r="T33" t="n">
         <v>18</v>
       </c>
+      <c r="V33" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3091,6 +3658,15 @@
       </c>
       <c r="AA33" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF33" t="n">
         <v>229.75</v>
@@ -3172,6 +3748,15 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3180,6 +3765,15 @@
       </c>
       <c r="AA34" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF34" t="n">
         <v>222.86</v>
@@ -3261,6 +3855,15 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3269,6 +3872,15 @@
       </c>
       <c r="AA35" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF35" t="n">
         <v>218.37</v>
@@ -3350,6 +3962,15 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3358,6 +3979,15 @@
       </c>
       <c r="AA36" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF36" t="n">
         <v>220.85</v>
@@ -3439,6 +4069,15 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
+      <c r="V37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3447,6 +4086,15 @@
       </c>
       <c r="AA37" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>6.3</v>
       </c>
       <c r="AF37" t="n">
         <v>225.87</v>
@@ -3528,6 +4176,15 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -3536,6 +4193,15 @@
       </c>
       <c r="AA38" t="n">
         <v>16.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF38" t="n">
         <v>229.48</v>
@@ -3614,6 +4280,15 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>18</v>
+      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -3622,6 +4297,15 @@
       </c>
       <c r="AA39" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF39" t="n">
         <v>230.54</v>
@@ -3700,6 +4384,15 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -3708,6 +4401,15 @@
       </c>
       <c r="AA40" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8</v>
       </c>
       <c r="AF40" t="n">
         <v>224.23</v>
@@ -3789,6 +4491,15 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
+      <c r="V41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -3797,6 +4508,15 @@
       </c>
       <c r="AA41" t="n">
         <v>7.9</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF41" t="n">
         <v>223.36</v>
@@ -3878,6 +4598,15 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -3886,6 +4615,15 @@
       </c>
       <c r="AA42" t="n">
         <v>12</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF42" t="n">
         <v>222.92</v>
@@ -3967,6 +4705,15 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
+      <c r="V43" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -3975,6 +4722,15 @@
       </c>
       <c r="AA43" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF43" t="n">
         <v>222.77</v>
@@ -4056,6 +4812,15 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4064,6 +4829,15 @@
       </c>
       <c r="AA44" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF44" t="n">
         <v>221.86</v>
@@ -4145,6 +4919,15 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -4153,6 +4936,15 @@
       </c>
       <c r="AA45" t="n">
         <v>18.8</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AF45" t="n">
         <v>227.49</v>
@@ -4231,6 +5023,15 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -4239,6 +5040,15 @@
       </c>
       <c r="AA46" t="n">
         <v>17.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AF46" t="n">
         <v>233.56</v>
@@ -4317,6 +5127,15 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
+      <c r="V47" t="n">
+        <v>16</v>
+      </c>
+      <c r="W47" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -4325,6 +5144,15 @@
       </c>
       <c r="AA47" t="n">
         <v>18.1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>12.8</v>
       </c>
       <c r="AF47" t="n">
         <v>234.94</v>
@@ -4406,6 +5234,15 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
+      <c r="V48" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -4414,6 +5251,15 @@
       </c>
       <c r="AA48" t="n">
         <v>16.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>7</v>
       </c>
       <c r="AF48" t="n">
         <v>229.19</v>
@@ -4495,6 +5341,15 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4503,6 +5358,15 @@
       </c>
       <c r="AA49" t="n">
         <v>13.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.4</v>
       </c>
       <c r="AF49" t="n">
         <v>224.91</v>
@@ -4584,6 +5448,15 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
+      <c r="V50" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -4592,6 +5465,15 @@
       </c>
       <c r="AA50" t="n">
         <v>9.6</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF50" t="n">
         <v>220.83</v>
@@ -4673,6 +5555,15 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y51" t="n">
         <v>6.8</v>
       </c>
@@ -4681,6 +5572,15 @@
       </c>
       <c r="AA51" t="n">
         <v>14</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
         <v>228.06</v>
@@ -4762,6 +5662,15 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y52" t="n">
         <v>12.2</v>
       </c>
@@ -4770,6 +5679,15 @@
       </c>
       <c r="AA52" t="n">
         <v>19.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
         <v>233.59</v>
@@ -4848,6 +5766,15 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25.6</v>
+      </c>
       <c r="Y53" t="n">
         <v>16.6</v>
       </c>
@@ -4856,6 +5783,15 @@
       </c>
       <c r="AA53" t="n">
         <v>21.2</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -4921,6 +5857,33 @@
       </c>
       <c r="T54" t="n">
         <v>16</v>
+      </c>
+      <c r="V54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46291</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,15 +696,6 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
       </c>
@@ -788,15 +779,6 @@
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AK3" t="n">
         <v>134.62</v>
       </c>
@@ -856,15 +838,6 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
@@ -930,15 +903,6 @@
       <c r="AA5" t="n">
         <v>10</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AF5" t="n">
         <v>224.37</v>
       </c>
@@ -1004,15 +968,6 @@
       <c r="AA6" t="n">
         <v>9</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="AF6" t="n">
         <v>225.93</v>
       </c>
@@ -1099,15 +1054,6 @@
       <c r="AA7" t="n">
         <v>8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="AF7" t="n">
         <v>218.63</v>
       </c>
@@ -1194,15 +1140,6 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
@@ -1301,15 +1238,6 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
@@ -1387,15 +1315,6 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
@@ -1473,15 +1392,6 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
@@ -1559,15 +1469,6 @@
       <c r="AA12" t="n">
         <v>14</v>
       </c>
-      <c r="AB12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF12" t="n">
         <v>225.14</v>
       </c>
@@ -1645,15 +1546,6 @@
       <c r="AA13" t="n">
         <v>15</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF13" t="n">
         <v>229.98</v>
       </c>
@@ -1752,15 +1644,6 @@
       <c r="AA14" t="n">
         <v>13</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF14" t="n">
         <v>229.96</v>
       </c>
@@ -1859,15 +1742,6 @@
       <c r="AA15" t="n">
         <v>10</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF15" t="n">
         <v>227.01</v>
       </c>
@@ -1966,15 +1840,6 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
@@ -2073,15 +1938,6 @@
       <c r="AA17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF17" t="n">
         <v>231.16</v>
       </c>
@@ -2159,15 +2015,6 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
-      <c r="AB18" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF18" t="n">
         <v>228.13</v>
       </c>
@@ -2245,15 +2092,6 @@
       <c r="AA19" t="n">
         <v>9</v>
       </c>
-      <c r="AB19" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4</v>
-      </c>
       <c r="AF19" t="n">
         <v>229.16</v>
       </c>
@@ -2352,15 +2190,6 @@
       <c r="AA20" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB20" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF20" t="n">
         <v>228.55</v>
       </c>
@@ -2459,15 +2288,6 @@
       <c r="AA21" t="n">
         <v>10</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF21" t="n">
         <v>219.99</v>
       </c>
@@ -2566,15 +2386,6 @@
       <c r="AA22" t="n">
         <v>11</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF22" t="n">
         <v>219.22</v>
       </c>
@@ -2673,15 +2484,6 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
@@ -2780,15 +2582,6 @@
       <c r="AA24" t="n">
         <v>14</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF24" t="n">
         <v>220.58</v>
       </c>
@@ -2866,15 +2659,6 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF25" t="n">
         <v>223.43</v>
       </c>
@@ -2952,15 +2736,6 @@
       <c r="AA26" t="n">
         <v>13</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF26" t="n">
         <v>229.48</v>
       </c>
@@ -3059,15 +2834,6 @@
       <c r="AA27" t="n">
         <v>14</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
-      </c>
       <c r="AF27" t="n">
         <v>241.48</v>
       </c>
@@ -3166,15 +2932,6 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB28" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
@@ -3273,15 +3030,6 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
@@ -3380,15 +3128,6 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
-      <c r="AB30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
@@ -3487,15 +3226,6 @@
       <c r="AA31" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB31" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF31" t="n">
         <v>234.87</v>
       </c>
@@ -3573,15 +3303,6 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AF32" t="n">
         <v>234.78</v>
       </c>
@@ -3659,15 +3380,6 @@
       <c r="AA33" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF33" t="n">
         <v>229.75</v>
       </c>
@@ -3766,15 +3478,6 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
@@ -3873,15 +3576,6 @@
       <c r="AA35" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF35" t="n">
         <v>218.37</v>
       </c>
@@ -3980,15 +3674,6 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF36" t="n">
         <v>220.85</v>
       </c>
@@ -4087,15 +3772,6 @@
       <c r="AA37" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AF37" t="n">
         <v>225.87</v>
       </c>
@@ -4194,15 +3870,6 @@
       <c r="AA38" t="n">
         <v>16.1</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF38" t="n">
         <v>229.48</v>
       </c>
@@ -4298,15 +3965,6 @@
       <c r="AA39" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF39" t="n">
         <v>230.54</v>
       </c>
@@ -4402,15 +4060,6 @@
       <c r="AA40" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB40" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AF40" t="n">
         <v>224.23</v>
       </c>
@@ -4509,15 +4158,6 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB41" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
@@ -4616,15 +4256,6 @@
       <c r="AA42" t="n">
         <v>12</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF42" t="n">
         <v>222.92</v>
       </c>
@@ -4723,15 +4354,6 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
-      <c r="AB43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
@@ -4830,15 +4452,6 @@
       <c r="AA44" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AF44" t="n">
         <v>221.86</v>
       </c>
@@ -4937,15 +4550,6 @@
       <c r="AA45" t="n">
         <v>18.8</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AF45" t="n">
         <v>227.49</v>
       </c>
@@ -5041,15 +4645,6 @@
       <c r="AA46" t="n">
         <v>17.2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AF46" t="n">
         <v>233.56</v>
       </c>
@@ -5145,15 +4740,6 @@
       <c r="AA47" t="n">
         <v>18.1</v>
       </c>
-      <c r="AB47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>12.8</v>
-      </c>
       <c r="AF47" t="n">
         <v>234.94</v>
       </c>
@@ -5252,15 +4838,6 @@
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
-      <c r="AB48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>7</v>
-      </c>
       <c r="AF48" t="n">
         <v>229.19</v>
       </c>
@@ -5359,15 +4936,6 @@
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AF49" t="n">
         <v>224.91</v>
       </c>
@@ -5466,15 +5034,6 @@
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
-      <c r="AB50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF50" t="n">
         <v>220.83</v>
       </c>
@@ -5573,15 +5132,6 @@
       <c r="AA51" t="n">
         <v>14</v>
       </c>
-      <c r="AB51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.1</v>
-      </c>
       <c r="AF51" t="n">
         <v>228.06</v>
       </c>
@@ -5680,15 +5230,6 @@
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
-      <c r="AB52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.1</v>
-      </c>
       <c r="AF52" t="n">
         <v>233.59</v>
       </c>
@@ -5784,15 +5325,6 @@
       <c r="AA53" t="n">
         <v>21.2</v>
       </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
-      </c>
       <c r="AF53" t="n">
         <v>231.92</v>
       </c>
@@ -5876,14 +5408,17 @@
       <c r="AA54" t="n">
         <v>17.3</v>
       </c>
-      <c r="AB54" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.300000000000001</v>
+      <c r="AF54" t="n">
+        <v>235</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46291</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,6 +696,15 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB2" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
       </c>
@@ -779,6 +788,15 @@
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="AK3" t="n">
         <v>134.62</v>
       </c>
@@ -838,6 +856,15 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
+      <c r="AB4" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
@@ -903,6 +930,15 @@
       <c r="AA5" t="n">
         <v>10</v>
       </c>
+      <c r="AB5" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AF5" t="n">
         <v>224.37</v>
       </c>
@@ -968,6 +1004,15 @@
       <c r="AA6" t="n">
         <v>9</v>
       </c>
+      <c r="AB6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="AF6" t="n">
         <v>225.93</v>
       </c>
@@ -1054,6 +1099,15 @@
       <c r="AA7" t="n">
         <v>8</v>
       </c>
+      <c r="AB7" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="AF7" t="n">
         <v>218.63</v>
       </c>
@@ -1140,6 +1194,15 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
@@ -1238,6 +1301,15 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
@@ -1315,6 +1387,15 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
@@ -1392,6 +1473,15 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
@@ -1469,6 +1559,15 @@
       <c r="AA12" t="n">
         <v>14</v>
       </c>
+      <c r="AB12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF12" t="n">
         <v>225.14</v>
       </c>
@@ -1546,6 +1645,15 @@
       <c r="AA13" t="n">
         <v>15</v>
       </c>
+      <c r="AB13" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="AF13" t="n">
         <v>229.98</v>
       </c>
@@ -1644,6 +1752,15 @@
       <c r="AA14" t="n">
         <v>13</v>
       </c>
+      <c r="AB14" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AF14" t="n">
         <v>229.96</v>
       </c>
@@ -1742,6 +1859,15 @@
       <c r="AA15" t="n">
         <v>10</v>
       </c>
+      <c r="AB15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.4</v>
+      </c>
       <c r="AF15" t="n">
         <v>227.01</v>
       </c>
@@ -1840,6 +1966,15 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
@@ -1938,6 +2073,15 @@
       <c r="AA17" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF17" t="n">
         <v>231.16</v>
       </c>
@@ -2015,6 +2159,15 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
+      <c r="AB18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AF18" t="n">
         <v>228.13</v>
       </c>
@@ -2092,6 +2245,15 @@
       <c r="AA19" t="n">
         <v>9</v>
       </c>
+      <c r="AB19" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
+      </c>
       <c r="AF19" t="n">
         <v>229.16</v>
       </c>
@@ -2190,6 +2352,15 @@
       <c r="AA20" t="n">
         <v>8.5</v>
       </c>
+      <c r="AB20" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF20" t="n">
         <v>228.55</v>
       </c>
@@ -2288,6 +2459,15 @@
       <c r="AA21" t="n">
         <v>10</v>
       </c>
+      <c r="AB21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF21" t="n">
         <v>219.99</v>
       </c>
@@ -2386,6 +2566,15 @@
       <c r="AA22" t="n">
         <v>11</v>
       </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5.5</v>
+      </c>
       <c r="AF22" t="n">
         <v>219.22</v>
       </c>
@@ -2484,6 +2673,15 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
@@ -2582,6 +2780,15 @@
       <c r="AA24" t="n">
         <v>14</v>
       </c>
+      <c r="AB24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF24" t="n">
         <v>220.58</v>
       </c>
@@ -2659,6 +2866,15 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
+      <c r="AB25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF25" t="n">
         <v>223.43</v>
       </c>
@@ -2736,6 +2952,15 @@
       <c r="AA26" t="n">
         <v>13</v>
       </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AF26" t="n">
         <v>229.48</v>
       </c>
@@ -2834,6 +3059,15 @@
       <c r="AA27" t="n">
         <v>14</v>
       </c>
+      <c r="AB27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
+      </c>
       <c r="AF27" t="n">
         <v>241.48</v>
       </c>
@@ -2932,6 +3166,15 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB28" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
@@ -3030,6 +3273,15 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
@@ -3128,6 +3380,15 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
+      <c r="AB30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
@@ -3226,6 +3487,15 @@
       <c r="AA31" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB31" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF31" t="n">
         <v>234.87</v>
       </c>
@@ -3303,6 +3573,15 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
+      <c r="AB32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.2</v>
+      </c>
       <c r="AF32" t="n">
         <v>234.78</v>
       </c>
@@ -3380,6 +3659,15 @@
       <c r="AA33" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB33" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AF33" t="n">
         <v>229.75</v>
       </c>
@@ -3478,6 +3766,15 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
+      <c r="AB34" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
@@ -3576,6 +3873,15 @@
       <c r="AA35" t="n">
         <v>9.5</v>
       </c>
+      <c r="AB35" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF35" t="n">
         <v>218.37</v>
       </c>
@@ -3674,6 +3980,15 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF36" t="n">
         <v>220.85</v>
       </c>
@@ -3772,6 +4087,15 @@
       <c r="AA37" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>6.3</v>
+      </c>
       <c r="AF37" t="n">
         <v>225.87</v>
       </c>
@@ -3870,6 +4194,15 @@
       <c r="AA38" t="n">
         <v>16.1</v>
       </c>
+      <c r="AB38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF38" t="n">
         <v>229.48</v>
       </c>
@@ -3914,6 +4247,9 @@
       <c r="E39" t="n">
         <v>26.4</v>
       </c>
+      <c r="F39" t="n">
+        <v>2.3</v>
+      </c>
       <c r="H39" t="n">
         <v>23.6</v>
       </c>
@@ -3964,6 +4300,15 @@
       </c>
       <c r="AA39" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF39" t="n">
         <v>230.54</v>
@@ -4009,6 +4354,9 @@
       <c r="E40" t="n">
         <v>25.9</v>
       </c>
+      <c r="F40" t="n">
+        <v>2.3</v>
+      </c>
       <c r="H40" t="n">
         <v>23.6</v>
       </c>
@@ -4059,6 +4407,15 @@
       </c>
       <c r="AA40" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8</v>
       </c>
       <c r="AF40" t="n">
         <v>224.23</v>
@@ -4158,6 +4515,15 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
+      <c r="AB41" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
@@ -4256,6 +4622,15 @@
       <c r="AA42" t="n">
         <v>12</v>
       </c>
+      <c r="AB42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF42" t="n">
         <v>222.92</v>
       </c>
@@ -4354,6 +4729,15 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
+      <c r="AB43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
@@ -4452,6 +4836,15 @@
       <c r="AA44" t="n">
         <v>11.6</v>
       </c>
+      <c r="AB44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AF44" t="n">
         <v>221.86</v>
       </c>
@@ -4550,6 +4943,15 @@
       <c r="AA45" t="n">
         <v>18.8</v>
       </c>
+      <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="AF45" t="n">
         <v>227.49</v>
       </c>
@@ -4594,6 +4996,9 @@
       <c r="E46" t="n">
         <v>23.2</v>
       </c>
+      <c r="F46" t="n">
+        <v>2.7</v>
+      </c>
       <c r="H46" t="n">
         <v>22.3</v>
       </c>
@@ -4644,6 +5049,15 @@
       </c>
       <c r="AA46" t="n">
         <v>17.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AF46" t="n">
         <v>233.56</v>
@@ -4689,6 +5103,9 @@
       <c r="E47" t="n">
         <v>19.8</v>
       </c>
+      <c r="F47" t="n">
+        <v>2.5</v>
+      </c>
       <c r="H47" t="n">
         <v>21.7</v>
       </c>
@@ -4739,6 +5156,15 @@
       </c>
       <c r="AA47" t="n">
         <v>18.1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>12.8</v>
       </c>
       <c r="AF47" t="n">
         <v>234.94</v>
@@ -4838,6 +5264,15 @@
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
+      <c r="AB48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>7</v>
+      </c>
       <c r="AF48" t="n">
         <v>229.19</v>
       </c>
@@ -4936,6 +5371,15 @@
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
+      <c r="AB49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.4</v>
+      </c>
       <c r="AF49" t="n">
         <v>224.91</v>
       </c>
@@ -5034,6 +5478,15 @@
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
+      <c r="AB50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF50" t="n">
         <v>220.83</v>
       </c>
@@ -5132,6 +5585,15 @@
       <c r="AA51" t="n">
         <v>14</v>
       </c>
+      <c r="AB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.1</v>
+      </c>
       <c r="AF51" t="n">
         <v>228.06</v>
       </c>
@@ -5230,6 +5692,15 @@
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.1</v>
+      </c>
       <c r="AF52" t="n">
         <v>233.59</v>
       </c>
@@ -5263,7 +5734,7 @@
         <v>46290</v>
       </c>
       <c r="B53" t="n">
-        <v>110.9</v>
+        <v>115.4</v>
       </c>
       <c r="C53" t="n">
         <v>41.3</v>
@@ -5274,6 +5745,9 @@
       <c r="E53" t="n">
         <v>28.79</v>
       </c>
+      <c r="F53" t="n">
+        <v>4.5</v>
+      </c>
       <c r="H53" t="n">
         <v>21.9</v>
       </c>
@@ -5324,6 +5798,15 @@
       </c>
       <c r="AA53" t="n">
         <v>21.2</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5346,7 +5829,7 @@
         <v>46291</v>
       </c>
       <c r="B54" t="n">
-        <v>106.3</v>
+        <v>110.8</v>
       </c>
       <c r="C54" t="n">
         <v>39.3</v>
@@ -5357,6 +5840,9 @@
       <c r="E54" t="n">
         <v>27.23</v>
       </c>
+      <c r="F54" t="n">
+        <v>4.5</v>
+      </c>
       <c r="H54" t="n">
         <v>21.9</v>
       </c>
@@ -5407,6 +5893,15 @@
       </c>
       <c r="AA54" t="n">
         <v>17.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5429,7 +5924,7 @@
         <v>46292</v>
       </c>
       <c r="B55" t="n">
-        <v>100.4</v>
+        <v>104.9</v>
       </c>
       <c r="C55" t="n">
         <v>35.8</v>
@@ -5439,6 +5934,9 @@
       </c>
       <c r="E55" t="n">
         <v>25.96</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.5</v>
       </c>
       <c r="H55" t="n">
         <v>21.9</v>
@@ -5482,7 +5980,7 @@
         <v>46293</v>
       </c>
       <c r="B56" t="n">
-        <v>111.9</v>
+        <v>115.4</v>
       </c>
       <c r="C56" t="n">
         <v>42.1</v>
@@ -5492,6 +5990,9 @@
       </c>
       <c r="E56" t="n">
         <v>28.84</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.5</v>
       </c>
       <c r="H56" t="n">
         <v>21.8</v>
@@ -5535,7 +6036,7 @@
         <v>46294</v>
       </c>
       <c r="B57" t="n">
-        <v>115</v>
+        <v>118.5</v>
       </c>
       <c r="C57" t="n">
         <v>45.2</v>
@@ -5545,6 +6046,9 @@
       </c>
       <c r="E57" t="n">
         <v>28.54</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.5</v>
       </c>
       <c r="H57" t="n">
         <v>21.8</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -770,15 +761,6 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -838,15 +820,6 @@
       <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -912,15 +885,6 @@
       <c r="T5" t="n">
         <v>18</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -986,15 +950,6 @@
       <c r="T6" t="n">
         <v>18</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1081,15 +1036,6 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1176,15 +1122,6 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1283,15 +1220,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1369,15 +1297,6 @@
       <c r="T10" t="n">
         <v>18</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1455,15 +1374,6 @@
       <c r="T11" t="n">
         <v>18</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1541,15 +1451,6 @@
       <c r="T12" t="n">
         <v>18</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1627,15 +1528,6 @@
       <c r="T13" t="n">
         <v>18</v>
       </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1734,15 +1626,6 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1841,15 +1724,6 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1948,15 +1822,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -2055,15 +1920,6 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2141,15 +1997,6 @@
       <c r="T18" t="n">
         <v>18</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2227,15 +2074,6 @@
       <c r="T19" t="n">
         <v>18</v>
       </c>
-      <c r="V19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2334,15 +2172,6 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2441,15 +2270,6 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2548,15 +2368,6 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2655,15 +2466,6 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2762,15 +2564,6 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2848,15 +2641,6 @@
       <c r="T25" t="n">
         <v>18</v>
       </c>
-      <c r="V25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2934,15 +2718,6 @@
       <c r="T26" t="n">
         <v>18</v>
       </c>
-      <c r="V26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -3041,15 +2816,6 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -3148,15 +2914,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3255,15 +3012,6 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3362,15 +3110,6 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3469,15 +3208,6 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3555,15 +3285,6 @@
       <c r="T32" t="n">
         <v>18</v>
       </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3641,15 +3362,6 @@
       <c r="T33" t="n">
         <v>18</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3748,15 +3460,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3855,15 +3558,6 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3962,15 +3656,6 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -4069,15 +3754,6 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4176,15 +3852,6 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -4283,15 +3950,6 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4390,15 +4048,6 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4497,15 +4146,6 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4604,15 +4244,6 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4711,15 +4342,6 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4818,15 +4440,6 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4925,15 +4538,6 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -5032,15 +4636,6 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -5139,15 +4734,6 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
-      <c r="V47" t="n">
-        <v>16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -5246,15 +4832,6 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -5353,21 +4930,6 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>16.1</v>
-      </c>
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
@@ -5460,21 +5022,6 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
@@ -5567,21 +5114,6 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5674,21 +5206,6 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21.4</v>
-      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5781,24 +5298,6 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5875,24 +5374,6 @@
       </c>
       <c r="T54" t="n">
         <v>16</v>
-      </c>
-      <c r="V54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
       </c>
       <c r="AB54" t="n">
         <v>5.8</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -4930,6 +4930,12 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="Y49" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>16.1</v>
+      </c>
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
@@ -5451,6 +5457,21 @@
       </c>
       <c r="T55" t="n">
         <v>13</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>136.95</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.34</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46292</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
+      <c r="V2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -761,6 +770,15 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
+      <c r="V3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -803,10 +821,10 @@
         <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>93.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="O4" t="n">
-        <v>39.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -818,7 +836,16 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
         <v>5</v>
@@ -868,10 +895,10 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>89.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="O5" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -883,7 +910,16 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
@@ -933,10 +969,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>90.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>38.1</v>
+        <v>38.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -948,7 +984,16 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y6" t="n">
         <v>3</v>
@@ -1036,6 +1081,15 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
+      <c r="V7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1122,6 +1176,15 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1220,6 +1283,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1280,10 +1352,10 @@
         <v>6.5</v>
       </c>
       <c r="K10" t="n">
-        <v>102.5</v>
+        <v>100.1</v>
       </c>
       <c r="O10" t="n">
-        <v>43.3</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1295,7 +1367,16 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
@@ -1357,10 +1438,10 @@
         <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>96.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1372,7 +1453,16 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y11" t="n">
         <v>10</v>
@@ -1434,10 +1524,10 @@
         <v>5.5</v>
       </c>
       <c r="K12" t="n">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="O12" t="n">
-        <v>36.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1449,7 +1539,16 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
@@ -1511,10 +1610,10 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>79.8</v>
+        <v>77.7</v>
       </c>
       <c r="O13" t="n">
-        <v>33.7</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1526,7 +1625,16 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y13" t="n">
         <v>12</v>
@@ -1626,6 +1734,15 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
+      <c r="V14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1724,6 +1841,15 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1822,6 +1948,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -1920,6 +2055,15 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1980,10 +2124,10 @@
         <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>94.3</v>
+        <v>92</v>
       </c>
       <c r="O18" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1995,7 +2139,16 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
         <v>6</v>
@@ -2057,10 +2210,10 @@
         <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>88.5</v>
+        <v>86.3</v>
       </c>
       <c r="O19" t="n">
-        <v>37.4</v>
+        <v>37.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2072,7 +2225,16 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y19" t="n">
         <v>4</v>
@@ -2172,6 +2334,15 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
+      <c r="V20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2270,6 +2441,15 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
+      <c r="V21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2368,6 +2548,15 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2466,6 +2655,15 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
+      <c r="V23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2564,6 +2762,15 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2624,10 +2831,10 @@
         <v>6.1</v>
       </c>
       <c r="K25" t="n">
-        <v>84.5</v>
+        <v>82.3</v>
       </c>
       <c r="O25" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2639,7 +2846,16 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y25" t="n">
         <v>9</v>
@@ -2701,10 +2917,10 @@
         <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>76.3</v>
+        <v>74.2</v>
       </c>
       <c r="O26" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2716,7 +2932,16 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y26" t="n">
         <v>8</v>
@@ -2816,6 +3041,15 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
+      <c r="V27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2914,6 +3148,15 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
+      <c r="V28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3012,6 +3255,15 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3110,6 +3362,15 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3208,6 +3469,15 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3268,10 +3538,10 @@
         <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>80.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3283,7 +3553,16 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y32" t="n">
         <v>7</v>
@@ -3345,10 +3624,10 @@
         <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>83.7</v>
+        <v>81.5</v>
       </c>
       <c r="O33" t="n">
-        <v>35.4</v>
+        <v>35.9</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3360,7 +3639,16 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>18</v>
+        <v>19.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y33" t="n">
         <v>7</v>
@@ -3460,6 +3748,15 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3558,6 +3855,15 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3656,6 +3962,15 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3754,6 +4069,15 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
+      <c r="V37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3852,6 +4176,15 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -3950,6 +4283,15 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>18</v>
+      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4048,6 +4390,15 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4146,6 +4497,15 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
+      <c r="V41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4244,6 +4604,15 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4342,6 +4711,15 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
+      <c r="V43" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4440,6 +4818,15 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4538,6 +4925,15 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -4636,6 +5032,15 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -4734,6 +5139,15 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
+      <c r="V47" t="n">
+        <v>16</v>
+      </c>
+      <c r="W47" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -4832,6 +5246,15 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
+      <c r="V48" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -4930,6 +5353,15 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5028,6 +5460,21 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
+      <c r="V50" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
@@ -5120,6 +5567,21 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5212,6 +5674,21 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.4</v>
+      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5304,6 +5781,24 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5327,6 +5822,18 @@
       </c>
       <c r="BL53" s="1" t="n">
         <v>46290</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5381,6 +5888,24 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
+      <c r="V54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
+      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5404,6 +5929,18 @@
       </c>
       <c r="BL54" s="1" t="n">
         <v>46291</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5411,43 +5948,43 @@
         <v>46292</v>
       </c>
       <c r="B55" t="n">
-        <v>104.9</v>
+        <v>101</v>
       </c>
       <c r="C55" t="n">
-        <v>35.8</v>
+        <v>37</v>
       </c>
       <c r="D55" t="n">
-        <v>33.5</v>
+        <v>32.4</v>
       </c>
       <c r="E55" t="n">
-        <v>25.96</v>
+        <v>23.5</v>
       </c>
       <c r="F55" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="H55" t="n">
-        <v>21.9</v>
+        <v>17.9</v>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J55" t="n">
-        <v>36</v>
+        <v>29.9</v>
       </c>
       <c r="K55" t="n">
-        <v>66.90000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="M55" t="n">
         <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="O55" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5456,7 +5993,25 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="V55" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>16</v>
       </c>
       <c r="AB55" t="n">
         <v>3.3</v>
@@ -5467,6 +6022,12 @@
       <c r="AD55" t="n">
         <v>8.800000000000001</v>
       </c>
+      <c r="AF55" t="n">
+        <v>233.68</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-1.32</v>
+      </c>
       <c r="AK55" t="n">
         <v>136.95</v>
       </c>
@@ -5475,6 +6036,18 @@
       </c>
       <c r="BL55" s="1" t="n">
         <v>46292</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5482,31 +6055,31 @@
         <v>46293</v>
       </c>
       <c r="B56" t="n">
-        <v>115.4</v>
+        <v>115.9</v>
       </c>
       <c r="C56" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="D56" t="n">
-        <v>35.3</v>
+        <v>36.3</v>
       </c>
       <c r="E56" t="n">
         <v>28.84</v>
       </c>
       <c r="F56" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H56" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="I56" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="J56" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K56" t="n">
-        <v>69.3</v>
+        <v>62.9</v>
       </c>
       <c r="M56" t="n">
         <v>1.9</v>
@@ -5518,7 +6091,7 @@
         <v>28.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5527,7 +6100,46 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="V56" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>234.37</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>-0.46</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46293</v>
@@ -5541,28 +6153,28 @@
         <v>118.5</v>
       </c>
       <c r="C57" t="n">
-        <v>45.2</v>
+        <v>43.2</v>
       </c>
       <c r="D57" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="E57" t="n">
         <v>28.54</v>
       </c>
       <c r="F57" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="H57" t="n">
-        <v>21.8</v>
+        <v>22.8</v>
       </c>
       <c r="I57" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="J57" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
-        <v>70.3</v>
+        <v>68.5</v>
       </c>
       <c r="M57" t="n">
         <v>1.9</v>
@@ -5594,19 +6206,43 @@
         <v>46295</v>
       </c>
       <c r="B58" t="n">
-        <v>27.9</v>
+        <v>124.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>38</v>
       </c>
       <c r="E58" t="n">
         <v>27.93</v>
       </c>
+      <c r="F58" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>35</v>
+      </c>
       <c r="K58" t="n">
-        <v>7</v>
+        <v>68.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N58" t="n">
+        <v>28</v>
       </c>
       <c r="O58" t="n">
-        <v>2.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -5615,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46295</v>
@@ -5626,19 +6262,43 @@
         <v>46296</v>
       </c>
       <c r="B59" t="n">
-        <v>27.1</v>
+        <v>123</v>
+      </c>
+      <c r="C59" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36.9</v>
       </c>
       <c r="E59" t="n">
         <v>27.12</v>
       </c>
+      <c r="F59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J59" t="n">
+        <v>35</v>
+      </c>
       <c r="K59" t="n">
-        <v>6.4</v>
+        <v>68.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N59" t="n">
+        <v>29</v>
       </c>
       <c r="O59" t="n">
-        <v>2.7</v>
+        <v>30.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -5647,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46296</v>
@@ -5658,19 +6318,43 @@
         <v>46297</v>
       </c>
       <c r="B60" t="n">
-        <v>25.7</v>
+        <v>120.5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>36.8</v>
       </c>
       <c r="E60" t="n">
         <v>25.73</v>
       </c>
+      <c r="F60" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J60" t="n">
+        <v>35</v>
+      </c>
       <c r="K60" t="n">
-        <v>5.4</v>
+        <v>68.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N60" t="n">
+        <v>29</v>
       </c>
       <c r="O60" t="n">
-        <v>2.3</v>
+        <v>30.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -5679,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46297</v>
@@ -5696,10 +6380,10 @@
         <v>24.44</v>
       </c>
       <c r="K61" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O61" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5711,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>18</v>
+        <v>19.7</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46298</v>
@@ -5728,10 +6412,10 @@
         <v>23.87</v>
       </c>
       <c r="K62" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O62" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -5743,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>18</v>
+        <v>19.7</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46299</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -770,15 +761,6 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -838,15 +820,6 @@
       <c r="T4" t="n">
         <v>19.7</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -912,15 +885,6 @@
       <c r="T5" t="n">
         <v>19.7</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -986,15 +950,6 @@
       <c r="T6" t="n">
         <v>19.7</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1081,15 +1036,6 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1176,15 +1122,6 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1283,15 +1220,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1369,15 +1297,6 @@
       <c r="T10" t="n">
         <v>19.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1455,15 +1374,6 @@
       <c r="T11" t="n">
         <v>19.7</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1541,15 +1451,6 @@
       <c r="T12" t="n">
         <v>19.7</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1627,15 +1528,6 @@
       <c r="T13" t="n">
         <v>19.7</v>
       </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1734,15 +1626,6 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1841,15 +1724,6 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1948,15 +1822,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -2055,15 +1920,6 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2141,15 +1997,6 @@
       <c r="T18" t="n">
         <v>19.7</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2227,15 +2074,6 @@
       <c r="T19" t="n">
         <v>19.7</v>
       </c>
-      <c r="V19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2334,15 +2172,6 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2441,15 +2270,6 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2548,15 +2368,6 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2655,15 +2466,6 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2762,15 +2564,6 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2848,15 +2641,6 @@
       <c r="T25" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2934,15 +2718,6 @@
       <c r="T26" t="n">
         <v>19.7</v>
       </c>
-      <c r="V26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -3041,15 +2816,6 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -3148,15 +2914,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3255,15 +3012,6 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3362,15 +3110,6 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3469,15 +3208,6 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3555,15 +3285,6 @@
       <c r="T32" t="n">
         <v>19.7</v>
       </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3641,15 +3362,6 @@
       <c r="T33" t="n">
         <v>19.7</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3748,15 +3460,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3855,15 +3558,6 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3962,15 +3656,6 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -4069,15 +3754,6 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4176,15 +3852,6 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -4283,15 +3950,6 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4390,15 +4048,6 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4497,15 +4146,6 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4604,15 +4244,6 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4711,15 +4342,6 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4818,15 +4440,6 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4925,15 +4538,6 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -5032,15 +4636,6 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -5139,15 +4734,6 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
-      <c r="V47" t="n">
-        <v>16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -5246,15 +4832,6 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -5353,15 +4930,6 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5460,15 +5028,6 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5567,15 +5126,6 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y51" t="n">
         <v>6.8</v>
       </c>
@@ -5584,15 +5134,6 @@
       </c>
       <c r="AA51" t="n">
         <v>14</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
         <v>228.06</v>
@@ -5674,15 +5215,6 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Y52" t="n">
         <v>12.2</v>
       </c>
@@ -5691,15 +5223,6 @@
       </c>
       <c r="AA52" t="n">
         <v>19.7</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
         <v>233.59</v>
@@ -5781,15 +5304,6 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
       <c r="Y53" t="n">
         <v>16.6</v>
       </c>
@@ -5798,15 +5312,6 @@
       </c>
       <c r="AA53" t="n">
         <v>21.2</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5888,15 +5393,6 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="V54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>26.7</v>
-      </c>
       <c r="Y54" t="n">
         <v>13.7</v>
       </c>
@@ -5905,15 +5401,6 @@
       </c>
       <c r="AA54" t="n">
         <v>17.3</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.4</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5995,15 +5482,6 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
-      <c r="V55" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W55" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>27.9</v>
-      </c>
       <c r="Y55" t="n">
         <v>13.6</v>
       </c>
@@ -6012,15 +5490,6 @@
       </c>
       <c r="AA55" t="n">
         <v>16</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AF55" t="n">
         <v>233.68</v>
@@ -6102,15 +5571,6 @@
       <c r="T56" t="n">
         <v>19</v>
       </c>
-      <c r="V56" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>27.5</v>
-      </c>
       <c r="Y56" t="n">
         <v>14.2</v>
       </c>
@@ -6119,15 +5579,6 @@
       </c>
       <c r="AA56" t="n">
         <v>16.8</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>7.4</v>
       </c>
       <c r="AF56" t="n">
         <v>234.37</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
+      <c r="V2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -761,6 +770,15 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
+      <c r="V3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -820,6 +838,15 @@
       <c r="T4" t="n">
         <v>19.7</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -885,6 +912,15 @@
       <c r="T5" t="n">
         <v>19.7</v>
       </c>
+      <c r="V5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -950,6 +986,15 @@
       <c r="T6" t="n">
         <v>19.7</v>
       </c>
+      <c r="V6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1036,6 +1081,15 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
+      <c r="V7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1122,6 +1176,15 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1220,6 +1283,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1297,6 +1369,15 @@
       <c r="T10" t="n">
         <v>19.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1374,6 +1455,15 @@
       <c r="T11" t="n">
         <v>19.7</v>
       </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1451,6 +1541,15 @@
       <c r="T12" t="n">
         <v>19.7</v>
       </c>
+      <c r="V12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1528,6 +1627,15 @@
       <c r="T13" t="n">
         <v>19.7</v>
       </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1626,6 +1734,15 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
+      <c r="V14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1724,6 +1841,15 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1822,6 +1948,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -1920,6 +2055,15 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1997,6 +2141,15 @@
       <c r="T18" t="n">
         <v>19.7</v>
       </c>
+      <c r="V18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2074,6 +2227,15 @@
       <c r="T19" t="n">
         <v>19.7</v>
       </c>
+      <c r="V19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2172,6 +2334,15 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
+      <c r="V20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2270,6 +2441,15 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
+      <c r="V21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2368,6 +2548,15 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2466,6 +2655,15 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
+      <c r="V23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2564,6 +2762,15 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2641,6 +2848,15 @@
       <c r="T25" t="n">
         <v>19.7</v>
       </c>
+      <c r="V25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2718,6 +2934,15 @@
       <c r="T26" t="n">
         <v>19.7</v>
       </c>
+      <c r="V26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2816,6 +3041,15 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
+      <c r="V27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2914,6 +3148,15 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
+      <c r="V28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3012,6 +3255,15 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3110,6 +3362,15 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3208,6 +3469,15 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3285,6 +3555,15 @@
       <c r="T32" t="n">
         <v>19.7</v>
       </c>
+      <c r="V32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3362,6 +3641,15 @@
       <c r="T33" t="n">
         <v>19.7</v>
       </c>
+      <c r="V33" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3460,6 +3748,15 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3558,6 +3855,15 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3656,6 +3962,15 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3754,6 +4069,15 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
+      <c r="V37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3852,6 +4176,15 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -3950,6 +4283,15 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>18</v>
+      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4048,6 +4390,15 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4146,6 +4497,15 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
+      <c r="V41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4244,6 +4604,15 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4342,6 +4711,15 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
+      <c r="V43" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4440,6 +4818,15 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4538,6 +4925,15 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -4636,6 +5032,15 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -4734,6 +5139,15 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
+      <c r="V47" t="n">
+        <v>16</v>
+      </c>
+      <c r="W47" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -4832,6 +5246,15 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
+      <c r="V48" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -4930,6 +5353,15 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5028,6 +5460,15 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
+      <c r="V50" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5126,6 +5567,15 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y51" t="n">
         <v>6.8</v>
       </c>
@@ -5134,6 +5584,15 @@
       </c>
       <c r="AA51" t="n">
         <v>14</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
         <v>228.06</v>
@@ -5215,6 +5674,15 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y52" t="n">
         <v>12.2</v>
       </c>
@@ -5223,6 +5691,15 @@
       </c>
       <c r="AA52" t="n">
         <v>19.7</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
         <v>233.59</v>
@@ -5304,6 +5781,15 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25.6</v>
+      </c>
       <c r="Y53" t="n">
         <v>16.6</v>
       </c>
@@ -5312,6 +5798,15 @@
       </c>
       <c r="AA53" t="n">
         <v>21.2</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5393,6 +5888,15 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
+      <c r="V54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>26.7</v>
+      </c>
       <c r="Y54" t="n">
         <v>13.7</v>
       </c>
@@ -5401,6 +5905,15 @@
       </c>
       <c r="AA54" t="n">
         <v>17.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5482,6 +5995,15 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
+      <c r="V55" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>27.9</v>
+      </c>
       <c r="Y55" t="n">
         <v>13.6</v>
       </c>
@@ -5490,6 +6012,15 @@
       </c>
       <c r="AA55" t="n">
         <v>16</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="AF55" t="n">
         <v>233.68</v>
@@ -5571,6 +6102,15 @@
       <c r="T56" t="n">
         <v>19</v>
       </c>
+      <c r="V56" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>27.5</v>
+      </c>
       <c r="Y56" t="n">
         <v>14.2</v>
       </c>
@@ -5580,6 +6120,15 @@
       <c r="AA56" t="n">
         <v>16.8</v>
       </c>
+      <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>7.4</v>
+      </c>
       <c r="AF56" t="n">
         <v>234.37</v>
       </c>
@@ -5594,6 +6143,18 @@
       </c>
       <c r="BL56" s="1" t="n">
         <v>46293</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5576,12 +5576,6 @@
       <c r="X51" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5683,12 +5677,6 @@
       <c r="X52" t="n">
         <v>21.6</v>
       </c>
-      <c r="Y52" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21.4</v>
-      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5790,15 +5778,6 @@
       <c r="X53" t="n">
         <v>25.6</v>
       </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5897,15 +5876,6 @@
       <c r="X54" t="n">
         <v>26.7</v>
       </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
-      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -6004,12 +5974,6 @@
       <c r="X55" t="n">
         <v>27.9</v>
       </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6110,15 +6074,6 @@
       </c>
       <c r="X56" t="n">
         <v>27.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>16.8</v>
       </c>
       <c r="AB56" t="n">
         <v>1.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -770,15 +761,6 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -838,15 +820,6 @@
       <c r="T4" t="n">
         <v>19.7</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -912,15 +885,6 @@
       <c r="T5" t="n">
         <v>19.7</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -986,15 +950,6 @@
       <c r="T6" t="n">
         <v>19.7</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1081,15 +1036,6 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1176,15 +1122,6 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1283,15 +1220,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1369,15 +1297,6 @@
       <c r="T10" t="n">
         <v>19.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1455,15 +1374,6 @@
       <c r="T11" t="n">
         <v>19.7</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1541,15 +1451,6 @@
       <c r="T12" t="n">
         <v>19.7</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1627,15 +1528,6 @@
       <c r="T13" t="n">
         <v>19.7</v>
       </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1734,15 +1626,6 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1841,15 +1724,6 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1948,15 +1822,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -2055,15 +1920,6 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2141,15 +1997,6 @@
       <c r="T18" t="n">
         <v>19.7</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2227,15 +2074,6 @@
       <c r="T19" t="n">
         <v>19.7</v>
       </c>
-      <c r="V19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2334,15 +2172,6 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2441,15 +2270,6 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2548,15 +2368,6 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2655,15 +2466,6 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2762,15 +2564,6 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2848,15 +2641,6 @@
       <c r="T25" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2934,15 +2718,6 @@
       <c r="T26" t="n">
         <v>19.7</v>
       </c>
-      <c r="V26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -3041,15 +2816,6 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -3148,15 +2914,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3255,15 +3012,6 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3362,15 +3110,6 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3469,15 +3208,6 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3555,15 +3285,6 @@
       <c r="T32" t="n">
         <v>19.7</v>
       </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3641,15 +3362,6 @@
       <c r="T33" t="n">
         <v>19.7</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3748,15 +3460,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3855,15 +3558,6 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3962,15 +3656,6 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -4069,15 +3754,6 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4176,15 +3852,6 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -4283,15 +3950,6 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4390,15 +4048,6 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4497,15 +4146,6 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4604,15 +4244,6 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4711,15 +4342,6 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4818,15 +4440,6 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4925,15 +4538,6 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -5032,15 +4636,6 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -5139,15 +4734,6 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
-      <c r="V47" t="n">
-        <v>16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -5246,15 +4832,6 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -5353,15 +4930,6 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5460,15 +5028,6 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5567,15 +5126,6 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.6</v>
-      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5668,15 +5218,6 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.6</v>
-      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5769,15 +5310,6 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5867,15 +5399,6 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="V54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>26.7</v>
-      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5965,15 +5488,6 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
-      <c r="V55" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W55" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>27.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6065,15 +5579,6 @@
       </c>
       <c r="T56" t="n">
         <v>19</v>
-      </c>
-      <c r="V56" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>27.5</v>
       </c>
       <c r="AB56" t="n">
         <v>1.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
+      <c r="V2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -761,6 +770,15 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
+      <c r="V3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -820,6 +838,15 @@
       <c r="T4" t="n">
         <v>19.7</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -885,6 +912,15 @@
       <c r="T5" t="n">
         <v>19.7</v>
       </c>
+      <c r="V5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -950,6 +986,15 @@
       <c r="T6" t="n">
         <v>19.7</v>
       </c>
+      <c r="V6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1036,6 +1081,15 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
+      <c r="V7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1122,6 +1176,15 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1220,6 +1283,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1297,6 +1369,15 @@
       <c r="T10" t="n">
         <v>19.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1374,6 +1455,15 @@
       <c r="T11" t="n">
         <v>19.7</v>
       </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1451,6 +1541,15 @@
       <c r="T12" t="n">
         <v>19.7</v>
       </c>
+      <c r="V12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1528,6 +1627,15 @@
       <c r="T13" t="n">
         <v>19.7</v>
       </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1626,6 +1734,15 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
+      <c r="V14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1724,6 +1841,15 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1822,6 +1948,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -1920,6 +2055,15 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1997,6 +2141,15 @@
       <c r="T18" t="n">
         <v>19.7</v>
       </c>
+      <c r="V18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2074,6 +2227,15 @@
       <c r="T19" t="n">
         <v>19.7</v>
       </c>
+      <c r="V19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2172,6 +2334,15 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
+      <c r="V20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2270,6 +2441,15 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
+      <c r="V21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2368,6 +2548,15 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2466,6 +2655,15 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
+      <c r="V23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2564,6 +2762,15 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2641,6 +2848,15 @@
       <c r="T25" t="n">
         <v>19.7</v>
       </c>
+      <c r="V25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2718,6 +2934,15 @@
       <c r="T26" t="n">
         <v>19.7</v>
       </c>
+      <c r="V26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2816,6 +3041,15 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
+      <c r="V27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2914,6 +3148,15 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
+      <c r="V28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3012,6 +3255,15 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3110,6 +3362,15 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3208,6 +3469,15 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3285,6 +3555,15 @@
       <c r="T32" t="n">
         <v>19.7</v>
       </c>
+      <c r="V32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3362,6 +3641,15 @@
       <c r="T33" t="n">
         <v>19.7</v>
       </c>
+      <c r="V33" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3460,6 +3748,15 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3558,6 +3855,15 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3656,6 +3962,15 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3754,6 +4069,15 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
+      <c r="V37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3852,6 +4176,15 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -3950,6 +4283,15 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>18</v>
+      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4048,6 +4390,15 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4146,6 +4497,15 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
+      <c r="V41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4244,6 +4604,15 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4342,6 +4711,15 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
+      <c r="V43" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4440,6 +4818,15 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4538,6 +4925,15 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -4636,6 +5032,15 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -4734,6 +5139,15 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
+      <c r="V47" t="n">
+        <v>16</v>
+      </c>
+      <c r="W47" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -4832,6 +5246,15 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
+      <c r="V48" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -4930,6 +5353,15 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5028,6 +5460,15 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
+      <c r="V50" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5126,6 +5567,21 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5218,6 +5674,21 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.4</v>
+      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5310,6 +5781,24 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5399,6 +5888,24 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
+      <c r="V54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
+      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5488,6 +5995,21 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
+      <c r="V55" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -5579,6 +6101,24 @@
       </c>
       <c r="T56" t="n">
         <v>19</v>
+      </c>
+      <c r="V56" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>16.8</v>
       </c>
       <c r="AB56" t="n">
         <v>1.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -770,15 +761,6 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -838,15 +820,6 @@
       <c r="T4" t="n">
         <v>19.7</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -912,15 +885,6 @@
       <c r="T5" t="n">
         <v>19.7</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -986,15 +950,6 @@
       <c r="T6" t="n">
         <v>19.7</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1081,15 +1036,6 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1176,15 +1122,6 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1283,15 +1220,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1369,15 +1297,6 @@
       <c r="T10" t="n">
         <v>19.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1455,15 +1374,6 @@
       <c r="T11" t="n">
         <v>19.7</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1541,15 +1451,6 @@
       <c r="T12" t="n">
         <v>19.7</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1627,15 +1528,6 @@
       <c r="T13" t="n">
         <v>19.7</v>
       </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1734,15 +1626,6 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1841,15 +1724,6 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1948,15 +1822,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -2055,15 +1920,6 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2141,15 +1997,6 @@
       <c r="T18" t="n">
         <v>19.7</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2227,15 +2074,6 @@
       <c r="T19" t="n">
         <v>19.7</v>
       </c>
-      <c r="V19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2334,15 +2172,6 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2441,15 +2270,6 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2548,15 +2368,6 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2655,15 +2466,6 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2762,15 +2564,6 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2848,15 +2641,6 @@
       <c r="T25" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2934,15 +2718,6 @@
       <c r="T26" t="n">
         <v>19.7</v>
       </c>
-      <c r="V26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -3041,15 +2816,6 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -3148,15 +2914,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3255,15 +3012,6 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3362,15 +3110,6 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3469,15 +3208,6 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3555,15 +3285,6 @@
       <c r="T32" t="n">
         <v>19.7</v>
       </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3641,15 +3362,6 @@
       <c r="T33" t="n">
         <v>19.7</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3748,15 +3460,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3855,15 +3558,6 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3962,15 +3656,6 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -4069,15 +3754,6 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4176,15 +3852,6 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -4283,15 +3950,6 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4390,15 +4048,6 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4497,15 +4146,6 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4604,15 +4244,6 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4711,15 +4342,6 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4818,15 +4440,6 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4925,15 +4538,6 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -5032,15 +4636,6 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -5139,15 +4734,6 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
-      <c r="V47" t="n">
-        <v>16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -5246,15 +4832,6 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -5353,15 +4930,6 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5460,15 +5028,6 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5567,21 +5126,6 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA51" t="n">
         <v>14</v>
       </c>
@@ -5674,21 +5218,6 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21.4</v>
-      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
@@ -5781,24 +5310,6 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5888,24 +5399,6 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="V54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
-      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5995,21 +5488,6 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
-      <c r="V55" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W55" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6101,24 +5579,6 @@
       </c>
       <c r="T56" t="n">
         <v>19</v>
-      </c>
-      <c r="V56" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>16.8</v>
       </c>
       <c r="AB56" t="n">
         <v>1.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5126,17 +5126,14 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="Y51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA51" t="n">
         <v>14</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.1</v>
       </c>
       <c r="AF51" t="n">
         <v>228.06</v>
@@ -5218,17 +5215,14 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="Y52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>21.4</v>
+      </c>
       <c r="AA52" t="n">
         <v>19.7</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.1</v>
       </c>
       <c r="AF52" t="n">
         <v>233.59</v>
@@ -5310,14 +5304,14 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5399,14 +5393,14 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="AB54" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.4</v>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5488,17 +5482,14 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA55" t="n">
         <v>16</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AF55" t="n">
         <v>233.68</v>
@@ -5580,14 +5571,14 @@
       <c r="T56" t="n">
         <v>19</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>7.4</v>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>16.8</v>
       </c>
       <c r="AF56" t="n">
         <v>234.37</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5135,6 +5135,15 @@
       <c r="AA51" t="n">
         <v>14</v>
       </c>
+      <c r="AB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.1</v>
+      </c>
       <c r="AF51" t="n">
         <v>228.06</v>
       </c>
@@ -5224,6 +5233,15 @@
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.1</v>
+      </c>
       <c r="AF52" t="n">
         <v>233.59</v>
       </c>
@@ -5313,6 +5331,15 @@
       <c r="AA53" t="n">
         <v>21.2</v>
       </c>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
+      </c>
       <c r="AF53" t="n">
         <v>231.92</v>
       </c>
@@ -5402,6 +5429,15 @@
       <c r="AA54" t="n">
         <v>17.3</v>
       </c>
+      <c r="AB54" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.4</v>
+      </c>
       <c r="AF54" t="n">
         <v>235</v>
       </c>
@@ -5491,6 +5527,15 @@
       <c r="AA55" t="n">
         <v>16</v>
       </c>
+      <c r="AB55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="AF55" t="n">
         <v>233.68</v>
       </c>
@@ -5580,6 +5625,15 @@
       <c r="AA56" t="n">
         <v>16.8</v>
       </c>
+      <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>7.4</v>
+      </c>
       <c r="AF56" t="n">
         <v>234.37</v>
       </c>
@@ -5660,8 +5714,44 @@
       <c r="T57" t="n">
         <v>20</v>
       </c>
+      <c r="Y57" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.76</v>
+      </c>
       <c r="BL57" s="1" t="n">
         <v>46294</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>271.8</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -806,7 +806,7 @@
         <v>91.5</v>
       </c>
       <c r="O4" t="n">
-        <v>40.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y4" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
         <v>87.2</v>
       </c>
       <c r="O5" t="n">
-        <v>38.3</v>
+        <v>39.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
@@ -936,7 +936,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>38.7</v>
+        <v>39.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y6" t="n">
         <v>3</v>
@@ -1280,10 +1280,10 @@
         <v>6.5</v>
       </c>
       <c r="K10" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
@@ -1357,10 +1357,10 @@
         <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="O11" t="n">
-        <v>41.6</v>
+        <v>42.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y11" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>84.5</v>
       </c>
       <c r="O12" t="n">
-        <v>37.1</v>
+        <v>38</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
@@ -1514,7 +1514,7 @@
         <v>77.7</v>
       </c>
       <c r="O13" t="n">
-        <v>34.1</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y13" t="n">
         <v>12</v>
@@ -1983,7 +1983,7 @@
         <v>92</v>
       </c>
       <c r="O18" t="n">
-        <v>40.5</v>
+        <v>41.4</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y18" t="n">
         <v>6</v>
@@ -2060,7 +2060,7 @@
         <v>86.3</v>
       </c>
       <c r="O19" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y19" t="n">
         <v>4</v>
@@ -2627,7 +2627,7 @@
         <v>82.3</v>
       </c>
       <c r="O25" t="n">
-        <v>36.2</v>
+        <v>37.1</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y25" t="n">
         <v>9</v>
@@ -2701,10 +2701,10 @@
         <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="O26" t="n">
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y26" t="n">
         <v>8</v>
@@ -3268,10 +3268,10 @@
         <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="O32" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y32" t="n">
         <v>7</v>
@@ -3345,10 +3345,10 @@
         <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>35.9</v>
+        <v>36.7</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y33" t="n">
         <v>7</v>
@@ -5322,15 +5322,6 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5420,15 +5411,6 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
-      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5518,12 +5500,6 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -5569,43 +5545,43 @@
         <v>46293</v>
       </c>
       <c r="B56" t="n">
-        <v>115.9</v>
+        <v>113.4</v>
       </c>
       <c r="C56" t="n">
-        <v>42</v>
+        <v>40.9</v>
       </c>
       <c r="D56" t="n">
-        <v>36.3</v>
+        <v>34.8</v>
       </c>
       <c r="E56" t="n">
-        <v>28.84</v>
+        <v>27.9</v>
       </c>
       <c r="F56" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H56" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I56" t="n">
-        <v>10.7</v>
+        <v>9.1</v>
       </c>
       <c r="J56" t="n">
-        <v>31</v>
+        <v>32.2</v>
       </c>
       <c r="K56" t="n">
-        <v>62.9</v>
+        <v>64.3</v>
       </c>
       <c r="M56" t="n">
         <v>1.9</v>
       </c>
       <c r="N56" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="O56" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5614,16 +5590,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
+        <v>20.3</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="AB56" t="n">
         <v>1.5</v>
@@ -5667,43 +5637,43 @@
         <v>46294</v>
       </c>
       <c r="B57" t="n">
-        <v>118.5</v>
+        <v>115.6</v>
       </c>
       <c r="C57" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="D57" t="n">
-        <v>37.2</v>
+        <v>36.1</v>
       </c>
       <c r="E57" t="n">
-        <v>28.54</v>
+        <v>23.9</v>
       </c>
       <c r="F57" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H57" t="n">
-        <v>22.8</v>
+        <v>23.6</v>
       </c>
       <c r="I57" t="n">
-        <v>10.7</v>
+        <v>9.1</v>
       </c>
       <c r="J57" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="K57" t="n">
-        <v>68.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M57" t="n">
         <v>1.9</v>
       </c>
       <c r="N57" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="O57" t="n">
-        <v>28.9</v>
+        <v>29.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -5712,16 +5682,10 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.9</v>
+        <v>20.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>16.6</v>
+        <v>18.2</v>
       </c>
       <c r="AB57" t="n">
         <v>0.5</v>
@@ -5731,6 +5695,12 @@
       </c>
       <c r="AD57" t="n">
         <v>6.2</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>237.85</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.48</v>
       </c>
       <c r="AK57" t="n">
         <v>137.25</v>
@@ -5759,43 +5729,43 @@
         <v>46295</v>
       </c>
       <c r="B58" t="n">
-        <v>124.2</v>
+        <v>123.4</v>
       </c>
       <c r="C58" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="D58" t="n">
-        <v>38</v>
+        <v>36.7</v>
       </c>
       <c r="E58" t="n">
         <v>27.93</v>
       </c>
       <c r="F58" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="H58" t="n">
-        <v>22.8</v>
+        <v>24</v>
       </c>
       <c r="I58" t="n">
-        <v>10.7</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K58" t="n">
-        <v>68.5</v>
+        <v>66</v>
       </c>
       <c r="M58" t="n">
         <v>1.9</v>
       </c>
       <c r="N58" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="O58" t="n">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -5804,10 +5774,43 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>22</v>
+        <v>20.5</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>228.13</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>136.92</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-0.33</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46295</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>447.8</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5815,43 +5818,43 @@
         <v>46296</v>
       </c>
       <c r="B59" t="n">
-        <v>123</v>
+        <v>121.6</v>
       </c>
       <c r="C59" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="D59" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="E59" t="n">
         <v>27.12</v>
       </c>
       <c r="F59" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H59" t="n">
-        <v>22.8</v>
+        <v>20.9</v>
       </c>
       <c r="I59" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="J59" t="n">
         <v>35</v>
       </c>
       <c r="K59" t="n">
-        <v>68.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M59" t="n">
         <v>1.9</v>
       </c>
       <c r="N59" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="O59" t="n">
-        <v>30.9</v>
+        <v>29.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -5860,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46296</v>
@@ -5871,43 +5874,43 @@
         <v>46297</v>
       </c>
       <c r="B60" t="n">
-        <v>120.5</v>
+        <v>118.5</v>
       </c>
       <c r="C60" t="n">
-        <v>47.2</v>
+        <v>46.1</v>
       </c>
       <c r="D60" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="E60" t="n">
         <v>25.73</v>
       </c>
       <c r="F60" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H60" t="n">
-        <v>22.8</v>
+        <v>20.9</v>
       </c>
       <c r="I60" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>68.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>1.9</v>
       </c>
       <c r="N60" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="O60" t="n">
-        <v>30.9</v>
+        <v>29.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -5916,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46297</v>
@@ -5927,19 +5930,43 @@
         <v>46298</v>
       </c>
       <c r="B61" t="n">
-        <v>24.4</v>
+        <v>108.4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35</v>
       </c>
       <c r="E61" t="n">
         <v>24.44</v>
       </c>
+      <c r="F61" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" t="n">
+        <v>33</v>
+      </c>
       <c r="K61" t="n">
-        <v>3.3</v>
+        <v>63.4</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N61" t="n">
+        <v>27.5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.4</v>
+        <v>29.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -5948,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>19.7</v>
+        <v>17</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46298</v>
@@ -5959,19 +5986,43 @@
         <v>46299</v>
       </c>
       <c r="B62" t="n">
-        <v>23.9</v>
+        <v>103.8</v>
+      </c>
+      <c r="C62" t="n">
+        <v>36</v>
+      </c>
+      <c r="D62" t="n">
+        <v>34.8</v>
       </c>
       <c r="E62" t="n">
         <v>23.87</v>
       </c>
+      <c r="F62" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" t="n">
+        <v>33</v>
+      </c>
       <c r="K62" t="n">
-        <v>2.9</v>
+        <v>63.4</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N62" t="n">
+        <v>27.5</v>
       </c>
       <c r="O62" t="n">
-        <v>1.3</v>
+        <v>29.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -5980,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>19.7</v>
+        <v>17</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46299</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
+      <c r="V2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -761,6 +770,15 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
+      <c r="V3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -820,6 +838,15 @@
       <c r="T4" t="n">
         <v>18.8</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -885,6 +912,15 @@
       <c r="T5" t="n">
         <v>18.8</v>
       </c>
+      <c r="V5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -950,6 +986,15 @@
       <c r="T6" t="n">
         <v>18.8</v>
       </c>
+      <c r="V6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1036,6 +1081,15 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
+      <c r="V7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1122,6 +1176,15 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1220,6 +1283,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1297,6 +1369,15 @@
       <c r="T10" t="n">
         <v>18.8</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1374,6 +1455,15 @@
       <c r="T11" t="n">
         <v>18.8</v>
       </c>
+      <c r="V11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1451,6 +1541,15 @@
       <c r="T12" t="n">
         <v>18.8</v>
       </c>
+      <c r="V12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1528,6 +1627,15 @@
       <c r="T13" t="n">
         <v>18.8</v>
       </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1626,6 +1734,15 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
+      <c r="V14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1724,6 +1841,15 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1822,6 +1948,15 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -1920,6 +2055,15 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1997,6 +2141,15 @@
       <c r="T18" t="n">
         <v>18.8</v>
       </c>
+      <c r="V18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2074,6 +2227,15 @@
       <c r="T19" t="n">
         <v>18.8</v>
       </c>
+      <c r="V19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2172,6 +2334,15 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
+      <c r="V20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2270,6 +2441,15 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
+      <c r="V21" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2368,6 +2548,15 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2466,6 +2655,15 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
+      <c r="V23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2564,6 +2762,15 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2641,6 +2848,15 @@
       <c r="T25" t="n">
         <v>18.8</v>
       </c>
+      <c r="V25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2718,6 +2934,15 @@
       <c r="T26" t="n">
         <v>18.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -2816,6 +3041,15 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
+      <c r="V27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -2914,6 +3148,15 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
+      <c r="V28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3012,6 +3255,15 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3110,6 +3362,15 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3208,6 +3469,15 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
+      <c r="V31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3285,6 +3555,15 @@
       <c r="T32" t="n">
         <v>18.8</v>
       </c>
+      <c r="V32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3362,6 +3641,15 @@
       <c r="T33" t="n">
         <v>18.8</v>
       </c>
+      <c r="V33" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3460,6 +3748,15 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3558,6 +3855,15 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3656,6 +3962,15 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
+      <c r="V36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>21</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -3754,6 +4069,15 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
+      <c r="V37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -3852,6 +4176,15 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -3950,6 +4283,15 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>18</v>
+      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4048,6 +4390,15 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4146,6 +4497,15 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
+      <c r="V41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4244,6 +4604,15 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
+      <c r="V42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4342,6 +4711,15 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
+      <c r="V43" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4440,6 +4818,15 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4538,6 +4925,15 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -4636,6 +5032,15 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
+      <c r="V46" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X46" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -4734,6 +5139,15 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
+      <c r="V47" t="n">
+        <v>16</v>
+      </c>
+      <c r="W47" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -4832,6 +5246,15 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
+      <c r="V48" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X48" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -4930,6 +5353,15 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5028,6 +5460,15 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
+      <c r="V50" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5126,6 +5567,15 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
+      <c r="V51" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y51" t="n">
         <v>6.8</v>
       </c>
@@ -5224,6 +5674,15 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y52" t="n">
         <v>12.2</v>
       </c>
@@ -5322,6 +5781,24 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5411,6 +5888,24 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
+      <c r="V54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X54" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
+      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5500,6 +5995,21 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
+      <c r="V55" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -5592,6 +6102,21 @@
       <c r="T56" t="n">
         <v>20.3</v>
       </c>
+      <c r="V56" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
       </c>
@@ -5684,6 +6209,21 @@
       <c r="T57" t="n">
         <v>20.5</v>
       </c>
+      <c r="V57" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W57" t="n">
+        <v>22</v>
+      </c>
+      <c r="X57" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
       </c>
@@ -5775,6 +6315,24 @@
       </c>
       <c r="T58" t="n">
         <v>20.5</v>
+      </c>
+      <c r="V58" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W58" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X58" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>13.2</v>
       </c>
       <c r="AB58" t="n">
         <v>3.7</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,15 +696,6 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
       </c>
@@ -788,15 +779,6 @@
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AK3" t="n">
         <v>134.62</v>
       </c>
@@ -856,15 +838,6 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
@@ -930,15 +903,6 @@
       <c r="AA5" t="n">
         <v>10</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AF5" t="n">
         <v>224.37</v>
       </c>
@@ -1004,15 +968,6 @@
       <c r="AA6" t="n">
         <v>9</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="AF6" t="n">
         <v>225.93</v>
       </c>
@@ -1099,15 +1054,6 @@
       <c r="AA7" t="n">
         <v>8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="AF7" t="n">
         <v>218.63</v>
       </c>
@@ -1194,15 +1140,6 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
@@ -1301,15 +1238,6 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
@@ -1387,15 +1315,6 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
@@ -1473,15 +1392,6 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
@@ -1559,15 +1469,6 @@
       <c r="AA12" t="n">
         <v>14</v>
       </c>
-      <c r="AB12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF12" t="n">
         <v>225.14</v>
       </c>
@@ -1645,15 +1546,6 @@
       <c r="AA13" t="n">
         <v>15</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF13" t="n">
         <v>229.98</v>
       </c>
@@ -1752,15 +1644,6 @@
       <c r="AA14" t="n">
         <v>13</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF14" t="n">
         <v>229.96</v>
       </c>
@@ -1859,15 +1742,6 @@
       <c r="AA15" t="n">
         <v>10</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF15" t="n">
         <v>227.01</v>
       </c>
@@ -1966,15 +1840,6 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
@@ -2073,15 +1938,6 @@
       <c r="AA17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF17" t="n">
         <v>231.16</v>
       </c>
@@ -2159,15 +2015,6 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
-      <c r="AB18" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF18" t="n">
         <v>228.13</v>
       </c>
@@ -2245,15 +2092,6 @@
       <c r="AA19" t="n">
         <v>9</v>
       </c>
-      <c r="AB19" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4</v>
-      </c>
       <c r="AF19" t="n">
         <v>229.16</v>
       </c>
@@ -2352,15 +2190,6 @@
       <c r="AA20" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB20" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF20" t="n">
         <v>228.55</v>
       </c>
@@ -2459,15 +2288,6 @@
       <c r="AA21" t="n">
         <v>10</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF21" t="n">
         <v>219.99</v>
       </c>
@@ -2566,15 +2386,6 @@
       <c r="AA22" t="n">
         <v>11</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF22" t="n">
         <v>219.22</v>
       </c>
@@ -2673,15 +2484,6 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
@@ -2780,15 +2582,6 @@
       <c r="AA24" t="n">
         <v>14</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF24" t="n">
         <v>220.58</v>
       </c>
@@ -2866,15 +2659,6 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF25" t="n">
         <v>223.43</v>
       </c>
@@ -2952,15 +2736,6 @@
       <c r="AA26" t="n">
         <v>13</v>
       </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF26" t="n">
         <v>229.48</v>
       </c>
@@ -3059,15 +2834,6 @@
       <c r="AA27" t="n">
         <v>14</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
-      </c>
       <c r="AF27" t="n">
         <v>241.48</v>
       </c>
@@ -3166,15 +2932,6 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB28" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
@@ -3273,15 +3030,6 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
@@ -3380,15 +3128,6 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
-      <c r="AB30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
@@ -3487,15 +3226,6 @@
       <c r="AA31" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB31" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF31" t="n">
         <v>234.87</v>
       </c>
@@ -3573,15 +3303,6 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
-      <c r="AB32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AF32" t="n">
         <v>234.78</v>
       </c>
@@ -3659,15 +3380,6 @@
       <c r="AA33" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF33" t="n">
         <v>229.75</v>
       </c>
@@ -3766,15 +3478,6 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
@@ -3873,15 +3576,6 @@
       <c r="AA35" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF35" t="n">
         <v>218.37</v>
       </c>
@@ -3980,15 +3674,6 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF36" t="n">
         <v>220.85</v>
       </c>
@@ -4087,15 +3772,6 @@
       <c r="AA37" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AF37" t="n">
         <v>225.87</v>
       </c>
@@ -4194,15 +3870,6 @@
       <c r="AA38" t="n">
         <v>16.1</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF38" t="n">
         <v>229.48</v>
       </c>
@@ -4301,15 +3968,6 @@
       <c r="AA39" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF39" t="n">
         <v>230.54</v>
       </c>
@@ -4408,15 +4066,6 @@
       <c r="AA40" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB40" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AF40" t="n">
         <v>224.23</v>
       </c>
@@ -4515,15 +4164,6 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB41" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
@@ -4622,15 +4262,6 @@
       <c r="AA42" t="n">
         <v>12</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF42" t="n">
         <v>222.92</v>
       </c>
@@ -4729,15 +4360,6 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
-      <c r="AB43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
@@ -4836,15 +4458,6 @@
       <c r="AA44" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AF44" t="n">
         <v>221.86</v>
       </c>
@@ -4943,15 +4556,6 @@
       <c r="AA45" t="n">
         <v>18.8</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AF45" t="n">
         <v>227.49</v>
       </c>
@@ -5050,15 +4654,6 @@
       <c r="AA46" t="n">
         <v>17.2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AF46" t="n">
         <v>233.56</v>
       </c>
@@ -5157,15 +4752,6 @@
       <c r="AA47" t="n">
         <v>18.1</v>
       </c>
-      <c r="AB47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>12.8</v>
-      </c>
       <c r="AF47" t="n">
         <v>234.94</v>
       </c>
@@ -5264,15 +4850,6 @@
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
-      <c r="AB48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>7</v>
-      </c>
       <c r="AF48" t="n">
         <v>229.19</v>
       </c>
@@ -5371,15 +4948,6 @@
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AF49" t="n">
         <v>224.91</v>
       </c>
@@ -5478,15 +5046,6 @@
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
-      <c r="AB50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF50" t="n">
         <v>220.83</v>
       </c>
@@ -5585,15 +5144,6 @@
       <c r="AA51" t="n">
         <v>14</v>
       </c>
-      <c r="AB51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>9.1</v>
-      </c>
       <c r="AF51" t="n">
         <v>228.06</v>
       </c>
@@ -5692,15 +5242,6 @@
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
-      <c r="AB52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>8.1</v>
-      </c>
       <c r="AF52" t="n">
         <v>233.59</v>
       </c>
@@ -5799,15 +5340,6 @@
       <c r="AA53" t="n">
         <v>21.2</v>
       </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
-      </c>
       <c r="AF53" t="n">
         <v>231.92</v>
       </c>
@@ -5906,15 +5438,6 @@
       <c r="AA54" t="n">
         <v>17.3</v>
       </c>
-      <c r="AB54" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AF54" t="n">
         <v>235</v>
       </c>
@@ -6013,15 +5536,6 @@
       <c r="AA55" t="n">
         <v>16</v>
       </c>
-      <c r="AB55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AF55" t="n">
         <v>233.68</v>
       </c>
@@ -6120,15 +5634,6 @@
       <c r="AA56" t="n">
         <v>17.5</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AF56" t="n">
         <v>234.37</v>
       </c>
@@ -6227,15 +5732,6 @@
       <c r="AA57" t="n">
         <v>18.2</v>
       </c>
-      <c r="AB57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AF57" t="n">
         <v>237.85</v>
       </c>
@@ -6333,15 +5829,6 @@
       </c>
       <c r="AA58" t="n">
         <v>13.2</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>7.6</v>
       </c>
       <c r="AF58" t="n">
         <v>228.13</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,6 +696,15 @@
       <c r="AA2" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB2" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF2" t="n">
         <v>225.08</v>
       </c>
@@ -779,6 +788,15 @@
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="AK3" t="n">
         <v>134.62</v>
       </c>
@@ -838,6 +856,15 @@
       <c r="AA4" t="n">
         <v>9</v>
       </c>
+      <c r="AB4" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF4" t="n">
         <v>221.37</v>
       </c>
@@ -903,6 +930,15 @@
       <c r="AA5" t="n">
         <v>10</v>
       </c>
+      <c r="AB5" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AF5" t="n">
         <v>224.37</v>
       </c>
@@ -968,6 +1004,15 @@
       <c r="AA6" t="n">
         <v>9</v>
       </c>
+      <c r="AB6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="AF6" t="n">
         <v>225.93</v>
       </c>
@@ -1054,6 +1099,15 @@
       <c r="AA7" t="n">
         <v>8</v>
       </c>
+      <c r="AB7" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="AF7" t="n">
         <v>218.63</v>
       </c>
@@ -1140,6 +1194,15 @@
       <c r="AA8" t="n">
         <v>9</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AF8" t="n">
         <v>216.39</v>
       </c>
@@ -1238,6 +1301,15 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AF9" t="n">
         <v>217.16</v>
       </c>
@@ -1315,6 +1387,15 @@
       <c r="AA10" t="n">
         <v>10</v>
       </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF10" t="n">
         <v>220.31</v>
       </c>
@@ -1392,6 +1473,15 @@
       <c r="AA11" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AF11" t="n">
         <v>221.99</v>
       </c>
@@ -1469,6 +1559,15 @@
       <c r="AA12" t="n">
         <v>14</v>
       </c>
+      <c r="AB12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF12" t="n">
         <v>225.14</v>
       </c>
@@ -1546,6 +1645,15 @@
       <c r="AA13" t="n">
         <v>15</v>
       </c>
+      <c r="AB13" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="AF13" t="n">
         <v>229.98</v>
       </c>
@@ -1644,6 +1752,15 @@
       <c r="AA14" t="n">
         <v>13</v>
       </c>
+      <c r="AB14" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AF14" t="n">
         <v>229.96</v>
       </c>
@@ -1742,6 +1859,15 @@
       <c r="AA15" t="n">
         <v>10</v>
       </c>
+      <c r="AB15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.4</v>
+      </c>
       <c r="AF15" t="n">
         <v>227.01</v>
       </c>
@@ -1840,6 +1966,15 @@
       <c r="AA16" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AF16" t="n">
         <v>228.35</v>
       </c>
@@ -1938,6 +2073,15 @@
       <c r="AA17" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF17" t="n">
         <v>231.16</v>
       </c>
@@ -2015,6 +2159,15 @@
       <c r="AA18" t="n">
         <v>9</v>
       </c>
+      <c r="AB18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AF18" t="n">
         <v>228.13</v>
       </c>
@@ -2092,6 +2245,15 @@
       <c r="AA19" t="n">
         <v>9</v>
       </c>
+      <c r="AB19" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
+      </c>
       <c r="AF19" t="n">
         <v>229.16</v>
       </c>
@@ -2190,6 +2352,15 @@
       <c r="AA20" t="n">
         <v>8.5</v>
       </c>
+      <c r="AB20" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF20" t="n">
         <v>228.55</v>
       </c>
@@ -2288,6 +2459,15 @@
       <c r="AA21" t="n">
         <v>10</v>
       </c>
+      <c r="AB21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF21" t="n">
         <v>219.99</v>
       </c>
@@ -2386,6 +2566,15 @@
       <c r="AA22" t="n">
         <v>11</v>
       </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5.5</v>
+      </c>
       <c r="AF22" t="n">
         <v>219.22</v>
       </c>
@@ -2484,6 +2673,15 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF23" t="n">
         <v>220.73</v>
       </c>
@@ -2582,6 +2780,15 @@
       <c r="AA24" t="n">
         <v>14</v>
       </c>
+      <c r="AB24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF24" t="n">
         <v>220.58</v>
       </c>
@@ -2659,6 +2866,15 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
+      <c r="AB25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF25" t="n">
         <v>223.43</v>
       </c>
@@ -2736,6 +2952,15 @@
       <c r="AA26" t="n">
         <v>13</v>
       </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AF26" t="n">
         <v>229.48</v>
       </c>
@@ -2834,6 +3059,15 @@
       <c r="AA27" t="n">
         <v>14</v>
       </c>
+      <c r="AB27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
+      </c>
       <c r="AF27" t="n">
         <v>241.48</v>
       </c>
@@ -2932,6 +3166,15 @@
       <c r="AA28" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB28" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AF28" t="n">
         <v>238.69</v>
       </c>
@@ -3030,6 +3273,15 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AF29" t="n">
         <v>233.48</v>
       </c>
@@ -3128,6 +3380,15 @@
       <c r="AA30" t="n">
         <v>17</v>
       </c>
+      <c r="AB30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AF30" t="n">
         <v>235.13</v>
       </c>
@@ -3226,6 +3487,15 @@
       <c r="AA31" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB31" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF31" t="n">
         <v>234.87</v>
       </c>
@@ -3303,6 +3573,15 @@
       <c r="AA32" t="n">
         <v>13</v>
       </c>
+      <c r="AB32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.2</v>
+      </c>
       <c r="AF32" t="n">
         <v>234.78</v>
       </c>
@@ -3380,6 +3659,15 @@
       <c r="AA33" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB33" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AF33" t="n">
         <v>229.75</v>
       </c>
@@ -3478,6 +3766,15 @@
       <c r="AA34" t="n">
         <v>6.5</v>
       </c>
+      <c r="AB34" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AF34" t="n">
         <v>222.86</v>
       </c>
@@ -3576,6 +3873,15 @@
       <c r="AA35" t="n">
         <v>9.5</v>
       </c>
+      <c r="AB35" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF35" t="n">
         <v>218.37</v>
       </c>
@@ -3674,6 +3980,15 @@
       <c r="AA36" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF36" t="n">
         <v>220.85</v>
       </c>
@@ -3772,6 +4087,15 @@
       <c r="AA37" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>6.3</v>
+      </c>
       <c r="AF37" t="n">
         <v>225.87</v>
       </c>
@@ -3870,6 +4194,15 @@
       <c r="AA38" t="n">
         <v>16.1</v>
       </c>
+      <c r="AB38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF38" t="n">
         <v>229.48</v>
       </c>
@@ -3968,6 +4301,15 @@
       <c r="AA39" t="n">
         <v>15.1</v>
       </c>
+      <c r="AB39" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="AF39" t="n">
         <v>230.54</v>
       </c>
@@ -4066,6 +4408,15 @@
       <c r="AA40" t="n">
         <v>10.3</v>
       </c>
+      <c r="AB40" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF40" t="n">
         <v>224.23</v>
       </c>
@@ -4164,6 +4515,15 @@
       <c r="AA41" t="n">
         <v>7.9</v>
       </c>
+      <c r="AB41" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF41" t="n">
         <v>223.36</v>
       </c>
@@ -4262,6 +4622,15 @@
       <c r="AA42" t="n">
         <v>12</v>
       </c>
+      <c r="AB42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF42" t="n">
         <v>222.92</v>
       </c>
@@ -4360,6 +4729,15 @@
       <c r="AA43" t="n">
         <v>12.9</v>
       </c>
+      <c r="AB43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF43" t="n">
         <v>222.77</v>
       </c>
@@ -4458,6 +4836,15 @@
       <c r="AA44" t="n">
         <v>11.6</v>
       </c>
+      <c r="AB44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AF44" t="n">
         <v>221.86</v>
       </c>
@@ -4556,6 +4943,15 @@
       <c r="AA45" t="n">
         <v>18.8</v>
       </c>
+      <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="AF45" t="n">
         <v>227.49</v>
       </c>
@@ -4654,6 +5050,15 @@
       <c r="AA46" t="n">
         <v>17.2</v>
       </c>
+      <c r="AB46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="AF46" t="n">
         <v>233.56</v>
       </c>
@@ -4752,6 +5157,15 @@
       <c r="AA47" t="n">
         <v>18.1</v>
       </c>
+      <c r="AB47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AF47" t="n">
         <v>234.94</v>
       </c>
@@ -4850,6 +5264,15 @@
       <c r="AA48" t="n">
         <v>16.9</v>
       </c>
+      <c r="AB48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>7</v>
+      </c>
       <c r="AF48" t="n">
         <v>229.19</v>
       </c>
@@ -4948,6 +5371,15 @@
       <c r="AA49" t="n">
         <v>13.8</v>
       </c>
+      <c r="AB49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.4</v>
+      </c>
       <c r="AF49" t="n">
         <v>224.91</v>
       </c>
@@ -5046,6 +5478,15 @@
       <c r="AA50" t="n">
         <v>9.6</v>
       </c>
+      <c r="AB50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF50" t="n">
         <v>220.83</v>
       </c>
@@ -5144,6 +5585,15 @@
       <c r="AA51" t="n">
         <v>14</v>
       </c>
+      <c r="AB51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>9.1</v>
+      </c>
       <c r="AF51" t="n">
         <v>228.06</v>
       </c>
@@ -5242,6 +5692,15 @@
       <c r="AA52" t="n">
         <v>19.7</v>
       </c>
+      <c r="AB52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>8.1</v>
+      </c>
       <c r="AF52" t="n">
         <v>233.59</v>
       </c>
@@ -5331,14 +5790,14 @@
       <c r="X53" t="n">
         <v>25.6</v>
       </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5429,14 +5888,14 @@
       <c r="X54" t="n">
         <v>26.7</v>
       </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
+      <c r="AB54" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5527,14 +5986,17 @@
       <c r="X55" t="n">
         <v>27.9</v>
       </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="AF55" t="n">
         <v>233.68</v>
@@ -5625,14 +6087,17 @@
       <c r="X56" t="n">
         <v>27.5</v>
       </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>7.4</v>
       </c>
       <c r="AF56" t="n">
         <v>234.37</v>
@@ -5723,14 +6188,17 @@
       <c r="X57" t="n">
         <v>19.9</v>
       </c>
-      <c r="Y57" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF57" t="n">
         <v>237.85</v>
@@ -5821,14 +6289,14 @@
       <c r="X58" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y58" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>13.2</v>
+      <c r="AB58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>7.6</v>
       </c>
       <c r="AF58" t="n">
         <v>228.13</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5790,6 +5790,15 @@
       <c r="X53" t="n">
         <v>25.6</v>
       </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5888,6 +5897,15 @@
       <c r="X54" t="n">
         <v>26.7</v>
       </c>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
+      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5986,6 +6004,12 @@
       <c r="X55" t="n">
         <v>27.9</v>
       </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6087,6 +6111,12 @@
       <c r="X56" t="n">
         <v>27.5</v>
       </c>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
       </c>
@@ -6188,6 +6218,12 @@
       <c r="X57" t="n">
         <v>19.9</v>
       </c>
+      <c r="Y57" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
       </c>
@@ -6288,6 +6324,15 @@
       </c>
       <c r="X58" t="n">
         <v>19.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>13.2</v>
       </c>
       <c r="AB58" t="n">
         <v>3.7</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>20.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
@@ -770,15 +761,6 @@
       <c r="T3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y3" t="n">
         <v>9</v>
       </c>
@@ -838,15 +820,6 @@
       <c r="T4" t="n">
         <v>18.8</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
       <c r="Y4" t="n">
         <v>5</v>
       </c>
@@ -912,15 +885,6 @@
       <c r="T5" t="n">
         <v>18.8</v>
       </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -986,15 +950,6 @@
       <c r="T6" t="n">
         <v>18.8</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y6" t="n">
         <v>3</v>
       </c>
@@ -1081,15 +1036,6 @@
       <c r="T7" t="n">
         <v>22.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
@@ -1176,15 +1122,6 @@
       <c r="T8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y8" t="n">
         <v>6</v>
       </c>
@@ -1283,15 +1220,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>8</v>
       </c>
@@ -1369,15 +1297,6 @@
       <c r="T10" t="n">
         <v>18.8</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1455,15 +1374,6 @@
       <c r="T11" t="n">
         <v>18.8</v>
       </c>
-      <c r="V11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y11" t="n">
         <v>10</v>
       </c>
@@ -1541,15 +1451,6 @@
       <c r="T12" t="n">
         <v>18.8</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
@@ -1627,15 +1528,6 @@
       <c r="T13" t="n">
         <v>18.8</v>
       </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
@@ -1734,15 +1626,6 @@
       <c r="T14" t="n">
         <v>23.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
@@ -1841,15 +1724,6 @@
       <c r="T15" t="n">
         <v>23.8</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>7</v>
       </c>
@@ -1948,15 +1822,6 @@
       <c r="T16" t="n">
         <v>23.6</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
@@ -2055,15 +1920,6 @@
       <c r="T17" t="n">
         <v>23.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -2141,15 +1997,6 @@
       <c r="T18" t="n">
         <v>18.8</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
@@ -2227,15 +2074,6 @@
       <c r="T19" t="n">
         <v>18.8</v>
       </c>
-      <c r="V19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y19" t="n">
         <v>4</v>
       </c>
@@ -2334,15 +2172,6 @@
       <c r="T20" t="n">
         <v>23.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y20" t="n">
         <v>4</v>
       </c>
@@ -2441,15 +2270,6 @@
       <c r="T21" t="n">
         <v>23.1</v>
       </c>
-      <c r="V21" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>7</v>
       </c>
@@ -2548,15 +2368,6 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2655,15 +2466,6 @@
       <c r="T23" t="n">
         <v>23.2</v>
       </c>
-      <c r="V23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y23" t="n">
         <v>10</v>
       </c>
@@ -2762,15 +2564,6 @@
       <c r="T24" t="n">
         <v>23.2</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y24" t="n">
         <v>10</v>
       </c>
@@ -2848,15 +2641,6 @@
       <c r="T25" t="n">
         <v>18.8</v>
       </c>
-      <c r="V25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
@@ -2934,15 +2718,6 @@
       <c r="T26" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>8</v>
       </c>
@@ -3041,15 +2816,6 @@
       <c r="T27" t="n">
         <v>21.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y27" t="n">
         <v>8</v>
       </c>
@@ -3148,15 +2914,6 @@
       <c r="T28" t="n">
         <v>19.7</v>
       </c>
-      <c r="V28" t="n">
-        <v>12</v>
-      </c>
-      <c r="W28" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>12</v>
       </c>
@@ -3255,15 +3012,6 @@
       <c r="T29" t="n">
         <v>20.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -3362,15 +3110,6 @@
       <c r="T30" t="n">
         <v>21.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3469,15 +3208,6 @@
       <c r="T31" t="n">
         <v>21</v>
       </c>
-      <c r="V31" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X31" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
@@ -3555,15 +3285,6 @@
       <c r="T32" t="n">
         <v>18.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y32" t="n">
         <v>7</v>
       </c>
@@ -3641,15 +3362,6 @@
       <c r="T33" t="n">
         <v>18.8</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
@@ -3748,15 +3460,6 @@
       <c r="T34" t="n">
         <v>23.7</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
@@ -3855,15 +3558,6 @@
       <c r="T35" t="n">
         <v>23.9</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
@@ -3962,15 +3656,6 @@
       <c r="T36" t="n">
         <v>21.7</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y36" t="n">
         <v>9</v>
       </c>
@@ -4069,15 +3754,6 @@
       <c r="T37" t="n">
         <v>21.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
@@ -4176,15 +3852,6 @@
       <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y38" t="n">
         <v>10.4</v>
       </c>
@@ -4283,15 +3950,6 @@
       <c r="T39" t="n">
         <v>22.3</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
         <v>12.1</v>
       </c>
@@ -4390,15 +4048,6 @@
       <c r="T40" t="n">
         <v>23.6</v>
       </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>7.7</v>
       </c>
@@ -4497,15 +4146,6 @@
       <c r="T41" t="n">
         <v>23.8</v>
       </c>
-      <c r="V41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>11</v>
-      </c>
-      <c r="X41" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y41" t="n">
         <v>3.4</v>
       </c>
@@ -4604,15 +4244,6 @@
       <c r="T42" t="n">
         <v>23.8</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y42" t="n">
         <v>6</v>
       </c>
@@ -4711,15 +4342,6 @@
       <c r="T43" t="n">
         <v>22.1</v>
       </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4818,15 +4440,6 @@
       <c r="T44" t="n">
         <v>23.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y44" t="n">
         <v>5.3</v>
       </c>
@@ -4925,15 +4538,6 @@
       <c r="T45" t="n">
         <v>23.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W45" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y45" t="n">
         <v>11.1</v>
       </c>
@@ -5032,15 +4636,6 @@
       <c r="T46" t="n">
         <v>20</v>
       </c>
-      <c r="V46" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X46" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y46" t="n">
         <v>13.4</v>
       </c>
@@ -5139,15 +4734,6 @@
       <c r="T47" t="n">
         <v>15</v>
       </c>
-      <c r="V47" t="n">
-        <v>16</v>
-      </c>
-      <c r="W47" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y47" t="n">
         <v>15.2</v>
       </c>
@@ -5246,15 +4832,6 @@
       <c r="T48" t="n">
         <v>10.5</v>
       </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y48" t="n">
         <v>14.8</v>
       </c>
@@ -5353,15 +4930,6 @@
       <c r="T49" t="n">
         <v>18.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y49" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5460,15 +5028,6 @@
       <c r="T50" t="n">
         <v>20.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y50" t="n">
         <v>4.9</v>
       </c>
@@ -5567,15 +5126,6 @@
       <c r="T51" t="n">
         <v>22.3</v>
       </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y51" t="n">
         <v>6.8</v>
       </c>
@@ -5674,15 +5224,6 @@
       <c r="T52" t="n">
         <v>22.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W52" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Y52" t="n">
         <v>12.2</v>
       </c>
@@ -5781,24 +5322,6 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5888,24 +5411,6 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="V54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
-      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5995,21 +5500,6 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
-      <c r="V55" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W55" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6102,21 +5592,6 @@
       <c r="T56" t="n">
         <v>20.3</v>
       </c>
-      <c r="V56" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
       </c>
@@ -6209,21 +5684,6 @@
       <c r="T57" t="n">
         <v>20.5</v>
       </c>
-      <c r="V57" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="W57" t="n">
-        <v>22</v>
-      </c>
-      <c r="X57" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
       </c>
@@ -6315,24 +5775,6 @@
       </c>
       <c r="T58" t="n">
         <v>20.5</v>
-      </c>
-      <c r="V58" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W58" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X58" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>13.2</v>
       </c>
       <c r="AB58" t="n">
         <v>3.7</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5322,14 +5322,14 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5411,14 +5411,14 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="AB54" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.4</v>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5500,17 +5500,14 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA55" t="n">
         <v>16</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AF55" t="n">
         <v>233.68</v>
@@ -5592,17 +5589,14 @@
       <c r="T56" t="n">
         <v>20.3</v>
       </c>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>7.4</v>
       </c>
       <c r="AF56" t="n">
         <v>234.37</v>
@@ -5684,17 +5678,14 @@
       <c r="T57" t="n">
         <v>20.5</v>
       </c>
+      <c r="Y57" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>6.2</v>
       </c>
       <c r="AF57" t="n">
         <v>237.85</v>
@@ -5776,14 +5767,14 @@
       <c r="T58" t="n">
         <v>20.5</v>
       </c>
-      <c r="AB58" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>7.6</v>
+      <c r="Y58" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>13.2</v>
       </c>
       <c r="AF58" t="n">
         <v>228.13</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5322,14 +5322,14 @@
       <c r="T53" t="n">
         <v>19.8</v>
       </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
+      <c r="AB53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF53" t="n">
         <v>231.92</v>
@@ -5411,14 +5411,14 @@
       <c r="T54" t="n">
         <v>16</v>
       </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
+      <c r="AB54" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF54" t="n">
         <v>235</v>
@@ -5500,14 +5500,17 @@
       <c r="T55" t="n">
         <v>17</v>
       </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="AF55" t="n">
         <v>233.68</v>
@@ -5589,14 +5592,17 @@
       <c r="T56" t="n">
         <v>20.3</v>
       </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>7.4</v>
       </c>
       <c r="AF56" t="n">
         <v>234.37</v>
@@ -5678,14 +5684,17 @@
       <c r="T57" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y57" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF57" t="n">
         <v>237.85</v>
@@ -5767,14 +5776,14 @@
       <c r="T58" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y58" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>13.2</v>
+      <c r="AB58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>7.6</v>
       </c>
       <c r="AF58" t="n">
         <v>228.13</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5790,15 +5790,6 @@
       <c r="X53" t="n">
         <v>25.6</v>
       </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5897,15 +5888,6 @@
       <c r="X54" t="n">
         <v>26.7</v>
       </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
-      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -6004,12 +5986,6 @@
       <c r="X55" t="n">
         <v>27.9</v>
       </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6111,12 +6087,6 @@
       <c r="X56" t="n">
         <v>27.5</v>
       </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
       </c>
@@ -6218,12 +6188,6 @@
       <c r="X57" t="n">
         <v>19.9</v>
       </c>
-      <c r="Y57" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
       </c>
@@ -6324,15 +6288,6 @@
       </c>
       <c r="X58" t="n">
         <v>19.5</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>13.2</v>
       </c>
       <c r="AB58" t="n">
         <v>3.7</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -821,10 +821,10 @@
         <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>91.5</v>
+        <v>92.3</v>
       </c>
       <c r="O4" t="n">
-        <v>41.2</v>
+        <v>39</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
         <v>8.699999999999999</v>
@@ -895,10 +895,10 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>87.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>39.2</v>
+        <v>37.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
         <v>7.1</v>
@@ -969,10 +969,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>87.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="O6" t="n">
-        <v>39.6</v>
+        <v>37.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
         <v>4.9</v>
@@ -1352,10 +1352,10 @@
         <v>6.5</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O10" t="n">
-        <v>45</v>
+        <v>42.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
         <v>6.3</v>
@@ -1438,10 +1438,10 @@
         <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>94.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V11" t="n">
         <v>8.9</v>
@@ -1524,10 +1524,10 @@
         <v>5.5</v>
       </c>
       <c r="K12" t="n">
-        <v>84.5</v>
+        <v>85.2</v>
       </c>
       <c r="O12" t="n">
-        <v>38</v>
+        <v>35.9</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V12" t="n">
         <v>9.5</v>
@@ -1610,10 +1610,10 @@
         <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>77.7</v>
+        <v>78.3</v>
       </c>
       <c r="O13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V13" t="n">
         <v>9</v>
@@ -2124,10 +2124,10 @@
         <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>92</v>
+        <v>92.8</v>
       </c>
       <c r="O18" t="n">
-        <v>41.4</v>
+        <v>39.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V18" t="n">
         <v>9.5</v>
@@ -2210,10 +2210,10 @@
         <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>86.3</v>
+        <v>87</v>
       </c>
       <c r="O19" t="n">
-        <v>38.8</v>
+        <v>36.7</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V19" t="n">
         <v>10.7</v>
@@ -2831,10 +2831,10 @@
         <v>6.1</v>
       </c>
       <c r="K25" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
-        <v>37.1</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V25" t="n">
         <v>15.5</v>
@@ -2917,10 +2917,10 @@
         <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>74.3</v>
+        <v>74.7</v>
       </c>
       <c r="O26" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
         <v>12.6</v>
@@ -3538,10 +3538,10 @@
         <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="O32" t="n">
-        <v>35.2</v>
+        <v>33.2</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V32" t="n">
         <v>11.6</v>
@@ -3624,10 +3624,10 @@
         <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>81.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="O33" t="n">
-        <v>36.7</v>
+        <v>34.7</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="V33" t="n">
         <v>11</v>
@@ -5790,6 +5790,15 @@
       <c r="X53" t="n">
         <v>25.6</v>
       </c>
+      <c r="Y53" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>21.2</v>
+      </c>
       <c r="AB53" t="n">
         <v>4.3</v>
       </c>
@@ -5888,6 +5897,15 @@
       <c r="X54" t="n">
         <v>26.7</v>
       </c>
+      <c r="Y54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>17.3</v>
+      </c>
       <c r="AB54" t="n">
         <v>5.8</v>
       </c>
@@ -5986,6 +6004,12 @@
       <c r="X55" t="n">
         <v>27.9</v>
       </c>
+      <c r="Y55" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA55" t="n">
         <v>16</v>
       </c>
@@ -6087,6 +6111,12 @@
       <c r="X56" t="n">
         <v>27.5</v>
       </c>
+      <c r="Y56" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA56" t="n">
         <v>17.5</v>
       </c>
@@ -6188,6 +6218,12 @@
       <c r="X57" t="n">
         <v>19.9</v>
       </c>
+      <c r="Y57" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA57" t="n">
         <v>18.2</v>
       </c>
@@ -6233,43 +6269,43 @@
         <v>46295</v>
       </c>
       <c r="B58" t="n">
-        <v>123.4</v>
+        <v>121.1</v>
       </c>
       <c r="C58" t="n">
-        <v>48</v>
+        <v>46.6</v>
       </c>
       <c r="D58" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
       <c r="E58" t="n">
-        <v>27.93</v>
+        <v>25</v>
       </c>
       <c r="F58" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="H58" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I58" t="n">
         <v>9</v>
       </c>
       <c r="J58" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="K58" t="n">
-        <v>66</v>
+        <v>64.2</v>
       </c>
       <c r="M58" t="n">
         <v>1.9</v>
       </c>
       <c r="N58" t="n">
-        <v>27.5</v>
+        <v>25.2</v>
       </c>
       <c r="O58" t="n">
-        <v>29.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6278,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="V58" t="n">
         <v>16.6</v>
@@ -6288,6 +6324,15 @@
       </c>
       <c r="X58" t="n">
         <v>19.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>14.3</v>
       </c>
       <c r="AB58" t="n">
         <v>3.7</v>
@@ -6331,43 +6376,43 @@
         <v>46296</v>
       </c>
       <c r="B59" t="n">
-        <v>121.6</v>
+        <v>122.3</v>
       </c>
       <c r="C59" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="D59" t="n">
-        <v>36.7</v>
+        <v>36.3</v>
       </c>
       <c r="E59" t="n">
         <v>27.12</v>
       </c>
       <c r="F59" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="H59" t="n">
-        <v>20.9</v>
+        <v>22.7</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>65.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M59" t="n">
         <v>1.9</v>
       </c>
       <c r="N59" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="O59" t="n">
-        <v>29.4</v>
+        <v>27.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6376,10 +6421,55 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="V59" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W59" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X59" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>132.56</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-4.36</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46296</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6387,13 +6477,13 @@
         <v>46297</v>
       </c>
       <c r="B60" t="n">
-        <v>118.5</v>
+        <v>117.4</v>
       </c>
       <c r="C60" t="n">
-        <v>46.1</v>
+        <v>45.2</v>
       </c>
       <c r="D60" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="E60" t="n">
         <v>25.73</v>
@@ -6402,28 +6492,28 @@
         <v>4.1</v>
       </c>
       <c r="H60" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K60" t="n">
-        <v>64.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="M60" t="n">
         <v>1.9</v>
       </c>
       <c r="N60" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="O60" t="n">
-        <v>29.4</v>
+        <v>27.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6432,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46297</v>
@@ -6443,13 +6533,13 @@
         <v>46298</v>
       </c>
       <c r="B61" t="n">
-        <v>108.4</v>
+        <v>108.9</v>
       </c>
       <c r="C61" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="D61" t="n">
-        <v>35</v>
+        <v>35.3</v>
       </c>
       <c r="E61" t="n">
         <v>24.44</v>
@@ -6458,28 +6548,28 @@
         <v>4.1</v>
       </c>
       <c r="H61" t="n">
-        <v>20.4</v>
+        <v>22</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K61" t="n">
-        <v>63.4</v>
+        <v>67.7</v>
       </c>
       <c r="M61" t="n">
         <v>1.9</v>
       </c>
       <c r="N61" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="O61" t="n">
-        <v>29.4</v>
+        <v>27.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6488,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46298</v>
@@ -6499,10 +6589,10 @@
         <v>46299</v>
       </c>
       <c r="B62" t="n">
-        <v>103.8</v>
+        <v>104.2</v>
       </c>
       <c r="C62" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="D62" t="n">
         <v>34.8</v>
@@ -6514,28 +6604,28 @@
         <v>4.1</v>
       </c>
       <c r="H62" t="n">
-        <v>20.4</v>
+        <v>22</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K62" t="n">
-        <v>63.4</v>
+        <v>67.7</v>
       </c>
       <c r="M62" t="n">
         <v>1.9</v>
       </c>
       <c r="N62" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="O62" t="n">
-        <v>29.4</v>
+        <v>27.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6544,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46299</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -628,203 +628,212 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="B2" t="n">
-        <v>160.4</v>
+        <v>183</v>
       </c>
       <c r="C2" t="n">
-        <v>62.6</v>
+        <v>84.7</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>30.9</v>
       </c>
       <c r="E2" t="n">
-        <v>32.2</v>
+        <v>33.7</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="I2" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="J2" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K2" t="n">
-        <v>75.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>32.6</v>
+        <v>36.7</v>
       </c>
       <c r="O2" t="n">
-        <v>38</v>
+        <v>40.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y2" t="n">
         <v>8</v>
       </c>
-      <c r="T2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="V2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>13</v>
       </c>
-      <c r="Z2" t="n">
-        <v>16</v>
-      </c>
       <c r="AA2" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3.1</v>
+        <v>0.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>225.08</v>
+        <v>217.16</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.5</v>
+        <v>0.76</v>
       </c>
       <c r="AK2" t="n">
-        <v>135.24</v>
+        <v>117.87</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>6995.8</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2380.8</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>3192.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B3" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C3" t="n">
-        <v>71.09999999999999</v>
+        <v>163.8</v>
       </c>
       <c r="D3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>27.3</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>101</v>
+      </c>
+      <c r="O3" t="n">
         <v>42.6</v>
       </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>37.3</v>
-      </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="V3" t="n">
-        <v>12.7</v>
+        <v>6.3</v>
       </c>
       <c r="W3" t="n">
-        <v>27</v>
+        <v>17.2</v>
       </c>
       <c r="X3" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>-5.2</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.3</v>
+        <v>2.8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>134.62</v>
+        <v>116.52</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.62</v>
+        <v>-1.35</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>2827.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3152.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B4" t="n">
-        <v>151.5</v>
+        <v>155.9</v>
       </c>
       <c r="D4" t="n">
-        <v>35.1</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>92.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>39</v>
+        <v>40.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -839,66 +848,78 @@
         <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>19.4</v>
+        <v>15.8</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
         <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4.7</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>221.37</v>
+        <v>221.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.05</v>
+        <v>1.67</v>
       </c>
       <c r="AK4" t="n">
-        <v>135.21</v>
+        <v>116.37</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.59</v>
+        <v>-0.15</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>3609.5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1161.2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>3077.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B5" t="n">
-        <v>145.2</v>
+        <v>141.3</v>
       </c>
       <c r="D5" t="n">
-        <v>33.5</v>
+        <v>26.3</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>87.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="O5" t="n">
-        <v>37.1</v>
+        <v>35.9</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -913,66 +934,78 @@
         <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
       <c r="X5" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB5" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>224.37</v>
+        <v>225.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>135.61</v>
+        <v>120.64</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4</v>
+        <v>4.27</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1884.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2636.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B6" t="n">
-        <v>146.3</v>
+        <v>131.5</v>
       </c>
       <c r="D6" t="n">
-        <v>33.4</v>
+        <v>27.3</v>
       </c>
       <c r="F6" t="n">
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>88.7</v>
+        <v>78.3</v>
       </c>
       <c r="O6" t="n">
-        <v>37.4</v>
+        <v>33</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -987,461 +1020,506 @@
         <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>16.4</v>
+        <v>13.9</v>
       </c>
       <c r="X6" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA6" t="n">
         <v>15</v>
       </c>
-      <c r="AA6" t="n">
-        <v>9</v>
-      </c>
       <c r="AB6" t="n">
-        <v>-6.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>-3.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>225.93</v>
+        <v>229.98</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.56</v>
+        <v>4.84</v>
       </c>
       <c r="AK6" t="n">
-        <v>135.28</v>
+        <v>128.14</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.33</v>
+        <v>7.5</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1894.8</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B7" t="n">
-        <v>182.8</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>86.8</v>
+        <v>71.8</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>24.7</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="J7" t="n">
         <v>41.1</v>
       </c>
       <c r="K7" t="n">
-        <v>74.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
         <v>33.5</v>
       </c>
       <c r="O7" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="V7" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X7" t="n">
         <v>12.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB7" t="n">
-        <v>-10.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>218.63</v>
+        <v>229.96</v>
       </c>
       <c r="AG7" t="n">
-        <v>-7.3</v>
+        <v>-0.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>126.27</v>
+        <v>128.15</v>
       </c>
       <c r="AL7" t="n">
-        <v>-9.01</v>
+        <v>0.01</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2723.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B8" t="n">
-        <v>181.8</v>
+        <v>165.8</v>
       </c>
       <c r="C8" t="n">
-        <v>86.5</v>
+        <v>77.3</v>
       </c>
       <c r="D8" t="n">
-        <v>31.4</v>
+        <v>29.3</v>
       </c>
       <c r="E8" t="n">
-        <v>34.2</v>
+        <v>27.7</v>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="I8" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="J8" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="K8" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>35.7</v>
+        <v>35.1</v>
       </c>
       <c r="O8" t="n">
         <v>39.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>20.1</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="W8" t="n">
-        <v>14.8</v>
+        <v>17.4</v>
       </c>
       <c r="X8" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>-4.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.4</v>
+        <v>4.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>216.39</v>
+        <v>227.01</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.23</v>
+        <v>-2.95</v>
       </c>
       <c r="AK8" t="n">
-        <v>123.32</v>
+        <v>128.86</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2.95</v>
+        <v>0.71</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="BM8" t="n">
-        <v>40.72</v>
+        <v>33.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>4649.3</v>
+        <v>6652.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>2021.1</v>
+        <v>1412.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>3016.3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B9" t="n">
-        <v>183</v>
+        <v>158.1</v>
       </c>
       <c r="C9" t="n">
-        <v>84.7</v>
+        <v>73.7</v>
       </c>
       <c r="D9" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="E9" t="n">
-        <v>33.7</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="H9" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="I9" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="K9" t="n">
-        <v>76.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>36.7</v>
+        <v>35.3</v>
       </c>
       <c r="O9" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q9" t="n">
         <v>23.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
       <c r="V9" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="W9" t="n">
-        <v>16.1</v>
+        <v>19.3</v>
       </c>
       <c r="X9" t="n">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>217.16</v>
+        <v>228.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.76</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>117.87</v>
+        <v>130.88</v>
       </c>
       <c r="AL9" t="n">
-        <v>-5.45</v>
+        <v>2.02</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="BM9" t="n">
-        <v>40.4</v>
+        <v>32.38</v>
       </c>
       <c r="BN9" t="n">
-        <v>6995.8</v>
+        <v>4993.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>2380.8</v>
+        <v>958.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>3192.8</v>
+        <v>2899.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B10" t="n">
-        <v>163.8</v>
+        <v>154.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>70.2</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>31.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.7</v>
       </c>
       <c r="F10" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.3</v>
       </c>
       <c r="K10" t="n">
-        <v>101</v>
+        <v>75.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.9</v>
       </c>
       <c r="O10" t="n">
-        <v>42.6</v>
+        <v>39</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T10" t="n">
-        <v>20.2</v>
+        <v>23.7</v>
       </c>
       <c r="V10" t="n">
         <v>6.3</v>
       </c>
       <c r="W10" t="n">
-        <v>17.2</v>
+        <v>25.2</v>
       </c>
       <c r="X10" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>220.31</v>
+        <v>231.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.16</v>
+        <v>2.81</v>
       </c>
       <c r="AK10" t="n">
-        <v>116.52</v>
+        <v>132.55</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="BM10" t="n">
-        <v>39.65</v>
+        <v>33.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>2827.2</v>
+        <v>1514.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>2051.2</v>
+        <v>799.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>3152.1</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B11" t="n">
-        <v>155.9</v>
+        <v>152.2</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>95.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="O11" t="n">
-        <v>40.3</v>
+        <v>39.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1456,78 +1534,78 @@
         <v>20.2</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W11" t="n">
-        <v>15.8</v>
+        <v>25.5</v>
       </c>
       <c r="X11" t="n">
-        <v>12.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.99</v>
+        <v>228.13</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>-3.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>116.37</v>
+        <v>128.02</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.15</v>
+        <v>-4.53</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="BM11" t="n">
-        <v>34.79</v>
+        <v>35.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>3609.5</v>
+        <v>1526.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1161.2</v>
+        <v>957.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>3077.1</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B12" t="n">
-        <v>141.3</v>
+        <v>143.9</v>
       </c>
       <c r="D12" t="n">
-        <v>26.3</v>
+        <v>30.8</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>85.2</v>
+        <v>87</v>
       </c>
       <c r="O12" t="n">
-        <v>35.9</v>
+        <v>36.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1542,592 +1620,613 @@
         <v>20.2</v>
       </c>
       <c r="V12" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W12" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="X12" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>225.14</v>
+        <v>229.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK12" t="n">
-        <v>120.64</v>
+        <v>127.06</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.27</v>
+        <v>-0.96</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="BM12" t="n">
-        <v>31.22</v>
+        <v>34.56</v>
       </c>
       <c r="BN12" t="n">
-        <v>1884.4</v>
+        <v>170.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>785.2</v>
+        <v>130.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>2636.2</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B13" t="n">
-        <v>131.5</v>
+        <v>163.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>73.7</v>
       </c>
       <c r="D13" t="n">
-        <v>27.3</v>
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28.2</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>40.1</v>
       </c>
       <c r="K13" t="n">
-        <v>78.3</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>32.9</v>
       </c>
       <c r="O13" t="n">
-        <v>33</v>
+        <v>39.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>20.2</v>
+        <v>23.5</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="X13" t="n">
-        <v>11.4</v>
+        <v>14.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.4</v>
+        <v>4.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>229.98</v>
+        <v>228.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.84</v>
+        <v>-0.61</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.14</v>
+        <v>125.61</v>
       </c>
       <c r="AL13" t="n">
-        <v>7.5</v>
+        <v>-1.45</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="BM13" t="n">
-        <v>26.41</v>
+        <v>34.78</v>
       </c>
       <c r="BN13" t="n">
-        <v>1894.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO13" t="n">
-        <v>223.6</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B14" t="n">
-        <v>153</v>
+        <v>174.4</v>
       </c>
       <c r="C14" t="n">
-        <v>71.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>28.6</v>
+        <v>32.1</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="H14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J14" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="K14" t="n">
-        <v>75.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="M14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD14" t="n">
         <v>4.8</v>
       </c>
-      <c r="N14" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF14" t="n">
-        <v>229.96</v>
+        <v>219.99</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.02</v>
+        <v>-8.56</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.15</v>
+        <v>124.36</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01</v>
+        <v>-1.25</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="BM14" t="n">
-        <v>29.83</v>
+        <v>36.78</v>
       </c>
       <c r="BN14" t="n">
-        <v>2723.2</v>
+        <v>108.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>271.1</v>
+        <v>204.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B15" t="n">
-        <v>165.8</v>
+        <v>163.2</v>
       </c>
       <c r="C15" t="n">
-        <v>77.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>29.3</v>
+        <v>32.9</v>
       </c>
       <c r="E15" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="H15" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I15" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>41.6</v>
+        <v>40.1</v>
       </c>
       <c r="K15" t="n">
-        <v>76.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="N15" t="n">
-        <v>35.1</v>
+        <v>34.3</v>
       </c>
       <c r="O15" t="n">
-        <v>39.8</v>
+        <v>41.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="V15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W15" t="n">
-        <v>17.4</v>
+        <v>23.3</v>
       </c>
       <c r="X15" t="n">
-        <v>13.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>227.01</v>
+        <v>219.22</v>
       </c>
       <c r="AG15" t="n">
-        <v>-2.95</v>
+        <v>-0.77</v>
       </c>
       <c r="AK15" t="n">
-        <v>128.86</v>
+        <v>120.93</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.71</v>
+        <v>-3.43</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="BM15" t="n">
-        <v>33.62</v>
+        <v>32.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>6652.6</v>
+        <v>42.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>1412.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP15" t="n">
-        <v>408</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B16" t="n">
-        <v>158.1</v>
+        <v>152.7</v>
       </c>
       <c r="C16" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D16" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I16" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="K16" t="n">
-        <v>74.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="N16" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="O16" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="V16" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="W16" t="n">
-        <v>19.3</v>
+        <v>27.3</v>
       </c>
       <c r="X16" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>228.35</v>
+        <v>220.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>130.88</v>
+        <v>120.28</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.02</v>
+        <v>-0.65</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="BM16" t="n">
-        <v>32.38</v>
+        <v>29.61</v>
       </c>
       <c r="BN16" t="n">
-        <v>4993.3</v>
+        <v>60.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>958.6</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2899.8</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B17" t="n">
-        <v>154.9</v>
+        <v>150.7</v>
       </c>
       <c r="C17" t="n">
-        <v>70.2</v>
+        <v>64.8</v>
       </c>
       <c r="D17" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="E17" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H17" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I17" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J17" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="K17" t="n">
-        <v>75.8</v>
+        <v>70.5</v>
       </c>
       <c r="M17" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="N17" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="O17" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S17" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="X17" t="n">
-        <v>15.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>231.16</v>
+        <v>220.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.81</v>
+        <v>-0.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>132.55</v>
+        <v>119.29</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.67</v>
+        <v>-0.99</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="BM17" t="n">
-        <v>33.01</v>
+        <v>31.11</v>
       </c>
       <c r="BN17" t="n">
-        <v>1514.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO17" t="n">
-        <v>799.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP17" t="n">
-        <v>2923.4</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B18" t="n">
-        <v>152.2</v>
+        <v>138.2</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>33.6</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="K18" t="n">
-        <v>92.8</v>
+        <v>83</v>
       </c>
       <c r="O18" t="n">
-        <v>39.2</v>
+        <v>35</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2142,78 +2241,78 @@
         <v>20.2</v>
       </c>
       <c r="V18" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="W18" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>228.13</v>
+        <v>223.43</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AK18" t="n">
-        <v>128.02</v>
+        <v>121.35</v>
       </c>
       <c r="AL18" t="n">
-        <v>-4.53</v>
+        <v>2.06</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="BM18" t="n">
-        <v>35.62</v>
+        <v>30.59</v>
       </c>
       <c r="BN18" t="n">
-        <v>1526.5</v>
+        <v>40.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>957.4</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2928.4</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B19" t="n">
-        <v>143.9</v>
+        <v>126.5</v>
       </c>
       <c r="D19" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>87</v>
+        <v>74.7</v>
       </c>
       <c r="O19" t="n">
-        <v>36.7</v>
+        <v>31.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2228,613 +2327,613 @@
         <v>20.2</v>
       </c>
       <c r="V19" t="n">
-        <v>10.7</v>
+        <v>12.6</v>
       </c>
       <c r="W19" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="X19" t="n">
-        <v>14.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>229.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>6.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>127.06</v>
+        <v>128.37</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.96</v>
+        <v>7.02</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="BM19" t="n">
-        <v>34.56</v>
+        <v>30.05</v>
       </c>
       <c r="BN19" t="n">
-        <v>170.6</v>
+        <v>34</v>
       </c>
       <c r="BO19" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>2825.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B20" t="n">
-        <v>163.2</v>
+        <v>129.4</v>
       </c>
       <c r="C20" t="n">
-        <v>73.7</v>
+        <v>50.6</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E20" t="n">
-        <v>28.2</v>
+        <v>19.4</v>
       </c>
       <c r="F20" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H20" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I20" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="J20" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
       <c r="K20" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M20" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="N20" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="O20" t="n">
-        <v>39.7</v>
+        <v>38</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="R20" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="W20" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="X20" t="n">
-        <v>14.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
         <v>4</v>
       </c>
-      <c r="Z20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF20" t="n">
-        <v>228.55</v>
+        <v>241.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.61</v>
+        <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>125.61</v>
+        <v>134.59</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.45</v>
+        <v>6.22</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="BM20" t="n">
-        <v>34.78</v>
+        <v>24.86</v>
       </c>
       <c r="BN20" t="n">
-        <v>69.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="BO20" t="n">
         <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>2769.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B21" t="n">
-        <v>174.4</v>
+        <v>142.9</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="D21" t="n">
-        <v>32.1</v>
+        <v>34.7</v>
       </c>
       <c r="E21" t="n">
-        <v>30.8</v>
+        <v>24.8</v>
       </c>
       <c r="F21" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I21" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="J21" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="K21" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M21" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O21" t="n">
         <v>35.8</v>
       </c>
-      <c r="O21" t="n">
-        <v>42.6</v>
-      </c>
       <c r="Q21" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="R21" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="V21" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="W21" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>219.99</v>
+        <v>238.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>-8.56</v>
+        <v>-2.8</v>
       </c>
       <c r="AK21" t="n">
-        <v>124.36</v>
+        <v>136.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>-1.25</v>
+        <v>2.01</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="BM21" t="n">
-        <v>36.78</v>
+        <v>29.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>108.8</v>
+        <v>61.9</v>
       </c>
       <c r="BO21" t="n">
-        <v>204.3</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>2982.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B22" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C22" t="n">
-        <v>70.90000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D22" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="F22" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H22" t="n">
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
       <c r="I22" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J22" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K22" t="n">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="M22" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="O22" t="n">
-        <v>41.5</v>
+        <v>33.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="S22" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="V22" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="W22" t="n">
-        <v>23.3</v>
+        <v>25.5</v>
       </c>
       <c r="X22" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>219.22</v>
+        <v>233.48</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.77</v>
+        <v>-4.86</v>
       </c>
       <c r="AK22" t="n">
-        <v>120.93</v>
+        <v>135.66</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3.43</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="BM22" t="n">
-        <v>32.64</v>
+        <v>36.03</v>
       </c>
       <c r="BN22" t="n">
-        <v>42.3</v>
+        <v>76.5</v>
       </c>
       <c r="BO22" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>3194.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B23" t="n">
-        <v>152.7</v>
+        <v>143.4</v>
       </c>
       <c r="C23" t="n">
-        <v>62.6</v>
+        <v>50.9</v>
       </c>
       <c r="D23" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="E23" t="n">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="F23" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="H23" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="I23" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K23" t="n">
-        <v>69.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>33.5</v>
+        <v>31.2</v>
       </c>
       <c r="O23" t="n">
-        <v>40.1</v>
+        <v>33.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="R23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="V23" t="n">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="W23" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="X23" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF23" t="n">
-        <v>220.73</v>
+        <v>235.13</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AK23" t="n">
-        <v>120.28</v>
+        <v>136.33</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="BM23" t="n">
-        <v>29.61</v>
+        <v>32</v>
       </c>
       <c r="BN23" t="n">
-        <v>60.1</v>
+        <v>29.5</v>
       </c>
       <c r="BO23" t="n">
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2717.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B24" t="n">
-        <v>150.7</v>
+        <v>144.9</v>
       </c>
       <c r="C24" t="n">
-        <v>64.8</v>
+        <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
       <c r="E24" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H24" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>21</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>21</v>
+      </c>
+      <c r="V24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>234.87</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>137.17</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BL24" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="BN24" t="n">
         <v>23.4</v>
       </c>
-      <c r="I24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>33</v>
-      </c>
-      <c r="O24" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>119.29</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="BL24" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>87.90000000000001</v>
-      </c>
       <c r="BO24" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3028.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B25" t="n">
-        <v>138.2</v>
+        <v>132.2</v>
       </c>
       <c r="D25" t="n">
-        <v>33.6</v>
+        <v>35.6</v>
       </c>
       <c r="F25" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>83</v>
+        <v>78.8</v>
       </c>
       <c r="O25" t="n">
-        <v>35</v>
+        <v>33.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2849,78 +2948,78 @@
         <v>20.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="W25" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="X25" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
         <v>13</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>223.43</v>
+        <v>234.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.85</v>
+        <v>-0.09</v>
       </c>
       <c r="AK25" t="n">
-        <v>121.35</v>
+        <v>136.08</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.06</v>
+        <v>-1.09</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="BM25" t="n">
-        <v>30.59</v>
+        <v>29.64</v>
       </c>
       <c r="BN25" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="BO25" t="n">
         <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>2959.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B26" t="n">
-        <v>126.5</v>
+        <v>137.1</v>
       </c>
       <c r="D26" t="n">
-        <v>33.2</v>
+        <v>35.1</v>
       </c>
       <c r="F26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>74.7</v>
+        <v>82.2</v>
       </c>
       <c r="O26" t="n">
-        <v>31.6</v>
+        <v>34.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2935,52 +3034,52 @@
         <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="W26" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="X26" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>229.48</v>
+        <v>229.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>6.05</v>
+        <v>-5.03</v>
       </c>
       <c r="AK26" t="n">
-        <v>128.37</v>
+        <v>135.42</v>
       </c>
       <c r="AL26" t="n">
-        <v>7.02</v>
+        <v>-0.66</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="BM26" t="n">
-        <v>30.05</v>
+        <v>31.45</v>
       </c>
       <c r="BN26" t="n">
-        <v>34</v>
+        <v>35.9</v>
       </c>
       <c r="BO26" t="n">
         <v>0</v>
@@ -2991,1987 +3090,2029 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B27" t="n">
-        <v>129.4</v>
+        <v>148.7</v>
       </c>
       <c r="C27" t="n">
-        <v>50.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E27" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
       </c>
       <c r="F27" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H27" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="K27" t="n">
-        <v>73.3</v>
+        <v>74.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="N27" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="O27" t="n">
-        <v>38</v>
+        <v>39.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="V27" t="n">
-        <v>14.3</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
-        <v>23.9</v>
+        <v>15.6</v>
       </c>
       <c r="X27" t="n">
-        <v>19.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>241.48</v>
+        <v>222.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>12</v>
+        <v>-6.9</v>
       </c>
       <c r="AK27" t="n">
-        <v>134.59</v>
+        <v>131.24</v>
       </c>
       <c r="AL27" t="n">
-        <v>6.22</v>
+        <v>-4.18</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="BM27" t="n">
-        <v>24.86</v>
+        <v>34.46</v>
       </c>
       <c r="BN27" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B28" t="n">
-        <v>142.9</v>
+        <v>149.3</v>
       </c>
       <c r="C28" t="n">
-        <v>52.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="E28" t="n">
-        <v>24.8</v>
+        <v>28.8</v>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="I28" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="K28" t="n">
-        <v>70</v>
+        <v>73.8</v>
       </c>
       <c r="M28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R28" t="n">
         <v>3.9</v>
       </c>
-      <c r="N28" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="O28" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>19.7</v>
+        <v>23.9</v>
       </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="W28" t="n">
-        <v>25.8</v>
+        <v>18.1</v>
       </c>
       <c r="X28" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>238.69</v>
+        <v>218.37</v>
       </c>
       <c r="AG28" t="n">
-        <v>-2.8</v>
+        <v>-4.49</v>
       </c>
       <c r="AK28" t="n">
-        <v>136.6</v>
+        <v>129.21</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.01</v>
+        <v>-2.03</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="BM28" t="n">
-        <v>29.8</v>
+        <v>35.4</v>
       </c>
       <c r="BN28" t="n">
-        <v>61.9</v>
+        <v>294.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B29" t="n">
-        <v>148.1</v>
+        <v>137</v>
       </c>
       <c r="C29" t="n">
-        <v>51.9</v>
+        <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>35.4</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>31.5</v>
+        <v>25.2</v>
       </c>
       <c r="F29" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H29" t="n">
-        <v>21.8</v>
+        <v>23.5</v>
       </c>
       <c r="I29" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
-        <v>39.6</v>
+        <v>38.5</v>
       </c>
       <c r="K29" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="N29" t="n">
-        <v>30.8</v>
+        <v>32.3</v>
       </c>
       <c r="O29" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="W29" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="X29" t="n">
-        <v>19.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>233.48</v>
+        <v>220.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>-4.86</v>
+        <v>2.48</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.66</v>
+        <v>129.07</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="BM29" t="n">
-        <v>36.03</v>
+        <v>32.31</v>
       </c>
       <c r="BN29" t="n">
-        <v>76.5</v>
+        <v>547</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B30" t="n">
-        <v>143.4</v>
+        <v>131.5</v>
       </c>
       <c r="C30" t="n">
-        <v>50.9</v>
+        <v>57.6</v>
       </c>
       <c r="D30" t="n">
-        <v>35.7</v>
+        <v>32.7</v>
       </c>
       <c r="E30" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="F30" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="H30" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="I30" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J30" t="n">
-        <v>39.9</v>
+        <v>41.6</v>
       </c>
       <c r="K30" t="n">
-        <v>72.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="N30" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="O30" t="n">
-        <v>33.1</v>
+        <v>42.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V30" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>28.3</v>
+        <v>24.1</v>
       </c>
       <c r="X30" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>235.13</v>
+        <v>225.87</v>
       </c>
       <c r="AG30" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>130.73</v>
+      </c>
+      <c r="AL30" t="n">
         <v>1.66</v>
       </c>
-      <c r="AK30" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="BM30" t="n">
-        <v>32</v>
+        <v>31.51</v>
       </c>
       <c r="BN30" t="n">
-        <v>29.5</v>
+        <v>124</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>164.4</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B31" t="n">
-        <v>144.9</v>
+        <v>129.4</v>
       </c>
       <c r="C31" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="D31" t="n">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="F31" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H31" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I31" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J31" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="K31" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="N31" t="n">
-        <v>31.6</v>
+        <v>33.1</v>
       </c>
       <c r="O31" t="n">
-        <v>33.6</v>
+        <v>38.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V31" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="W31" t="n">
-        <v>27.7</v>
+        <v>22.9</v>
       </c>
       <c r="X31" t="n">
-        <v>21.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="Z31" t="n">
         <v>19</v>
       </c>
       <c r="AA31" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>-1.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>234.87</v>
+        <v>229.48</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.26</v>
+        <v>3.61</v>
       </c>
       <c r="AK31" t="n">
-        <v>137.17</v>
+        <v>132</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.84</v>
+        <v>1.27</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="BM31" t="n">
-        <v>32.57</v>
+        <v>34.36</v>
       </c>
       <c r="BN31" t="n">
-        <v>23.4</v>
+        <v>62.8</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B32" t="n">
-        <v>132.2</v>
+        <v>130.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>56.9</v>
       </c>
       <c r="D32" t="n">
-        <v>35.6</v>
+        <v>33.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>2.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>42.3</v>
       </c>
       <c r="K32" t="n">
-        <v>78.8</v>
+        <v>75.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>32.3</v>
       </c>
       <c r="O32" t="n">
-        <v>33.2</v>
+        <v>37.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>20.2</v>
+        <v>22.3</v>
       </c>
       <c r="V32" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="W32" t="n">
-        <v>23.2</v>
+        <v>21.7</v>
       </c>
       <c r="X32" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="Y32" t="n">
-        <v>7</v>
+        <v>12.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>234.78</v>
+        <v>230.54</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>136.08</v>
+        <v>132.25</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.09</v>
+        <v>0.25</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="BM32" t="n">
-        <v>29.64</v>
+        <v>32.26</v>
       </c>
       <c r="BN32" t="n">
-        <v>36.4</v>
+        <v>28.3</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>2545.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B33" t="n">
-        <v>137.1</v>
+        <v>138.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>35.1</v>
+        <v>32.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>25.9</v>
       </c>
       <c r="F33" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>42.8</v>
       </c>
       <c r="K33" t="n">
-        <v>82.2</v>
+        <v>75.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32.3</v>
       </c>
       <c r="O33" t="n">
-        <v>34.7</v>
+        <v>35.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>20.2</v>
+        <v>23.6</v>
       </c>
       <c r="V33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
-        <v>22</v>
+        <v>15.7</v>
       </c>
       <c r="X33" t="n">
-        <v>16.5</v>
+        <v>12.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>-5.3</v>
+        <v>-6.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>229.75</v>
+        <v>224.23</v>
       </c>
       <c r="AG33" t="n">
-        <v>-5.03</v>
+        <v>-6.3</v>
       </c>
       <c r="AK33" t="n">
-        <v>135.42</v>
+        <v>128.6</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.66</v>
+        <v>-3.65</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="BM33" t="n">
-        <v>31.45</v>
+        <v>33.93</v>
       </c>
       <c r="BN33" t="n">
-        <v>35.9</v>
+        <v>73</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>2697.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B34" t="n">
-        <v>148.7</v>
+        <v>140.8</v>
       </c>
       <c r="C34" t="n">
-        <v>72.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>32.7</v>
+        <v>31.7</v>
       </c>
       <c r="E34" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="F34" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I34" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="K34" t="n">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
       <c r="M34" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>33.7</v>
+        <v>33.4</v>
       </c>
       <c r="O34" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="R34" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AA34" t="n">
         <v>7.9</v>
       </c>
-      <c r="W34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AB34" t="n">
-        <v>-3.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.4</v>
+        <v>12.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>222.86</v>
+        <v>223.36</v>
       </c>
       <c r="AG34" t="n">
-        <v>-6.9</v>
+        <v>-0.88</v>
       </c>
       <c r="AK34" t="n">
-        <v>131.24</v>
+        <v>127.19</v>
       </c>
       <c r="AL34" t="n">
-        <v>-4.18</v>
+        <v>-1.41</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="BM34" t="n">
-        <v>34.46</v>
+        <v>31.16</v>
       </c>
       <c r="BN34" t="n">
-        <v>80.40000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="BO34" t="n">
-        <v>373.6</v>
+        <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>249.4</v>
+        <v>2603.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B35" t="n">
-        <v>149.3</v>
+        <v>139.6</v>
       </c>
       <c r="C35" t="n">
-        <v>74.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E35" t="n">
-        <v>28.8</v>
+        <v>25.9</v>
       </c>
       <c r="F35" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="H35" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="I35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>41.2</v>
+        <v>39.6</v>
       </c>
       <c r="K35" t="n">
-        <v>73.8</v>
+        <v>73.3</v>
       </c>
       <c r="M35" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="N35" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="O35" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="R35" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V35" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W35" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="X35" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AB35" t="n">
-        <v>-2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>218.37</v>
+        <v>222.92</v>
       </c>
       <c r="AG35" t="n">
-        <v>-4.49</v>
+        <v>-0.44</v>
       </c>
       <c r="AK35" t="n">
-        <v>129.21</v>
+        <v>129.17</v>
       </c>
       <c r="AL35" t="n">
-        <v>-2.03</v>
+        <v>1.98</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="BM35" t="n">
-        <v>35.4</v>
+        <v>32.41</v>
       </c>
       <c r="BN35" t="n">
-        <v>294.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BO35" t="n">
-        <v>227</v>
+        <v>297.8</v>
       </c>
       <c r="BP35" t="n">
-        <v>2758.6</v>
+        <v>2677.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B36" t="n">
-        <v>137</v>
+        <v>133.5</v>
       </c>
       <c r="C36" t="n">
-        <v>65</v>
+        <v>62.3</v>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E36" t="n">
-        <v>25.2</v>
+        <v>22.5</v>
       </c>
       <c r="F36" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J36" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="K36" t="n">
-        <v>70.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="N36" t="n">
-        <v>32.3</v>
+        <v>30.4</v>
       </c>
       <c r="O36" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="R36" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="S36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="V36" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="W36" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="X36" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z36" t="n">
-        <v>18</v>
+        <v>20.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.3</v>
+        <v>12.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>220.85</v>
+        <v>222.77</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.48</v>
+        <v>-0.16</v>
       </c>
       <c r="AK36" t="n">
-        <v>129.07</v>
+        <v>130.42</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.14</v>
+        <v>1.25</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="BM36" t="n">
-        <v>32.31</v>
+        <v>26.56</v>
       </c>
       <c r="BN36" t="n">
-        <v>547</v>
+        <v>46.1</v>
       </c>
       <c r="BO36" t="n">
-        <v>85</v>
+        <v>266.8</v>
       </c>
       <c r="BP36" t="n">
-        <v>2654.5</v>
+        <v>2801.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B37" t="n">
-        <v>131.5</v>
+        <v>133.5</v>
       </c>
       <c r="C37" t="n">
-        <v>57.6</v>
+        <v>61.6</v>
       </c>
       <c r="D37" t="n">
-        <v>32.7</v>
+        <v>33.9</v>
       </c>
       <c r="E37" t="n">
-        <v>26.3</v>
+        <v>25</v>
       </c>
       <c r="F37" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="H37" t="n">
-        <v>23.6</v>
+        <v>25.1</v>
       </c>
       <c r="I37" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="J37" t="n">
-        <v>41.6</v>
+        <v>39.5</v>
       </c>
       <c r="K37" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="N37" t="n">
-        <v>35</v>
+        <v>28.6</v>
       </c>
       <c r="O37" t="n">
-        <v>42.4</v>
+        <v>34.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="R37" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="V37" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W37" t="n">
-        <v>24.1</v>
+        <v>26</v>
       </c>
       <c r="X37" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>12.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>14.5</v>
+        <v>11.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>225.87</v>
+        <v>221.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.02</v>
+        <v>-0.91</v>
       </c>
       <c r="AK37" t="n">
-        <v>130.73</v>
+        <v>129.71</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.66</v>
+        <v>-0.71</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="BM37" t="n">
-        <v>31.51</v>
+        <v>31.32</v>
       </c>
       <c r="BN37" t="n">
-        <v>124</v>
+        <v>54.7</v>
       </c>
       <c r="BO37" t="n">
-        <v>164.4</v>
+        <v>235.3</v>
       </c>
       <c r="BP37" t="n">
-        <v>2635.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="B38" t="n">
-        <v>129.4</v>
+        <v>120.6</v>
       </c>
       <c r="C38" t="n">
-        <v>52.8</v>
+        <v>47.7</v>
       </c>
       <c r="D38" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="E38" t="n">
-        <v>28.9</v>
+        <v>24.1</v>
       </c>
       <c r="F38" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="I38" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>40.8</v>
+        <v>38.4</v>
       </c>
       <c r="K38" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M38" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>33.1</v>
+        <v>30.3</v>
       </c>
       <c r="O38" t="n">
-        <v>38.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="R38" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V38" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="W38" t="n">
-        <v>22.9</v>
+        <v>27.6</v>
       </c>
       <c r="X38" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.1</v>
+        <v>18.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.48</v>
+        <v>227.49</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.61</v>
+        <v>5.63</v>
       </c>
       <c r="AK38" t="n">
-        <v>132</v>
+        <v>133.39</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.27</v>
+        <v>3.68</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="BM38" t="n">
-        <v>34.36</v>
+        <v>29.84</v>
       </c>
       <c r="BN38" t="n">
-        <v>62.8</v>
+        <v>41.3</v>
       </c>
       <c r="BO38" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="BP38" t="n">
-        <v>2693.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B39" t="n">
-        <v>130.2</v>
+        <v>116.8</v>
       </c>
       <c r="C39" t="n">
-        <v>56.9</v>
+        <v>45.4</v>
       </c>
       <c r="D39" t="n">
-        <v>33.9</v>
+        <v>35.3</v>
       </c>
       <c r="E39" t="n">
-        <v>26.4</v>
+        <v>23.2</v>
       </c>
       <c r="F39" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="H39" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="I39" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>42.3</v>
+        <v>38</v>
       </c>
       <c r="K39" t="n">
-        <v>75.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="N39" t="n">
-        <v>32.3</v>
+        <v>28.2</v>
       </c>
       <c r="O39" t="n">
-        <v>37.1</v>
+        <v>30.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="V39" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W39" t="n">
-        <v>21.7</v>
+        <v>27.6</v>
       </c>
       <c r="X39" t="n">
-        <v>18</v>
+        <v>20.9</v>
       </c>
       <c r="Y39" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="n">
-        <v>15.1</v>
+        <v>17.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>-3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.2</v>
+        <v>14.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF39" t="n">
-        <v>230.54</v>
+        <v>233.56</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.06</v>
+        <v>6.07</v>
       </c>
       <c r="AK39" t="n">
-        <v>132.25</v>
+        <v>137.14</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.25</v>
+        <v>3.75</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="BM39" t="n">
-        <v>32.26</v>
+        <v>26.51</v>
       </c>
       <c r="BN39" t="n">
-        <v>28.3</v>
+        <v>107.4</v>
       </c>
       <c r="BO39" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="BP39" t="n">
-        <v>2545.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B40" t="n">
-        <v>138.4</v>
+        <v>102.9</v>
       </c>
       <c r="C40" t="n">
-        <v>66.90000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="D40" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>25.9</v>
+        <v>19.8</v>
       </c>
       <c r="F40" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H40" t="n">
-        <v>23.6</v>
+        <v>21.7</v>
       </c>
       <c r="I40" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>42.8</v>
+        <v>34</v>
       </c>
       <c r="K40" t="n">
-        <v>75.8</v>
+        <v>65.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="N40" t="n">
-        <v>32.3</v>
+        <v>27</v>
       </c>
       <c r="O40" t="n">
-        <v>35.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W40" t="n">
-        <v>15.7</v>
+        <v>30.6</v>
       </c>
       <c r="X40" t="n">
-        <v>12.3</v>
+        <v>23.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.7</v>
+        <v>15.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.3</v>
+        <v>18.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.1</v>
+        <v>16.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.8</v>
+        <v>12.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>224.23</v>
+        <v>234.94</v>
       </c>
       <c r="AG40" t="n">
-        <v>-6.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK40" t="n">
-        <v>128.6</v>
+        <v>137.51</v>
       </c>
       <c r="AL40" t="n">
-        <v>-3.65</v>
+        <v>0.37</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="BM40" t="n">
-        <v>33.93</v>
+        <v>20.4</v>
       </c>
       <c r="BN40" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BP40" t="n">
-        <v>2697.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="B41" t="n">
-        <v>140.8</v>
+        <v>93.2</v>
       </c>
       <c r="C41" t="n">
-        <v>73.09999999999999</v>
+        <v>36.3</v>
       </c>
       <c r="D41" t="n">
-        <v>31.7</v>
+        <v>32.7</v>
       </c>
       <c r="E41" t="n">
-        <v>26.1</v>
+        <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H41" t="n">
-        <v>23.6</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J41" t="n">
-        <v>40.5</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>73.5</v>
+        <v>51.2</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="N41" t="n">
-        <v>33.4</v>
+        <v>25.5</v>
       </c>
       <c r="O41" t="n">
-        <v>39.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="R41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="V41" t="n">
-        <v>6.8</v>
+        <v>15.8</v>
       </c>
       <c r="W41" t="n">
-        <v>11</v>
+        <v>33.6</v>
       </c>
       <c r="X41" t="n">
-        <v>8.9</v>
+        <v>24.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
       <c r="AA41" t="n">
-        <v>7.9</v>
+        <v>16.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>-1.2</v>
+        <v>4</v>
       </c>
       <c r="AC41" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AF41" t="n">
-        <v>223.36</v>
+        <v>229.19</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.88</v>
+        <v>-5.75</v>
       </c>
       <c r="AK41" t="n">
-        <v>127.19</v>
+        <v>138.98</v>
       </c>
       <c r="AL41" t="n">
-        <v>-1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="BM41" t="n">
-        <v>31.16</v>
+        <v>19.88</v>
       </c>
       <c r="BN41" t="n">
-        <v>21.2</v>
+        <v>35.1</v>
       </c>
       <c r="BO41" t="n">
         <v>0</v>
       </c>
       <c r="BP41" t="n">
-        <v>2603.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B42" t="n">
-        <v>139.6</v>
+        <v>120.3</v>
       </c>
       <c r="C42" t="n">
-        <v>69.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="D42" t="n">
-        <v>32.2</v>
+        <v>36.3</v>
       </c>
       <c r="E42" t="n">
-        <v>25.9</v>
+        <v>20.6</v>
       </c>
       <c r="F42" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H42" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
       </c>
       <c r="I42" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J42" t="n">
-        <v>39.6</v>
+        <v>35.4</v>
       </c>
       <c r="K42" t="n">
-        <v>73.3</v>
+        <v>66</v>
       </c>
       <c r="M42" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="N42" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="O42" t="n">
-        <v>40.1</v>
+        <v>26.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.8</v>
+        <v>18.3</v>
       </c>
       <c r="R42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>23.8</v>
+        <v>18.3</v>
       </c>
       <c r="V42" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="W42" t="n">
-        <v>15.2</v>
+        <v>22.5</v>
       </c>
       <c r="X42" t="n">
-        <v>10.9</v>
+        <v>20.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z42" t="n">
-        <v>13.6</v>
+        <v>16.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AF42" t="n">
-        <v>222.92</v>
+        <v>224.91</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.44</v>
+        <v>-4.28</v>
       </c>
       <c r="AK42" t="n">
-        <v>129.17</v>
+        <v>134.04</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.98</v>
+        <v>-4.94</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="BM42" t="n">
-        <v>32.41</v>
+        <v>22.59</v>
       </c>
       <c r="BN42" t="n">
-        <v>74.59999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="BO42" t="n">
-        <v>297.8</v>
+        <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>2677.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B43" t="n">
-        <v>133.5</v>
+        <v>131.1</v>
       </c>
       <c r="C43" t="n">
-        <v>62.3</v>
+        <v>60.2</v>
       </c>
       <c r="D43" t="n">
-        <v>34</v>
+        <v>35.6</v>
       </c>
       <c r="E43" t="n">
-        <v>22.5</v>
+        <v>24.2</v>
       </c>
       <c r="F43" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="H43" t="n">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="I43" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>40.8</v>
+        <v>38.2</v>
       </c>
       <c r="K43" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M43" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="N43" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="O43" t="n">
-        <v>37.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V43" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y43" t="n">
         <v>4.9</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z43" t="n">
-        <v>20.2</v>
+        <v>12.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="AC43" t="n">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>222.77</v>
+        <v>220.83</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.16</v>
+        <v>-4.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>130.42</v>
+        <v>131.01</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.25</v>
+        <v>-3.03</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="BM43" t="n">
-        <v>26.56</v>
+        <v>29.62</v>
       </c>
       <c r="BN43" t="n">
-        <v>46.1</v>
+        <v>58.2</v>
       </c>
       <c r="BO43" t="n">
-        <v>266.8</v>
+        <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>2801.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B44" t="n">
-        <v>133.5</v>
+        <v>117.2</v>
       </c>
       <c r="C44" t="n">
-        <v>61.6</v>
+        <v>53.7</v>
       </c>
       <c r="D44" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="F44" t="n">
         <v>2.2</v>
       </c>
       <c r="H44" t="n">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="I44" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="J44" t="n">
-        <v>39.5</v>
+        <v>37</v>
       </c>
       <c r="K44" t="n">
-        <v>74.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="M44" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="N44" t="n">
-        <v>28.6</v>
+        <v>31.4</v>
       </c>
       <c r="O44" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="R44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="V44" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="W44" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="X44" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>12.9</v>
+        <v>16.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AC44" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="AD44" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="AF44" t="n">
-        <v>221.86</v>
+        <v>228.06</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.91</v>
+        <v>7.23</v>
       </c>
       <c r="AK44" t="n">
-        <v>129.71</v>
+        <v>131.96</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.71</v>
+        <v>0.95</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="BM44" t="n">
-        <v>31.32</v>
+        <v>23.82</v>
       </c>
       <c r="BN44" t="n">
-        <v>54.7</v>
+        <v>49.9</v>
       </c>
       <c r="BO44" t="n">
-        <v>235.3</v>
+        <v>0</v>
       </c>
       <c r="BP44" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B45" t="n">
-        <v>120.6</v>
+        <v>112.8</v>
       </c>
       <c r="C45" t="n">
-        <v>47.7</v>
+        <v>42.7</v>
       </c>
       <c r="D45" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="E45" t="n">
-        <v>24.1</v>
+        <v>20.7</v>
       </c>
       <c r="F45" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H45" t="n">
-        <v>24.9</v>
+        <v>21.2</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="J45" t="n">
-        <v>38.4</v>
+        <v>36.8</v>
       </c>
       <c r="K45" t="n">
-        <v>73.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>30.3</v>
+        <v>27.9</v>
       </c>
       <c r="O45" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="V45" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="W45" t="n">
-        <v>27.6</v>
+        <v>31.2</v>
       </c>
       <c r="X45" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="Y45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC45" t="n">
         <v>11.1</v>
       </c>
-      <c r="Z45" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AD45" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AF45" t="n">
-        <v>227.49</v>
+        <v>233.59</v>
       </c>
       <c r="AG45" t="n">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="AK45" t="n">
-        <v>133.39</v>
+        <v>132.79</v>
       </c>
       <c r="AL45" t="n">
-        <v>3.68</v>
+        <v>0.83</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="BM45" t="n">
-        <v>29.84</v>
+        <v>23.43</v>
       </c>
       <c r="BN45" t="n">
-        <v>41.3</v>
+        <v>83.8</v>
       </c>
       <c r="BO45" t="n">
         <v>0</v>
@@ -4982,46 +5123,46 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B46" t="n">
-        <v>116.8</v>
+        <v>109.2</v>
       </c>
       <c r="C46" t="n">
-        <v>45.4</v>
+        <v>41.3</v>
       </c>
       <c r="D46" t="n">
-        <v>35.3</v>
+        <v>34.9</v>
       </c>
       <c r="E46" t="n">
-        <v>23.2</v>
+        <v>21.2</v>
       </c>
       <c r="F46" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="H46" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="I46" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J46" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
-        <v>70.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N46" t="n">
-        <v>28.2</v>
+        <v>25</v>
       </c>
       <c r="O46" t="n">
-        <v>30.3</v>
+        <v>26.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5030,55 +5171,55 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="V46" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="W46" t="n">
-        <v>27.6</v>
+        <v>35.4</v>
       </c>
       <c r="X46" t="n">
-        <v>20.9</v>
+        <v>25.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>13.4</v>
+        <v>16.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>21</v>
+        <v>25.8</v>
       </c>
       <c r="AA46" t="n">
-        <v>17.2</v>
+        <v>21.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>14.9</v>
+        <v>10.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>233.56</v>
+        <v>231.92</v>
       </c>
       <c r="AG46" t="n">
-        <v>6.07</v>
+        <v>-1.67</v>
       </c>
       <c r="AK46" t="n">
-        <v>137.14</v>
+        <v>136.54</v>
       </c>
       <c r="AL46" t="n">
         <v>3.75</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="BM46" t="n">
-        <v>26.51</v>
+        <v>25.29</v>
       </c>
       <c r="BN46" t="n">
-        <v>107.4</v>
+        <v>170.5</v>
       </c>
       <c r="BO46" t="n">
         <v>0</v>
@@ -5089,46 +5230,46 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B47" t="n">
-        <v>102.9</v>
+        <v>108.1</v>
       </c>
       <c r="C47" t="n">
-        <v>36.8</v>
+        <v>39.3</v>
       </c>
       <c r="D47" t="n">
         <v>34</v>
       </c>
       <c r="E47" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="H47" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="I47" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J47" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K47" t="n">
-        <v>65.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N47" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O47" t="n">
-        <v>29.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5137,55 +5278,55 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V47" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="W47" t="n">
-        <v>30.6</v>
+        <v>33.8</v>
       </c>
       <c r="X47" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="Y47" t="n">
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA47" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>16.7</v>
+        <v>13</v>
       </c>
       <c r="AD47" t="n">
-        <v>12.8</v>
+        <v>9.4</v>
       </c>
       <c r="AF47" t="n">
-        <v>234.94</v>
+        <v>235</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.38</v>
+        <v>3.09</v>
       </c>
       <c r="AK47" t="n">
-        <v>137.51</v>
+        <v>136.61</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.37</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="BM47" t="n">
-        <v>20.4</v>
+        <v>20.23</v>
       </c>
       <c r="BN47" t="n">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="BO47" t="n">
         <v>0</v>
@@ -5196,103 +5337,103 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B48" t="n">
-        <v>93.2</v>
+        <v>101</v>
       </c>
       <c r="C48" t="n">
+        <v>37</v>
+      </c>
+      <c r="D48" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O48" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>17</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>17</v>
+      </c>
+      <c r="V48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W48" t="n">
         <v>36.3</v>
       </c>
-      <c r="D48" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E48" t="n">
-        <v>17</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H48" t="n">
+      <c r="X48" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AA48" t="n">
         <v>16</v>
       </c>
-      <c r="I48" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>25</v>
-      </c>
-      <c r="K48" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N48" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O48" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="V48" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W48" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X48" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AB48" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AC48" t="n">
-        <v>10.1</v>
+        <v>14.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AF48" t="n">
-        <v>229.19</v>
+        <v>233.68</v>
       </c>
       <c r="AG48" t="n">
-        <v>-5.75</v>
+        <v>-1.32</v>
       </c>
       <c r="AK48" t="n">
-        <v>138.98</v>
+        <v>136.95</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.47</v>
+        <v>0.34</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="BM48" t="n">
-        <v>19.88</v>
+        <v>23.7</v>
       </c>
       <c r="BN48" t="n">
-        <v>35.1</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="BO48" t="n">
         <v>0</v>
@@ -5303,46 +5444,46 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B49" t="n">
-        <v>120.3</v>
+        <v>113.4</v>
       </c>
       <c r="C49" t="n">
-        <v>53.3</v>
+        <v>40.9</v>
       </c>
       <c r="D49" t="n">
-        <v>36.3</v>
+        <v>34.8</v>
       </c>
       <c r="E49" t="n">
-        <v>20.6</v>
+        <v>27.9</v>
       </c>
       <c r="F49" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="H49" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I49" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J49" t="n">
-        <v>35.4</v>
+        <v>32.2</v>
       </c>
       <c r="K49" t="n">
-        <v>66</v>
+        <v>64.3</v>
       </c>
       <c r="M49" t="n">
         <v>1.9</v>
       </c>
       <c r="N49" t="n">
-        <v>24.8</v>
+        <v>27.3</v>
       </c>
       <c r="O49" t="n">
-        <v>26.7</v>
+        <v>29.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>18.3</v>
+        <v>20.3</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -5351,55 +5492,55 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>18.3</v>
+        <v>20.3</v>
       </c>
       <c r="V49" t="n">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="W49" t="n">
-        <v>22.5</v>
+        <v>32.8</v>
       </c>
       <c r="X49" t="n">
-        <v>20.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.699999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="Z49" t="n">
-        <v>16.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA49" t="n">
-        <v>13.8</v>
+        <v>17.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.5</v>
+        <v>13.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AF49" t="n">
-        <v>224.91</v>
+        <v>234.37</v>
       </c>
       <c r="AG49" t="n">
-        <v>-4.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AK49" t="n">
-        <v>134.04</v>
+        <v>136.49</v>
       </c>
       <c r="AL49" t="n">
-        <v>-4.94</v>
+        <v>-0.46</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="BM49" t="n">
-        <v>22.59</v>
+        <v>28.89</v>
       </c>
       <c r="BN49" t="n">
-        <v>48.3</v>
+        <v>152.3</v>
       </c>
       <c r="BO49" t="n">
         <v>0</v>
@@ -5410,46 +5551,46 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B50" t="n">
-        <v>131.1</v>
+        <v>115.6</v>
       </c>
       <c r="C50" t="n">
-        <v>60.2</v>
+        <v>43</v>
       </c>
       <c r="D50" t="n">
-        <v>35.6</v>
+        <v>36.1</v>
       </c>
       <c r="E50" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="F50" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="H50" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="I50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J50" t="n">
-        <v>38.2</v>
+        <v>36.7</v>
       </c>
       <c r="K50" t="n">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N50" t="n">
-        <v>30.2</v>
+        <v>27.8</v>
       </c>
       <c r="O50" t="n">
-        <v>31.9</v>
+        <v>29.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -5458,55 +5599,55 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="V50" t="n">
-        <v>14.1</v>
+        <v>17.8</v>
       </c>
       <c r="W50" t="n">
-        <v>20.2</v>
+        <v>22</v>
       </c>
       <c r="X50" t="n">
-        <v>17.1</v>
+        <v>19.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>4.9</v>
+        <v>13.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>12.5</v>
+        <v>19.9</v>
       </c>
       <c r="AA50" t="n">
-        <v>9.6</v>
+        <v>18.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0</v>
+        <v>0.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>220.83</v>
+        <v>237.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>-4.08</v>
+        <v>3.48</v>
       </c>
       <c r="AK50" t="n">
-        <v>131.01</v>
+        <v>137.25</v>
       </c>
       <c r="AL50" t="n">
-        <v>-3.03</v>
+        <v>0.76</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="BM50" t="n">
-        <v>29.62</v>
+        <v>25.43</v>
       </c>
       <c r="BN50" t="n">
-        <v>58.2</v>
+        <v>271.8</v>
       </c>
       <c r="BO50" t="n">
         <v>0</v>
@@ -5517,103 +5658,103 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B51" t="n">
-        <v>117.2</v>
+        <v>121.1</v>
       </c>
       <c r="C51" t="n">
-        <v>53.7</v>
+        <v>46.6</v>
       </c>
       <c r="D51" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="E51" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="F51" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="H51" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="I51" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J51" t="n">
-        <v>37</v>
+        <v>32.3</v>
       </c>
       <c r="K51" t="n">
-        <v>69.8</v>
+        <v>64.2</v>
       </c>
       <c r="M51" t="n">
         <v>1.9</v>
       </c>
       <c r="N51" t="n">
-        <v>31.4</v>
+        <v>25.2</v>
       </c>
       <c r="O51" t="n">
-        <v>33.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q51" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V51" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W51" t="n">
         <v>22.3</v>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V51" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>26.1</v>
-      </c>
       <c r="X51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z51" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA51" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="AC51" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>228.06</v>
+        <v>228.13</v>
       </c>
       <c r="AG51" t="n">
-        <v>7.23</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="AK51" t="n">
-        <v>131.96</v>
+        <v>136.92</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.95</v>
+        <v>-0.33</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="BM51" t="n">
-        <v>23.82</v>
+        <v>27.54</v>
       </c>
       <c r="BN51" t="n">
-        <v>49.9</v>
+        <v>447.8</v>
       </c>
       <c r="BO51" t="n">
         <v>0</v>
@@ -5624,46 +5765,46 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B52" t="n">
-        <v>112.8</v>
+        <v>122.3</v>
       </c>
       <c r="C52" t="n">
-        <v>42.7</v>
+        <v>47.9</v>
       </c>
       <c r="D52" t="n">
-        <v>34.6</v>
+        <v>36.3</v>
       </c>
       <c r="E52" t="n">
-        <v>20.7</v>
+        <v>27.12</v>
       </c>
       <c r="F52" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="H52" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="I52" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="J52" t="n">
-        <v>36.8</v>
+        <v>36</v>
       </c>
       <c r="K52" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N52" t="n">
+        <v>26</v>
+      </c>
+      <c r="O52" t="n">
         <v>27.9</v>
       </c>
-      <c r="O52" t="n">
-        <v>29.8</v>
-      </c>
       <c r="Q52" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5672,55 +5813,55 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="V52" t="n">
-        <v>11.9</v>
+        <v>14.7</v>
       </c>
       <c r="W52" t="n">
-        <v>31.2</v>
+        <v>18.6</v>
       </c>
       <c r="X52" t="n">
-        <v>21.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>21.4</v>
+        <v>14.6</v>
       </c>
       <c r="AA52" t="n">
-        <v>19.7</v>
+        <v>12.4</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>11.1</v>
+        <v>12.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AF52" t="n">
-        <v>233.59</v>
+        <v>224.64</v>
       </c>
       <c r="AG52" t="n">
-        <v>5.53</v>
+        <v>-3.49</v>
       </c>
       <c r="AK52" t="n">
-        <v>132.79</v>
+        <v>132.56</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.83</v>
+        <v>-4.36</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="BM52" t="n">
-        <v>23.43</v>
+        <v>28.03</v>
       </c>
       <c r="BN52" t="n">
-        <v>83.8</v>
+        <v>526.8</v>
       </c>
       <c r="BO52" t="n">
         <v>0</v>
@@ -5731,46 +5872,46 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B53" t="n">
-        <v>115.4</v>
+        <v>117.4</v>
       </c>
       <c r="C53" t="n">
-        <v>41.3</v>
+        <v>45.2</v>
       </c>
       <c r="D53" t="n">
-        <v>34.9</v>
+        <v>36.4</v>
       </c>
       <c r="E53" t="n">
-        <v>28.79</v>
+        <v>25.73</v>
       </c>
       <c r="F53" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H53" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>36</v>
       </c>
       <c r="K53" t="n">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="M53" t="n">
         <v>1.9</v>
       </c>
       <c r="N53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>26.9</v>
+        <v>27.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5779,105 +5920,54 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V53" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>231.92</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>136.54</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>3.75</v>
+        <v>22</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>25.29</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>0</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="B54" t="n">
-        <v>110.8</v>
+        <v>108.9</v>
       </c>
       <c r="C54" t="n">
         <v>39.3</v>
       </c>
       <c r="D54" t="n">
-        <v>34</v>
+        <v>35.3</v>
       </c>
       <c r="E54" t="n">
-        <v>27.23</v>
+        <v>24.44</v>
       </c>
       <c r="F54" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H54" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="M54" t="n">
         <v>1.9</v>
       </c>
       <c r="N54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>26.9</v>
+        <v>27.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5886,105 +5976,54 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>16</v>
-      </c>
-      <c r="V54" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X54" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>235</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>136.61</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.07000000000000001</v>
+        <v>18</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="BM54" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="BN54" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="BO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP54" t="n">
-        <v>0</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46292</v>
+        <v>46299</v>
       </c>
       <c r="B55" t="n">
-        <v>101</v>
+        <v>104.2</v>
       </c>
       <c r="C55" t="n">
-        <v>37</v>
+        <v>36.2</v>
       </c>
       <c r="D55" t="n">
-        <v>32.4</v>
+        <v>34.8</v>
       </c>
       <c r="E55" t="n">
-        <v>23.5</v>
+        <v>23.87</v>
       </c>
       <c r="F55" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="H55" t="n">
-        <v>17.9</v>
+        <v>22</v>
       </c>
       <c r="I55" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>29.9</v>
+        <v>36</v>
       </c>
       <c r="K55" t="n">
-        <v>56.9</v>
+        <v>67.7</v>
       </c>
       <c r="M55" t="n">
         <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>24.2</v>
+        <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>26.2</v>
+        <v>27.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5993,105 +6032,30 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>17</v>
-      </c>
-      <c r="V55" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W55" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>233.68</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>136.95</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0.34</v>
+        <v>18</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="B56" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="C56" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="D56" t="n">
-        <v>34.8</v>
+        <v>28.2</v>
       </c>
       <c r="E56" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H56" t="n">
-        <v>23</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>32.2</v>
+        <v>28.24</v>
       </c>
       <c r="K56" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>27.3</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
-        <v>29.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6100,105 +6064,30 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>234.37</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>-0.46</v>
+        <v>20.2</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>152.3</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="B57" t="n">
-        <v>115.6</v>
-      </c>
-      <c r="C57" t="n">
-        <v>43</v>
-      </c>
-      <c r="D57" t="n">
-        <v>36.1</v>
+        <v>28.5</v>
       </c>
       <c r="E57" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H57" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>36.7</v>
+        <v>28.52</v>
       </c>
       <c r="K57" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N57" t="n">
-        <v>27.8</v>
+        <v>5.8</v>
       </c>
       <c r="O57" t="n">
-        <v>29.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6207,105 +6096,30 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="V57" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="W57" t="n">
-        <v>22</v>
-      </c>
-      <c r="X57" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>237.85</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>137.25</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0.76</v>
+        <v>20.2</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>271.8</v>
-      </c>
-      <c r="BO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP57" t="n">
-        <v>0</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="B58" t="n">
-        <v>121.1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="D58" t="n">
-        <v>37</v>
+        <v>29.3</v>
       </c>
       <c r="E58" t="n">
-        <v>25</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H58" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" t="n">
-        <v>32.3</v>
+        <v>29.26</v>
       </c>
       <c r="K58" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25.2</v>
+        <v>6.4</v>
       </c>
       <c r="O58" t="n">
-        <v>27.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q58" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6314,105 +6128,30 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V58" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W58" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X58" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>228.13</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>136.92</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-0.33</v>
+        <v>20.2</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>27.54</v>
-      </c>
-      <c r="BN58" t="n">
-        <v>447.8</v>
-      </c>
-      <c r="BO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP58" t="n">
-        <v>0</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="B59" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="C59" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="D59" t="n">
-        <v>36.3</v>
+        <v>28.9</v>
       </c>
       <c r="E59" t="n">
-        <v>27.12</v>
-      </c>
-      <c r="F59" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H59" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J59" t="n">
-        <v>36</v>
+        <v>28.89</v>
       </c>
       <c r="K59" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N59" t="n">
-        <v>26</v>
+        <v>6.1</v>
       </c>
       <c r="O59" t="n">
-        <v>27.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6421,99 +6160,30 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>23</v>
-      </c>
-      <c r="V59" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W59" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X59" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>132.56</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>-4.36</v>
+        <v>20.2</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="BM59" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="BN59" t="n">
-        <v>526.8</v>
-      </c>
-      <c r="BO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP59" t="n">
-        <v>0</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="B60" t="n">
-        <v>117.4</v>
-      </c>
-      <c r="C60" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="D60" t="n">
-        <v>36.4</v>
+        <v>28.4</v>
       </c>
       <c r="E60" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>22</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J60" t="n">
-        <v>36</v>
+        <v>28.38</v>
       </c>
       <c r="K60" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N60" t="n">
-        <v>26</v>
+        <v>5.8</v>
       </c>
       <c r="O60" t="n">
-        <v>27.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6522,54 +6192,30 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="B61" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="C61" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="D61" t="n">
-        <v>35.3</v>
+        <v>22.1</v>
       </c>
       <c r="E61" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="F61" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H61" t="n">
-        <v>22</v>
-      </c>
-      <c r="I61" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J61" t="n">
-        <v>36</v>
+        <v>22.05</v>
       </c>
       <c r="K61" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N61" t="n">
-        <v>26</v>
+        <v>1.3</v>
       </c>
       <c r="O61" t="n">
-        <v>27.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6578,54 +6224,30 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>18</v>
+        <v>20.2</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="B62" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="C62" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="D62" t="n">
-        <v>34.8</v>
+        <v>21.1</v>
       </c>
       <c r="E62" t="n">
-        <v>23.87</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H62" t="n">
-        <v>22</v>
-      </c>
-      <c r="I62" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J62" t="n">
-        <v>36</v>
+        <v>21.05</v>
       </c>
       <c r="K62" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N62" t="n">
-        <v>26</v>
+        <v>0.6</v>
       </c>
       <c r="O62" t="n">
-        <v>27.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6634,10 +6256,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>18</v>
+        <v>20.2</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46299</v>
+        <v>46306</v>
       </c>
     </row>
   </sheetData>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
-      <c r="V2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -761,15 +752,6 @@
       <c r="T3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -847,15 +829,6 @@
       <c r="T4" t="n">
         <v>20.2</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -933,15 +906,6 @@
       <c r="T5" t="n">
         <v>20.2</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -1019,15 +983,6 @@
       <c r="T6" t="n">
         <v>20.2</v>
       </c>
-      <c r="V6" t="n">
-        <v>9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1126,15 +1081,6 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
-      <c r="V7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1233,15 +1179,6 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1340,15 +1277,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1447,15 +1375,6 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1533,15 +1452,6 @@
       <c r="T11" t="n">
         <v>20.2</v>
       </c>
-      <c r="V11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1619,15 +1529,6 @@
       <c r="T12" t="n">
         <v>20.2</v>
       </c>
-      <c r="V12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1726,15 +1627,6 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1833,15 +1725,6 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
-      <c r="V14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1940,15 +1823,6 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -2047,15 +1921,6 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
-      <c r="V16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2154,15 +2019,6 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2240,15 +2096,6 @@
       <c r="T18" t="n">
         <v>20.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2326,15 +2173,6 @@
       <c r="T19" t="n">
         <v>20.2</v>
       </c>
-      <c r="V19" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2433,15 +2271,6 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
-      <c r="V20" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2540,15 +2369,6 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
-      <c r="V21" t="n">
-        <v>12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X21" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2647,15 +2467,6 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
-      <c r="V22" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2754,15 +2565,6 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2861,15 +2663,6 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2947,15 +2740,6 @@
       <c r="T25" t="n">
         <v>20.2</v>
       </c>
-      <c r="V25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -3033,15 +2817,6 @@
       <c r="T26" t="n">
         <v>20.2</v>
       </c>
-      <c r="V26" t="n">
-        <v>11</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -3140,15 +2915,6 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3247,15 +3013,6 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
-      <c r="V28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3354,15 +3111,6 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>21</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3461,15 +3209,6 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W30" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3568,15 +3307,6 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
-      <c r="V31" t="n">
-        <v>11</v>
-      </c>
-      <c r="W31" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3675,15 +3405,6 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
-      <c r="V32" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>18</v>
-      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3782,15 +3503,6 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
-      <c r="V33" t="n">
-        <v>9</v>
-      </c>
-      <c r="W33" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3889,15 +3601,6 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
-      <c r="V34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3996,15 +3699,6 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W35" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -4103,15 +3797,6 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4210,15 +3895,6 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
-      <c r="V37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W37" t="n">
-        <v>26</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -4317,15 +3993,6 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
-      <c r="V38" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X38" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4424,15 +4091,6 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X39" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4531,15 +4189,6 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
-      <c r="V40" t="n">
-        <v>16</v>
-      </c>
-      <c r="W40" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X40" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4638,15 +4287,6 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
-      <c r="V41" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4745,15 +4385,6 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
-      <c r="V42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4852,15 +4483,6 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
-      <c r="V43" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4959,15 +4581,6 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -5066,15 +4679,6 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W45" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -5173,15 +4777,6 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
-      <c r="V46" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W46" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>25.6</v>
-      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -5280,24 +4875,6 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
-      <c r="V47" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X47" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>17.3</v>
-      </c>
       <c r="AB47" t="n">
         <v>5.8</v>
       </c>
@@ -5387,21 +4964,6 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
-      <c r="V48" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5494,21 +5056,6 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W49" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X49" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5601,21 +5148,6 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
-      <c r="V50" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5708,21 +5240,6 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
-      <c r="V51" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>17.6</v>
-      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5814,24 +5331,6 @@
       </c>
       <c r="T52" t="n">
         <v>23</v>
-      </c>
-      <c r="V52" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>12.4</v>
       </c>
       <c r="AB52" t="n">
         <v>0.6</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -752,6 +761,15 @@
       <c r="T3" t="n">
         <v>20.2</v>
       </c>
+      <c r="V3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -829,6 +847,15 @@
       <c r="T4" t="n">
         <v>20.2</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -906,6 +933,15 @@
       <c r="T5" t="n">
         <v>20.2</v>
       </c>
+      <c r="V5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -983,6 +1019,15 @@
       <c r="T6" t="n">
         <v>20.2</v>
       </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1081,6 +1126,15 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
+      <c r="V7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1179,6 +1233,15 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
+      <c r="V8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1277,6 +1340,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1375,6 +1447,15 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1452,6 +1533,15 @@
       <c r="T11" t="n">
         <v>20.2</v>
       </c>
+      <c r="V11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1529,6 +1619,15 @@
       <c r="T12" t="n">
         <v>20.2</v>
       </c>
+      <c r="V12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1627,6 +1726,15 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1725,6 +1833,15 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
+      <c r="V14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1823,6 +1940,15 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -1921,6 +2047,15 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
+      <c r="V16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2019,6 +2154,15 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
+      <c r="V17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2096,6 +2240,15 @@
       <c r="T18" t="n">
         <v>20.2</v>
       </c>
+      <c r="V18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2173,6 +2326,15 @@
       <c r="T19" t="n">
         <v>20.2</v>
       </c>
+      <c r="V19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2271,6 +2433,15 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
+      <c r="V20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2369,6 +2540,15 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
+      <c r="V21" t="n">
+        <v>12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2467,6 +2647,15 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
+      <c r="V22" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2565,6 +2754,15 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2663,6 +2861,15 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2740,6 +2947,15 @@
       <c r="T25" t="n">
         <v>20.2</v>
       </c>
+      <c r="V25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -2817,6 +3033,15 @@
       <c r="T26" t="n">
         <v>20.2</v>
       </c>
+      <c r="V26" t="n">
+        <v>11</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -2915,6 +3140,15 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3013,6 +3247,15 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
+      <c r="V28" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3111,6 +3354,15 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>21</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3209,6 +3461,15 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
+      <c r="V30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3307,6 +3568,15 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
+      <c r="V31" t="n">
+        <v>11</v>
+      </c>
+      <c r="W31" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3405,6 +3675,15 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
+      <c r="V32" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>18</v>
+      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3503,6 +3782,15 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
+      <c r="V33" t="n">
+        <v>9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3601,6 +3889,15 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
+      <c r="V34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3699,6 +3996,15 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -3797,6 +4103,15 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -3895,6 +4210,15 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
+      <c r="V37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>26</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -3993,6 +4317,15 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
+      <c r="V38" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4091,6 +4424,15 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4189,6 +4531,15 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
+      <c r="V40" t="n">
+        <v>16</v>
+      </c>
+      <c r="W40" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4287,6 +4638,15 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
+      <c r="V41" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4385,6 +4745,15 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
+      <c r="V42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4483,6 +4852,15 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
+      <c r="V43" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4581,6 +4959,15 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -4679,6 +5066,15 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -4777,6 +5173,15 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
+      <c r="V46" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>25.6</v>
+      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -4875,6 +5280,15 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
+      <c r="V47" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.7</v>
+      </c>
       <c r="AB47" t="n">
         <v>5.8</v>
       </c>
@@ -4964,6 +5378,15 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
+      <c r="V48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>27.9</v>
+      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5056,6 +5479,15 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X49" t="n">
+        <v>27.5</v>
+      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5148,6 +5580,15 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
+      <c r="V50" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5240,6 +5681,15 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
+      <c r="V51" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W51" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5331,6 +5781,15 @@
       </c>
       <c r="T52" t="n">
         <v>23</v>
+      </c>
+      <c r="V52" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.6</v>
       </c>
       <c r="AB52" t="n">
         <v>0.6</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5289,6 +5289,15 @@
       <c r="X47" t="n">
         <v>26.7</v>
       </c>
+      <c r="Y47" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>17.3</v>
+      </c>
       <c r="AB47" t="n">
         <v>5.8</v>
       </c>
@@ -5387,6 +5396,12 @@
       <c r="X48" t="n">
         <v>27.9</v>
       </c>
+      <c r="Y48" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5488,6 +5503,12 @@
       <c r="X49" t="n">
         <v>27.5</v>
       </c>
+      <c r="Y49" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5589,6 +5610,12 @@
       <c r="X50" t="n">
         <v>19.9</v>
       </c>
+      <c r="Y50" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5690,6 +5717,12 @@
       <c r="X51" t="n">
         <v>19.5</v>
       </c>
+      <c r="Y51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5791,6 +5824,15 @@
       <c r="X52" t="n">
         <v>16.6</v>
       </c>
+      <c r="Y52" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AB52" t="n">
         <v>0.6</v>
       </c>
@@ -5879,6 +5921,33 @@
       </c>
       <c r="T53" t="n">
         <v>22</v>
+      </c>
+      <c r="V53" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X53" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="BL53" s="1" t="n">
         <v>46297</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
-      <c r="V2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -761,15 +752,6 @@
       <c r="T3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -847,15 +829,6 @@
       <c r="T4" t="n">
         <v>20.2</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -933,15 +906,6 @@
       <c r="T5" t="n">
         <v>20.2</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -1019,15 +983,6 @@
       <c r="T6" t="n">
         <v>20.2</v>
       </c>
-      <c r="V6" t="n">
-        <v>9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1126,15 +1081,6 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
-      <c r="V7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1233,15 +1179,6 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1340,15 +1277,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1447,15 +1375,6 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1533,15 +1452,6 @@
       <c r="T11" t="n">
         <v>20.2</v>
       </c>
-      <c r="V11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1619,15 +1529,6 @@
       <c r="T12" t="n">
         <v>20.2</v>
       </c>
-      <c r="V12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1726,15 +1627,6 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1833,15 +1725,6 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
-      <c r="V14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1940,15 +1823,6 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -2047,15 +1921,6 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
-      <c r="V16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2154,15 +2019,6 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2240,15 +2096,6 @@
       <c r="T18" t="n">
         <v>20.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2326,15 +2173,6 @@
       <c r="T19" t="n">
         <v>20.2</v>
       </c>
-      <c r="V19" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2433,15 +2271,6 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
-      <c r="V20" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2540,15 +2369,6 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
-      <c r="V21" t="n">
-        <v>12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X21" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2647,15 +2467,6 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
-      <c r="V22" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2754,15 +2565,6 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2861,15 +2663,6 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2947,15 +2740,6 @@
       <c r="T25" t="n">
         <v>20.2</v>
       </c>
-      <c r="V25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -3033,15 +2817,6 @@
       <c r="T26" t="n">
         <v>20.2</v>
       </c>
-      <c r="V26" t="n">
-        <v>11</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -3140,15 +2915,6 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3247,15 +3013,6 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
-      <c r="V28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3354,15 +3111,6 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>21</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3461,15 +3209,6 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W30" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3568,15 +3307,6 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
-      <c r="V31" t="n">
-        <v>11</v>
-      </c>
-      <c r="W31" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3675,15 +3405,6 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
-      <c r="V32" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>18</v>
-      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3782,15 +3503,6 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
-      <c r="V33" t="n">
-        <v>9</v>
-      </c>
-      <c r="W33" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3889,15 +3601,6 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
-      <c r="V34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3996,15 +3699,6 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W35" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -4103,15 +3797,6 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4210,15 +3895,6 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
-      <c r="V37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W37" t="n">
-        <v>26</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -4317,15 +3993,6 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
-      <c r="V38" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X38" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4424,15 +4091,6 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X39" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4531,15 +4189,6 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
-      <c r="V40" t="n">
-        <v>16</v>
-      </c>
-      <c r="W40" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X40" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4638,15 +4287,6 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
-      <c r="V41" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4745,15 +4385,6 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
-      <c r="V42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4852,15 +4483,6 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
-      <c r="V43" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4959,15 +4581,6 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -5066,15 +4679,6 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W45" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -5173,15 +4777,6 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
-      <c r="V46" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W46" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>25.6</v>
-      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -5280,15 +4875,6 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
-      <c r="V47" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X47" t="n">
-        <v>26.7</v>
-      </c>
       <c r="Y47" t="n">
         <v>13.7</v>
       </c>
@@ -5387,21 +4973,6 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
-      <c r="V48" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5494,21 +5065,6 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W49" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X49" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5601,21 +5157,6 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
-      <c r="V50" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5708,21 +5249,6 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
-      <c r="V51" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>17.6</v>
-      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5815,24 +5341,6 @@
       <c r="T52" t="n">
         <v>23</v>
       </c>
-      <c r="V52" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>12.4</v>
-      </c>
       <c r="AB52" t="n">
         <v>0.6</v>
       </c>
@@ -5921,24 +5429,6 @@
       </c>
       <c r="T53" t="n">
         <v>22</v>
-      </c>
-      <c r="V53" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W53" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X53" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>11.9</v>
       </c>
       <c r="AB53" t="n">
         <v>3.9</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -752,6 +761,15 @@
       <c r="T3" t="n">
         <v>20.2</v>
       </c>
+      <c r="V3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -829,6 +847,15 @@
       <c r="T4" t="n">
         <v>20.2</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -906,6 +933,15 @@
       <c r="T5" t="n">
         <v>20.2</v>
       </c>
+      <c r="V5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -983,6 +1019,15 @@
       <c r="T6" t="n">
         <v>20.2</v>
       </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1081,6 +1126,15 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
+      <c r="V7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1179,6 +1233,15 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
+      <c r="V8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1277,6 +1340,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1375,6 +1447,15 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1452,6 +1533,15 @@
       <c r="T11" t="n">
         <v>20.2</v>
       </c>
+      <c r="V11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1529,6 +1619,15 @@
       <c r="T12" t="n">
         <v>20.2</v>
       </c>
+      <c r="V12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1627,6 +1726,15 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1725,6 +1833,15 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
+      <c r="V14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1823,6 +1940,15 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -1921,6 +2047,15 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
+      <c r="V16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2019,6 +2154,15 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
+      <c r="V17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2096,6 +2240,15 @@
       <c r="T18" t="n">
         <v>20.2</v>
       </c>
+      <c r="V18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2173,6 +2326,15 @@
       <c r="T19" t="n">
         <v>20.2</v>
       </c>
+      <c r="V19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2271,6 +2433,15 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
+      <c r="V20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2369,6 +2540,15 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
+      <c r="V21" t="n">
+        <v>12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2467,6 +2647,15 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
+      <c r="V22" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2565,6 +2754,15 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2663,6 +2861,15 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2740,6 +2947,15 @@
       <c r="T25" t="n">
         <v>20.2</v>
       </c>
+      <c r="V25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -2817,6 +3033,15 @@
       <c r="T26" t="n">
         <v>20.2</v>
       </c>
+      <c r="V26" t="n">
+        <v>11</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -2915,6 +3140,15 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3013,6 +3247,15 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
+      <c r="V28" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3111,6 +3354,15 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>21</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3209,6 +3461,15 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
+      <c r="V30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3307,6 +3568,15 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
+      <c r="V31" t="n">
+        <v>11</v>
+      </c>
+      <c r="W31" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3405,6 +3675,15 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
+      <c r="V32" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>18</v>
+      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3503,6 +3782,15 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
+      <c r="V33" t="n">
+        <v>9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3601,6 +3889,15 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
+      <c r="V34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3699,6 +3996,15 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -3797,6 +4103,15 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -3895,6 +4210,15 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
+      <c r="V37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>26</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -3993,6 +4317,15 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
+      <c r="V38" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4091,6 +4424,15 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4189,6 +4531,15 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
+      <c r="V40" t="n">
+        <v>16</v>
+      </c>
+      <c r="W40" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4287,6 +4638,15 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
+      <c r="V41" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4385,6 +4745,15 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
+      <c r="V42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4483,6 +4852,15 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
+      <c r="V43" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4581,6 +4959,15 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -4679,6 +5066,15 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -4777,6 +5173,15 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
+      <c r="V46" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>25.6</v>
+      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -4875,6 +5280,15 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
+      <c r="V47" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.7</v>
+      </c>
       <c r="Y47" t="n">
         <v>13.7</v>
       </c>
@@ -4973,6 +5387,21 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
+      <c r="V48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5065,6 +5494,21 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X49" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5157,6 +5601,21 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
+      <c r="V50" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5249,6 +5708,21 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
+      <c r="V51" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W51" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5341,6 +5815,24 @@
       <c r="T52" t="n">
         <v>23</v>
       </c>
+      <c r="V52" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AB52" t="n">
         <v>0.6</v>
       </c>
@@ -5429,6 +5921,24 @@
       </c>
       <c r="T53" t="n">
         <v>22</v>
+      </c>
+      <c r="V53" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X53" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>11.9</v>
       </c>
       <c r="AB53" t="n">
         <v>3.9</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -744,10 +744,10 @@
         <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>101</v>
+        <v>101.9</v>
       </c>
       <c r="O3" t="n">
-        <v>42.6</v>
+        <v>41.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V3" t="n">
         <v>6.3</v>
@@ -830,10 +830,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>95.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="O4" t="n">
-        <v>40.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
         <v>8.9</v>
@@ -916,10 +916,10 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>85.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>35.9</v>
+        <v>35.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
         <v>9.5</v>
@@ -1002,10 +1002,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="O6" t="n">
-        <v>33</v>
+        <v>32.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
         <v>9</v>
@@ -1516,10 +1516,10 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>92.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>39.2</v>
+        <v>38.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V11" t="n">
         <v>9.5</v>
@@ -1602,10 +1602,10 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>87</v>
+        <v>87.8</v>
       </c>
       <c r="O12" t="n">
-        <v>36.7</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V12" t="n">
         <v>10.7</v>
@@ -2223,10 +2223,10 @@
         <v>6.1</v>
       </c>
       <c r="K18" t="n">
-        <v>83</v>
+        <v>83.7</v>
       </c>
       <c r="O18" t="n">
-        <v>35</v>
+        <v>34.4</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -2309,10 +2309,10 @@
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>31.6</v>
+        <v>31</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V19" t="n">
         <v>12.6</v>
@@ -2930,10 +2930,10 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>78.8</v>
+        <v>79.5</v>
       </c>
       <c r="O25" t="n">
-        <v>33.2</v>
+        <v>32.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V25" t="n">
         <v>11.6</v>
@@ -3016,10 +3016,10 @@
         <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>82.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V26" t="n">
         <v>11</v>
@@ -5768,43 +5768,43 @@
         <v>46296</v>
       </c>
       <c r="B52" t="n">
-        <v>122.3</v>
+        <v>127</v>
       </c>
       <c r="C52" t="n">
-        <v>47.9</v>
+        <v>51.3</v>
       </c>
       <c r="D52" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="E52" t="n">
-        <v>27.12</v>
+        <v>23.5</v>
       </c>
       <c r="F52" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="H52" t="n">
-        <v>22.7</v>
+        <v>24.3</v>
       </c>
       <c r="I52" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
-        <v>36</v>
+        <v>38.8</v>
       </c>
       <c r="K52" t="n">
-        <v>67.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="N52" t="n">
-        <v>26</v>
+        <v>24.7</v>
       </c>
       <c r="O52" t="n">
-        <v>27.9</v>
+        <v>26.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="V52" t="n">
         <v>14.7</v>
@@ -5831,7 +5831,7 @@
         <v>14.6</v>
       </c>
       <c r="AA52" t="n">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="AB52" t="n">
         <v>0.6</v>
@@ -5875,31 +5875,31 @@
         <v>46297</v>
       </c>
       <c r="B53" t="n">
-        <v>117.4</v>
+        <v>122.4</v>
       </c>
       <c r="C53" t="n">
-        <v>45.2</v>
+        <v>50.7</v>
       </c>
       <c r="D53" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="E53" t="n">
         <v>25.73</v>
       </c>
       <c r="F53" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>22</v>
+        <v>23.6</v>
       </c>
       <c r="I53" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J53" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>67.7</v>
+        <v>70</v>
       </c>
       <c r="M53" t="n">
         <v>1.9</v>
@@ -5911,7 +5911,7 @@
         <v>27.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="V53" t="n">
         <v>14.3</v>
@@ -5941,13 +5941,25 @@
         <v>11.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AC53" t="n">
         <v>12.7</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>223.71</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>130.87</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>-1.69</v>
       </c>
       <c r="BL53" s="1" t="n">
         <v>46297</v>
@@ -5958,31 +5970,31 @@
         <v>46298</v>
       </c>
       <c r="B54" t="n">
-        <v>108.9</v>
+        <v>112</v>
       </c>
       <c r="C54" t="n">
-        <v>39.3</v>
+        <v>42.8</v>
       </c>
       <c r="D54" t="n">
-        <v>35.3</v>
+        <v>35</v>
       </c>
       <c r="E54" t="n">
         <v>24.44</v>
       </c>
       <c r="F54" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H54" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="I54" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J54" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K54" t="n">
-        <v>67.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M54" t="n">
         <v>1.9</v>
@@ -5994,7 +6006,7 @@
         <v>27.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -6003,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46298</v>
@@ -6014,31 +6026,31 @@
         <v>46299</v>
       </c>
       <c r="B55" t="n">
-        <v>104.2</v>
+        <v>105.4</v>
       </c>
       <c r="C55" t="n">
-        <v>36.2</v>
+        <v>37.9</v>
       </c>
       <c r="D55" t="n">
-        <v>34.8</v>
+        <v>34.4</v>
       </c>
       <c r="E55" t="n">
         <v>23.87</v>
       </c>
       <c r="F55" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H55" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="I55" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J55" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K55" t="n">
-        <v>67.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>1.9</v>
@@ -6050,7 +6062,7 @@
         <v>27.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6059,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46299</v>
@@ -6070,19 +6082,43 @@
         <v>46300</v>
       </c>
       <c r="B56" t="n">
-        <v>28.2</v>
+        <v>117.2</v>
+      </c>
+      <c r="C56" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>36.1</v>
       </c>
       <c r="E56" t="n">
         <v>28.24</v>
       </c>
+      <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>38</v>
+      </c>
       <c r="K56" t="n">
-        <v>5.6</v>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N56" t="n">
+        <v>27.5</v>
       </c>
       <c r="O56" t="n">
-        <v>2.4</v>
+        <v>29.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6091,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46300</v>
@@ -6102,19 +6138,43 @@
         <v>46301</v>
       </c>
       <c r="B57" t="n">
-        <v>28.5</v>
+        <v>118.3</v>
+      </c>
+      <c r="C57" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>36.3</v>
       </c>
       <c r="E57" t="n">
         <v>28.52</v>
       </c>
+      <c r="F57" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>38</v>
+      </c>
       <c r="K57" t="n">
-        <v>5.8</v>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>28</v>
       </c>
       <c r="O57" t="n">
-        <v>2.5</v>
+        <v>29.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6123,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46301</v>
@@ -6140,7 +6200,7 @@
         <v>29.26</v>
       </c>
       <c r="K58" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O58" t="n">
         <v>2.7</v>
@@ -6155,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46302</v>
@@ -6172,7 +6232,7 @@
         <v>28.89</v>
       </c>
       <c r="K59" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="O59" t="n">
         <v>2.6</v>
@@ -6187,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46303</v>
@@ -6204,7 +6264,7 @@
         <v>28.38</v>
       </c>
       <c r="K60" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O60" t="n">
         <v>2.4</v>
@@ -6219,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46304</v>
@@ -6236,7 +6296,7 @@
         <v>22.05</v>
       </c>
       <c r="K61" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O61" t="n">
         <v>0.6</v>
@@ -6251,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46305</v>
@@ -6268,7 +6328,7 @@
         <v>21.05</v>
       </c>
       <c r="K62" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="O62" t="n">
         <v>0.3</v>
@@ -6283,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46306</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
-      <c r="V2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -695,15 +686,6 @@
       </c>
       <c r="AA2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
         <v>217.16</v>
@@ -761,15 +743,6 @@
       <c r="T3" t="n">
         <v>20.1</v>
       </c>
-      <c r="V3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -778,15 +751,6 @@
       </c>
       <c r="AA3" t="n">
         <v>10</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
         <v>220.31</v>
@@ -847,15 +811,6 @@
       <c r="T4" t="n">
         <v>20.1</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -864,15 +819,6 @@
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.5</v>
       </c>
       <c r="AF4" t="n">
         <v>221.99</v>
@@ -933,15 +879,6 @@
       <c r="T5" t="n">
         <v>20.1</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -950,15 +887,6 @@
       </c>
       <c r="AA5" t="n">
         <v>14</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.9</v>
       </c>
       <c r="AF5" t="n">
         <v>225.14</v>
@@ -1019,15 +947,6 @@
       <c r="T6" t="n">
         <v>20.1</v>
       </c>
-      <c r="V6" t="n">
-        <v>9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1036,15 +955,6 @@
       </c>
       <c r="AA6" t="n">
         <v>15</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.4</v>
       </c>
       <c r="AF6" t="n">
         <v>229.98</v>
@@ -1126,15 +1036,6 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
-      <c r="V7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1143,15 +1044,6 @@
       </c>
       <c r="AA7" t="n">
         <v>13</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.6</v>
       </c>
       <c r="AF7" t="n">
         <v>229.96</v>
@@ -1233,15 +1125,6 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1250,15 +1133,6 @@
       </c>
       <c r="AA8" t="n">
         <v>10</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4.4</v>
       </c>
       <c r="AF8" t="n">
         <v>227.01</v>
@@ -1340,15 +1214,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1357,15 +1222,6 @@
       </c>
       <c r="AA9" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6.5</v>
       </c>
       <c r="AF9" t="n">
         <v>228.35</v>
@@ -1447,15 +1303,6 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1464,15 +1311,6 @@
       </c>
       <c r="AA10" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.8</v>
       </c>
       <c r="AF10" t="n">
         <v>231.16</v>
@@ -1533,15 +1371,6 @@
       <c r="T11" t="n">
         <v>20.1</v>
       </c>
-      <c r="V11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1550,15 +1379,6 @@
       </c>
       <c r="AA11" t="n">
         <v>9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.8</v>
       </c>
       <c r="AF11" t="n">
         <v>228.13</v>
@@ -1619,15 +1439,6 @@
       <c r="T12" t="n">
         <v>20.1</v>
       </c>
-      <c r="V12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1636,15 +1447,6 @@
       </c>
       <c r="AA12" t="n">
         <v>9</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>229.16</v>
@@ -1726,15 +1528,6 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1743,15 +1536,6 @@
       </c>
       <c r="AA13" t="n">
         <v>8.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
       </c>
       <c r="AF13" t="n">
         <v>228.55</v>
@@ -1833,15 +1617,6 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
-      <c r="V14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1850,15 +1625,6 @@
       </c>
       <c r="AA14" t="n">
         <v>10</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.8</v>
       </c>
       <c r="AF14" t="n">
         <v>219.99</v>
@@ -1940,15 +1706,6 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -1957,15 +1714,6 @@
       </c>
       <c r="AA15" t="n">
         <v>11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.5</v>
       </c>
       <c r="AF15" t="n">
         <v>219.22</v>
@@ -2047,15 +1795,6 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
-      <c r="V16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2064,15 +1803,6 @@
       </c>
       <c r="AA16" t="n">
         <v>14</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.7</v>
       </c>
       <c r="AF16" t="n">
         <v>220.73</v>
@@ -2154,15 +1884,6 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2171,15 +1892,6 @@
       </c>
       <c r="AA17" t="n">
         <v>14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.7</v>
       </c>
       <c r="AF17" t="n">
         <v>220.58</v>
@@ -2240,15 +1952,6 @@
       <c r="T18" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2257,15 +1960,6 @@
       </c>
       <c r="AA18" t="n">
         <v>13</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.5</v>
       </c>
       <c r="AF18" t="n">
         <v>223.43</v>
@@ -2326,15 +2020,6 @@
       <c r="T19" t="n">
         <v>20.1</v>
       </c>
-      <c r="V19" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2343,15 +2028,6 @@
       </c>
       <c r="AA19" t="n">
         <v>13</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.4</v>
       </c>
       <c r="AF19" t="n">
         <v>229.48</v>
@@ -2433,15 +2109,6 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
-      <c r="V20" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2450,15 +2117,6 @@
       </c>
       <c r="AA20" t="n">
         <v>14</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>241.48</v>
@@ -2540,15 +2198,6 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
-      <c r="V21" t="n">
-        <v>12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X21" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2557,15 +2206,6 @@
       </c>
       <c r="AA21" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.9</v>
       </c>
       <c r="AF21" t="n">
         <v>238.69</v>
@@ -2647,15 +2287,6 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
-      <c r="V22" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2664,15 +2295,6 @@
       </c>
       <c r="AA22" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
         <v>233.48</v>
@@ -2754,15 +2376,6 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2771,15 +2384,6 @@
       </c>
       <c r="AA23" t="n">
         <v>17</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.6</v>
       </c>
       <c r="AF23" t="n">
         <v>235.13</v>
@@ -2861,15 +2465,6 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2878,15 +2473,6 @@
       </c>
       <c r="AA24" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF24" t="n">
         <v>234.87</v>
@@ -2947,15 +2533,6 @@
       <c r="T25" t="n">
         <v>20.1</v>
       </c>
-      <c r="V25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -2964,15 +2541,6 @@
       </c>
       <c r="AA25" t="n">
         <v>13</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.2</v>
       </c>
       <c r="AF25" t="n">
         <v>234.78</v>
@@ -3033,15 +2601,6 @@
       <c r="T26" t="n">
         <v>20.1</v>
       </c>
-      <c r="V26" t="n">
-        <v>11</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -3050,15 +2609,6 @@
       </c>
       <c r="AA26" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.75</v>
@@ -3140,15 +2690,6 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3157,15 +2698,6 @@
       </c>
       <c r="AA27" t="n">
         <v>6.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.5</v>
       </c>
       <c r="AF27" t="n">
         <v>222.86</v>
@@ -3247,15 +2779,6 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
-      <c r="V28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3264,15 +2787,6 @@
       </c>
       <c r="AA28" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.3</v>
       </c>
       <c r="AF28" t="n">
         <v>218.37</v>
@@ -3354,15 +2868,6 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>21</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3371,15 +2876,6 @@
       </c>
       <c r="AA29" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.9</v>
       </c>
       <c r="AF29" t="n">
         <v>220.85</v>
@@ -3461,15 +2957,6 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W30" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3478,15 +2965,6 @@
       </c>
       <c r="AA30" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>6.3</v>
       </c>
       <c r="AF30" t="n">
         <v>225.87</v>
@@ -3568,15 +3046,6 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
-      <c r="V31" t="n">
-        <v>11</v>
-      </c>
-      <c r="W31" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3585,15 +3054,6 @@
       </c>
       <c r="AA31" t="n">
         <v>16.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.5</v>
       </c>
       <c r="AF31" t="n">
         <v>229.48</v>
@@ -3675,15 +3135,6 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
-      <c r="V32" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>18</v>
-      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3692,15 +3143,6 @@
       </c>
       <c r="AA32" t="n">
         <v>15.1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>-0.1</v>
       </c>
       <c r="AF32" t="n">
         <v>230.54</v>
@@ -3782,15 +3224,6 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
-      <c r="V33" t="n">
-        <v>9</v>
-      </c>
-      <c r="W33" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3799,15 +3232,6 @@
       </c>
       <c r="AA33" t="n">
         <v>10.3</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.8</v>
       </c>
       <c r="AF33" t="n">
         <v>224.23</v>
@@ -3889,15 +3313,6 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
-      <c r="V34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3906,15 +3321,6 @@
       </c>
       <c r="AA34" t="n">
         <v>7.9</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>5.7</v>
       </c>
       <c r="AF34" t="n">
         <v>223.36</v>
@@ -3996,15 +3402,6 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W35" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -4013,15 +3410,6 @@
       </c>
       <c r="AA35" t="n">
         <v>12</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>5.8</v>
       </c>
       <c r="AF35" t="n">
         <v>222.92</v>
@@ -4103,15 +3491,6 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4120,15 +3499,6 @@
       </c>
       <c r="AA36" t="n">
         <v>12.9</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>6.7</v>
       </c>
       <c r="AF36" t="n">
         <v>222.77</v>
@@ -4210,15 +3580,6 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
-      <c r="V37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W37" t="n">
-        <v>26</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -4227,15 +3588,6 @@
       </c>
       <c r="AA37" t="n">
         <v>11.6</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>7.8</v>
       </c>
       <c r="AF37" t="n">
         <v>221.86</v>
@@ -4317,15 +3669,6 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
-      <c r="V38" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X38" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4334,15 +3677,6 @@
       </c>
       <c r="AA38" t="n">
         <v>18.8</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>8.699999999999999</v>
       </c>
       <c r="AF38" t="n">
         <v>227.49</v>
@@ -4424,15 +3758,6 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X39" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4441,15 +3766,6 @@
       </c>
       <c r="AA39" t="n">
         <v>17.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AF39" t="n">
         <v>233.56</v>
@@ -4531,15 +3847,6 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
-      <c r="V40" t="n">
-        <v>16</v>
-      </c>
-      <c r="W40" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X40" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4548,15 +3855,6 @@
       </c>
       <c r="AA40" t="n">
         <v>18.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>12.8</v>
       </c>
       <c r="AF40" t="n">
         <v>234.94</v>
@@ -4638,15 +3936,6 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
-      <c r="V41" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4655,15 +3944,6 @@
       </c>
       <c r="AA41" t="n">
         <v>16.9</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>7</v>
       </c>
       <c r="AF41" t="n">
         <v>229.19</v>
@@ -4745,15 +4025,6 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
-      <c r="V42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4762,15 +4033,6 @@
       </c>
       <c r="AA42" t="n">
         <v>13.8</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.4</v>
       </c>
       <c r="AF42" t="n">
         <v>224.91</v>
@@ -4852,15 +4114,6 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
-      <c r="V43" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4869,15 +4122,6 @@
       </c>
       <c r="AA43" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4.8</v>
       </c>
       <c r="AF43" t="n">
         <v>220.83</v>
@@ -4959,15 +4203,6 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -4976,15 +4211,6 @@
       </c>
       <c r="AA44" t="n">
         <v>14</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>9.1</v>
       </c>
       <c r="AF44" t="n">
         <v>228.06</v>
@@ -5066,15 +4292,6 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W45" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -5083,15 +4300,6 @@
       </c>
       <c r="AA45" t="n">
         <v>19.7</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>8.1</v>
       </c>
       <c r="AF45" t="n">
         <v>233.59</v>
@@ -5173,15 +4381,6 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
-      <c r="V46" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W46" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>25.6</v>
-      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -5190,15 +4389,6 @@
       </c>
       <c r="AA46" t="n">
         <v>21.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>7.3</v>
       </c>
       <c r="AF46" t="n">
         <v>231.92</v>
@@ -5280,15 +4470,6 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
-      <c r="V47" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X47" t="n">
-        <v>26.7</v>
-      </c>
       <c r="Y47" t="n">
         <v>13.7</v>
       </c>
@@ -5297,15 +4478,6 @@
       </c>
       <c r="AA47" t="n">
         <v>17.3</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>9.4</v>
       </c>
       <c r="AF47" t="n">
         <v>235</v>
@@ -5387,15 +4559,6 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
-      <c r="V48" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>27.9</v>
-      </c>
       <c r="Y48" t="n">
         <v>13.6</v>
       </c>
@@ -5404,15 +4567,6 @@
       </c>
       <c r="AA48" t="n">
         <v>16</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AF48" t="n">
         <v>233.68</v>
@@ -5494,15 +4648,6 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W49" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X49" t="n">
-        <v>27.5</v>
-      </c>
       <c r="Y49" t="n">
         <v>14.2</v>
       </c>
@@ -5511,15 +4656,6 @@
       </c>
       <c r="AA49" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>7.4</v>
       </c>
       <c r="AF49" t="n">
         <v>234.37</v>
@@ -5601,15 +4737,6 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
-      <c r="V50" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y50" t="n">
         <v>13.4</v>
       </c>
@@ -5618,15 +4745,6 @@
       </c>
       <c r="AA50" t="n">
         <v>18.2</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>6.2</v>
       </c>
       <c r="AF50" t="n">
         <v>237.85</v>
@@ -5708,15 +4826,6 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
-      <c r="V51" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y51" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -5725,15 +4834,6 @@
       </c>
       <c r="AA51" t="n">
         <v>14.3</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>7.6</v>
       </c>
       <c r="AF51" t="n">
         <v>228.13</v>
@@ -5815,15 +4915,6 @@
       <c r="T52" t="n">
         <v>20.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y52" t="n">
         <v>10.2</v>
       </c>
@@ -5832,15 +4923,6 @@
       </c>
       <c r="AA52" t="n">
         <v>14.3</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>6.6</v>
       </c>
       <c r="AF52" t="n">
         <v>224.64</v>
@@ -5922,15 +5004,6 @@
       <c r="T53" t="n">
         <v>20.5</v>
       </c>
-      <c r="V53" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W53" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X53" t="n">
-        <v>18.6</v>
-      </c>
       <c r="Y53" t="n">
         <v>7.4</v>
       </c>
@@ -5939,15 +5012,6 @@
       </c>
       <c r="AA53" t="n">
         <v>11.9</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>8.6</v>
       </c>
       <c r="AF53" t="n">
         <v>223.71</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -686,6 +695,15 @@
       </c>
       <c r="AA2" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
         <v>217.16</v>
@@ -743,6 +761,15 @@
       <c r="T3" t="n">
         <v>20.1</v>
       </c>
+      <c r="V3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -751,6 +778,15 @@
       </c>
       <c r="AA3" t="n">
         <v>10</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
         <v>220.31</v>
@@ -811,6 +847,15 @@
       <c r="T4" t="n">
         <v>20.1</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -819,6 +864,15 @@
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.5</v>
       </c>
       <c r="AF4" t="n">
         <v>221.99</v>
@@ -879,6 +933,15 @@
       <c r="T5" t="n">
         <v>20.1</v>
       </c>
+      <c r="V5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -887,6 +950,15 @@
       </c>
       <c r="AA5" t="n">
         <v>14</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF5" t="n">
         <v>225.14</v>
@@ -947,6 +1019,15 @@
       <c r="T6" t="n">
         <v>20.1</v>
       </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -955,6 +1036,15 @@
       </c>
       <c r="AA6" t="n">
         <v>15</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF6" t="n">
         <v>229.98</v>
@@ -1036,6 +1126,15 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
+      <c r="V7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1044,6 +1143,15 @@
       </c>
       <c r="AA7" t="n">
         <v>13</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AF7" t="n">
         <v>229.96</v>
@@ -1125,6 +1233,15 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
+      <c r="V8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1133,6 +1250,15 @@
       </c>
       <c r="AA8" t="n">
         <v>10</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.4</v>
       </c>
       <c r="AF8" t="n">
         <v>227.01</v>
@@ -1214,6 +1340,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1222,6 +1357,15 @@
       </c>
       <c r="AA9" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.5</v>
       </c>
       <c r="AF9" t="n">
         <v>228.35</v>
@@ -1303,6 +1447,15 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1311,6 +1464,15 @@
       </c>
       <c r="AA10" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF10" t="n">
         <v>231.16</v>
@@ -1371,6 +1533,15 @@
       <c r="T11" t="n">
         <v>20.1</v>
       </c>
+      <c r="V11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1379,6 +1550,15 @@
       </c>
       <c r="AA11" t="n">
         <v>9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF11" t="n">
         <v>228.13</v>
@@ -1439,6 +1619,15 @@
       <c r="T12" t="n">
         <v>20.1</v>
       </c>
+      <c r="V12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1447,6 +1636,15 @@
       </c>
       <c r="AA12" t="n">
         <v>9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>229.16</v>
@@ -1528,6 +1726,15 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1536,6 +1743,15 @@
       </c>
       <c r="AA13" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF13" t="n">
         <v>228.55</v>
@@ -1617,6 +1833,15 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
+      <c r="V14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1625,6 +1850,15 @@
       </c>
       <c r="AA14" t="n">
         <v>10</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF14" t="n">
         <v>219.99</v>
@@ -1706,6 +1940,15 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -1714,6 +1957,15 @@
       </c>
       <c r="AA15" t="n">
         <v>11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF15" t="n">
         <v>219.22</v>
@@ -1795,6 +2047,15 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
+      <c r="V16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -1803,6 +2064,15 @@
       </c>
       <c r="AA16" t="n">
         <v>14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF16" t="n">
         <v>220.73</v>
@@ -1884,6 +2154,15 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
+      <c r="V17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -1892,6 +2171,15 @@
       </c>
       <c r="AA17" t="n">
         <v>14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF17" t="n">
         <v>220.58</v>
@@ -1952,6 +2240,15 @@
       <c r="T18" t="n">
         <v>20.1</v>
       </c>
+      <c r="V18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -1960,6 +2257,15 @@
       </c>
       <c r="AA18" t="n">
         <v>13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF18" t="n">
         <v>223.43</v>
@@ -2020,6 +2326,15 @@
       <c r="T19" t="n">
         <v>20.1</v>
       </c>
+      <c r="V19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2028,6 +2343,15 @@
       </c>
       <c r="AA19" t="n">
         <v>13</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF19" t="n">
         <v>229.48</v>
@@ -2109,6 +2433,15 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
+      <c r="V20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2117,6 +2450,15 @@
       </c>
       <c r="AA20" t="n">
         <v>14</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>241.48</v>
@@ -2198,6 +2540,15 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
+      <c r="V21" t="n">
+        <v>12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2206,6 +2557,15 @@
       </c>
       <c r="AA21" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF21" t="n">
         <v>238.69</v>
@@ -2287,6 +2647,15 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
+      <c r="V22" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2295,6 +2664,15 @@
       </c>
       <c r="AA22" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
         <v>233.48</v>
@@ -2376,6 +2754,15 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2384,6 +2771,15 @@
       </c>
       <c r="AA23" t="n">
         <v>17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF23" t="n">
         <v>235.13</v>
@@ -2465,6 +2861,15 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2473,6 +2878,15 @@
       </c>
       <c r="AA24" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF24" t="n">
         <v>234.87</v>
@@ -2533,6 +2947,15 @@
       <c r="T25" t="n">
         <v>20.1</v>
       </c>
+      <c r="V25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -2541,6 +2964,15 @@
       </c>
       <c r="AA25" t="n">
         <v>13</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.2</v>
       </c>
       <c r="AF25" t="n">
         <v>234.78</v>
@@ -2601,6 +3033,15 @@
       <c r="T26" t="n">
         <v>20.1</v>
       </c>
+      <c r="V26" t="n">
+        <v>11</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -2609,6 +3050,15 @@
       </c>
       <c r="AA26" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF26" t="n">
         <v>229.75</v>
@@ -2690,6 +3140,15 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -2698,6 +3157,15 @@
       </c>
       <c r="AA27" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF27" t="n">
         <v>222.86</v>
@@ -2779,6 +3247,15 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
+      <c r="V28" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -2787,6 +3264,15 @@
       </c>
       <c r="AA28" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF28" t="n">
         <v>218.37</v>
@@ -2868,6 +3354,15 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>21</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -2876,6 +3371,15 @@
       </c>
       <c r="AA29" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF29" t="n">
         <v>220.85</v>
@@ -2957,6 +3461,15 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
+      <c r="V30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -2965,6 +3478,15 @@
       </c>
       <c r="AA30" t="n">
         <v>14.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>6.3</v>
       </c>
       <c r="AF30" t="n">
         <v>225.87</v>
@@ -3046,6 +3568,15 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
+      <c r="V31" t="n">
+        <v>11</v>
+      </c>
+      <c r="W31" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3054,6 +3585,15 @@
       </c>
       <c r="AA31" t="n">
         <v>16.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF31" t="n">
         <v>229.48</v>
@@ -3135,6 +3675,15 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
+      <c r="V32" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>18</v>
+      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3143,6 +3692,15 @@
       </c>
       <c r="AA32" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF32" t="n">
         <v>230.54</v>
@@ -3224,6 +3782,15 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
+      <c r="V33" t="n">
+        <v>9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3232,6 +3799,15 @@
       </c>
       <c r="AA33" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8</v>
       </c>
       <c r="AF33" t="n">
         <v>224.23</v>
@@ -3313,6 +3889,15 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
+      <c r="V34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3321,6 +3906,15 @@
       </c>
       <c r="AA34" t="n">
         <v>7.9</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF34" t="n">
         <v>223.36</v>
@@ -3402,6 +3996,15 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -3410,6 +4013,15 @@
       </c>
       <c r="AA35" t="n">
         <v>12</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.8</v>
       </c>
       <c r="AF35" t="n">
         <v>222.92</v>
@@ -3491,6 +4103,15 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -3499,6 +4120,15 @@
       </c>
       <c r="AA36" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF36" t="n">
         <v>222.77</v>
@@ -3580,6 +4210,15 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
+      <c r="V37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>26</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -3588,6 +4227,15 @@
       </c>
       <c r="AA37" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7.8</v>
       </c>
       <c r="AF37" t="n">
         <v>221.86</v>
@@ -3669,6 +4317,15 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
+      <c r="V38" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -3677,6 +4334,15 @@
       </c>
       <c r="AA38" t="n">
         <v>18.8</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AF38" t="n">
         <v>227.49</v>
@@ -3758,6 +4424,15 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -3766,6 +4441,15 @@
       </c>
       <c r="AA39" t="n">
         <v>17.2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AF39" t="n">
         <v>233.56</v>
@@ -3847,6 +4531,15 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
+      <c r="V40" t="n">
+        <v>16</v>
+      </c>
+      <c r="W40" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -3855,6 +4548,15 @@
       </c>
       <c r="AA40" t="n">
         <v>18.1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>12.8</v>
       </c>
       <c r="AF40" t="n">
         <v>234.94</v>
@@ -3936,6 +4638,15 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
+      <c r="V41" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -3944,6 +4655,15 @@
       </c>
       <c r="AA41" t="n">
         <v>16.9</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7</v>
       </c>
       <c r="AF41" t="n">
         <v>229.19</v>
@@ -4025,6 +4745,15 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
+      <c r="V42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4033,6 +4762,15 @@
       </c>
       <c r="AA42" t="n">
         <v>13.8</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.4</v>
       </c>
       <c r="AF42" t="n">
         <v>224.91</v>
@@ -4114,6 +4852,15 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
+      <c r="V43" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4122,6 +4869,15 @@
       </c>
       <c r="AA43" t="n">
         <v>9.6</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF43" t="n">
         <v>220.83</v>
@@ -4203,6 +4959,15 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -4211,6 +4976,15 @@
       </c>
       <c r="AA44" t="n">
         <v>14</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>9.1</v>
       </c>
       <c r="AF44" t="n">
         <v>228.06</v>
@@ -4292,6 +5066,15 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -4300,6 +5083,15 @@
       </c>
       <c r="AA45" t="n">
         <v>19.7</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.1</v>
       </c>
       <c r="AF45" t="n">
         <v>233.59</v>
@@ -4381,6 +5173,15 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
+      <c r="V46" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>25.6</v>
+      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -4389,6 +5190,15 @@
       </c>
       <c r="AA46" t="n">
         <v>21.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>7.3</v>
       </c>
       <c r="AF46" t="n">
         <v>231.92</v>
@@ -4470,6 +5280,15 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
+      <c r="V47" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.7</v>
+      </c>
       <c r="Y47" t="n">
         <v>13.7</v>
       </c>
@@ -4478,6 +5297,15 @@
       </c>
       <c r="AA47" t="n">
         <v>17.3</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>9.4</v>
       </c>
       <c r="AF47" t="n">
         <v>235</v>
@@ -4559,6 +5387,15 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
+      <c r="V48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>27.9</v>
+      </c>
       <c r="Y48" t="n">
         <v>13.6</v>
       </c>
@@ -4567,6 +5404,15 @@
       </c>
       <c r="AA48" t="n">
         <v>16</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="AF48" t="n">
         <v>233.68</v>
@@ -4648,6 +5494,15 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X49" t="n">
+        <v>27.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>14.2</v>
       </c>
@@ -4656,6 +5511,15 @@
       </c>
       <c r="AA49" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>7.4</v>
       </c>
       <c r="AF49" t="n">
         <v>234.37</v>
@@ -4737,6 +5601,15 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
+      <c r="V50" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y50" t="n">
         <v>13.4</v>
       </c>
@@ -4745,6 +5618,15 @@
       </c>
       <c r="AA50" t="n">
         <v>18.2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF50" t="n">
         <v>237.85</v>
@@ -4826,6 +5708,15 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
+      <c r="V51" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W51" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y51" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -4834,6 +5725,15 @@
       </c>
       <c r="AA51" t="n">
         <v>14.3</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>7.6</v>
       </c>
       <c r="AF51" t="n">
         <v>228.13</v>
@@ -4915,6 +5815,15 @@
       <c r="T52" t="n">
         <v>20.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y52" t="n">
         <v>10.2</v>
       </c>
@@ -4923,6 +5832,15 @@
       </c>
       <c r="AA52" t="n">
         <v>14.3</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>6.6</v>
       </c>
       <c r="AF52" t="n">
         <v>224.64</v>
@@ -5004,6 +5922,15 @@
       <c r="T53" t="n">
         <v>20.5</v>
       </c>
+      <c r="V53" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X53" t="n">
+        <v>18.6</v>
+      </c>
       <c r="Y53" t="n">
         <v>7.4</v>
       </c>
@@ -5012,6 +5939,15 @@
       </c>
       <c r="AA53" t="n">
         <v>11.9</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>8.6</v>
       </c>
       <c r="AF53" t="n">
         <v>223.71</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
-      <c r="V2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -761,15 +752,6 @@
       <c r="T3" t="n">
         <v>20.1</v>
       </c>
-      <c r="V3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -847,15 +829,6 @@
       <c r="T4" t="n">
         <v>20.1</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -933,15 +906,6 @@
       <c r="T5" t="n">
         <v>20.1</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -1019,15 +983,6 @@
       <c r="T6" t="n">
         <v>20.1</v>
       </c>
-      <c r="V6" t="n">
-        <v>9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1126,15 +1081,6 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
-      <c r="V7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1233,15 +1179,6 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1340,15 +1277,6 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1447,15 +1375,6 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1533,15 +1452,6 @@
       <c r="T11" t="n">
         <v>20.1</v>
       </c>
-      <c r="V11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1619,15 +1529,6 @@
       <c r="T12" t="n">
         <v>20.1</v>
       </c>
-      <c r="V12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1726,15 +1627,6 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1833,15 +1725,6 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
-      <c r="V14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1940,15 +1823,6 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
-      <c r="V15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -2047,15 +1921,6 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
-      <c r="V16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2154,15 +2019,6 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2240,15 +2096,6 @@
       <c r="T18" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2326,15 +2173,6 @@
       <c r="T19" t="n">
         <v>20.1</v>
       </c>
-      <c r="V19" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2433,15 +2271,6 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
-      <c r="V20" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2540,15 +2369,6 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
-      <c r="V21" t="n">
-        <v>12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X21" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2647,15 +2467,6 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
-      <c r="V22" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2754,15 +2565,6 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2861,15 +2663,6 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
-      <c r="V24" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2947,15 +2740,6 @@
       <c r="T25" t="n">
         <v>20.1</v>
       </c>
-      <c r="V25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -3033,15 +2817,6 @@
       <c r="T26" t="n">
         <v>20.1</v>
       </c>
-      <c r="V26" t="n">
-        <v>11</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -3140,15 +2915,6 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
-      <c r="V27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3247,15 +3013,6 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
-      <c r="V28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3354,15 +3111,6 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
-      <c r="V29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>21</v>
-      </c>
-      <c r="X29" t="n">
-        <v>13.2</v>
-      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3461,15 +3209,6 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W30" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>16.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3568,15 +3307,6 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
-      <c r="V31" t="n">
-        <v>11</v>
-      </c>
-      <c r="W31" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X31" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3675,15 +3405,6 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
-      <c r="V32" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>18</v>
-      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3782,15 +3503,6 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
-      <c r="V33" t="n">
-        <v>9</v>
-      </c>
-      <c r="W33" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3889,15 +3601,6 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
-      <c r="V34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3996,15 +3699,6 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W35" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -4103,15 +3797,6 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -4210,15 +3895,6 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
-      <c r="V37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W37" t="n">
-        <v>26</v>
-      </c>
-      <c r="X37" t="n">
-        <v>16.9</v>
-      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -4317,15 +3993,6 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
-      <c r="V38" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X38" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4424,15 +4091,6 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
-      <c r="V39" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="X39" t="n">
-        <v>20.9</v>
-      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4531,15 +4189,6 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
-      <c r="V40" t="n">
-        <v>16</v>
-      </c>
-      <c r="W40" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="X40" t="n">
-        <v>23.3</v>
-      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4638,15 +4287,6 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
-      <c r="V41" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>24.7</v>
-      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4745,15 +4385,6 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
-      <c r="V42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>20.5</v>
-      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4852,15 +4483,6 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
-      <c r="V43" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>17.1</v>
-      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4959,15 +4581,6 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>17.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -5066,15 +4679,6 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
-      <c r="V45" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W45" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="X45" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -5173,15 +4777,6 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
-      <c r="V46" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W46" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>25.6</v>
-      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -5280,15 +4875,6 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
-      <c r="V47" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X47" t="n">
-        <v>26.7</v>
-      </c>
       <c r="Y47" t="n">
         <v>13.7</v>
       </c>
@@ -5387,21 +4973,6 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
-      <c r="V48" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5494,21 +5065,6 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W49" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="X49" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>19.3</v>
-      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5601,21 +5157,6 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
-      <c r="V50" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5708,21 +5249,6 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
-      <c r="V51" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>17.6</v>
-      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5815,21 +5341,6 @@
       <c r="T52" t="n">
         <v>20.2</v>
       </c>
-      <c r="V52" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X52" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>14.6</v>
-      </c>
       <c r="AA52" t="n">
         <v>14.3</v>
       </c>
@@ -5921,24 +5432,6 @@
       </c>
       <c r="T53" t="n">
         <v>20.5</v>
-      </c>
-      <c r="V53" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W53" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X53" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>11.9</v>
       </c>
       <c r="AB53" t="n">
         <v>4.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
@@ -752,6 +761,15 @@
       <c r="T3" t="n">
         <v>20.1</v>
       </c>
+      <c r="V3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -829,6 +847,15 @@
       <c r="T4" t="n">
         <v>20.1</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
@@ -906,6 +933,15 @@
       <c r="T5" t="n">
         <v>20.1</v>
       </c>
+      <c r="V5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
@@ -983,6 +1019,15 @@
       <c r="T6" t="n">
         <v>20.1</v>
       </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
@@ -1081,6 +1126,15 @@
       <c r="T7" t="n">
         <v>23.2</v>
       </c>
+      <c r="V7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
@@ -1179,6 +1233,15 @@
       <c r="T8" t="n">
         <v>23.8</v>
       </c>
+      <c r="V8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y8" t="n">
         <v>7</v>
       </c>
@@ -1277,6 +1340,15 @@
       <c r="T9" t="n">
         <v>23.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
@@ -1375,6 +1447,15 @@
       <c r="T10" t="n">
         <v>23.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1452,6 +1533,15 @@
       <c r="T11" t="n">
         <v>20.1</v>
       </c>
+      <c r="V11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y11" t="n">
         <v>6</v>
       </c>
@@ -1529,6 +1619,15 @@
       <c r="T12" t="n">
         <v>20.1</v>
       </c>
+      <c r="V12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y12" t="n">
         <v>4</v>
       </c>
@@ -1627,6 +1726,15 @@
       <c r="T13" t="n">
         <v>23.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y13" t="n">
         <v>4</v>
       </c>
@@ -1725,6 +1833,15 @@
       <c r="T14" t="n">
         <v>23.1</v>
       </c>
+      <c r="V14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y14" t="n">
         <v>7</v>
       </c>
@@ -1823,6 +1940,15 @@
       <c r="T15" t="n">
         <v>23.1</v>
       </c>
+      <c r="V15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
@@ -1921,6 +2047,15 @@
       <c r="T16" t="n">
         <v>23.2</v>
       </c>
+      <c r="V16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
@@ -2019,6 +2154,15 @@
       <c r="T17" t="n">
         <v>23.2</v>
       </c>
+      <c r="V17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
@@ -2096,6 +2240,15 @@
       <c r="T18" t="n">
         <v>20.1</v>
       </c>
+      <c r="V18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
@@ -2173,6 +2326,15 @@
       <c r="T19" t="n">
         <v>20.1</v>
       </c>
+      <c r="V19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y19" t="n">
         <v>8</v>
       </c>
@@ -2271,6 +2433,15 @@
       <c r="T20" t="n">
         <v>21.4</v>
       </c>
+      <c r="V20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y20" t="n">
         <v>8</v>
       </c>
@@ -2369,6 +2540,15 @@
       <c r="T21" t="n">
         <v>19.7</v>
       </c>
+      <c r="V21" t="n">
+        <v>12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
@@ -2467,6 +2647,15 @@
       <c r="T22" t="n">
         <v>20.7</v>
       </c>
+      <c r="V22" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y22" t="n">
         <v>10</v>
       </c>
@@ -2565,6 +2754,15 @@
       <c r="T23" t="n">
         <v>21.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2663,6 +2861,15 @@
       <c r="T24" t="n">
         <v>21</v>
       </c>
+      <c r="V24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2740,6 +2947,15 @@
       <c r="T25" t="n">
         <v>20.1</v>
       </c>
+      <c r="V25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y25" t="n">
         <v>7</v>
       </c>
@@ -2817,6 +3033,15 @@
       <c r="T26" t="n">
         <v>20.1</v>
       </c>
+      <c r="V26" t="n">
+        <v>11</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -2915,6 +3140,15 @@
       <c r="T27" t="n">
         <v>23.7</v>
       </c>
+      <c r="V27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y27" t="n">
         <v>3</v>
       </c>
@@ -3013,6 +3247,15 @@
       <c r="T28" t="n">
         <v>23.9</v>
       </c>
+      <c r="V28" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
@@ -3111,6 +3354,15 @@
       <c r="T29" t="n">
         <v>21.7</v>
       </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>21</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.2</v>
+      </c>
       <c r="Y29" t="n">
         <v>9</v>
       </c>
@@ -3209,6 +3461,15 @@
       <c r="T30" t="n">
         <v>21.7</v>
       </c>
+      <c r="V30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>16.1</v>
+      </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
@@ -3307,6 +3568,15 @@
       <c r="T31" t="n">
         <v>22</v>
       </c>
+      <c r="V31" t="n">
+        <v>11</v>
+      </c>
+      <c r="W31" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y31" t="n">
         <v>10.4</v>
       </c>
@@ -3405,6 +3675,15 @@
       <c r="T32" t="n">
         <v>22.3</v>
       </c>
+      <c r="V32" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>18</v>
+      </c>
       <c r="Y32" t="n">
         <v>12.1</v>
       </c>
@@ -3503,6 +3782,15 @@
       <c r="T33" t="n">
         <v>23.6</v>
       </c>
+      <c r="V33" t="n">
+        <v>9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y33" t="n">
         <v>7.7</v>
       </c>
@@ -3601,6 +3889,15 @@
       <c r="T34" t="n">
         <v>23.8</v>
       </c>
+      <c r="V34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8.9</v>
+      </c>
       <c r="Y34" t="n">
         <v>3.4</v>
       </c>
@@ -3699,6 +3996,15 @@
       <c r="T35" t="n">
         <v>23.8</v>
       </c>
+      <c r="V35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y35" t="n">
         <v>6</v>
       </c>
@@ -3797,6 +4103,15 @@
       <c r="T36" t="n">
         <v>22.1</v>
       </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -3895,6 +4210,15 @@
       <c r="T37" t="n">
         <v>23.3</v>
       </c>
+      <c r="V37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>26</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y37" t="n">
         <v>5.3</v>
       </c>
@@ -3993,6 +4317,15 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
+      <c r="V38" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.5</v>
+      </c>
       <c r="Y38" t="n">
         <v>11.1</v>
       </c>
@@ -4091,6 +4424,15 @@
       <c r="T39" t="n">
         <v>20</v>
       </c>
+      <c r="V39" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y39" t="n">
         <v>13.4</v>
       </c>
@@ -4189,6 +4531,15 @@
       <c r="T40" t="n">
         <v>15</v>
       </c>
+      <c r="V40" t="n">
+        <v>16</v>
+      </c>
+      <c r="W40" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>23.3</v>
+      </c>
       <c r="Y40" t="n">
         <v>15.2</v>
       </c>
@@ -4287,6 +4638,15 @@
       <c r="T41" t="n">
         <v>10.5</v>
       </c>
+      <c r="V41" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>24.7</v>
+      </c>
       <c r="Y41" t="n">
         <v>14.8</v>
       </c>
@@ -4385,6 +4745,15 @@
       <c r="T42" t="n">
         <v>18.3</v>
       </c>
+      <c r="V42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>20.5</v>
+      </c>
       <c r="Y42" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -4483,6 +4852,15 @@
       <c r="T43" t="n">
         <v>20.2</v>
       </c>
+      <c r="V43" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17.1</v>
+      </c>
       <c r="Y43" t="n">
         <v>4.9</v>
       </c>
@@ -4581,6 +4959,15 @@
       <c r="T44" t="n">
         <v>22.3</v>
       </c>
+      <c r="V44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>17.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>6.8</v>
       </c>
@@ -4679,6 +5066,15 @@
       <c r="T45" t="n">
         <v>22.2</v>
       </c>
+      <c r="V45" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>21.6</v>
+      </c>
       <c r="Y45" t="n">
         <v>12.2</v>
       </c>
@@ -4777,6 +5173,15 @@
       <c r="T46" t="n">
         <v>19.8</v>
       </c>
+      <c r="V46" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>25.6</v>
+      </c>
       <c r="Y46" t="n">
         <v>16.6</v>
       </c>
@@ -4875,6 +5280,15 @@
       <c r="T47" t="n">
         <v>16</v>
       </c>
+      <c r="V47" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="X47" t="n">
+        <v>26.7</v>
+      </c>
       <c r="Y47" t="n">
         <v>13.7</v>
       </c>
@@ -4973,6 +5387,21 @@
       <c r="T48" t="n">
         <v>17</v>
       </c>
+      <c r="V48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>16.9</v>
+      </c>
       <c r="AA48" t="n">
         <v>16</v>
       </c>
@@ -5065,6 +5494,21 @@
       <c r="T49" t="n">
         <v>20.3</v>
       </c>
+      <c r="V49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="X49" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
@@ -5157,6 +5601,21 @@
       <c r="T50" t="n">
         <v>20.5</v>
       </c>
+      <c r="V50" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>19.9</v>
+      </c>
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
@@ -5249,6 +5708,21 @@
       <c r="T51" t="n">
         <v>19.7</v>
       </c>
+      <c r="V51" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W51" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
@@ -5341,6 +5815,21 @@
       <c r="T52" t="n">
         <v>20.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X52" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>14.6</v>
+      </c>
       <c r="AA52" t="n">
         <v>14.3</v>
       </c>
@@ -5432,6 +5921,24 @@
       </c>
       <c r="T53" t="n">
         <v>20.5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X53" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>11.9</v>
       </c>
       <c r="AB53" t="n">
         <v>4.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,15 +696,6 @@
       <c r="AA2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF2" t="n">
         <v>217.16</v>
       </c>
@@ -779,15 +770,6 @@
       <c r="AA3" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF3" t="n">
         <v>220.31</v>
       </c>
@@ -865,15 +847,6 @@
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AF4" t="n">
         <v>221.99</v>
       </c>
@@ -951,15 +924,6 @@
       <c r="AA5" t="n">
         <v>14</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF5" t="n">
         <v>225.14</v>
       </c>
@@ -1037,15 +1001,6 @@
       <c r="AA6" t="n">
         <v>15</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF6" t="n">
         <v>229.98</v>
       </c>
@@ -1144,15 +1099,6 @@
       <c r="AA7" t="n">
         <v>13</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF7" t="n">
         <v>229.96</v>
       </c>
@@ -1251,15 +1197,6 @@
       <c r="AA8" t="n">
         <v>10</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AF8" t="n">
         <v>227.01</v>
       </c>
@@ -1358,15 +1295,6 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AF9" t="n">
         <v>228.35</v>
       </c>
@@ -1465,15 +1393,6 @@
       <c r="AA10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF10" t="n">
         <v>231.16</v>
       </c>
@@ -1551,15 +1470,6 @@
       <c r="AA11" t="n">
         <v>9</v>
       </c>
-      <c r="AB11" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF11" t="n">
         <v>228.13</v>
       </c>
@@ -1637,15 +1547,6 @@
       <c r="AA12" t="n">
         <v>9</v>
       </c>
-      <c r="AB12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4</v>
-      </c>
       <c r="AF12" t="n">
         <v>229.16</v>
       </c>
@@ -1744,15 +1645,6 @@
       <c r="AA13" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF13" t="n">
         <v>228.55</v>
       </c>
@@ -1851,15 +1743,6 @@
       <c r="AA14" t="n">
         <v>10</v>
       </c>
-      <c r="AB14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF14" t="n">
         <v>219.99</v>
       </c>
@@ -1958,15 +1841,6 @@
       <c r="AA15" t="n">
         <v>11</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF15" t="n">
         <v>219.22</v>
       </c>
@@ -2065,15 +1939,6 @@
       <c r="AA16" t="n">
         <v>14</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF16" t="n">
         <v>220.73</v>
       </c>
@@ -2172,15 +2037,6 @@
       <c r="AA17" t="n">
         <v>14</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF17" t="n">
         <v>220.58</v>
       </c>
@@ -2258,15 +2114,6 @@
       <c r="AA18" t="n">
         <v>13</v>
       </c>
-      <c r="AB18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF18" t="n">
         <v>223.43</v>
       </c>
@@ -2344,15 +2191,6 @@
       <c r="AA19" t="n">
         <v>13</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF19" t="n">
         <v>229.48</v>
       </c>
@@ -2451,15 +2289,6 @@
       <c r="AA20" t="n">
         <v>14</v>
       </c>
-      <c r="AB20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4</v>
-      </c>
       <c r="AF20" t="n">
         <v>241.48</v>
       </c>
@@ -2558,15 +2387,6 @@
       <c r="AA21" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF21" t="n">
         <v>238.69</v>
       </c>
@@ -2665,15 +2485,6 @@
       <c r="AA22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AF22" t="n">
         <v>233.48</v>
       </c>
@@ -2772,15 +2583,6 @@
       <c r="AA23" t="n">
         <v>17</v>
       </c>
-      <c r="AB23" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF23" t="n">
         <v>235.13</v>
       </c>
@@ -2879,15 +2681,6 @@
       <c r="AA24" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB24" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF24" t="n">
         <v>234.87</v>
       </c>
@@ -2965,15 +2758,6 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AF25" t="n">
         <v>234.78</v>
       </c>
@@ -3051,15 +2835,6 @@
       <c r="AA26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AB26" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF26" t="n">
         <v>229.75</v>
       </c>
@@ -3158,15 +2933,6 @@
       <c r="AA27" t="n">
         <v>6.5</v>
       </c>
-      <c r="AB27" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF27" t="n">
         <v>222.86</v>
       </c>
@@ -3265,15 +3031,6 @@
       <c r="AA28" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB28" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF28" t="n">
         <v>218.37</v>
       </c>
@@ -3372,15 +3129,6 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AF29" t="n">
         <v>220.85</v>
       </c>
@@ -3479,15 +3227,6 @@
       <c r="AA30" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>6.3</v>
-      </c>
       <c r="AF30" t="n">
         <v>225.87</v>
       </c>
@@ -3586,15 +3325,6 @@
       <c r="AA31" t="n">
         <v>16.1</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF31" t="n">
         <v>229.48</v>
       </c>
@@ -3693,15 +3423,6 @@
       <c r="AA32" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB32" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF32" t="n">
         <v>230.54</v>
       </c>
@@ -3800,15 +3521,6 @@
       <c r="AA33" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AF33" t="n">
         <v>224.23</v>
       </c>
@@ -3907,15 +3619,6 @@
       <c r="AA34" t="n">
         <v>7.9</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF34" t="n">
         <v>223.36</v>
       </c>
@@ -4014,15 +3717,6 @@
       <c r="AA35" t="n">
         <v>12</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AF35" t="n">
         <v>222.92</v>
       </c>
@@ -4121,15 +3815,6 @@
       <c r="AA36" t="n">
         <v>12.9</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>6.7</v>
-      </c>
       <c r="AF36" t="n">
         <v>222.77</v>
       </c>
@@ -4228,15 +3913,6 @@
       <c r="AA37" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AF37" t="n">
         <v>221.86</v>
       </c>
@@ -4335,15 +4011,6 @@
       <c r="AA38" t="n">
         <v>18.8</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AF38" t="n">
         <v>227.49</v>
       </c>
@@ -4442,15 +4109,6 @@
       <c r="AA39" t="n">
         <v>17.2</v>
       </c>
-      <c r="AB39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AF39" t="n">
         <v>233.56</v>
       </c>
@@ -4549,15 +4207,6 @@
       <c r="AA40" t="n">
         <v>18.1</v>
       </c>
-      <c r="AB40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>12.8</v>
-      </c>
       <c r="AF40" t="n">
         <v>234.94</v>
       </c>
@@ -4656,15 +4305,6 @@
       <c r="AA41" t="n">
         <v>16.9</v>
       </c>
-      <c r="AB41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>7</v>
-      </c>
       <c r="AF41" t="n">
         <v>229.19</v>
       </c>
@@ -4763,15 +4403,6 @@
       <c r="AA42" t="n">
         <v>13.8</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AF42" t="n">
         <v>224.91</v>
       </c>
@@ -4870,15 +4501,6 @@
       <c r="AA43" t="n">
         <v>9.6</v>
       </c>
-      <c r="AB43" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AF43" t="n">
         <v>220.83</v>
       </c>
@@ -4977,15 +4599,6 @@
       <c r="AA44" t="n">
         <v>14</v>
       </c>
-      <c r="AB44" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>9.1</v>
-      </c>
       <c r="AF44" t="n">
         <v>228.06</v>
       </c>
@@ -5084,15 +4697,6 @@
       <c r="AA45" t="n">
         <v>19.7</v>
       </c>
-      <c r="AB45" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>8.1</v>
-      </c>
       <c r="AF45" t="n">
         <v>233.59</v>
       </c>
@@ -5191,15 +4795,6 @@
       <c r="AA46" t="n">
         <v>21.2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>7.3</v>
-      </c>
       <c r="AF46" t="n">
         <v>231.92</v>
       </c>
@@ -5298,15 +4893,6 @@
       <c r="AA47" t="n">
         <v>17.3</v>
       </c>
-      <c r="AB47" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AF47" t="n">
         <v>235</v>
       </c>
@@ -5405,15 +4991,6 @@
       <c r="AA48" t="n">
         <v>16</v>
       </c>
-      <c r="AB48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AF48" t="n">
         <v>233.68</v>
       </c>
@@ -5512,15 +5089,6 @@
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AF49" t="n">
         <v>234.37</v>
       </c>
@@ -5619,15 +5187,6 @@
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
-      <c r="AB50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AF50" t="n">
         <v>237.85</v>
       </c>
@@ -5726,15 +5285,6 @@
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
-      <c r="AB51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AF51" t="n">
         <v>228.13</v>
       </c>
@@ -5833,15 +5383,6 @@
       <c r="AA52" t="n">
         <v>14.3</v>
       </c>
-      <c r="AB52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AF52" t="n">
         <v>224.64</v>
       </c>
@@ -5939,15 +5480,6 @@
       </c>
       <c r="AA53" t="n">
         <v>11.9</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>8.6</v>
       </c>
       <c r="AF53" t="n">
         <v>223.71</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -696,6 +696,15 @@
       <c r="AA2" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AF2" t="n">
         <v>217.16</v>
       </c>
@@ -770,6 +779,15 @@
       <c r="AA3" t="n">
         <v>10</v>
       </c>
+      <c r="AB3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF3" t="n">
         <v>220.31</v>
       </c>
@@ -847,6 +865,15 @@
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AF4" t="n">
         <v>221.99</v>
       </c>
@@ -924,6 +951,15 @@
       <c r="AA5" t="n">
         <v>14</v>
       </c>
+      <c r="AB5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF5" t="n">
         <v>225.14</v>
       </c>
@@ -1001,6 +1037,15 @@
       <c r="AA6" t="n">
         <v>15</v>
       </c>
+      <c r="AB6" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="AF6" t="n">
         <v>229.98</v>
       </c>
@@ -1099,6 +1144,15 @@
       <c r="AA7" t="n">
         <v>13</v>
       </c>
+      <c r="AB7" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AF7" t="n">
         <v>229.96</v>
       </c>
@@ -1197,6 +1251,15 @@
       <c r="AA8" t="n">
         <v>10</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4.4</v>
+      </c>
       <c r="AF8" t="n">
         <v>227.01</v>
       </c>
@@ -1295,6 +1358,15 @@
       <c r="AA9" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AF9" t="n">
         <v>228.35</v>
       </c>
@@ -1393,6 +1465,15 @@
       <c r="AA10" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF10" t="n">
         <v>231.16</v>
       </c>
@@ -1470,6 +1551,15 @@
       <c r="AA11" t="n">
         <v>9</v>
       </c>
+      <c r="AB11" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AF11" t="n">
         <v>228.13</v>
       </c>
@@ -1547,6 +1637,15 @@
       <c r="AA12" t="n">
         <v>9</v>
       </c>
+      <c r="AB12" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4</v>
+      </c>
       <c r="AF12" t="n">
         <v>229.16</v>
       </c>
@@ -1645,6 +1744,15 @@
       <c r="AA13" t="n">
         <v>8.5</v>
       </c>
+      <c r="AB13" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF13" t="n">
         <v>228.55</v>
       </c>
@@ -1743,6 +1851,15 @@
       <c r="AA14" t="n">
         <v>10</v>
       </c>
+      <c r="AB14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF14" t="n">
         <v>219.99</v>
       </c>
@@ -1841,6 +1958,15 @@
       <c r="AA15" t="n">
         <v>11</v>
       </c>
+      <c r="AB15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>5.5</v>
+      </c>
       <c r="AF15" t="n">
         <v>219.22</v>
       </c>
@@ -1939,6 +2065,15 @@
       <c r="AA16" t="n">
         <v>14</v>
       </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF16" t="n">
         <v>220.73</v>
       </c>
@@ -2037,6 +2172,15 @@
       <c r="AA17" t="n">
         <v>14</v>
       </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF17" t="n">
         <v>220.58</v>
       </c>
@@ -2114,6 +2258,15 @@
       <c r="AA18" t="n">
         <v>13</v>
       </c>
+      <c r="AB18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF18" t="n">
         <v>223.43</v>
       </c>
@@ -2191,6 +2344,15 @@
       <c r="AA19" t="n">
         <v>13</v>
       </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AF19" t="n">
         <v>229.48</v>
       </c>
@@ -2289,6 +2451,15 @@
       <c r="AA20" t="n">
         <v>14</v>
       </c>
+      <c r="AB20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4</v>
+      </c>
       <c r="AF20" t="n">
         <v>241.48</v>
       </c>
@@ -2387,6 +2558,15 @@
       <c r="AA21" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AF21" t="n">
         <v>238.69</v>
       </c>
@@ -2485,6 +2665,15 @@
       <c r="AA22" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AF22" t="n">
         <v>233.48</v>
       </c>
@@ -2583,6 +2772,15 @@
       <c r="AA23" t="n">
         <v>17</v>
       </c>
+      <c r="AB23" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AF23" t="n">
         <v>235.13</v>
       </c>
@@ -2681,6 +2879,15 @@
       <c r="AA24" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB24" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF24" t="n">
         <v>234.87</v>
       </c>
@@ -2758,6 +2965,15 @@
       <c r="AA25" t="n">
         <v>13</v>
       </c>
+      <c r="AB25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.2</v>
+      </c>
       <c r="AF25" t="n">
         <v>234.78</v>
       </c>
@@ -2835,6 +3051,15 @@
       <c r="AA26" t="n">
         <v>10.5</v>
       </c>
+      <c r="AB26" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AF26" t="n">
         <v>229.75</v>
       </c>
@@ -2933,6 +3158,15 @@
       <c r="AA27" t="n">
         <v>6.5</v>
       </c>
+      <c r="AB27" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AF27" t="n">
         <v>222.86</v>
       </c>
@@ -3031,6 +3265,15 @@
       <c r="AA28" t="n">
         <v>9.5</v>
       </c>
+      <c r="AB28" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF28" t="n">
         <v>218.37</v>
       </c>
@@ -3129,6 +3372,15 @@
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.9</v>
+      </c>
       <c r="AF29" t="n">
         <v>220.85</v>
       </c>
@@ -3227,6 +3479,15 @@
       <c r="AA30" t="n">
         <v>14.5</v>
       </c>
+      <c r="AB30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>6.3</v>
+      </c>
       <c r="AF30" t="n">
         <v>225.87</v>
       </c>
@@ -3325,6 +3586,15 @@
       <c r="AA31" t="n">
         <v>16.1</v>
       </c>
+      <c r="AB31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF31" t="n">
         <v>229.48</v>
       </c>
@@ -3423,6 +3693,15 @@
       <c r="AA32" t="n">
         <v>15.1</v>
       </c>
+      <c r="AB32" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="AF32" t="n">
         <v>230.54</v>
       </c>
@@ -3521,6 +3800,15 @@
       <c r="AA33" t="n">
         <v>10.3</v>
       </c>
+      <c r="AB33" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AF33" t="n">
         <v>224.23</v>
       </c>
@@ -3619,6 +3907,15 @@
       <c r="AA34" t="n">
         <v>7.9</v>
       </c>
+      <c r="AB34" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF34" t="n">
         <v>223.36</v>
       </c>
@@ -3717,6 +4014,15 @@
       <c r="AA35" t="n">
         <v>12</v>
       </c>
+      <c r="AB35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.8</v>
+      </c>
       <c r="AF35" t="n">
         <v>222.92</v>
       </c>
@@ -3815,6 +4121,15 @@
       <c r="AA36" t="n">
         <v>12.9</v>
       </c>
+      <c r="AB36" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>6.7</v>
+      </c>
       <c r="AF36" t="n">
         <v>222.77</v>
       </c>
@@ -3913,6 +4228,15 @@
       <c r="AA37" t="n">
         <v>11.6</v>
       </c>
+      <c r="AB37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>7.8</v>
+      </c>
       <c r="AF37" t="n">
         <v>221.86</v>
       </c>
@@ -4011,6 +4335,15 @@
       <c r="AA38" t="n">
         <v>18.8</v>
       </c>
+      <c r="AB38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="AF38" t="n">
         <v>227.49</v>
       </c>
@@ -4109,6 +4442,15 @@
       <c r="AA39" t="n">
         <v>17.2</v>
       </c>
+      <c r="AB39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="AF39" t="n">
         <v>233.56</v>
       </c>
@@ -4207,6 +4549,15 @@
       <c r="AA40" t="n">
         <v>18.1</v>
       </c>
+      <c r="AB40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AF40" t="n">
         <v>234.94</v>
       </c>
@@ -4305,6 +4656,15 @@
       <c r="AA41" t="n">
         <v>16.9</v>
       </c>
+      <c r="AB41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7</v>
+      </c>
       <c r="AF41" t="n">
         <v>229.19</v>
       </c>
@@ -4403,6 +4763,15 @@
       <c r="AA42" t="n">
         <v>13.8</v>
       </c>
+      <c r="AB42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.4</v>
+      </c>
       <c r="AF42" t="n">
         <v>224.91</v>
       </c>
@@ -4501,6 +4870,15 @@
       <c r="AA43" t="n">
         <v>9.6</v>
       </c>
+      <c r="AB43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AF43" t="n">
         <v>220.83</v>
       </c>
@@ -4599,6 +4977,15 @@
       <c r="AA44" t="n">
         <v>14</v>
       </c>
+      <c r="AB44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>9.1</v>
+      </c>
       <c r="AF44" t="n">
         <v>228.06</v>
       </c>
@@ -4697,6 +5084,15 @@
       <c r="AA45" t="n">
         <v>19.7</v>
       </c>
+      <c r="AB45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.1</v>
+      </c>
       <c r="AF45" t="n">
         <v>233.59</v>
       </c>
@@ -4795,6 +5191,15 @@
       <c r="AA46" t="n">
         <v>21.2</v>
       </c>
+      <c r="AB46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>7.3</v>
+      </c>
       <c r="AF46" t="n">
         <v>231.92</v>
       </c>
@@ -4893,6 +5298,15 @@
       <c r="AA47" t="n">
         <v>17.3</v>
       </c>
+      <c r="AB47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>9.4</v>
+      </c>
       <c r="AF47" t="n">
         <v>235</v>
       </c>
@@ -4991,6 +5405,15 @@
       <c r="AA48" t="n">
         <v>16</v>
       </c>
+      <c r="AB48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="AF48" t="n">
         <v>233.68</v>
       </c>
@@ -5089,6 +5512,15 @@
       <c r="AA49" t="n">
         <v>17.5</v>
       </c>
+      <c r="AB49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>7.4</v>
+      </c>
       <c r="AF49" t="n">
         <v>234.37</v>
       </c>
@@ -5187,6 +5619,15 @@
       <c r="AA50" t="n">
         <v>18.2</v>
       </c>
+      <c r="AB50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AF50" t="n">
         <v>237.85</v>
       </c>
@@ -5285,6 +5726,15 @@
       <c r="AA51" t="n">
         <v>14.3</v>
       </c>
+      <c r="AB51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>7.6</v>
+      </c>
       <c r="AF51" t="n">
         <v>228.13</v>
       </c>
@@ -5383,6 +5833,15 @@
       <c r="AA52" t="n">
         <v>14.3</v>
       </c>
+      <c r="AB52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>6.6</v>
+      </c>
       <c r="AF52" t="n">
         <v>224.64</v>
       </c>
@@ -5481,6 +5940,15 @@
       <c r="AA53" t="n">
         <v>11.9</v>
       </c>
+      <c r="AB53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>8.6</v>
+      </c>
       <c r="AF53" t="n">
         <v>223.71</v>
       </c>
@@ -5548,6 +6016,33 @@
       </c>
       <c r="T54" t="n">
         <v>19</v>
+      </c>
+      <c r="V54" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="X54" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>6.4</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46298</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6044,6 +6044,12 @@
       <c r="AD54" t="n">
         <v>6.4</v>
       </c>
+      <c r="AK54" t="n">
+        <v>131.98</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.11</v>
+      </c>
       <c r="BL54" s="1" t="n">
         <v>46298</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6044,6 +6044,12 @@
       <c r="AD54" t="n">
         <v>6.4</v>
       </c>
+      <c r="AF54" t="n">
+        <v>226.76</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.05</v>
+      </c>
       <c r="AK54" t="n">
         <v>131.98</v>
       </c>
@@ -6105,6 +6111,27 @@
       </c>
       <c r="T55" t="n">
         <v>19</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>234.88</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>136.09</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>4.11</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46299</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -744,10 +744,10 @@
         <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>101.9</v>
+        <v>104.1</v>
       </c>
       <c r="O3" t="n">
-        <v>41.8</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V3" t="n">
         <v>6.3</v>
@@ -830,10 +830,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>96.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>39.5</v>
+        <v>42.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V4" t="n">
         <v>8.9</v>
@@ -916,10 +916,10 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>85.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>35.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V5" t="n">
         <v>9.5</v>
@@ -1002,10 +1002,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>79</v>
+        <v>81.5</v>
       </c>
       <c r="O6" t="n">
-        <v>32.4</v>
+        <v>35.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V6" t="n">
         <v>9</v>
@@ -1516,10 +1516,10 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>93.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="O11" t="n">
-        <v>38.5</v>
+        <v>41.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V11" t="n">
         <v>9.5</v>
@@ -1602,10 +1602,10 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>87.8</v>
+        <v>90.2</v>
       </c>
       <c r="O12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V12" t="n">
         <v>10.7</v>
@@ -2223,10 +2223,10 @@
         <v>6.1</v>
       </c>
       <c r="K18" t="n">
-        <v>83.7</v>
+        <v>86.2</v>
       </c>
       <c r="O18" t="n">
-        <v>34.4</v>
+        <v>37.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -2309,10 +2309,10 @@
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>75.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="O19" t="n">
-        <v>31</v>
+        <v>33.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V19" t="n">
         <v>12.6</v>
@@ -2930,10 +2930,10 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>79.5</v>
+        <v>82</v>
       </c>
       <c r="O25" t="n">
-        <v>32.6</v>
+        <v>35.5</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V25" t="n">
         <v>11.6</v>
@@ -3016,10 +3016,10 @@
         <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>82.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>34.1</v>
+        <v>37</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="V26" t="n">
         <v>11</v>
@@ -5964,6 +5964,18 @@
       <c r="BL53" s="1" t="n">
         <v>46297</v>
       </c>
+      <c r="BM53" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -6059,49 +6071,61 @@
       <c r="BL54" s="1" t="n">
         <v>46298</v>
       </c>
+      <c r="BM54" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>16</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>46299</v>
       </c>
       <c r="B55" t="n">
-        <v>105.4</v>
+        <v>101.4</v>
       </c>
       <c r="C55" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="D55" t="n">
-        <v>34.4</v>
+        <v>33.3</v>
       </c>
       <c r="E55" t="n">
-        <v>23.87</v>
+        <v>16.7</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="H55" t="n">
         <v>22.7</v>
       </c>
       <c r="I55" t="n">
-        <v>7.4</v>
+        <v>9.5</v>
       </c>
       <c r="J55" t="n">
-        <v>38</v>
+        <v>36.2</v>
       </c>
       <c r="K55" t="n">
-        <v>68.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O55" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6110,7 +6134,16 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>19</v>
+        <v>16.2</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>18.5</v>
       </c>
       <c r="AB55" t="n">
         <v>2.8</v>
@@ -6135,6 +6168,18 @@
       </c>
       <c r="BL55" s="1" t="n">
         <v>46299</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6142,43 +6187,43 @@
         <v>46300</v>
       </c>
       <c r="B56" t="n">
-        <v>117.2</v>
+        <v>116.1</v>
       </c>
       <c r="C56" t="n">
-        <v>43.2</v>
+        <v>40.3</v>
       </c>
       <c r="D56" t="n">
-        <v>36.1</v>
+        <v>35.7</v>
       </c>
       <c r="E56" t="n">
         <v>28.24</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="H56" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="I56" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="M56" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N56" t="n">
-        <v>27.5</v>
+        <v>28.9</v>
       </c>
       <c r="O56" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6187,7 +6232,37 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>21</v>
+        <v>13.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>138.83</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2.74</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46300</v>
@@ -6198,43 +6273,43 @@
         <v>46301</v>
       </c>
       <c r="B57" t="n">
-        <v>118.3</v>
+        <v>117.9</v>
       </c>
       <c r="C57" t="n">
-        <v>43.8</v>
+        <v>40.9</v>
       </c>
       <c r="D57" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="E57" t="n">
         <v>28.52</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="H57" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="I57" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="M57" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N57" t="n">
-        <v>28</v>
+        <v>29.4</v>
       </c>
       <c r="O57" t="n">
-        <v>29.9</v>
+        <v>30.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6243,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46301</v>
@@ -6254,19 +6329,43 @@
         <v>46302</v>
       </c>
       <c r="B58" t="n">
-        <v>29.3</v>
+        <v>122</v>
+      </c>
+      <c r="C58" t="n">
+        <v>44</v>
+      </c>
+      <c r="D58" t="n">
+        <v>36.7</v>
       </c>
       <c r="E58" t="n">
         <v>29.26</v>
       </c>
+      <c r="F58" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H58" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J58" t="n">
+        <v>37</v>
+      </c>
       <c r="K58" t="n">
-        <v>6.5</v>
+        <v>68.8</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N58" t="n">
+        <v>29.4</v>
       </c>
       <c r="O58" t="n">
-        <v>2.7</v>
+        <v>30.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6275,7 +6374,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>20.1</v>
+        <v>13.5</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46302</v>
@@ -6286,19 +6385,43 @@
         <v>46303</v>
       </c>
       <c r="B59" t="n">
-        <v>28.9</v>
+        <v>123</v>
+      </c>
+      <c r="C59" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36.6</v>
       </c>
       <c r="E59" t="n">
         <v>28.89</v>
       </c>
+      <c r="F59" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J59" t="n">
+        <v>37</v>
+      </c>
       <c r="K59" t="n">
-        <v>6.2</v>
+        <v>68.8</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N59" t="n">
+        <v>29.4</v>
       </c>
       <c r="O59" t="n">
-        <v>2.6</v>
+        <v>30.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6307,7 +6430,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>20.1</v>
+        <v>13.5</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46303</v>
@@ -6318,19 +6441,43 @@
         <v>46304</v>
       </c>
       <c r="B60" t="n">
-        <v>28.4</v>
+        <v>124.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="D60" t="n">
+        <v>36.5</v>
       </c>
       <c r="E60" t="n">
         <v>28.38</v>
       </c>
+      <c r="F60" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>37</v>
+      </c>
       <c r="K60" t="n">
-        <v>5.9</v>
+        <v>68.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N60" t="n">
+        <v>29.4</v>
       </c>
       <c r="O60" t="n">
-        <v>2.4</v>
+        <v>30.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6339,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>20.1</v>
+        <v>13.5</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46304</v>
@@ -6356,10 +6503,10 @@
         <v>22.05</v>
       </c>
       <c r="K61" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6371,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46305</v>
@@ -6388,10 +6535,10 @@
         <v>21.05</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6403,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46306</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -744,10 +744,10 @@
         <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>104.1</v>
+        <v>104.7</v>
       </c>
       <c r="O3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V3" t="n">
         <v>6.3</v>
@@ -830,10 +830,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>98.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="O4" t="n">
-        <v>42.6</v>
+        <v>43.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V4" t="n">
         <v>8.9</v>
@@ -916,10 +916,10 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>88.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>38.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V5" t="n">
         <v>9.5</v>
@@ -1002,10 +1002,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>81.5</v>
+        <v>82.3</v>
       </c>
       <c r="O6" t="n">
-        <v>35.3</v>
+        <v>36.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V6" t="n">
         <v>9</v>
@@ -1516,10 +1516,10 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>96</v>
+        <v>96.7</v>
       </c>
       <c r="O11" t="n">
-        <v>41.5</v>
+        <v>42.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V11" t="n">
         <v>9.5</v>
@@ -1602,10 +1602,10 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>90.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>39</v>
+        <v>39.9</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V12" t="n">
         <v>10.7</v>
@@ -2223,10 +2223,10 @@
         <v>6.1</v>
       </c>
       <c r="K18" t="n">
-        <v>86.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>37.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -2309,10 +2309,10 @@
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>78</v>
+        <v>78.8</v>
       </c>
       <c r="O19" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V19" t="n">
         <v>12.6</v>
@@ -2930,10 +2930,10 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="O25" t="n">
-        <v>35.5</v>
+        <v>36.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V25" t="n">
         <v>11.6</v>
@@ -3016,10 +3016,10 @@
         <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>85.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="O26" t="n">
-        <v>37</v>
+        <v>37.8</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="V26" t="n">
         <v>11</v>
@@ -6136,6 +6136,15 @@
       <c r="T55" t="n">
         <v>16.2</v>
       </c>
+      <c r="V55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W55" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X55" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y55" t="n">
         <v>11.2</v>
       </c>
@@ -6187,43 +6196,43 @@
         <v>46300</v>
       </c>
       <c r="B56" t="n">
-        <v>116.1</v>
+        <v>106.8</v>
       </c>
       <c r="C56" t="n">
-        <v>40.3</v>
+        <v>38.4</v>
       </c>
       <c r="D56" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="E56" t="n">
-        <v>28.24</v>
+        <v>22.1</v>
       </c>
       <c r="F56" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="I56" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="K56" t="n">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>28.9</v>
       </c>
       <c r="O56" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6232,7 +6241,16 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>13.5</v>
+        <v>12</v>
+      </c>
+      <c r="V56" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X56" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y56" t="n">
         <v>13.4</v>
@@ -6241,7 +6259,7 @@
         <v>20.7</v>
       </c>
       <c r="AA56" t="n">
-        <v>17.1</v>
+        <v>18.7</v>
       </c>
       <c r="AB56" t="n">
         <v>-0.2</v>
@@ -6266,6 +6284,18 @@
       </c>
       <c r="BL56" s="1" t="n">
         <v>46300</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6273,43 +6303,43 @@
         <v>46301</v>
       </c>
       <c r="B57" t="n">
-        <v>117.9</v>
+        <v>115.4</v>
       </c>
       <c r="C57" t="n">
-        <v>40.9</v>
+        <v>39.1</v>
       </c>
       <c r="D57" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="E57" t="n">
         <v>28.52</v>
       </c>
       <c r="F57" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H57" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="I57" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="K57" t="n">
-        <v>68.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M57" t="n">
         <v>0.9</v>
       </c>
       <c r="N57" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O57" t="n">
         <v>29.4</v>
       </c>
-      <c r="O57" t="n">
-        <v>30.3</v>
-      </c>
       <c r="Q57" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6318,7 +6348,31 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
+      </c>
+      <c r="V57" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="W57" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="X57" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>140.91</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.08</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46301</v>
@@ -6329,31 +6383,31 @@
         <v>46302</v>
       </c>
       <c r="B58" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="C58" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="D58" t="n">
-        <v>36.7</v>
+        <v>37.2</v>
       </c>
       <c r="E58" t="n">
         <v>29.26</v>
       </c>
       <c r="F58" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H58" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="I58" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="K58" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="M58" t="n">
         <v>0.9</v>
@@ -6365,7 +6419,7 @@
         <v>30.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6374,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46302</v>
@@ -6385,31 +6439,31 @@
         <v>46303</v>
       </c>
       <c r="B59" t="n">
-        <v>123</v>
+        <v>125.2</v>
       </c>
       <c r="C59" t="n">
-        <v>45.4</v>
+        <v>46.8</v>
       </c>
       <c r="D59" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="E59" t="n">
         <v>28.89</v>
       </c>
       <c r="F59" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H59" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="I59" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="K59" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="M59" t="n">
         <v>0.9</v>
@@ -6421,7 +6475,7 @@
         <v>30.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6430,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46303</v>
@@ -6441,31 +6495,31 @@
         <v>46304</v>
       </c>
       <c r="B60" t="n">
-        <v>124.2</v>
+        <v>126.1</v>
       </c>
       <c r="C60" t="n">
-        <v>46.9</v>
+        <v>48.1</v>
       </c>
       <c r="D60" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="E60" t="n">
         <v>28.38</v>
       </c>
       <c r="F60" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H60" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="I60" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="K60" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="M60" t="n">
         <v>0.9</v>
@@ -6477,7 +6531,7 @@
         <v>30.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6486,7 +6540,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46304</v>
@@ -6497,19 +6551,43 @@
         <v>46305</v>
       </c>
       <c r="B61" t="n">
-        <v>22.1</v>
+        <v>115.2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>36.1</v>
       </c>
       <c r="E61" t="n">
         <v>22.05</v>
       </c>
+      <c r="F61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>38.1</v>
+      </c>
       <c r="K61" t="n">
-        <v>5.2</v>
+        <v>68</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N61" t="n">
+        <v>29.4</v>
       </c>
       <c r="O61" t="n">
-        <v>2.2</v>
+        <v>30.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6518,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46305</v>
@@ -6529,19 +6607,43 @@
         <v>46306</v>
       </c>
       <c r="B62" t="n">
-        <v>21.1</v>
+        <v>108.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>40</v>
+      </c>
+      <c r="D62" t="n">
+        <v>36</v>
       </c>
       <c r="E62" t="n">
         <v>21.05</v>
       </c>
+      <c r="F62" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J62" t="n">
+        <v>38.1</v>
+      </c>
       <c r="K62" t="n">
-        <v>4.5</v>
+        <v>68</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N62" t="n">
+        <v>29</v>
       </c>
       <c r="O62" t="n">
-        <v>1.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6550,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46306</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6368,6 +6368,12 @@
       <c r="AD57" t="n">
         <v>6.5</v>
       </c>
+      <c r="AF57" t="n">
+        <v>237.89</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.18</v>
+      </c>
       <c r="AK57" t="n">
         <v>140.91</v>
       </c>
@@ -6376,6 +6382,18 @@
       </c>
       <c r="BL57" s="1" t="n">
         <v>46301</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6429,6 +6447,24 @@
       </c>
       <c r="T58" t="n">
         <v>13.3</v>
+      </c>
+      <c r="V58" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W58" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X58" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46302</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -744,10 +744,10 @@
         <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>104.7</v>
+        <v>103.1</v>
       </c>
       <c r="O3" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V3" t="n">
         <v>6.3</v>
@@ -830,10 +830,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>99.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V4" t="n">
         <v>8.9</v>
@@ -916,10 +916,10 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>89.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>39.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V5" t="n">
         <v>9.5</v>
@@ -1002,10 +1002,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>82.3</v>
+        <v>80.8</v>
       </c>
       <c r="O6" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V6" t="n">
         <v>9</v>
@@ -1516,10 +1516,10 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>96.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>42.4</v>
+        <v>42.9</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V11" t="n">
         <v>9.5</v>
@@ -1602,10 +1602,10 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>90.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V12" t="n">
         <v>10.7</v>
@@ -2223,10 +2223,10 @@
         <v>6.1</v>
       </c>
       <c r="K18" t="n">
-        <v>86.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>38.2</v>
+        <v>38.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -2309,10 +2309,10 @@
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>78.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V19" t="n">
         <v>12.6</v>
@@ -2930,10 +2930,10 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>82.8</v>
+        <v>81.3</v>
       </c>
       <c r="O25" t="n">
-        <v>36.3</v>
+        <v>36.7</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V25" t="n">
         <v>11.6</v>
@@ -3016,10 +3016,10 @@
         <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>86.2</v>
+        <v>84.7</v>
       </c>
       <c r="O26" t="n">
-        <v>37.8</v>
+        <v>38.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="V26" t="n">
         <v>11</v>
@@ -6303,43 +6303,43 @@
         <v>46301</v>
       </c>
       <c r="B57" t="n">
-        <v>115.4</v>
+        <v>108.3</v>
       </c>
       <c r="C57" t="n">
-        <v>39.1</v>
+        <v>38</v>
       </c>
       <c r="D57" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="E57" t="n">
-        <v>28.52</v>
+        <v>24.2</v>
       </c>
       <c r="F57" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H57" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="I57" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J57" t="n">
-        <v>37.1</v>
+        <v>36.2</v>
       </c>
       <c r="K57" t="n">
-        <v>68.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="M57" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>28.5</v>
+        <v>29.2</v>
       </c>
       <c r="O57" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6348,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="V57" t="n">
         <v>15.7</v>
@@ -6358,6 +6358,9 @@
       </c>
       <c r="X57" t="n">
         <v>21.8</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>17.9</v>
       </c>
       <c r="AB57" t="n">
         <v>2.1</v>
@@ -6401,13 +6404,13 @@
         <v>46302</v>
       </c>
       <c r="B58" t="n">
-        <v>122.5</v>
+        <v>119.9</v>
       </c>
       <c r="C58" t="n">
-        <v>43.8</v>
+        <v>40.3</v>
       </c>
       <c r="D58" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
       <c r="E58" t="n">
         <v>29.26</v>
@@ -6416,16 +6419,16 @@
         <v>6.6</v>
       </c>
       <c r="H58" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="I58" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J58" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
       <c r="K58" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="M58" t="n">
         <v>0.9</v>
@@ -6437,7 +6440,7 @@
         <v>30.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6446,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="V58" t="n">
         <v>15.5</v>
@@ -6466,8 +6469,26 @@
       <c r="AD58" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="AK58" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-0.41</v>
+      </c>
       <c r="BL58" s="1" t="n">
         <v>46302</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -6475,13 +6496,13 @@
         <v>46303</v>
       </c>
       <c r="B59" t="n">
-        <v>125.2</v>
+        <v>122.8</v>
       </c>
       <c r="C59" t="n">
-        <v>46.8</v>
+        <v>44.7</v>
       </c>
       <c r="D59" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="E59" t="n">
         <v>28.89</v>
@@ -6490,16 +6511,16 @@
         <v>6.6</v>
       </c>
       <c r="H59" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="I59" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J59" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>68.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="M59" t="n">
         <v>0.9</v>
@@ -6511,7 +6532,7 @@
         <v>30.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6520,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46303</v>
@@ -6531,13 +6552,13 @@
         <v>46304</v>
       </c>
       <c r="B60" t="n">
-        <v>126.1</v>
+        <v>124.1</v>
       </c>
       <c r="C60" t="n">
-        <v>48.1</v>
+        <v>46.3</v>
       </c>
       <c r="D60" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="E60" t="n">
         <v>28.38</v>
@@ -6546,16 +6567,16 @@
         <v>6.6</v>
       </c>
       <c r="H60" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="I60" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J60" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
       <c r="K60" t="n">
-        <v>68.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>0.9</v>
@@ -6567,7 +6588,7 @@
         <v>30.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6576,7 +6597,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46304</v>
@@ -6587,13 +6608,13 @@
         <v>46305</v>
       </c>
       <c r="B61" t="n">
-        <v>115.2</v>
+        <v>113.4</v>
       </c>
       <c r="C61" t="n">
-        <v>44.7</v>
+        <v>43.5</v>
       </c>
       <c r="D61" t="n">
-        <v>36.1</v>
+        <v>35.5</v>
       </c>
       <c r="E61" t="n">
         <v>22.05</v>
@@ -6605,13 +6626,13 @@
         <v>20.8</v>
       </c>
       <c r="I61" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J61" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
       <c r="K61" t="n">
-        <v>68</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M61" t="n">
         <v>0.9</v>
@@ -6623,7 +6644,7 @@
         <v>30.3</v>
       </c>
       <c r="Q61" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6632,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46305</v>
@@ -6643,13 +6664,13 @@
         <v>46306</v>
       </c>
       <c r="B62" t="n">
-        <v>108.3</v>
+        <v>106.8</v>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>39.1</v>
       </c>
       <c r="D62" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="E62" t="n">
         <v>21.05</v>
@@ -6661,13 +6682,13 @@
         <v>20.8</v>
       </c>
       <c r="I62" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J62" t="n">
-        <v>38.1</v>
+        <v>36</v>
       </c>
       <c r="K62" t="n">
-        <v>68</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M62" t="n">
         <v>0.9</v>
@@ -6679,7 +6700,7 @@
         <v>29.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6688,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46306</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6359,6 +6359,12 @@
       <c r="X57" t="n">
         <v>21.8</v>
       </c>
+      <c r="Y57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>19.7</v>
+      </c>
       <c r="AA57" t="n">
         <v>17.9</v>
       </c>
@@ -6460,6 +6466,15 @@
       <c r="X58" t="n">
         <v>22.6</v>
       </c>
+      <c r="Y58" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>17.5</v>
+      </c>
       <c r="AB58" t="n">
         <v>6.9</v>
       </c>
@@ -6468,6 +6483,12 @@
       </c>
       <c r="AD58" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>233.22</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>-4.67</v>
       </c>
       <c r="AK58" t="n">
         <v>140.5</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -744,10 +744,10 @@
         <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>103.1</v>
+        <v>103.5</v>
       </c>
       <c r="O3" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V3" t="n">
         <v>6.3</v>
@@ -830,10 +830,10 @@
         <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>97.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="O4" t="n">
-        <v>44.1</v>
+        <v>42.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V4" t="n">
         <v>8.9</v>
@@ -916,10 +916,10 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="O5" t="n">
-        <v>39.5</v>
+        <v>37.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V5" t="n">
         <v>9.5</v>
@@ -1002,10 +1002,10 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>36.5</v>
+        <v>34.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V6" t="n">
         <v>9</v>
@@ -1516,10 +1516,10 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>95.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>42.9</v>
+        <v>41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V11" t="n">
         <v>9.5</v>
@@ -1602,10 +1602,10 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>40.3</v>
+        <v>38.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V12" t="n">
         <v>10.7</v>
@@ -2223,10 +2223,10 @@
         <v>6.1</v>
       </c>
       <c r="K18" t="n">
-        <v>85.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>38.6</v>
+        <v>36.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -2312,7 +2312,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>34.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V19" t="n">
         <v>12.6</v>
@@ -2930,10 +2930,10 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>36.7</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V25" t="n">
         <v>11.6</v>
@@ -3016,10 +3016,10 @@
         <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="O26" t="n">
-        <v>38.2</v>
+        <v>36.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="V26" t="n">
         <v>11</v>
@@ -6410,43 +6410,43 @@
         <v>46302</v>
       </c>
       <c r="B58" t="n">
-        <v>119.9</v>
+        <v>118.7</v>
       </c>
       <c r="C58" t="n">
-        <v>40.3</v>
+        <v>43</v>
       </c>
       <c r="D58" t="n">
-        <v>38.2</v>
+        <v>35.9</v>
       </c>
       <c r="E58" t="n">
-        <v>29.26</v>
+        <v>24.6</v>
       </c>
       <c r="F58" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="H58" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="I58" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="K58" t="n">
-        <v>67.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N58" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="O58" t="n">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="V58" t="n">
         <v>15.5</v>
@@ -6473,7 +6473,7 @@
         <v>19.1</v>
       </c>
       <c r="AA58" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="AB58" t="n">
         <v>6.9</v>
@@ -6517,43 +6517,43 @@
         <v>46303</v>
       </c>
       <c r="B59" t="n">
-        <v>122.8</v>
+        <v>124.1</v>
       </c>
       <c r="C59" t="n">
-        <v>44.7</v>
+        <v>46.3</v>
       </c>
       <c r="D59" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="E59" t="n">
         <v>28.89</v>
       </c>
       <c r="F59" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H59" t="n">
-        <v>21.8</v>
+        <v>23.8</v>
       </c>
       <c r="I59" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J59" t="n">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="K59" t="n">
-        <v>66.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="M59" t="n">
         <v>0.9</v>
       </c>
       <c r="N59" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="O59" t="n">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>17.8</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6562,10 +6562,40 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>15</v>
+        <v>17.8</v>
+      </c>
+      <c r="V59" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="W59" t="n">
+        <v>22</v>
+      </c>
+      <c r="X59" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46303</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6573,43 +6603,43 @@
         <v>46304</v>
       </c>
       <c r="B60" t="n">
-        <v>124.1</v>
+        <v>127.5</v>
       </c>
       <c r="C60" t="n">
-        <v>46.3</v>
+        <v>48.1</v>
       </c>
       <c r="D60" t="n">
-        <v>36.8</v>
+        <v>37.3</v>
       </c>
       <c r="E60" t="n">
         <v>28.38</v>
       </c>
       <c r="F60" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="H60" t="n">
-        <v>21.8</v>
+        <v>23.7</v>
       </c>
       <c r="I60" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K60" t="n">
-        <v>66.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="N60" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="O60" t="n">
-        <v>30.3</v>
+        <v>29.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6618,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46304</v>
@@ -6629,43 +6659,43 @@
         <v>46305</v>
       </c>
       <c r="B61" t="n">
-        <v>113.4</v>
+        <v>115.7</v>
       </c>
       <c r="C61" t="n">
-        <v>43.5</v>
+        <v>45.4</v>
       </c>
       <c r="D61" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="E61" t="n">
         <v>22.05</v>
       </c>
       <c r="F61" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H61" t="n">
-        <v>20.8</v>
+        <v>22.8</v>
       </c>
       <c r="I61" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K61" t="n">
-        <v>65.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="M61" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="N61" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="O61" t="n">
-        <v>30.3</v>
+        <v>29.7</v>
       </c>
       <c r="Q61" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6674,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46305</v>
@@ -6685,43 +6715,43 @@
         <v>46306</v>
       </c>
       <c r="B62" t="n">
-        <v>106.8</v>
+        <v>109.9</v>
       </c>
       <c r="C62" t="n">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="D62" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E62" t="n">
         <v>21.05</v>
       </c>
       <c r="F62" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H62" t="n">
-        <v>20.8</v>
+        <v>22.8</v>
       </c>
       <c r="I62" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K62" t="n">
-        <v>65.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="M62" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="N62" t="n">
         <v>29</v>
       </c>
       <c r="O62" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="Q62" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6730,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46306</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6573,6 +6573,15 @@
       <c r="X59" t="n">
         <v>19.4</v>
       </c>
+      <c r="Y59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>15.2</v>
+      </c>
       <c r="AB59" t="n">
         <v>6.1</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6591,6 +6591,18 @@
       <c r="AD59" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="AF59" t="n">
+        <v>226.46</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>138.43</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-2.07</v>
+      </c>
       <c r="BL59" s="1" t="n">
         <v>46303</v>
       </c>
@@ -6658,6 +6670,36 @@
       </c>
       <c r="T60" t="n">
         <v>17.2</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>220.99</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>128.95</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>-9.48</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46304</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6671,6 +6671,15 @@
       <c r="T60" t="n">
         <v>17.2</v>
       </c>
+      <c r="V60" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W60" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X60" t="n">
+        <v>15.8</v>
+      </c>
       <c r="Y60" t="n">
         <v>11.5</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -628,212 +628,233 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="n">
-        <v>183</v>
+        <v>158.1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.7</v>
+        <v>73.7</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>33.7</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="I2" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="K2" t="n">
-        <v>76.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>36.7</v>
+        <v>35.3</v>
       </c>
       <c r="O2" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q2" t="n">
         <v>23.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
         <v>23.6</v>
       </c>
       <c r="V2" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="W2" t="n">
-        <v>16.1</v>
+        <v>19.3</v>
       </c>
       <c r="X2" t="n">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
         <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>217.16</v>
+        <v>228.35</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.76</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>117.87</v>
+        <v>130.88</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="BM2" t="n">
-        <v>40.4</v>
+        <v>32.38</v>
       </c>
       <c r="BN2" t="n">
-        <v>6995.8</v>
+        <v>4993.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>2380.8</v>
+        <v>958.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>3192.8</v>
+        <v>2899.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B3" t="n">
-        <v>163.8</v>
+        <v>154.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>70.2</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>31.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27.7</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.3</v>
       </c>
       <c r="K3" t="n">
-        <v>103.5</v>
+        <v>75.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32.9</v>
       </c>
       <c r="O3" t="n">
-        <v>44.5</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T3" t="n">
-        <v>15.8</v>
+        <v>23.7</v>
       </c>
       <c r="V3" t="n">
         <v>6.3</v>
       </c>
       <c r="W3" t="n">
-        <v>17.2</v>
+        <v>25.2</v>
       </c>
       <c r="X3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>220.31</v>
+        <v>231.16</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.16</v>
+        <v>2.81</v>
       </c>
       <c r="AK3" t="n">
-        <v>116.52</v>
+        <v>132.55</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="BM3" t="n">
-        <v>39.65</v>
+        <v>33.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>2827.2</v>
+        <v>1514.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>2051.2</v>
+        <v>799.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>3152.1</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B4" t="n">
-        <v>155.9</v>
+        <v>152.2</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>98</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>42.1</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -848,78 +869,78 @@
         <v>15.8</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W4" t="n">
-        <v>15.8</v>
+        <v>25.5</v>
       </c>
       <c r="X4" t="n">
-        <v>12.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>221.99</v>
+        <v>228.13</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>-3.03</v>
       </c>
       <c r="AK4" t="n">
-        <v>116.37</v>
+        <v>128.02</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.15</v>
+        <v>-4.53</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="BM4" t="n">
-        <v>34.79</v>
+        <v>35.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>3609.5</v>
+        <v>1526.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1161.2</v>
+        <v>957.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>3077.1</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B5" t="n">
-        <v>141.3</v>
+        <v>143.9</v>
       </c>
       <c r="D5" t="n">
-        <v>26.3</v>
+        <v>30.8</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>87.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -934,592 +955,613 @@
         <v>15.8</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W5" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="X5" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AF5" t="n">
-        <v>225.14</v>
+        <v>229.16</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>120.64</v>
+        <v>127.06</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.27</v>
+        <v>-0.96</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="BM5" t="n">
-        <v>31.22</v>
+        <v>34.56</v>
       </c>
       <c r="BN5" t="n">
-        <v>1884.4</v>
+        <v>170.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>785.2</v>
+        <v>130.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>2636.2</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B6" t="n">
-        <v>131.5</v>
+        <v>163.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>73.7</v>
       </c>
       <c r="D6" t="n">
-        <v>27.3</v>
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>28.2</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.1</v>
       </c>
       <c r="K6" t="n">
-        <v>80.90000000000001</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32.9</v>
       </c>
       <c r="O6" t="n">
-        <v>34.8</v>
+        <v>39.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>15.8</v>
+        <v>23.5</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W6" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="X6" t="n">
-        <v>11.4</v>
+        <v>14.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.4</v>
+        <v>4.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>229.98</v>
+        <v>228.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.84</v>
+        <v>-0.61</v>
       </c>
       <c r="AK6" t="n">
-        <v>128.14</v>
+        <v>125.61</v>
       </c>
       <c r="AL6" t="n">
-        <v>7.5</v>
+        <v>-1.45</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="BM6" t="n">
-        <v>26.41</v>
+        <v>34.78</v>
       </c>
       <c r="BN6" t="n">
-        <v>1894.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>223.6</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>174.4</v>
       </c>
       <c r="C7" t="n">
-        <v>71.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>28.6</v>
+        <v>32.1</v>
       </c>
       <c r="E7" t="n">
-        <v>24.7</v>
+        <v>30.8</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I7" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="K7" t="n">
-        <v>75.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD7" t="n">
         <v>4.8</v>
       </c>
-      <c r="N7" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF7" t="n">
-        <v>229.96</v>
+        <v>219.99</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.02</v>
+        <v>-8.56</v>
       </c>
       <c r="AK7" t="n">
-        <v>128.15</v>
+        <v>124.36</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01</v>
+        <v>-1.25</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="BM7" t="n">
-        <v>29.83</v>
+        <v>36.78</v>
       </c>
       <c r="BN7" t="n">
-        <v>2723.2</v>
+        <v>108.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>271.1</v>
+        <v>204.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B8" t="n">
-        <v>165.8</v>
+        <v>163.2</v>
       </c>
       <c r="C8" t="n">
-        <v>77.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>29.3</v>
+        <v>32.9</v>
       </c>
       <c r="E8" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="H8" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I8" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>41.6</v>
+        <v>40.1</v>
       </c>
       <c r="K8" t="n">
-        <v>76.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="N8" t="n">
-        <v>35.1</v>
+        <v>34.3</v>
       </c>
       <c r="O8" t="n">
-        <v>39.8</v>
+        <v>41.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="T8" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W8" t="n">
-        <v>17.4</v>
+        <v>23.3</v>
       </c>
       <c r="X8" t="n">
-        <v>13.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>227.01</v>
+        <v>219.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.95</v>
+        <v>-0.77</v>
       </c>
       <c r="AK8" t="n">
-        <v>128.86</v>
+        <v>120.93</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.71</v>
+        <v>-3.43</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="BM8" t="n">
-        <v>33.62</v>
+        <v>32.64</v>
       </c>
       <c r="BN8" t="n">
-        <v>6652.6</v>
+        <v>42.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>1412.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP8" t="n">
-        <v>408</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B9" t="n">
-        <v>158.1</v>
+        <v>152.7</v>
       </c>
       <c r="C9" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D9" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I9" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J9" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="K9" t="n">
-        <v>74.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="N9" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="O9" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="V9" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>19.3</v>
+        <v>27.3</v>
       </c>
       <c r="X9" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>228.35</v>
+        <v>220.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>130.88</v>
+        <v>120.28</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.02</v>
+        <v>-0.65</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="BM9" t="n">
-        <v>32.38</v>
+        <v>29.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>4993.3</v>
+        <v>60.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>958.6</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>2899.8</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B10" t="n">
-        <v>154.9</v>
+        <v>150.7</v>
       </c>
       <c r="C10" t="n">
-        <v>70.2</v>
+        <v>64.8</v>
       </c>
       <c r="D10" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="E10" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I10" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="K10" t="n">
-        <v>75.8</v>
+        <v>70.5</v>
       </c>
       <c r="M10" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="N10" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="O10" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S10" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="V10" t="n">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="W10" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="X10" t="n">
-        <v>15.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>231.16</v>
+        <v>220.58</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.81</v>
+        <v>-0.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>132.55</v>
+        <v>119.29</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.67</v>
+        <v>-0.99</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="BM10" t="n">
-        <v>33.01</v>
+        <v>31.11</v>
       </c>
       <c r="BN10" t="n">
-        <v>1514.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>799.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP10" t="n">
-        <v>2923.4</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B11" t="n">
-        <v>152.2</v>
+        <v>138.2</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>33.6</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="K11" t="n">
-        <v>95.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>41</v>
+        <v>36.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1534,78 +1576,78 @@
         <v>15.8</v>
       </c>
       <c r="V11" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="W11" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="X11" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>228.13</v>
+        <v>223.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>-3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.02</v>
+        <v>121.35</v>
       </c>
       <c r="AL11" t="n">
-        <v>-4.53</v>
+        <v>2.06</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="BM11" t="n">
-        <v>35.62</v>
+        <v>30.59</v>
       </c>
       <c r="BN11" t="n">
-        <v>1526.5</v>
+        <v>40.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>957.4</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>2928.4</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B12" t="n">
-        <v>143.9</v>
+        <v>126.5</v>
       </c>
       <c r="D12" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>89.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1620,613 +1662,613 @@
         <v>15.8</v>
       </c>
       <c r="V12" t="n">
-        <v>10.7</v>
+        <v>12.6</v>
       </c>
       <c r="W12" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="X12" t="n">
-        <v>14.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>229.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.03</v>
+        <v>6.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>127.06</v>
+        <v>128.37</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.96</v>
+        <v>7.02</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="BM12" t="n">
-        <v>34.56</v>
+        <v>30.05</v>
       </c>
       <c r="BN12" t="n">
-        <v>170.6</v>
+        <v>34</v>
       </c>
       <c r="BO12" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>2825.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B13" t="n">
-        <v>163.2</v>
+        <v>129.4</v>
       </c>
       <c r="C13" t="n">
-        <v>73.7</v>
+        <v>50.6</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E13" t="n">
-        <v>28.2</v>
+        <v>19.4</v>
       </c>
       <c r="F13" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I13" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="J13" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
       <c r="K13" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M13" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="O13" t="n">
-        <v>39.7</v>
+        <v>38</v>
       </c>
       <c r="Q13" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="R13" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="V13" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="W13" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="X13" t="n">
-        <v>14.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
         <v>4</v>
       </c>
-      <c r="Z13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF13" t="n">
-        <v>228.55</v>
+        <v>241.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.61</v>
+        <v>12</v>
       </c>
       <c r="AK13" t="n">
-        <v>125.61</v>
+        <v>134.59</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.45</v>
+        <v>6.22</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="BM13" t="n">
-        <v>34.78</v>
+        <v>24.86</v>
       </c>
       <c r="BN13" t="n">
-        <v>69.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>2769.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B14" t="n">
-        <v>174.4</v>
+        <v>142.9</v>
       </c>
       <c r="C14" t="n">
-        <v>75.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="D14" t="n">
-        <v>32.1</v>
+        <v>34.7</v>
       </c>
       <c r="E14" t="n">
-        <v>30.8</v>
+        <v>24.8</v>
       </c>
       <c r="F14" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I14" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="J14" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="K14" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M14" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O14" t="n">
         <v>35.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>42.6</v>
-      </c>
       <c r="Q14" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="R14" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>219.99</v>
+        <v>238.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>-8.56</v>
+        <v>-2.8</v>
       </c>
       <c r="AK14" t="n">
-        <v>124.36</v>
+        <v>136.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>-1.25</v>
+        <v>2.01</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="BM14" t="n">
-        <v>36.78</v>
+        <v>29.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>108.8</v>
+        <v>61.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>204.3</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>2982.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B15" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C15" t="n">
-        <v>70.90000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D15" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="F15" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H15" t="n">
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J15" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K15" t="n">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="M15" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="O15" t="n">
-        <v>41.5</v>
+        <v>33.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="W15" t="n">
-        <v>23.3</v>
+        <v>25.5</v>
       </c>
       <c r="X15" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>219.22</v>
+        <v>233.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.77</v>
+        <v>-4.86</v>
       </c>
       <c r="AK15" t="n">
-        <v>120.93</v>
+        <v>135.66</v>
       </c>
       <c r="AL15" t="n">
-        <v>-3.43</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="BM15" t="n">
-        <v>32.64</v>
+        <v>36.03</v>
       </c>
       <c r="BN15" t="n">
-        <v>42.3</v>
+        <v>76.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>3194.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B16" t="n">
-        <v>152.7</v>
+        <v>143.4</v>
       </c>
       <c r="C16" t="n">
-        <v>62.6</v>
+        <v>50.9</v>
       </c>
       <c r="D16" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="E16" t="n">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="H16" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="I16" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K16" t="n">
-        <v>69.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>33.5</v>
+        <v>31.2</v>
       </c>
       <c r="O16" t="n">
-        <v>40.1</v>
+        <v>33.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="W16" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="X16" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>220.73</v>
+        <v>235.13</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AK16" t="n">
-        <v>120.28</v>
+        <v>136.33</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="BM16" t="n">
-        <v>29.61</v>
+        <v>32</v>
       </c>
       <c r="BN16" t="n">
-        <v>60.1</v>
+        <v>29.5</v>
       </c>
       <c r="BO16" t="n">
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2717.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B17" t="n">
-        <v>150.7</v>
+        <v>144.9</v>
       </c>
       <c r="C17" t="n">
-        <v>64.8</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
       <c r="E17" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
+        <v>24</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>21</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>234.87</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>137.17</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BL17" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="BN17" t="n">
         <v>23.4</v>
       </c>
-      <c r="I17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N17" t="n">
-        <v>33</v>
-      </c>
-      <c r="O17" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>119.29</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="BL17" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>87.90000000000001</v>
-      </c>
       <c r="BO17" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>3028.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B18" t="n">
-        <v>138.2</v>
+        <v>132.2</v>
       </c>
       <c r="D18" t="n">
-        <v>33.6</v>
+        <v>35.6</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>85.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>36.8</v>
+        <v>35</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2241,78 +2283,78 @@
         <v>15.8</v>
       </c>
       <c r="V18" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="W18" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="X18" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
         <v>13</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>223.43</v>
+        <v>234.78</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.85</v>
+        <v>-0.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>121.35</v>
+        <v>136.08</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.06</v>
+        <v>-1.09</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="BM18" t="n">
-        <v>30.59</v>
+        <v>29.64</v>
       </c>
       <c r="BN18" t="n">
-        <v>40.8</v>
+        <v>36.4</v>
       </c>
       <c r="BO18" t="n">
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2959.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B19" t="n">
-        <v>126.5</v>
+        <v>137.1</v>
       </c>
       <c r="D19" t="n">
-        <v>33.2</v>
+        <v>35.1</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>77.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="O19" t="n">
-        <v>33.3</v>
+        <v>36.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2327,52 +2369,52 @@
         <v>15.8</v>
       </c>
       <c r="V19" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="X19" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>229.48</v>
+        <v>229.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>6.05</v>
+        <v>-5.03</v>
       </c>
       <c r="AK19" t="n">
-        <v>128.37</v>
+        <v>135.42</v>
       </c>
       <c r="AL19" t="n">
-        <v>7.02</v>
+        <v>-0.66</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="BM19" t="n">
-        <v>30.05</v>
+        <v>31.45</v>
       </c>
       <c r="BN19" t="n">
-        <v>34</v>
+        <v>35.9</v>
       </c>
       <c r="BO19" t="n">
         <v>0</v>
@@ -2383,1987 +2425,2029 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B20" t="n">
-        <v>129.4</v>
+        <v>148.7</v>
       </c>
       <c r="C20" t="n">
-        <v>50.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E20" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I20" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="K20" t="n">
-        <v>73.3</v>
+        <v>74.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="O20" t="n">
-        <v>38</v>
+        <v>39.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="V20" t="n">
-        <v>14.3</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>23.9</v>
+        <v>15.6</v>
       </c>
       <c r="X20" t="n">
-        <v>19.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA20" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>241.48</v>
+        <v>222.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>-6.9</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.59</v>
+        <v>131.24</v>
       </c>
       <c r="AL20" t="n">
-        <v>6.22</v>
+        <v>-4.18</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="BM20" t="n">
-        <v>24.86</v>
+        <v>34.46</v>
       </c>
       <c r="BN20" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B21" t="n">
-        <v>142.9</v>
+        <v>149.3</v>
       </c>
       <c r="C21" t="n">
-        <v>52.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="E21" t="n">
-        <v>24.8</v>
+        <v>28.8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="I21" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="K21" t="n">
-        <v>70</v>
+        <v>73.8</v>
       </c>
       <c r="M21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R21" t="n">
         <v>3.9</v>
       </c>
-      <c r="N21" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.7</v>
-      </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>19.7</v>
+        <v>23.9</v>
       </c>
       <c r="V21" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="W21" t="n">
-        <v>25.8</v>
+        <v>18.1</v>
       </c>
       <c r="X21" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>238.69</v>
+        <v>218.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>-2.8</v>
+        <v>-4.49</v>
       </c>
       <c r="AK21" t="n">
-        <v>136.6</v>
+        <v>129.21</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.01</v>
+        <v>-2.03</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="BM21" t="n">
-        <v>29.8</v>
+        <v>35.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>61.9</v>
+        <v>294.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B22" t="n">
-        <v>148.1</v>
+        <v>137</v>
       </c>
       <c r="C22" t="n">
-        <v>51.9</v>
+        <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>35.4</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>31.5</v>
+        <v>25.2</v>
       </c>
       <c r="F22" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>21.8</v>
+        <v>23.5</v>
       </c>
       <c r="I22" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>39.6</v>
+        <v>38.5</v>
       </c>
       <c r="K22" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
-        <v>30.8</v>
+        <v>32.3</v>
       </c>
       <c r="O22" t="n">
-        <v>33.7</v>
+        <v>40.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="V22" t="n">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="X22" t="n">
-        <v>19.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA22" t="n">
         <v>13.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>233.48</v>
+        <v>220.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>-4.86</v>
+        <v>2.48</v>
       </c>
       <c r="AK22" t="n">
-        <v>135.66</v>
+        <v>129.07</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="BM22" t="n">
-        <v>36.03</v>
+        <v>32.31</v>
       </c>
       <c r="BN22" t="n">
-        <v>76.5</v>
+        <v>547</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B23" t="n">
-        <v>143.4</v>
+        <v>131.5</v>
       </c>
       <c r="C23" t="n">
-        <v>50.9</v>
+        <v>57.6</v>
       </c>
       <c r="D23" t="n">
-        <v>35.7</v>
+        <v>32.7</v>
       </c>
       <c r="E23" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="F23" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="H23" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="I23" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J23" t="n">
-        <v>39.9</v>
+        <v>41.6</v>
       </c>
       <c r="K23" t="n">
-        <v>72.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="N23" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="O23" t="n">
-        <v>33.1</v>
+        <v>42.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V23" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>28.3</v>
+        <v>24.1</v>
       </c>
       <c r="X23" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>235.13</v>
+        <v>225.87</v>
       </c>
       <c r="AG23" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>130.73</v>
+      </c>
+      <c r="AL23" t="n">
         <v>1.66</v>
       </c>
-      <c r="AK23" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="BM23" t="n">
-        <v>32</v>
+        <v>31.51</v>
       </c>
       <c r="BN23" t="n">
-        <v>29.5</v>
+        <v>124</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>164.4</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B24" t="n">
-        <v>144.9</v>
+        <v>129.4</v>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="D24" t="n">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I24" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J24" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="K24" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>31.6</v>
+        <v>33.1</v>
       </c>
       <c r="O24" t="n">
-        <v>33.6</v>
+        <v>38.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
-        <v>27.7</v>
+        <v>22.9</v>
       </c>
       <c r="X24" t="n">
-        <v>21.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="Z24" t="n">
         <v>19</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>-1.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>234.87</v>
+        <v>229.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.26</v>
+        <v>3.61</v>
       </c>
       <c r="AK24" t="n">
-        <v>137.17</v>
+        <v>132</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.84</v>
+        <v>1.27</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="BM24" t="n">
-        <v>32.57</v>
+        <v>34.36</v>
       </c>
       <c r="BN24" t="n">
-        <v>23.4</v>
+        <v>62.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B25" t="n">
-        <v>132.2</v>
+        <v>130.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>56.9</v>
       </c>
       <c r="D25" t="n">
-        <v>35.6</v>
+        <v>33.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26.4</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>2.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>42.3</v>
       </c>
       <c r="K25" t="n">
-        <v>81.40000000000001</v>
+        <v>75.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>32.3</v>
       </c>
       <c r="O25" t="n">
-        <v>35</v>
+        <v>37.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>15.8</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="W25" t="n">
-        <v>23.2</v>
+        <v>21.7</v>
       </c>
       <c r="X25" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>12.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>234.78</v>
+        <v>230.54</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>136.08</v>
+        <v>132.25</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.09</v>
+        <v>0.25</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="BM25" t="n">
-        <v>29.64</v>
+        <v>32.26</v>
       </c>
       <c r="BN25" t="n">
-        <v>36.4</v>
+        <v>28.3</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>2545.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B26" t="n">
-        <v>137.1</v>
+        <v>138.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>35.1</v>
+        <v>32.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>25.9</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>42.8</v>
       </c>
       <c r="K26" t="n">
-        <v>84.8</v>
+        <v>75.8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>32.3</v>
       </c>
       <c r="O26" t="n">
-        <v>36.5</v>
+        <v>35.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>15.8</v>
+        <v>23.6</v>
       </c>
       <c r="V26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W26" t="n">
-        <v>22</v>
+        <v>15.7</v>
       </c>
       <c r="X26" t="n">
-        <v>16.5</v>
+        <v>12.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>-5.3</v>
+        <v>-6.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>229.75</v>
+        <v>224.23</v>
       </c>
       <c r="AG26" t="n">
-        <v>-5.03</v>
+        <v>-6.3</v>
       </c>
       <c r="AK26" t="n">
-        <v>135.42</v>
+        <v>128.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.66</v>
+        <v>-3.65</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="BM26" t="n">
-        <v>31.45</v>
+        <v>33.93</v>
       </c>
       <c r="BN26" t="n">
-        <v>35.9</v>
+        <v>73</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>2697.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B27" t="n">
-        <v>148.7</v>
+        <v>140.8</v>
       </c>
       <c r="C27" t="n">
-        <v>72.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>32.7</v>
+        <v>31.7</v>
       </c>
       <c r="E27" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>42.1</v>
+        <v>40.5</v>
       </c>
       <c r="K27" t="n">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
       <c r="M27" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>33.7</v>
+        <v>33.4</v>
       </c>
       <c r="O27" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="R27" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>7.9</v>
       </c>
-      <c r="W27" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AB27" t="n">
-        <v>-3.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.4</v>
+        <v>12.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>222.86</v>
+        <v>223.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>-6.9</v>
+        <v>-0.88</v>
       </c>
       <c r="AK27" t="n">
-        <v>131.24</v>
+        <v>127.19</v>
       </c>
       <c r="AL27" t="n">
-        <v>-4.18</v>
+        <v>-1.41</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="BM27" t="n">
-        <v>34.46</v>
+        <v>31.16</v>
       </c>
       <c r="BN27" t="n">
-        <v>80.40000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="BO27" t="n">
-        <v>373.6</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>249.4</v>
+        <v>2603.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B28" t="n">
-        <v>149.3</v>
+        <v>139.6</v>
       </c>
       <c r="C28" t="n">
-        <v>74.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E28" t="n">
-        <v>28.8</v>
+        <v>25.9</v>
       </c>
       <c r="F28" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="H28" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="I28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>41.2</v>
+        <v>39.6</v>
       </c>
       <c r="K28" t="n">
-        <v>73.8</v>
+        <v>73.3</v>
       </c>
       <c r="M28" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="N28" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="O28" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="R28" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V28" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W28" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="X28" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="AB28" t="n">
-        <v>-2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>218.37</v>
+        <v>222.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>-4.49</v>
+        <v>-0.44</v>
       </c>
       <c r="AK28" t="n">
-        <v>129.21</v>
+        <v>129.17</v>
       </c>
       <c r="AL28" t="n">
-        <v>-2.03</v>
+        <v>1.98</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="BM28" t="n">
-        <v>35.4</v>
+        <v>32.41</v>
       </c>
       <c r="BN28" t="n">
-        <v>294.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BO28" t="n">
-        <v>227</v>
+        <v>297.8</v>
       </c>
       <c r="BP28" t="n">
-        <v>2758.6</v>
+        <v>2677.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B29" t="n">
-        <v>137</v>
+        <v>133.5</v>
       </c>
       <c r="C29" t="n">
-        <v>65</v>
+        <v>62.3</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>25.2</v>
+        <v>22.5</v>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H29" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J29" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="K29" t="n">
-        <v>70.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M29" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="N29" t="n">
-        <v>32.3</v>
+        <v>30.4</v>
       </c>
       <c r="O29" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="S29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="V29" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="W29" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="X29" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z29" t="n">
-        <v>18</v>
+        <v>20.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.3</v>
+        <v>12.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>220.85</v>
+        <v>222.77</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.48</v>
+        <v>-0.16</v>
       </c>
       <c r="AK29" t="n">
-        <v>129.07</v>
+        <v>130.42</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.14</v>
+        <v>1.25</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="BM29" t="n">
-        <v>32.31</v>
+        <v>26.56</v>
       </c>
       <c r="BN29" t="n">
-        <v>547</v>
+        <v>46.1</v>
       </c>
       <c r="BO29" t="n">
-        <v>85</v>
+        <v>266.8</v>
       </c>
       <c r="BP29" t="n">
-        <v>2654.5</v>
+        <v>2801.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B30" t="n">
-        <v>131.5</v>
+        <v>133.5</v>
       </c>
       <c r="C30" t="n">
-        <v>57.6</v>
+        <v>61.6</v>
       </c>
       <c r="D30" t="n">
-        <v>32.7</v>
+        <v>33.9</v>
       </c>
       <c r="E30" t="n">
-        <v>26.3</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="H30" t="n">
-        <v>23.6</v>
+        <v>25.1</v>
       </c>
       <c r="I30" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="J30" t="n">
-        <v>41.6</v>
+        <v>39.5</v>
       </c>
       <c r="K30" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="N30" t="n">
-        <v>35</v>
+        <v>28.6</v>
       </c>
       <c r="O30" t="n">
-        <v>42.4</v>
+        <v>34.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="R30" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="V30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W30" t="n">
-        <v>24.1</v>
+        <v>26</v>
       </c>
       <c r="X30" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>12.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>14.5</v>
+        <v>11.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.87</v>
+        <v>221.86</v>
       </c>
       <c r="AG30" t="n">
-        <v>5.02</v>
+        <v>-0.91</v>
       </c>
       <c r="AK30" t="n">
-        <v>130.73</v>
+        <v>129.71</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.66</v>
+        <v>-0.71</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="BM30" t="n">
-        <v>31.51</v>
+        <v>31.32</v>
       </c>
       <c r="BN30" t="n">
-        <v>124</v>
+        <v>54.7</v>
       </c>
       <c r="BO30" t="n">
-        <v>164.4</v>
+        <v>235.3</v>
       </c>
       <c r="BP30" t="n">
-        <v>2635.8</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="B31" t="n">
-        <v>129.4</v>
+        <v>120.6</v>
       </c>
       <c r="C31" t="n">
-        <v>52.8</v>
+        <v>47.7</v>
       </c>
       <c r="D31" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="E31" t="n">
-        <v>28.9</v>
+        <v>24.1</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="I31" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>40.8</v>
+        <v>38.4</v>
       </c>
       <c r="K31" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="M31" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>33.1</v>
+        <v>30.3</v>
       </c>
       <c r="O31" t="n">
-        <v>38.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="R31" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V31" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="W31" t="n">
-        <v>22.9</v>
+        <v>27.6</v>
       </c>
       <c r="X31" t="n">
-        <v>16.9</v>
+        <v>19.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>16.1</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF31" t="n">
-        <v>229.48</v>
+        <v>227.49</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.61</v>
+        <v>5.63</v>
       </c>
       <c r="AK31" t="n">
-        <v>132</v>
+        <v>133.39</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.27</v>
+        <v>3.68</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="BM31" t="n">
-        <v>34.36</v>
+        <v>29.84</v>
       </c>
       <c r="BN31" t="n">
-        <v>62.8</v>
+        <v>41.3</v>
       </c>
       <c r="BO31" t="n">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="BP31" t="n">
-        <v>2693.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B32" t="n">
-        <v>130.2</v>
+        <v>116.8</v>
       </c>
       <c r="C32" t="n">
-        <v>56.9</v>
+        <v>45.4</v>
       </c>
       <c r="D32" t="n">
-        <v>33.9</v>
+        <v>35.3</v>
       </c>
       <c r="E32" t="n">
-        <v>26.4</v>
+        <v>23.2</v>
       </c>
       <c r="F32" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="H32" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="I32" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>42.3</v>
+        <v>38</v>
       </c>
       <c r="K32" t="n">
-        <v>75.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="N32" t="n">
-        <v>32.3</v>
+        <v>28.2</v>
       </c>
       <c r="O32" t="n">
-        <v>37.1</v>
+        <v>30.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="V32" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W32" t="n">
-        <v>21.7</v>
+        <v>27.6</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>20.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>15.1</v>
+        <v>17.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>-3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.2</v>
+        <v>14.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF32" t="n">
-        <v>230.54</v>
+        <v>233.56</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.06</v>
+        <v>6.07</v>
       </c>
       <c r="AK32" t="n">
-        <v>132.25</v>
+        <v>137.14</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.25</v>
+        <v>3.75</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="BM32" t="n">
-        <v>32.26</v>
+        <v>26.51</v>
       </c>
       <c r="BN32" t="n">
-        <v>28.3</v>
+        <v>107.4</v>
       </c>
       <c r="BO32" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="BP32" t="n">
-        <v>2545.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B33" t="n">
-        <v>138.4</v>
+        <v>102.9</v>
       </c>
       <c r="C33" t="n">
-        <v>66.90000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="D33" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>25.9</v>
+        <v>19.8</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
-        <v>23.6</v>
+        <v>21.7</v>
       </c>
       <c r="I33" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>42.8</v>
+        <v>34</v>
       </c>
       <c r="K33" t="n">
-        <v>75.8</v>
+        <v>65.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="N33" t="n">
-        <v>32.3</v>
+        <v>27</v>
       </c>
       <c r="O33" t="n">
-        <v>35.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W33" t="n">
-        <v>15.7</v>
+        <v>30.6</v>
       </c>
       <c r="X33" t="n">
-        <v>12.3</v>
+        <v>23.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.7</v>
+        <v>15.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>10.3</v>
+        <v>18.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>-6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.1</v>
+        <v>16.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.8</v>
+        <v>12.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>224.23</v>
+        <v>234.94</v>
       </c>
       <c r="AG33" t="n">
-        <v>-6.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK33" t="n">
-        <v>128.6</v>
+        <v>137.51</v>
       </c>
       <c r="AL33" t="n">
-        <v>-3.65</v>
+        <v>0.37</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="BM33" t="n">
-        <v>33.93</v>
+        <v>20.4</v>
       </c>
       <c r="BN33" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2697.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="B34" t="n">
-        <v>140.8</v>
+        <v>93.2</v>
       </c>
       <c r="C34" t="n">
-        <v>73.09999999999999</v>
+        <v>36.3</v>
       </c>
       <c r="D34" t="n">
-        <v>31.7</v>
+        <v>32.7</v>
       </c>
       <c r="E34" t="n">
-        <v>26.1</v>
+        <v>17</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H34" t="n">
-        <v>23.6</v>
+        <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J34" t="n">
-        <v>40.5</v>
+        <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>73.5</v>
+        <v>51.2</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="N34" t="n">
-        <v>33.4</v>
+        <v>25.5</v>
       </c>
       <c r="O34" t="n">
-        <v>39.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="R34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="V34" t="n">
-        <v>6.8</v>
+        <v>15.8</v>
       </c>
       <c r="W34" t="n">
-        <v>11</v>
+        <v>33.6</v>
       </c>
       <c r="X34" t="n">
-        <v>8.9</v>
+        <v>24.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
       <c r="AA34" t="n">
-        <v>7.9</v>
+        <v>16.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>-1.2</v>
+        <v>4</v>
       </c>
       <c r="AC34" t="n">
-        <v>12.6</v>
+        <v>10.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AF34" t="n">
-        <v>223.36</v>
+        <v>229.19</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.88</v>
+        <v>-5.75</v>
       </c>
       <c r="AK34" t="n">
-        <v>127.19</v>
+        <v>138.98</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="BM34" t="n">
-        <v>31.16</v>
+        <v>19.88</v>
       </c>
       <c r="BN34" t="n">
-        <v>21.2</v>
+        <v>35.1</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2603.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B35" t="n">
-        <v>139.6</v>
+        <v>120.3</v>
       </c>
       <c r="C35" t="n">
-        <v>69.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="D35" t="n">
-        <v>32.2</v>
+        <v>36.3</v>
       </c>
       <c r="E35" t="n">
-        <v>25.9</v>
+        <v>20.6</v>
       </c>
       <c r="F35" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H35" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
       </c>
       <c r="I35" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
-        <v>39.6</v>
+        <v>35.4</v>
       </c>
       <c r="K35" t="n">
-        <v>73.3</v>
+        <v>66</v>
       </c>
       <c r="M35" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="N35" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="O35" t="n">
-        <v>40.1</v>
+        <v>26.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.8</v>
+        <v>18.3</v>
       </c>
       <c r="R35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>23.8</v>
+        <v>18.3</v>
       </c>
       <c r="V35" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="W35" t="n">
-        <v>15.2</v>
+        <v>22.5</v>
       </c>
       <c r="X35" t="n">
-        <v>10.9</v>
+        <v>20.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z35" t="n">
-        <v>13.6</v>
+        <v>16.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>222.92</v>
+        <v>224.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.44</v>
+        <v>-4.28</v>
       </c>
       <c r="AK35" t="n">
-        <v>129.17</v>
+        <v>134.04</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.98</v>
+        <v>-4.94</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="BM35" t="n">
-        <v>32.41</v>
+        <v>22.59</v>
       </c>
       <c r="BN35" t="n">
-        <v>74.59999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="BO35" t="n">
-        <v>297.8</v>
+        <v>0</v>
       </c>
       <c r="BP35" t="n">
-        <v>2677.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B36" t="n">
-        <v>133.5</v>
+        <v>131.1</v>
       </c>
       <c r="C36" t="n">
-        <v>62.3</v>
+        <v>60.2</v>
       </c>
       <c r="D36" t="n">
-        <v>34</v>
+        <v>35.6</v>
       </c>
       <c r="E36" t="n">
-        <v>22.5</v>
+        <v>24.2</v>
       </c>
       <c r="F36" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="H36" t="n">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="I36" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>40.8</v>
+        <v>38.2</v>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M36" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="N36" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="O36" t="n">
-        <v>37.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V36" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y36" t="n">
         <v>4.9</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V36" t="n">
-        <v>4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X36" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z36" t="n">
-        <v>20.2</v>
+        <v>12.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="AC36" t="n">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>222.77</v>
+        <v>220.83</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.16</v>
+        <v>-4.08</v>
       </c>
       <c r="AK36" t="n">
-        <v>130.42</v>
+        <v>131.01</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.25</v>
+        <v>-3.03</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="BM36" t="n">
-        <v>26.56</v>
+        <v>29.62</v>
       </c>
       <c r="BN36" t="n">
-        <v>46.1</v>
+        <v>58.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>266.8</v>
+        <v>0</v>
       </c>
       <c r="BP36" t="n">
-        <v>2801.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B37" t="n">
-        <v>133.5</v>
+        <v>117.2</v>
       </c>
       <c r="C37" t="n">
-        <v>61.6</v>
+        <v>53.7</v>
       </c>
       <c r="D37" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="F37" t="n">
         <v>2.2</v>
       </c>
       <c r="H37" t="n">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="I37" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="J37" t="n">
-        <v>39.5</v>
+        <v>37</v>
       </c>
       <c r="K37" t="n">
-        <v>74.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="M37" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="N37" t="n">
-        <v>28.6</v>
+        <v>31.4</v>
       </c>
       <c r="O37" t="n">
-        <v>34.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="R37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="V37" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="W37" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="X37" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>12.9</v>
+        <v>16.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="AF37" t="n">
-        <v>221.86</v>
+        <v>228.06</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.91</v>
+        <v>7.23</v>
       </c>
       <c r="AK37" t="n">
-        <v>129.71</v>
+        <v>131.96</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.71</v>
+        <v>0.95</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="BM37" t="n">
-        <v>31.32</v>
+        <v>23.82</v>
       </c>
       <c r="BN37" t="n">
-        <v>54.7</v>
+        <v>49.9</v>
       </c>
       <c r="BO37" t="n">
-        <v>235.3</v>
+        <v>0</v>
       </c>
       <c r="BP37" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B38" t="n">
-        <v>120.6</v>
+        <v>112.8</v>
       </c>
       <c r="C38" t="n">
-        <v>47.7</v>
+        <v>42.7</v>
       </c>
       <c r="D38" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="E38" t="n">
-        <v>24.1</v>
+        <v>20.7</v>
       </c>
       <c r="F38" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H38" t="n">
-        <v>24.9</v>
+        <v>21.2</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="J38" t="n">
-        <v>38.4</v>
+        <v>36.8</v>
       </c>
       <c r="K38" t="n">
-        <v>73.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>30.3</v>
+        <v>27.9</v>
       </c>
       <c r="O38" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="V38" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="W38" t="n">
-        <v>27.6</v>
+        <v>31.2</v>
       </c>
       <c r="X38" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="Y38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC38" t="n">
         <v>11.1</v>
       </c>
-      <c r="Z38" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AD38" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>227.49</v>
+        <v>233.59</v>
       </c>
       <c r="AG38" t="n">
-        <v>5.63</v>
+        <v>5.53</v>
       </c>
       <c r="AK38" t="n">
-        <v>133.39</v>
+        <v>132.79</v>
       </c>
       <c r="AL38" t="n">
-        <v>3.68</v>
+        <v>0.83</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="BM38" t="n">
-        <v>29.84</v>
+        <v>23.43</v>
       </c>
       <c r="BN38" t="n">
-        <v>41.3</v>
+        <v>83.8</v>
       </c>
       <c r="BO38" t="n">
         <v>0</v>
@@ -4374,46 +4458,46 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B39" t="n">
-        <v>116.8</v>
+        <v>109.2</v>
       </c>
       <c r="C39" t="n">
-        <v>45.4</v>
+        <v>41.3</v>
       </c>
       <c r="D39" t="n">
-        <v>35.3</v>
+        <v>34.9</v>
       </c>
       <c r="E39" t="n">
-        <v>23.2</v>
+        <v>21.2</v>
       </c>
       <c r="F39" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="H39" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="I39" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K39" t="n">
-        <v>70.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N39" t="n">
-        <v>28.2</v>
+        <v>25</v>
       </c>
       <c r="O39" t="n">
-        <v>30.3</v>
+        <v>26.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4422,55 +4506,55 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="V39" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="W39" t="n">
-        <v>27.6</v>
+        <v>35.4</v>
       </c>
       <c r="X39" t="n">
-        <v>20.9</v>
+        <v>25.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>13.4</v>
+        <v>16.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>21</v>
+        <v>25.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>17.2</v>
+        <v>21.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AC39" t="n">
-        <v>14.9</v>
+        <v>10.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>233.56</v>
+        <v>231.92</v>
       </c>
       <c r="AG39" t="n">
-        <v>6.07</v>
+        <v>-1.67</v>
       </c>
       <c r="AK39" t="n">
-        <v>137.14</v>
+        <v>136.54</v>
       </c>
       <c r="AL39" t="n">
         <v>3.75</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="BM39" t="n">
-        <v>26.51</v>
+        <v>25.29</v>
       </c>
       <c r="BN39" t="n">
-        <v>107.4</v>
+        <v>170.5</v>
       </c>
       <c r="BO39" t="n">
         <v>0</v>
@@ -4481,46 +4565,46 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B40" t="n">
-        <v>102.9</v>
+        <v>108.1</v>
       </c>
       <c r="C40" t="n">
-        <v>36.8</v>
+        <v>39.3</v>
       </c>
       <c r="D40" t="n">
         <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="F40" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="H40" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="I40" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K40" t="n">
-        <v>65.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="N40" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O40" t="n">
-        <v>29.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4529,55 +4613,55 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="W40" t="n">
-        <v>30.6</v>
+        <v>33.8</v>
       </c>
       <c r="X40" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="Y40" t="n">
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>16.7</v>
+        <v>13</v>
       </c>
       <c r="AD40" t="n">
-        <v>12.8</v>
+        <v>9.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>234.94</v>
+        <v>235</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.38</v>
+        <v>3.09</v>
       </c>
       <c r="AK40" t="n">
-        <v>137.51</v>
+        <v>136.61</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.37</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="BM40" t="n">
-        <v>20.4</v>
+        <v>20.23</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="BO40" t="n">
         <v>0</v>
@@ -4588,103 +4672,103 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B41" t="n">
-        <v>93.2</v>
+        <v>101</v>
       </c>
       <c r="C41" t="n">
+        <v>37</v>
+      </c>
+      <c r="D41" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K41" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N41" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>17</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>17</v>
+      </c>
+      <c r="V41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W41" t="n">
         <v>36.3</v>
       </c>
-      <c r="D41" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E41" t="n">
-        <v>17</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H41" t="n">
+      <c r="X41" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AA41" t="n">
         <v>16</v>
       </c>
-      <c r="I41" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>25</v>
-      </c>
-      <c r="K41" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N41" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="X41" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>16.9</v>
-      </c>
       <c r="AB41" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>10.1</v>
+        <v>14.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AF41" t="n">
-        <v>229.19</v>
+        <v>233.68</v>
       </c>
       <c r="AG41" t="n">
-        <v>-5.75</v>
+        <v>-1.32</v>
       </c>
       <c r="AK41" t="n">
-        <v>138.98</v>
+        <v>136.95</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.47</v>
+        <v>0.34</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="BM41" t="n">
-        <v>19.88</v>
+        <v>23.7</v>
       </c>
       <c r="BN41" t="n">
-        <v>35.1</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="BO41" t="n">
         <v>0</v>
@@ -4695,46 +4779,46 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B42" t="n">
-        <v>120.3</v>
+        <v>113.4</v>
       </c>
       <c r="C42" t="n">
-        <v>53.3</v>
+        <v>40.9</v>
       </c>
       <c r="D42" t="n">
-        <v>36.3</v>
+        <v>34.8</v>
       </c>
       <c r="E42" t="n">
-        <v>20.6</v>
+        <v>27.9</v>
       </c>
       <c r="F42" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="H42" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="I42" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J42" t="n">
-        <v>35.4</v>
+        <v>32.2</v>
       </c>
       <c r="K42" t="n">
-        <v>66</v>
+        <v>64.3</v>
       </c>
       <c r="M42" t="n">
         <v>1.9</v>
       </c>
       <c r="N42" t="n">
-        <v>24.8</v>
+        <v>27.3</v>
       </c>
       <c r="O42" t="n">
-        <v>26.7</v>
+        <v>29.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>18.3</v>
+        <v>20.3</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -4743,55 +4827,55 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>18.3</v>
+        <v>20.3</v>
       </c>
       <c r="V42" t="n">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="W42" t="n">
-        <v>22.5</v>
+        <v>32.8</v>
       </c>
       <c r="X42" t="n">
-        <v>20.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>9.699999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>16.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>13.8</v>
+        <v>17.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.5</v>
+        <v>13.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AF42" t="n">
-        <v>224.91</v>
+        <v>234.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>-4.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AK42" t="n">
-        <v>134.04</v>
+        <v>136.49</v>
       </c>
       <c r="AL42" t="n">
-        <v>-4.94</v>
+        <v>-0.46</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="BM42" t="n">
-        <v>22.59</v>
+        <v>28.89</v>
       </c>
       <c r="BN42" t="n">
-        <v>48.3</v>
+        <v>152.3</v>
       </c>
       <c r="BO42" t="n">
         <v>0</v>
@@ -4802,46 +4886,46 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B43" t="n">
-        <v>131.1</v>
+        <v>115.6</v>
       </c>
       <c r="C43" t="n">
-        <v>60.2</v>
+        <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>35.6</v>
+        <v>36.1</v>
       </c>
       <c r="E43" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="I43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J43" t="n">
-        <v>38.2</v>
+        <v>36.7</v>
       </c>
       <c r="K43" t="n">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N43" t="n">
-        <v>30.2</v>
+        <v>27.8</v>
       </c>
       <c r="O43" t="n">
-        <v>31.9</v>
+        <v>29.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -4850,55 +4934,55 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="V43" t="n">
-        <v>14.1</v>
+        <v>17.8</v>
       </c>
       <c r="W43" t="n">
-        <v>20.2</v>
+        <v>22</v>
       </c>
       <c r="X43" t="n">
-        <v>17.1</v>
+        <v>19.9</v>
       </c>
       <c r="Y43" t="n">
-        <v>4.9</v>
+        <v>13.4</v>
       </c>
       <c r="Z43" t="n">
-        <v>12.5</v>
+        <v>19.9</v>
       </c>
       <c r="AA43" t="n">
-        <v>9.6</v>
+        <v>18.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0</v>
+        <v>0.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AF43" t="n">
-        <v>220.83</v>
+        <v>237.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>-4.08</v>
+        <v>3.48</v>
       </c>
       <c r="AK43" t="n">
-        <v>131.01</v>
+        <v>137.25</v>
       </c>
       <c r="AL43" t="n">
-        <v>-3.03</v>
+        <v>0.76</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="BM43" t="n">
-        <v>29.62</v>
+        <v>25.43</v>
       </c>
       <c r="BN43" t="n">
-        <v>58.2</v>
+        <v>271.8</v>
       </c>
       <c r="BO43" t="n">
         <v>0</v>
@@ -4909,103 +4993,103 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B44" t="n">
-        <v>117.2</v>
+        <v>121.1</v>
       </c>
       <c r="C44" t="n">
-        <v>53.7</v>
+        <v>46.6</v>
       </c>
       <c r="D44" t="n">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="E44" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="F44" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="H44" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="I44" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>37</v>
+        <v>32.3</v>
       </c>
       <c r="K44" t="n">
-        <v>69.8</v>
+        <v>64.2</v>
       </c>
       <c r="M44" t="n">
         <v>1.9</v>
       </c>
       <c r="N44" t="n">
-        <v>31.4</v>
+        <v>25.2</v>
       </c>
       <c r="O44" t="n">
-        <v>33.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q44" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V44" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W44" t="n">
         <v>22.3</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V44" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>26.1</v>
-      </c>
       <c r="X44" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z44" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y44" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>16.8</v>
-      </c>
       <c r="AA44" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="AF44" t="n">
-        <v>228.06</v>
+        <v>228.13</v>
       </c>
       <c r="AG44" t="n">
-        <v>7.23</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="AK44" t="n">
-        <v>131.96</v>
+        <v>136.92</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.95</v>
+        <v>-0.33</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="BM44" t="n">
-        <v>23.82</v>
+        <v>27.54</v>
       </c>
       <c r="BN44" t="n">
-        <v>49.9</v>
+        <v>447.8</v>
       </c>
       <c r="BO44" t="n">
         <v>0</v>
@@ -5016,46 +5100,46 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B45" t="n">
-        <v>112.8</v>
+        <v>127</v>
       </c>
       <c r="C45" t="n">
-        <v>42.7</v>
+        <v>51.3</v>
       </c>
       <c r="D45" t="n">
-        <v>34.6</v>
+        <v>36.1</v>
       </c>
       <c r="E45" t="n">
-        <v>20.7</v>
+        <v>23.5</v>
       </c>
       <c r="F45" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="H45" t="n">
-        <v>21.2</v>
+        <v>24.3</v>
       </c>
       <c r="I45" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J45" t="n">
-        <v>36.8</v>
+        <v>38.8</v>
       </c>
       <c r="K45" t="n">
-        <v>67.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="N45" t="n">
-        <v>27.9</v>
+        <v>24.7</v>
       </c>
       <c r="O45" t="n">
-        <v>29.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5064,55 +5148,55 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="V45" t="n">
-        <v>11.9</v>
+        <v>14.7</v>
       </c>
       <c r="W45" t="n">
-        <v>31.2</v>
+        <v>18.6</v>
       </c>
       <c r="X45" t="n">
-        <v>21.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>21.4</v>
+        <v>14.6</v>
       </c>
       <c r="AA45" t="n">
-        <v>19.7</v>
+        <v>14.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>11.1</v>
+        <v>12.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AF45" t="n">
-        <v>233.59</v>
+        <v>224.64</v>
       </c>
       <c r="AG45" t="n">
-        <v>5.53</v>
+        <v>-3.49</v>
       </c>
       <c r="AK45" t="n">
-        <v>132.79</v>
+        <v>132.56</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.83</v>
+        <v>-4.36</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="BM45" t="n">
-        <v>23.43</v>
+        <v>28.03</v>
       </c>
       <c r="BN45" t="n">
-        <v>83.8</v>
+        <v>526.8</v>
       </c>
       <c r="BO45" t="n">
         <v>0</v>
@@ -5123,46 +5207,46 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B46" t="n">
-        <v>109.2</v>
+        <v>121.3</v>
       </c>
       <c r="C46" t="n">
-        <v>41.3</v>
+        <v>50.7</v>
       </c>
       <c r="D46" t="n">
-        <v>34.9</v>
+        <v>36.1</v>
       </c>
       <c r="E46" t="n">
-        <v>21.2</v>
+        <v>19.2</v>
       </c>
       <c r="F46" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>21.9</v>
+        <v>23.6</v>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="J46" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K46" t="n">
-        <v>66.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="M46" t="n">
         <v>1.9</v>
       </c>
       <c r="N46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O46" t="n">
-        <v>26.9</v>
+        <v>27.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5171,55 +5255,55 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
       <c r="V46" t="n">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="W46" t="n">
-        <v>35.4</v>
+        <v>22.9</v>
       </c>
       <c r="X46" t="n">
-        <v>25.6</v>
+        <v>18.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>16.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>25.8</v>
+        <v>16.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>21.2</v>
+        <v>11.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>10.4</v>
+        <v>12.7</v>
       </c>
       <c r="AD46" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="AF46" t="n">
-        <v>231.92</v>
+        <v>223.71</v>
       </c>
       <c r="AG46" t="n">
-        <v>-1.67</v>
+        <v>-0.93</v>
       </c>
       <c r="AK46" t="n">
-        <v>136.54</v>
+        <v>130.87</v>
       </c>
       <c r="AL46" t="n">
-        <v>3.75</v>
+        <v>-1.69</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="BM46" t="n">
-        <v>25.29</v>
+        <v>23.64</v>
       </c>
       <c r="BN46" t="n">
-        <v>170.5</v>
+        <v>28.7</v>
       </c>
       <c r="BO46" t="n">
         <v>0</v>
@@ -5230,103 +5314,103 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="B47" t="n">
-        <v>108.1</v>
+        <v>110.6</v>
       </c>
       <c r="C47" t="n">
-        <v>39.3</v>
+        <v>42.8</v>
       </c>
       <c r="D47" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E47" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="F47" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>21.9</v>
+        <v>22.7</v>
       </c>
       <c r="I47" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="J47" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>66.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>1.9</v>
       </c>
       <c r="N47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O47" t="n">
-        <v>26.9</v>
+        <v>27.9</v>
       </c>
       <c r="Q47" t="n">
+        <v>19</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>19</v>
+      </c>
+      <c r="V47" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="X47" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>226.76</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>131.98</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BL47" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="BN47" t="n">
         <v>16</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>16</v>
-      </c>
-      <c r="V47" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="X47" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>235</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>136.61</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL47" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="BN47" t="n">
-        <v>91.09999999999999</v>
       </c>
       <c r="BO47" t="n">
         <v>0</v>
@@ -5337,46 +5421,46 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46292</v>
+        <v>46299</v>
       </c>
       <c r="B48" t="n">
-        <v>101</v>
+        <v>101.4</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="D48" t="n">
-        <v>32.4</v>
+        <v>33.3</v>
       </c>
       <c r="E48" t="n">
-        <v>23.5</v>
+        <v>16.7</v>
       </c>
       <c r="F48" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="H48" t="n">
-        <v>17.9</v>
+        <v>22.7</v>
       </c>
       <c r="I48" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="J48" t="n">
-        <v>29.9</v>
+        <v>36.2</v>
       </c>
       <c r="K48" t="n">
-        <v>56.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>24.2</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>26.2</v>
+        <v>29</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5385,55 +5469,55 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
       <c r="V48" t="n">
-        <v>19.5</v>
+        <v>16.7</v>
       </c>
       <c r="W48" t="n">
-        <v>36.3</v>
+        <v>22.9</v>
       </c>
       <c r="X48" t="n">
-        <v>27.9</v>
+        <v>19.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>13.6</v>
+        <v>11.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>16.9</v>
+        <v>22.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AC48" t="n">
-        <v>14.2</v>
+        <v>9.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>8.800000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>233.68</v>
+        <v>234.88</v>
       </c>
       <c r="AG48" t="n">
-        <v>-1.32</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AK48" t="n">
-        <v>136.95</v>
+        <v>136.09</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.34</v>
+        <v>4.11</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46292</v>
+        <v>46299</v>
       </c>
       <c r="BM48" t="n">
-        <v>23.7</v>
+        <v>20.48</v>
       </c>
       <c r="BN48" t="n">
-        <v>79.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="BO48" t="n">
         <v>0</v>
@@ -5444,46 +5528,46 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="B49" t="n">
-        <v>113.4</v>
+        <v>106.8</v>
       </c>
       <c r="C49" t="n">
-        <v>40.9</v>
+        <v>38.4</v>
       </c>
       <c r="D49" t="n">
-        <v>34.8</v>
+        <v>36</v>
       </c>
       <c r="E49" t="n">
-        <v>27.9</v>
+        <v>22.1</v>
       </c>
       <c r="F49" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="H49" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="I49" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J49" t="n">
-        <v>32.2</v>
+        <v>36.4</v>
       </c>
       <c r="K49" t="n">
-        <v>64.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="O49" t="n">
-        <v>29.2</v>
+        <v>29.9</v>
       </c>
       <c r="Q49" t="n">
-        <v>20.3</v>
+        <v>12</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -5492,55 +5576,55 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>20.3</v>
+        <v>12</v>
       </c>
       <c r="V49" t="n">
-        <v>22.2</v>
+        <v>15.5</v>
       </c>
       <c r="W49" t="n">
-        <v>32.8</v>
+        <v>22.4</v>
       </c>
       <c r="X49" t="n">
-        <v>27.5</v>
+        <v>18.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>19.3</v>
+        <v>20.7</v>
       </c>
       <c r="AA49" t="n">
-        <v>17.5</v>
+        <v>18.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>234.37</v>
+        <v>236.72</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="AK49" t="n">
-        <v>136.49</v>
+        <v>138.83</v>
       </c>
       <c r="AL49" t="n">
-        <v>-0.46</v>
+        <v>2.74</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="BM49" t="n">
-        <v>28.89</v>
+        <v>24.5</v>
       </c>
       <c r="BN49" t="n">
-        <v>152.3</v>
+        <v>55.6</v>
       </c>
       <c r="BO49" t="n">
         <v>0</v>
@@ -5551,46 +5635,46 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="B50" t="n">
-        <v>115.6</v>
+        <v>108.3</v>
       </c>
       <c r="C50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D50" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="E50" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="F50" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="H50" t="n">
-        <v>23.6</v>
+        <v>22.5</v>
       </c>
       <c r="I50" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
-        <v>36.7</v>
+        <v>36.2</v>
       </c>
       <c r="K50" t="n">
-        <v>69.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="M50" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>27.8</v>
+        <v>29.2</v>
       </c>
       <c r="O50" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.5</v>
+        <v>13.6</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -5599,55 +5683,55 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>20.5</v>
+        <v>13.6</v>
       </c>
       <c r="V50" t="n">
-        <v>17.8</v>
+        <v>15.7</v>
       </c>
       <c r="W50" t="n">
-        <v>22</v>
+        <v>27.9</v>
       </c>
       <c r="X50" t="n">
-        <v>19.9</v>
+        <v>21.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="AD50" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>237.85</v>
+        <v>237.89</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.48</v>
+        <v>1.18</v>
       </c>
       <c r="AK50" t="n">
-        <v>137.25</v>
+        <v>140.91</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.76</v>
+        <v>2.08</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="BM50" t="n">
-        <v>25.43</v>
+        <v>28.04</v>
       </c>
       <c r="BN50" t="n">
-        <v>271.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="BO50" t="n">
         <v>0</v>
@@ -5658,46 +5742,46 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="B51" t="n">
-        <v>121.1</v>
+        <v>118.7</v>
       </c>
       <c r="C51" t="n">
-        <v>46.6</v>
+        <v>43</v>
       </c>
       <c r="D51" t="n">
-        <v>37</v>
+        <v>35.9</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="F51" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="H51" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J51" t="n">
-        <v>32.3</v>
+        <v>35.7</v>
       </c>
       <c r="K51" t="n">
-        <v>64.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="N51" t="n">
-        <v>25.2</v>
+        <v>29.1</v>
       </c>
       <c r="O51" t="n">
-        <v>27.1</v>
+        <v>29.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>19.7</v>
+        <v>15.6</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -5706,55 +5790,55 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>19.7</v>
+        <v>15.6</v>
       </c>
       <c r="V51" t="n">
-        <v>16.6</v>
+        <v>15.5</v>
       </c>
       <c r="W51" t="n">
-        <v>22.3</v>
+        <v>29.6</v>
       </c>
       <c r="X51" t="n">
-        <v>19.5</v>
+        <v>22.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>8.800000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="Z51" t="n">
-        <v>17.6</v>
+        <v>19.1</v>
       </c>
       <c r="AA51" t="n">
-        <v>14.3</v>
+        <v>17.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="AC51" t="n">
         <v>11.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF51" t="n">
-        <v>228.13</v>
+        <v>233.22</v>
       </c>
       <c r="AG51" t="n">
-        <v>-9.720000000000001</v>
+        <v>-4.67</v>
       </c>
       <c r="AK51" t="n">
-        <v>136.92</v>
+        <v>140.5</v>
       </c>
       <c r="AL51" t="n">
-        <v>-0.33</v>
+        <v>-0.41</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="BM51" t="n">
-        <v>27.54</v>
+        <v>28.61</v>
       </c>
       <c r="BN51" t="n">
-        <v>447.8</v>
+        <v>6.9</v>
       </c>
       <c r="BO51" t="n">
         <v>0</v>
@@ -5765,46 +5849,46 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="B52" t="n">
-        <v>127</v>
+        <v>124.1</v>
       </c>
       <c r="C52" t="n">
-        <v>51.3</v>
+        <v>46.3</v>
       </c>
       <c r="D52" t="n">
-        <v>36.1</v>
+        <v>37</v>
       </c>
       <c r="E52" t="n">
-        <v>23.5</v>
+        <v>28.89</v>
       </c>
       <c r="F52" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="H52" t="n">
-        <v>24.3</v>
+        <v>23.8</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J52" t="n">
-        <v>38.8</v>
+        <v>37.5</v>
       </c>
       <c r="K52" t="n">
-        <v>72.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="M52" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="N52" t="n">
-        <v>24.7</v>
+        <v>29</v>
       </c>
       <c r="O52" t="n">
-        <v>26.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>20.2</v>
+        <v>17.8</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5813,55 +5897,55 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>20.2</v>
+        <v>17.8</v>
       </c>
       <c r="V52" t="n">
-        <v>14.7</v>
+        <v>16.9</v>
       </c>
       <c r="W52" t="n">
-        <v>18.6</v>
+        <v>22</v>
       </c>
       <c r="X52" t="n">
-        <v>16.6</v>
+        <v>19.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>10.2</v>
+        <v>12.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>14.6</v>
+        <v>18.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="AC52" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF52" t="n">
-        <v>224.64</v>
+        <v>226.46</v>
       </c>
       <c r="AG52" t="n">
-        <v>-3.49</v>
+        <v>-6.77</v>
       </c>
       <c r="AK52" t="n">
-        <v>132.56</v>
+        <v>138.43</v>
       </c>
       <c r="AL52" t="n">
-        <v>-4.36</v>
+        <v>-2.07</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="BM52" t="n">
-        <v>28.03</v>
+        <v>29.82</v>
       </c>
       <c r="BN52" t="n">
-        <v>526.8</v>
+        <v>21.5</v>
       </c>
       <c r="BO52" t="n">
         <v>0</v>
@@ -5872,46 +5956,46 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="B53" t="n">
-        <v>122.4</v>
+        <v>127.5</v>
       </c>
       <c r="C53" t="n">
-        <v>50.7</v>
+        <v>48.1</v>
       </c>
       <c r="D53" t="n">
-        <v>36.1</v>
+        <v>37.3</v>
       </c>
       <c r="E53" t="n">
-        <v>25.73</v>
+        <v>28.38</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="H53" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I53" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K53" t="n">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="N53" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O53" t="n">
-        <v>27.9</v>
+        <v>29.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>20.5</v>
+        <v>17.2</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5920,105 +6004,93 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>20.5</v>
+        <v>17.2</v>
       </c>
       <c r="V53" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="W53" t="n">
-        <v>22.9</v>
+        <v>16.8</v>
       </c>
       <c r="X53" t="n">
-        <v>18.6</v>
+        <v>15.8</v>
       </c>
       <c r="Y53" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="AA53" t="n">
-        <v>11.9</v>
+        <v>13.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AC53" t="n">
-        <v>12.7</v>
+        <v>15.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.6</v>
+        <v>10.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>223.71</v>
+        <v>220.99</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.93</v>
+        <v>-5.46</v>
       </c>
       <c r="AK53" t="n">
-        <v>130.87</v>
+        <v>128.95</v>
       </c>
       <c r="AL53" t="n">
-        <v>-1.69</v>
+        <v>-9.48</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>23.64</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>0</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="B54" t="n">
-        <v>112</v>
+        <v>115.7</v>
       </c>
       <c r="C54" t="n">
-        <v>42.8</v>
+        <v>45.4</v>
       </c>
       <c r="D54" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E54" t="n">
-        <v>24.44</v>
+        <v>22.05</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="H54" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="I54" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>38</v>
       </c>
       <c r="K54" t="n">
-        <v>68.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="M54" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="N54" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O54" t="n">
-        <v>27.9</v>
+        <v>29.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>17.2</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -6027,105 +6099,54 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>19</v>
-      </c>
-      <c r="V54" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W54" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="X54" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>226.76</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>131.98</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.11</v>
+        <v>17.2</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="BM54" t="n">
-        <v>25.87</v>
-      </c>
-      <c r="BN54" t="n">
-        <v>16</v>
-      </c>
-      <c r="BO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP54" t="n">
-        <v>0</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="B55" t="n">
-        <v>101.4</v>
+        <v>109.9</v>
       </c>
       <c r="C55" t="n">
-        <v>38.1</v>
+        <v>41.6</v>
       </c>
       <c r="D55" t="n">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
       <c r="E55" t="n">
-        <v>16.7</v>
+        <v>21.05</v>
       </c>
       <c r="F55" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="H55" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="I55" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>36.2</v>
+        <v>38</v>
       </c>
       <c r="K55" t="n">
-        <v>68.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N55" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O55" t="n">
-        <v>29</v>
+        <v>29.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6134,105 +6155,30 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V55" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="W55" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X55" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>234.88</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>136.09</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>4.11</v>
+        <v>17.2</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B56" t="n">
-        <v>106.8</v>
-      </c>
-      <c r="C56" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="D56" t="n">
-        <v>36</v>
+        <v>22.4</v>
       </c>
       <c r="E56" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H56" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J56" t="n">
-        <v>36.4</v>
+        <v>22.39</v>
       </c>
       <c r="K56" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>28.9</v>
+        <v>4.6</v>
       </c>
       <c r="O56" t="n">
-        <v>29.9</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6241,105 +6187,30 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>12</v>
-      </c>
-      <c r="V56" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W56" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X56" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>236.72</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>138.83</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2.74</v>
+        <v>15.8</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="B57" t="n">
-        <v>108.3</v>
-      </c>
-      <c r="C57" t="n">
-        <v>38</v>
-      </c>
-      <c r="D57" t="n">
-        <v>36.2</v>
+        <v>26.3</v>
       </c>
       <c r="E57" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F57" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>36.2</v>
+        <v>26.27</v>
       </c>
       <c r="K57" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>29.2</v>
+        <v>7.3</v>
       </c>
       <c r="O57" t="n">
-        <v>30.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6348,105 +6219,30 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="V57" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="W57" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="X57" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>237.89</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>140.91</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>2.08</v>
+        <v>15.8</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="BO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP57" t="n">
-        <v>0</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="B58" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="C58" t="n">
-        <v>43</v>
-      </c>
-      <c r="D58" t="n">
-        <v>35.9</v>
+        <v>27.2</v>
       </c>
       <c r="E58" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F58" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H58" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>35.7</v>
+        <v>27.18</v>
       </c>
       <c r="K58" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N58" t="n">
-        <v>29.1</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
-        <v>29.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6455,105 +6251,30 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="V58" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W58" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="X58" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Y58" t="n">
         <v>15.8</v>
       </c>
-      <c r="Z58" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>233.22</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>140.5</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-0.41</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>28.61</v>
-      </c>
-      <c r="BN58" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="BO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP58" t="n">
-        <v>0</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="B59" t="n">
-        <v>124.1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>37</v>
+        <v>28.7</v>
       </c>
       <c r="E59" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="F59" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H59" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J59" t="n">
-        <v>37.5</v>
+        <v>28.7</v>
       </c>
       <c r="K59" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N59" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="O59" t="n">
-        <v>29.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6562,105 +6283,30 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V59" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W59" t="n">
-        <v>22</v>
-      </c>
-      <c r="X59" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>226.46</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>-6.77</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>138.43</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>-2.07</v>
+        <v>15.8</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="BM59" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="BN59" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="BO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP59" t="n">
-        <v>0</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B60" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="C60" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>37.3</v>
+        <v>28.8</v>
       </c>
       <c r="E60" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="F60" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I60" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J60" t="n">
-        <v>38</v>
+        <v>28.8</v>
       </c>
       <c r="K60" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N60" t="n">
-        <v>29</v>
+        <v>9.1</v>
       </c>
       <c r="O60" t="n">
-        <v>29.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6669,93 +6315,30 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="V60" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W60" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X60" t="n">
         <v>15.8</v>
       </c>
-      <c r="Y60" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>220.99</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>-5.46</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>128.95</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>-9.48</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B61" t="n">
-        <v>115.7</v>
-      </c>
-      <c r="C61" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="D61" t="n">
-        <v>36</v>
+        <v>24.9</v>
       </c>
       <c r="E61" t="n">
-        <v>22.05</v>
-      </c>
-      <c r="F61" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="K61" t="n">
         <v>6.4</v>
       </c>
-      <c r="H61" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I61" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J61" t="n">
-        <v>38</v>
-      </c>
-      <c r="K61" t="n">
-        <v>70</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N61" t="n">
-        <v>29</v>
-      </c>
       <c r="O61" t="n">
-        <v>29.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q61" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6764,54 +6347,30 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B62" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="C62" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="D62" t="n">
-        <v>35.7</v>
+        <v>21.2</v>
       </c>
       <c r="E62" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F62" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H62" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I62" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J62" t="n">
-        <v>38</v>
+        <v>21.2</v>
       </c>
       <c r="K62" t="n">
-        <v>70</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N62" t="n">
-        <v>29</v>
+        <v>3.8</v>
       </c>
       <c r="O62" t="n">
-        <v>29.7</v>
+        <v>1.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6820,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
     </row>
   </sheetData>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -854,7 +854,7 @@
         <v>95.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>41</v>
+        <v>39.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="V4" t="n">
         <v>9.5</v>
@@ -937,10 +937,10 @@
         <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="O5" t="n">
-        <v>38.5</v>
+        <v>37</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="V5" t="n">
         <v>10.7</v>
@@ -1558,10 +1558,10 @@
         <v>6.1</v>
       </c>
       <c r="K11" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="O11" t="n">
-        <v>36.8</v>
+        <v>35.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="V11" t="n">
         <v>15.5</v>
@@ -1644,10 +1644,10 @@
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="O12" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="V12" t="n">
         <v>12.6</v>
@@ -2265,10 +2265,10 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O18" t="n">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="V18" t="n">
         <v>11.6</v>
@@ -2351,10 +2351,10 @@
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O19" t="n">
-        <v>36.5</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="V19" t="n">
         <v>11</v>
@@ -5852,43 +5852,43 @@
         <v>46303</v>
       </c>
       <c r="B52" t="n">
-        <v>124.1</v>
+        <v>126.8</v>
       </c>
       <c r="C52" t="n">
-        <v>46.3</v>
+        <v>48.7</v>
       </c>
       <c r="D52" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="E52" t="n">
-        <v>28.89</v>
+        <v>26.6</v>
       </c>
       <c r="F52" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H52" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="J52" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="K52" t="n">
-        <v>69.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N52" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="O52" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="V52" t="n">
         <v>16.9</v>
@@ -5915,7 +5915,7 @@
         <v>18.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="AB52" t="n">
         <v>6.1</v>
@@ -5959,43 +5959,43 @@
         <v>46304</v>
       </c>
       <c r="B53" t="n">
-        <v>127.5</v>
+        <v>132.6</v>
       </c>
       <c r="C53" t="n">
-        <v>48.1</v>
+        <v>53</v>
       </c>
       <c r="D53" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="E53" t="n">
         <v>28.38</v>
       </c>
       <c r="F53" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="H53" t="n">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
       <c r="I53" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J53" t="n">
-        <v>38</v>
+        <v>40.5</v>
       </c>
       <c r="K53" t="n">
-        <v>70.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="M53" t="n">
         <v>0.7</v>
       </c>
       <c r="N53" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="O53" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="V53" t="n">
         <v>14.8</v>
@@ -6054,43 +6054,43 @@
         <v>46305</v>
       </c>
       <c r="B54" t="n">
-        <v>115.7</v>
+        <v>120</v>
       </c>
       <c r="C54" t="n">
-        <v>45.4</v>
+        <v>48.8</v>
       </c>
       <c r="D54" t="n">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="E54" t="n">
         <v>22.05</v>
       </c>
       <c r="F54" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H54" t="n">
-        <v>22.8</v>
+        <v>24.8</v>
       </c>
       <c r="I54" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J54" t="n">
-        <v>38</v>
+        <v>41.6</v>
       </c>
       <c r="K54" t="n">
-        <v>70</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M54" t="n">
         <v>0.7</v>
       </c>
       <c r="N54" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="O54" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="BL54" s="1" t="n">
         <v>46305</v>
@@ -6110,43 +6110,43 @@
         <v>46306</v>
       </c>
       <c r="B55" t="n">
-        <v>109.9</v>
+        <v>113.1</v>
       </c>
       <c r="C55" t="n">
-        <v>41.6</v>
+        <v>44.2</v>
       </c>
       <c r="D55" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="E55" t="n">
         <v>21.05</v>
       </c>
       <c r="F55" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H55" t="n">
-        <v>22.8</v>
+        <v>24.8</v>
       </c>
       <c r="I55" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J55" t="n">
-        <v>38</v>
+        <v>41.6</v>
       </c>
       <c r="K55" t="n">
-        <v>70</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0.7</v>
       </c>
       <c r="N55" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="O55" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46306</v>
@@ -6166,19 +6166,43 @@
         <v>46307</v>
       </c>
       <c r="B56" t="n">
-        <v>22.4</v>
+        <v>117.3</v>
+      </c>
+      <c r="C56" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>36.3</v>
       </c>
       <c r="E56" t="n">
         <v>22.39</v>
       </c>
+      <c r="F56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>40</v>
+      </c>
       <c r="K56" t="n">
-        <v>4.6</v>
+        <v>74.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N56" t="n">
+        <v>29.6</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>30.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6187,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>15.8</v>
+        <v>17.8</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46307</v>
@@ -6198,19 +6222,43 @@
         <v>46308</v>
       </c>
       <c r="B57" t="n">
-        <v>26.3</v>
+        <v>121.8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>36.9</v>
       </c>
       <c r="E57" t="n">
         <v>26.27</v>
       </c>
+      <c r="F57" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40</v>
+      </c>
       <c r="K57" t="n">
-        <v>7.3</v>
+        <v>74.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N57" t="n">
+        <v>29.6</v>
       </c>
       <c r="O57" t="n">
-        <v>3.2</v>
+        <v>30.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6219,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>15.8</v>
+        <v>17.8</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46308</v>
@@ -6236,10 +6284,10 @@
         <v>27.18</v>
       </c>
       <c r="K58" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="O58" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -6251,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46309</v>
@@ -6268,10 +6316,10 @@
         <v>28.7</v>
       </c>
       <c r="K59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O59" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -6283,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46310</v>
@@ -6300,10 +6348,10 @@
         <v>28.8</v>
       </c>
       <c r="K60" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="O60" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -6315,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46311</v>
@@ -6332,10 +6380,10 @@
         <v>24.91</v>
       </c>
       <c r="K61" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6347,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46312</v>
@@ -6364,10 +6412,10 @@
         <v>21.2</v>
       </c>
       <c r="K62" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6379,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46313</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6101,6 +6101,30 @@
       <c r="T54" t="n">
         <v>17.8</v>
       </c>
+      <c r="V54" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="W54" t="n">
+        <v>18</v>
+      </c>
+      <c r="X54" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>129.24</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.29</v>
+      </c>
       <c r="BL54" s="1" t="n">
         <v>46305</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6110,6 +6110,15 @@
       <c r="X54" t="n">
         <v>15.8</v>
       </c>
+      <c r="Y54" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>13.9</v>
+      </c>
       <c r="AB54" t="n">
         <v>3.2</v>
       </c>
@@ -6118,6 +6127,12 @@
       </c>
       <c r="AD54" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>221.09</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.1</v>
       </c>
       <c r="AK54" t="n">
         <v>129.24</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6196,6 +6196,30 @@
       <c r="T55" t="n">
         <v>17.8</v>
       </c>
+      <c r="V55" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X55" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.37</v>
+      </c>
       <c r="BL55" s="1" t="n">
         <v>46306</v>
       </c>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -6205,6 +6205,15 @@
       <c r="X55" t="n">
         <v>16.2</v>
       </c>
+      <c r="Y55" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>12.6</v>
+      </c>
       <c r="AB55" t="n">
         <v>4.2</v>
       </c>
@@ -6213,6 +6222,12 @@
       </c>
       <c r="AD55" t="n">
         <v>9.800000000000001</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>225.81</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>4.72</v>
       </c>
       <c r="AK55" t="n">
         <v>130.61</v>
@@ -6275,6 +6290,45 @@
       </c>
       <c r="T56" t="n">
         <v>17.8</v>
+      </c>
+      <c r="V56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="W56" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X56" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>228.19</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>134.32</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>3.71</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46307</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -3225,16 +3225,16 @@
         <v>23.8</v>
       </c>
       <c r="V27" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="W27" t="n">
         <v>11</v>
       </c>
       <c r="X27" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z27" t="n">
         <v>11.2</v>
@@ -3243,10 +3243,10 @@
         <v>7.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="AD27" t="n">
         <v>5.7</v>
@@ -3332,16 +3332,16 @@
         <v>23.8</v>
       </c>
       <c r="V28" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
         <v>15.2</v>
       </c>
       <c r="X28" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z28" t="n">
         <v>13.6</v>
@@ -3350,10 +3350,10 @@
         <v>12</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="AD28" t="n">
         <v>5.8</v>
@@ -3448,7 +3448,7 @@
         <v>13.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z29" t="n">
         <v>20.2</v>
@@ -3546,7 +3546,7 @@
         <v>23.3</v>
       </c>
       <c r="V30" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="W30" t="n">
         <v>26</v>
@@ -3555,7 +3555,7 @@
         <v>16.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z30" t="n">
         <v>12.9</v>
@@ -3564,10 +3564,10 @@
         <v>11.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
         <v>7.8</v>
@@ -3653,16 +3653,16 @@
         <v>23.3</v>
       </c>
       <c r="V31" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="W31" t="n">
         <v>27.6</v>
       </c>
       <c r="X31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
         <v>23.2</v>
@@ -3760,13 +3760,13 @@
         <v>20</v>
       </c>
       <c r="V32" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W32" t="n">
         <v>27.6</v>
       </c>
       <c r="X32" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Y32" t="n">
         <v>13.4</v>
@@ -3778,10 +3778,10 @@
         <v>17.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="AD32" t="n">
         <v>9.199999999999999</v>
@@ -3867,16 +3867,16 @@
         <v>15</v>
       </c>
       <c r="V33" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W33" t="n">
         <v>30.6</v>
       </c>
       <c r="X33" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="Z33" t="n">
         <v>21</v>
@@ -3885,10 +3885,10 @@
         <v>18.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AC33" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="AD33" t="n">
         <v>12.8</v>
@@ -3977,13 +3977,13 @@
         <v>15.8</v>
       </c>
       <c r="W34" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="X34" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="Z34" t="n">
         <v>23</v>
@@ -3992,7 +3992,7 @@
         <v>16.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC34" t="n">
         <v>10.1</v>
@@ -4081,16 +4081,16 @@
         <v>18.3</v>
       </c>
       <c r="V35" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="W35" t="n">
         <v>22.5</v>
       </c>
       <c r="X35" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="Z35" t="n">
         <v>16.1</v>
@@ -4099,13 +4099,13 @@
         <v>13.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AF35" t="n">
         <v>224.91</v>
@@ -4188,16 +4188,16 @@
         <v>20.2</v>
       </c>
       <c r="V36" t="n">
-        <v>14.1</v>
+        <v>12.7</v>
       </c>
       <c r="W36" t="n">
         <v>20.2</v>
       </c>
       <c r="X36" t="n">
-        <v>17.1</v>
+        <v>16.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z36" t="n">
         <v>12.5</v>
@@ -4209,10 +4209,10 @@
         <v>-0</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AF36" t="n">
         <v>220.83</v>
@@ -4304,7 +4304,7 @@
         <v>17.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Z37" t="n">
         <v>16.8</v>
@@ -4402,16 +4402,16 @@
         <v>22.2</v>
       </c>
       <c r="V38" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="W38" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="X38" t="n">
         <v>21.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="Z38" t="n">
         <v>21.4</v>
@@ -4509,7 +4509,7 @@
         <v>19.8</v>
       </c>
       <c r="V39" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W39" t="n">
         <v>35.4</v>
@@ -4518,13 +4518,13 @@
         <v>25.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="Z39" t="n">
         <v>25.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB39" t="n">
         <v>4.3</v>
@@ -4625,10 +4625,10 @@
         <v>26.7</v>
       </c>
       <c r="Y40" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="n">
         <v>17.3</v>
@@ -4637,7 +4637,7 @@
         <v>5.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="AD40" t="n">
         <v>9.4</v>
@@ -4744,7 +4744,7 @@
         <v>3.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="AD41" t="n">
         <v>8.800000000000001</v>
@@ -4830,13 +4830,13 @@
         <v>20.3</v>
       </c>
       <c r="V42" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="W42" t="n">
         <v>32.8</v>
       </c>
       <c r="X42" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Y42" t="n">
         <v>14.2</v>
@@ -4848,13 +4848,13 @@
         <v>17.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AC42" t="n">
         <v>13.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AF42" t="n">
         <v>234.37</v>
@@ -4937,16 +4937,16 @@
         <v>20.5</v>
       </c>
       <c r="V43" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="W43" t="n">
         <v>22</v>
       </c>
       <c r="X43" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z43" t="n">
         <v>19.9</v>
@@ -5044,16 +5044,16 @@
         <v>19.7</v>
       </c>
       <c r="V44" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W44" t="n">
         <v>22.3</v>
       </c>
       <c r="X44" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z44" t="n">
         <v>17.6</v>
@@ -5065,10 +5065,10 @@
         <v>3.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AF44" t="n">
         <v>228.13</v>
@@ -5151,16 +5151,16 @@
         <v>20.2</v>
       </c>
       <c r="V45" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="W45" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="X45" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="Z45" t="n">
         <v>14.6</v>
@@ -5258,16 +5258,16 @@
         <v>20.5</v>
       </c>
       <c r="V46" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W46" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="X46" t="n">
         <v>18.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Z46" t="n">
         <v>16.5</v>
@@ -5276,13 +5276,13 @@
         <v>11.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="AF46" t="n">
         <v>223.71</v>
@@ -5368,19 +5368,19 @@
         <v>12.6</v>
       </c>
       <c r="W47" t="n">
-        <v>27.9</v>
+        <v>28.5</v>
       </c>
       <c r="X47" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="Z47" t="n">
         <v>16.9</v>
       </c>
       <c r="AA47" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="AB47" t="n">
         <v>2.4</v>
@@ -5481,7 +5481,7 @@
         <v>19.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="Z48" t="n">
         <v>22.1</v>
@@ -5490,10 +5490,10 @@
         <v>18.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AD48" t="n">
         <v>6.1</v>
@@ -5579,13 +5579,13 @@
         <v>12</v>
       </c>
       <c r="V49" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W49" t="n">
         <v>22.4</v>
       </c>
       <c r="X49" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="Y49" t="n">
         <v>13.4</v>
@@ -5796,7 +5796,7 @@
         <v>15.5</v>
       </c>
       <c r="W51" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="X51" t="n">
         <v>22.6</v>
@@ -6025,10 +6025,10 @@
         <v>13.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC53" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="AD53" t="n">
         <v>10.7</v>
@@ -6047,6 +6047,18 @@
       </c>
       <c r="BL53" s="1" t="n">
         <v>46304</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -6123,10 +6135,10 @@
         <v>3.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF54" t="n">
         <v>221.09</v>
@@ -6142,6 +6154,18 @@
       </c>
       <c r="BL54" s="1" t="n">
         <v>46305</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6200,10 +6224,10 @@
         <v>14.1</v>
       </c>
       <c r="W55" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="X55" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y55" t="n">
         <v>9.300000000000001</v>
@@ -6218,7 +6242,7 @@
         <v>4.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="AD55" t="n">
         <v>9.800000000000001</v>
@@ -6237,6 +6261,18 @@
       </c>
       <c r="BL55" s="1" t="n">
         <v>46306</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6310,10 +6346,10 @@
         <v>13</v>
       </c>
       <c r="AB56" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AC56" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AD56" t="n">
         <v>11</v>
@@ -6332,6 +6368,18 @@
       </c>
       <c r="BL56" s="1" t="n">
         <v>46307</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5365,13 +5365,13 @@
         <v>19</v>
       </c>
       <c r="V47" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W47" t="n">
-        <v>28.5</v>
+        <v>27.9</v>
       </c>
       <c r="X47" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="Y47" t="n">
         <v>12</v>
@@ -5481,10 +5481,10 @@
         <v>19.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="Z48" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA48" t="n">
         <v>18.5</v>
@@ -5591,7 +5591,7 @@
         <v>13.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA49" t="n">
         <v>18.7</v>
@@ -5698,7 +5698,7 @@
         <v>13.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA50" t="n">
         <v>17.9</v>
@@ -5802,7 +5802,7 @@
         <v>22.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="Z51" t="n">
         <v>19.1</v>
@@ -5909,10 +5909,10 @@
         <v>19.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
       </c>
       <c r="AA52" t="n">
         <v>14.9</v>
@@ -6019,7 +6019,7 @@
         <v>11.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="AA53" t="n">
         <v>13.9</v>
@@ -6123,13 +6123,13 @@
         <v>15.8</v>
       </c>
       <c r="Y54" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="Z54" t="n">
         <v>16.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="AB54" t="n">
         <v>3.2</v>
@@ -6233,10 +6233,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="Z55" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="AA55" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="AB55" t="n">
         <v>4.2</v>
@@ -6434,8 +6434,59 @@
       <c r="T57" t="n">
         <v>17.8</v>
       </c>
+      <c r="V57" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X57" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>229.59</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>131.59</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-2.73</v>
+      </c>
       <c r="BL57" s="1" t="n">
         <v>46308</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5481,19 +5481,19 @@
         <v>19.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA48" t="n">
         <v>18.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD48" t="n">
         <v>6.1</v>
@@ -5579,19 +5579,19 @@
         <v>12</v>
       </c>
       <c r="V49" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W49" t="n">
         <v>22.4</v>
       </c>
       <c r="X49" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="Y49" t="n">
         <v>13.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA49" t="n">
         <v>18.7</v>
@@ -5698,7 +5698,7 @@
         <v>13.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA50" t="n">
         <v>17.9</v>
@@ -5796,13 +5796,13 @@
         <v>15.5</v>
       </c>
       <c r="W51" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="X51" t="n">
         <v>22.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="Z51" t="n">
         <v>19.1</v>
@@ -5909,10 +5909,10 @@
         <v>19.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="AA52" t="n">
         <v>14.9</v>
@@ -6019,16 +6019,16 @@
         <v>11.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="AA53" t="n">
         <v>13.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AC53" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="AD53" t="n">
         <v>10.7</v>
@@ -6049,10 +6049,10 @@
         <v>46304</v>
       </c>
       <c r="BM53" t="n">
-        <v>0</v>
+        <v>29.55</v>
       </c>
       <c r="BN53" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BO53" t="n">
         <v>0</v>
@@ -6123,22 +6123,22 @@
         <v>15.8</v>
       </c>
       <c r="Y54" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="Z54" t="n">
         <v>16.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="AB54" t="n">
         <v>3.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF54" t="n">
         <v>221.09</v>
@@ -6156,10 +6156,10 @@
         <v>46305</v>
       </c>
       <c r="BM54" t="n">
-        <v>0</v>
+        <v>26.93</v>
       </c>
       <c r="BN54" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BO54" t="n">
         <v>0</v>
@@ -6224,25 +6224,25 @@
         <v>14.1</v>
       </c>
       <c r="W55" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="X55" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="Y55" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="Z55" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="AB55" t="n">
         <v>4.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="AD55" t="n">
         <v>9.800000000000001</v>
@@ -6263,10 +6263,10 @@
         <v>46306</v>
       </c>
       <c r="BM55" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="BN55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
@@ -6346,10 +6346,10 @@
         <v>13</v>
       </c>
       <c r="AB56" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AC56" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="AD56" t="n">
         <v>11</v>
@@ -6370,7 +6370,7 @@
         <v>46307</v>
       </c>
       <c r="BM56" t="n">
-        <v>0</v>
+        <v>25.54</v>
       </c>
       <c r="BN56" t="n">
         <v>0</v>
@@ -6444,7 +6444,7 @@
         <v>15.8</v>
       </c>
       <c r="Y57" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="Z57" t="n">
         <v>18.6</v>
@@ -6453,13 +6453,13 @@
         <v>15.9</v>
       </c>
       <c r="AB57" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AC57" t="n">
         <v>18.4</v>
       </c>
       <c r="AD57" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="AF57" t="n">
         <v>229.59</v>
@@ -6477,10 +6477,10 @@
         <v>46308</v>
       </c>
       <c r="BM57" t="n">
-        <v>0</v>
+        <v>29.78</v>
       </c>
       <c r="BN57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BO57" t="n">
         <v>0</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -851,10 +851,10 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>95.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="O4" t="n">
-        <v>39.4</v>
+        <v>38.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
         <v>9.5</v>
@@ -937,10 +937,10 @@
         <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>89.5</v>
+        <v>87</v>
       </c>
       <c r="O5" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
         <v>10.7</v>
@@ -1558,10 +1558,10 @@
         <v>6.1</v>
       </c>
       <c r="K11" t="n">
-        <v>85.5</v>
+        <v>83</v>
       </c>
       <c r="O11" t="n">
-        <v>35.3</v>
+        <v>34.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="V11" t="n">
         <v>15.5</v>
@@ -1644,10 +1644,10 @@
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>77.2</v>
+        <v>74.7</v>
       </c>
       <c r="O12" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="V12" t="n">
         <v>12.6</v>
@@ -2265,10 +2265,10 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>81.3</v>
+        <v>78.7</v>
       </c>
       <c r="O18" t="n">
-        <v>33.5</v>
+        <v>32.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="V18" t="n">
         <v>11.6</v>
@@ -2351,10 +2351,10 @@
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>84.7</v>
+        <v>82.2</v>
       </c>
       <c r="O19" t="n">
-        <v>35</v>
+        <v>34.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="V19" t="n">
         <v>11</v>
@@ -5472,16 +5472,16 @@
         <v>16.2</v>
       </c>
       <c r="V48" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W48" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="X48" t="n">
         <v>19.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="Z48" t="n">
         <v>22.1</v>
@@ -5490,10 +5490,10 @@
         <v>18.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AD48" t="n">
         <v>6.1</v>
@@ -5686,7 +5686,7 @@
         <v>13.6</v>
       </c>
       <c r="V50" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W50" t="n">
         <v>27.9</v>
@@ -5793,10 +5793,10 @@
         <v>15.6</v>
       </c>
       <c r="V51" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W51" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="X51" t="n">
         <v>22.6</v>
@@ -6025,10 +6025,10 @@
         <v>13.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC53" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="AD53" t="n">
         <v>10.7</v>
@@ -6135,10 +6135,10 @@
         <v>3.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF54" t="n">
         <v>221.09</v>
@@ -6242,7 +6242,7 @@
         <v>4.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="AD55" t="n">
         <v>9.800000000000001</v>
@@ -6280,43 +6280,43 @@
         <v>46307</v>
       </c>
       <c r="B56" t="n">
-        <v>117.3</v>
+        <v>119.4</v>
       </c>
       <c r="C56" t="n">
-        <v>46.5</v>
+        <v>51.4</v>
       </c>
       <c r="D56" t="n">
-        <v>36.3</v>
+        <v>34.7</v>
       </c>
       <c r="E56" t="n">
-        <v>22.39</v>
+        <v>20.8</v>
       </c>
       <c r="F56" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I56" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="J56" t="n">
-        <v>40</v>
+        <v>36.8</v>
       </c>
       <c r="K56" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N56" t="n">
-        <v>29.6</v>
+        <v>31.2</v>
       </c>
       <c r="O56" t="n">
-        <v>30.3</v>
+        <v>31.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="V56" t="n">
         <v>13.3</v>
@@ -6343,13 +6343,13 @@
         <v>15.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="AB56" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AC56" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AD56" t="n">
         <v>11</v>
@@ -6387,43 +6387,43 @@
         <v>46308</v>
       </c>
       <c r="B57" t="n">
-        <v>121.8</v>
+        <v>125</v>
       </c>
       <c r="C57" t="n">
-        <v>46.2</v>
+        <v>49.9</v>
       </c>
       <c r="D57" t="n">
-        <v>36.9</v>
+        <v>36.4</v>
       </c>
       <c r="E57" t="n">
         <v>26.27</v>
       </c>
       <c r="F57" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H57" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I57" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="K57" t="n">
-        <v>74.2</v>
+        <v>72.5</v>
       </c>
       <c r="M57" t="n">
         <v>0.7</v>
       </c>
       <c r="N57" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
       <c r="O57" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="V57" t="n">
         <v>14.2</v>
@@ -6453,13 +6453,13 @@
         <v>15.9</v>
       </c>
       <c r="AB57" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AC57" t="n">
         <v>18.4</v>
       </c>
       <c r="AD57" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="AF57" t="n">
         <v>229.59</v>
@@ -6494,19 +6494,43 @@
         <v>46309</v>
       </c>
       <c r="B58" t="n">
-        <v>27.2</v>
+        <v>124.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>36.6</v>
       </c>
       <c r="E58" t="n">
         <v>27.18</v>
       </c>
+      <c r="F58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J58" t="n">
+        <v>39.5</v>
+      </c>
       <c r="K58" t="n">
-        <v>6.9</v>
+        <v>73.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N58" t="n">
+        <v>29.1</v>
       </c>
       <c r="O58" t="n">
-        <v>2.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6515,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>17.4</v>
+        <v>21.1</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46309</v>
@@ -6526,19 +6550,43 @@
         <v>46310</v>
       </c>
       <c r="B59" t="n">
-        <v>28.7</v>
+        <v>127</v>
+      </c>
+      <c r="C59" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36.7</v>
       </c>
       <c r="E59" t="n">
         <v>28.7</v>
       </c>
+      <c r="F59" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J59" t="n">
+        <v>37</v>
+      </c>
       <c r="K59" t="n">
-        <v>8</v>
+        <v>71</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N59" t="n">
+        <v>29.5</v>
       </c>
       <c r="O59" t="n">
-        <v>3.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6547,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>17.4</v>
+        <v>21.1</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46310</v>
@@ -6558,19 +6606,43 @@
         <v>46311</v>
       </c>
       <c r="B60" t="n">
-        <v>28.8</v>
+        <v>128.7</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50</v>
+      </c>
+      <c r="D60" t="n">
+        <v>36.6</v>
       </c>
       <c r="E60" t="n">
         <v>28.8</v>
       </c>
+      <c r="F60" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>37</v>
+      </c>
       <c r="K60" t="n">
-        <v>8.1</v>
+        <v>71</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>29.5</v>
       </c>
       <c r="O60" t="n">
-        <v>3.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6579,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>17.4</v>
+        <v>21.1</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46311</v>
@@ -6596,10 +6668,10 @@
         <v>24.91</v>
       </c>
       <c r="K61" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6611,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46312</v>
@@ -6628,10 +6700,10 @@
         <v>21.2</v>
       </c>
       <c r="K62" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="O62" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -6643,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>17.4</v>
+        <v>20.6</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46313</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -851,10 +851,10 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>92.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="V4" t="n">
         <v>9.5</v>
@@ -937,10 +937,10 @@
         <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>87</v>
+        <v>86.5</v>
       </c>
       <c r="O5" t="n">
-        <v>36.3</v>
+        <v>35.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="V5" t="n">
         <v>10.7</v>
@@ -1558,10 +1558,10 @@
         <v>6.1</v>
       </c>
       <c r="K11" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="O11" t="n">
-        <v>34.6</v>
+        <v>33.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.5</v>
@@ -1644,10 +1644,10 @@
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="O12" t="n">
-        <v>31.2</v>
+        <v>30.4</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="V12" t="n">
         <v>12.6</v>
@@ -2265,10 +2265,10 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="O18" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="V18" t="n">
         <v>11.6</v>
@@ -2351,10 +2351,10 @@
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>82.2</v>
+        <v>81.7</v>
       </c>
       <c r="O19" t="n">
-        <v>34.3</v>
+        <v>33.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
         <v>11</v>
@@ -5490,13 +5490,13 @@
         <v>18.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AF48" t="n">
         <v>234.88</v>
@@ -5579,13 +5579,13 @@
         <v>12</v>
       </c>
       <c r="V49" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W49" t="n">
         <v>22.4</v>
       </c>
       <c r="X49" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="Y49" t="n">
         <v>13.4</v>
@@ -5686,7 +5686,7 @@
         <v>13.6</v>
       </c>
       <c r="V50" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W50" t="n">
         <v>27.9</v>
@@ -5793,10 +5793,10 @@
         <v>15.6</v>
       </c>
       <c r="V51" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W51" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="X51" t="n">
         <v>22.6</v>
@@ -5909,7 +5909,7 @@
         <v>19.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
         <v>18.2</v>
@@ -6224,10 +6224,10 @@
         <v>14.1</v>
       </c>
       <c r="W55" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="X55" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y55" t="n">
         <v>9.300000000000001</v>
@@ -6387,43 +6387,43 @@
         <v>46308</v>
       </c>
       <c r="B57" t="n">
-        <v>125</v>
+        <v>124.5</v>
       </c>
       <c r="C57" t="n">
-        <v>49.9</v>
+        <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>36.4</v>
+        <v>37.5</v>
       </c>
       <c r="E57" t="n">
-        <v>26.27</v>
+        <v>25.3</v>
       </c>
       <c r="F57" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H57" t="n">
         <v>24.8</v>
       </c>
       <c r="I57" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J57" t="n">
-        <v>38.5</v>
+        <v>37.7</v>
       </c>
       <c r="K57" t="n">
-        <v>72.5</v>
+        <v>71.5</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N57" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="O57" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="V57" t="n">
         <v>14.2</v>
@@ -6450,7 +6450,7 @@
         <v>18.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB57" t="n">
         <v>5.3</v>
@@ -6494,19 +6494,19 @@
         <v>46309</v>
       </c>
       <c r="B58" t="n">
-        <v>124.6</v>
+        <v>125.5</v>
       </c>
       <c r="C58" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="D58" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="E58" t="n">
         <v>27.18</v>
       </c>
       <c r="F58" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H58" t="n">
         <v>24.8</v>
@@ -6515,10 +6515,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="K58" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="M58" t="n">
         <v>0.7</v>
@@ -6530,7 +6530,7 @@
         <v>29.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6539,10 +6539,52 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>21.1</v>
+        <v>22</v>
+      </c>
+      <c r="V58" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="W58" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X58" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>230.03</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>127.71</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-3.88</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46309</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -6550,19 +6592,19 @@
         <v>46310</v>
       </c>
       <c r="B59" t="n">
-        <v>127</v>
+        <v>128.6</v>
       </c>
       <c r="C59" t="n">
-        <v>48.6</v>
+        <v>50.2</v>
       </c>
       <c r="D59" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
       <c r="E59" t="n">
         <v>28.7</v>
       </c>
       <c r="F59" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H59" t="n">
         <v>24.8</v>
@@ -6571,22 +6613,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K59" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M59" t="n">
         <v>0.7</v>
       </c>
       <c r="N59" t="n">
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="O59" t="n">
-        <v>30.2</v>
+        <v>28.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6595,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46310</v>
@@ -6606,19 +6648,19 @@
         <v>46311</v>
       </c>
       <c r="B60" t="n">
-        <v>128.7</v>
+        <v>129.6</v>
       </c>
       <c r="C60" t="n">
-        <v>50</v>
+        <v>51.3</v>
       </c>
       <c r="D60" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="E60" t="n">
         <v>28.8</v>
       </c>
       <c r="F60" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="H60" t="n">
         <v>24.8</v>
@@ -6627,22 +6669,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>37</v>
+        <v>36.5</v>
       </c>
       <c r="K60" t="n">
-        <v>71</v>
+        <v>70.5</v>
       </c>
       <c r="M60" t="n">
         <v>0.7</v>
       </c>
       <c r="N60" t="n">
-        <v>29.5</v>
+        <v>27.5</v>
       </c>
       <c r="O60" t="n">
-        <v>30.2</v>
+        <v>28.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -6651,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="BL60" s="1" t="n">
         <v>46311</v>
@@ -6662,19 +6704,43 @@
         <v>46312</v>
       </c>
       <c r="B61" t="n">
-        <v>24.9</v>
+        <v>125.4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>51</v>
+      </c>
+      <c r="D61" t="n">
+        <v>36.1</v>
       </c>
       <c r="E61" t="n">
         <v>24.91</v>
       </c>
+      <c r="F61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>39</v>
+      </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>73</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N61" t="n">
+        <v>28.5</v>
       </c>
       <c r="O61" t="n">
-        <v>1.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -6683,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>20.6</v>
+        <v>22</v>
       </c>
       <c r="BL61" s="1" t="n">
         <v>46312</v>
@@ -6694,19 +6760,43 @@
         <v>46313</v>
       </c>
       <c r="B62" t="n">
-        <v>21.2</v>
+        <v>117.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>35.9</v>
       </c>
       <c r="E62" t="n">
         <v>21.2</v>
       </c>
+      <c r="F62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J62" t="n">
+        <v>39</v>
+      </c>
       <c r="K62" t="n">
-        <v>0.4</v>
+        <v>73</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N62" t="n">
+        <v>29.5</v>
       </c>
       <c r="O62" t="n">
-        <v>0.2</v>
+        <v>30.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6715,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="BL62" s="1" t="n">
         <v>46313</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -5591,7 +5591,7 @@
         <v>13.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA49" t="n">
         <v>18.7</v>
@@ -5698,7 +5698,7 @@
         <v>13.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA50" t="n">
         <v>17.9</v>
@@ -5802,7 +5802,7 @@
         <v>22.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="Z51" t="n">
         <v>19.1</v>
@@ -5912,7 +5912,7 @@
         <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
       </c>
       <c r="AA52" t="n">
         <v>14.9</v>
@@ -6019,7 +6019,7 @@
         <v>11.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="AA53" t="n">
         <v>13.9</v>
@@ -6123,13 +6123,13 @@
         <v>15.8</v>
       </c>
       <c r="Y54" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="Z54" t="n">
         <v>16.7</v>
       </c>
       <c r="AA54" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="AB54" t="n">
         <v>3.2</v>
@@ -6233,10 +6233,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="Z55" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="AA55" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="AB55" t="n">
         <v>4.2</v>
@@ -6444,7 +6444,7 @@
         <v>15.8</v>
       </c>
       <c r="Y57" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="Z57" t="n">
         <v>18.6</v>
@@ -6549,6 +6549,15 @@
       </c>
       <c r="X58" t="n">
         <v>16.1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>16.8</v>
       </c>
       <c r="AB58" t="n">
         <v>8.199999999999999</v>

--- a/data/carga_datos.xlsx
+++ b/data/carga_datos.xlsx
@@ -628,233 +628,233 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B2" t="n">
-        <v>158.1</v>
+        <v>152.7</v>
       </c>
       <c r="C2" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I2" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="K2" t="n">
-        <v>74.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="N2" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="O2" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="V2" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="W2" t="n">
-        <v>19.3</v>
+        <v>27.3</v>
       </c>
       <c r="X2" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>228.35</v>
+        <v>220.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>130.88</v>
+        <v>120.28</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="BM2" t="n">
-        <v>32.38</v>
+        <v>29.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>4993.3</v>
+        <v>60.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>958.6</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>2899.8</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B3" t="n">
-        <v>154.9</v>
+        <v>150.7</v>
       </c>
       <c r="C3" t="n">
-        <v>70.2</v>
+        <v>64.8</v>
       </c>
       <c r="D3" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I3" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="K3" t="n">
-        <v>75.8</v>
+        <v>70.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="N3" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="R3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="V3" t="n">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="X3" t="n">
-        <v>15.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>231.16</v>
+        <v>220.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.81</v>
+        <v>-0.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>132.55</v>
+        <v>119.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.67</v>
+        <v>-0.99</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="BM3" t="n">
-        <v>33.01</v>
+        <v>31.11</v>
       </c>
       <c r="BN3" t="n">
-        <v>1514.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO3" t="n">
-        <v>799.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP3" t="n">
-        <v>2923.4</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B4" t="n">
-        <v>152.2</v>
+        <v>138.2</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>33.6</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="K4" t="n">
-        <v>92.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O4" t="n">
-        <v>37.9</v>
+        <v>35.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -866,81 +866,81 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V4" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>228.13</v>
+        <v>223.43</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AK4" t="n">
-        <v>128.02</v>
+        <v>121.35</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.53</v>
+        <v>2.06</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="BM4" t="n">
-        <v>35.62</v>
+        <v>30.59</v>
       </c>
       <c r="BN4" t="n">
-        <v>1526.5</v>
+        <v>40.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>957.4</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>2928.4</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B5" t="n">
-        <v>143.9</v>
+        <v>126.5</v>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>33.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>86.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>35.5</v>
+        <v>31.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -952,616 +952,616 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V5" t="n">
-        <v>10.7</v>
+        <v>12.6</v>
       </c>
       <c r="W5" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="X5" t="n">
-        <v>14.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>229.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.03</v>
+        <v>6.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>127.06</v>
+        <v>128.37</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.96</v>
+        <v>7.02</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="BM5" t="n">
-        <v>34.56</v>
+        <v>30.05</v>
       </c>
       <c r="BN5" t="n">
-        <v>170.6</v>
+        <v>34</v>
       </c>
       <c r="BO5" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>2825.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B6" t="n">
-        <v>163.2</v>
+        <v>129.4</v>
       </c>
       <c r="C6" t="n">
-        <v>73.7</v>
+        <v>50.6</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E6" t="n">
-        <v>28.2</v>
+        <v>19.4</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="J6" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
       <c r="K6" t="n">
-        <v>75.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M6" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="N6" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="O6" t="n">
-        <v>39.7</v>
+        <v>38</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="W6" t="n">
-        <v>20.1</v>
+        <v>23.9</v>
       </c>
       <c r="X6" t="n">
-        <v>14.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD6" t="n">
         <v>4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF6" t="n">
-        <v>228.55</v>
+        <v>241.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.61</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>125.61</v>
+        <v>134.59</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1.45</v>
+        <v>6.22</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="BM6" t="n">
-        <v>34.78</v>
+        <v>24.86</v>
       </c>
       <c r="BN6" t="n">
-        <v>69.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>2769.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B7" t="n">
-        <v>174.4</v>
+        <v>142.9</v>
       </c>
       <c r="C7" t="n">
-        <v>75.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="D7" t="n">
-        <v>32.1</v>
+        <v>34.7</v>
       </c>
       <c r="E7" t="n">
-        <v>30.8</v>
+        <v>24.8</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="J7" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="K7" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O7" t="n">
         <v>35.8</v>
       </c>
-      <c r="O7" t="n">
-        <v>42.6</v>
-      </c>
       <c r="Q7" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="R7" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="V7" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="W7" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>219.99</v>
+        <v>238.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>-8.56</v>
+        <v>-2.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>124.36</v>
+        <v>136.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.25</v>
+        <v>2.01</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="BM7" t="n">
-        <v>36.78</v>
+        <v>29.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>108.8</v>
+        <v>61.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>204.3</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>2982.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B8" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C8" t="n">
-        <v>70.90000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D8" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>23.8</v>
+        <v>21.8</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J8" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K8" t="n">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="M8" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="O8" t="n">
-        <v>41.5</v>
+        <v>33.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="S8" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>23.1</v>
+        <v>20.7</v>
       </c>
       <c r="V8" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="W8" t="n">
-        <v>23.3</v>
+        <v>25.5</v>
       </c>
       <c r="X8" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>219.22</v>
+        <v>233.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.77</v>
+        <v>-4.86</v>
       </c>
       <c r="AK8" t="n">
-        <v>120.93</v>
+        <v>135.